--- a/수양회_서식_template.xlsx
+++ b/수양회_서식_template.xlsx
@@ -6307,23 +6307,23 @@
       <c r="A38" s="45" t="n">
         <v>36</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="32">
         <f>IF(전도대상자!B38="","",전도대상자!B38)</f>
         <v/>
       </c>
-      <c r="C38">
+      <c r="C38" s="32">
         <f>IF(전도대상자!D38="","",전도대상자!D38)</f>
         <v/>
       </c>
-      <c r="D38">
+      <c r="D38" s="32">
         <f>IF(전도대상자!C38="","",전도대상자!C38)</f>
         <v/>
       </c>
-      <c r="E38">
+      <c r="E38" s="32">
         <f>IF(전도대상자!F38="","",전도대상자!F38)</f>
         <v/>
       </c>
-      <c r="F38">
+      <c r="F38" s="32">
         <f>IF(전도대상자!E38="","",전도대상자!E38)</f>
         <v/>
       </c>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="C2" s="52" t="inlineStr">
         <is>
-          <t>부서(회별)</t>
+          <t>회(부서)</t>
         </is>
       </c>
       <c r="D2" s="52" t="inlineStr">
@@ -8295,56 +8295,56 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>34구역</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B15" s="32">
         <f>IF(COUNTIFS(34구역!F4:F43,"1호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"2호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"3호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"4호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"5호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"6호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"7호차",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!F4:F43,"1호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"2호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"3호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"4호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"5호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"6호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"7호차",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
-      <c r="C15">
+      <c r="C15" s="32">
         <f>IF(COUNTIFS(34구역!G4:G43,"1호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"2호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"3호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"4호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"5호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"6호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"7호차",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!G4:G43,"1호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"2호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"3호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"4호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"5호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"6호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"7호차",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
-      <c r="D15">
+      <c r="D15" s="32">
         <f>IF(COUNTIFS(34구역!H4:H43,"&lt;&gt;",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!H4:H43,"&lt;&gt;",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
-      <c r="E15">
+      <c r="E15" s="32">
         <f>IF(COUNTIFS(34구역!I4:I43,"&lt;&gt;",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!I4:I43,"&lt;&gt;",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
-      <c r="F15">
+      <c r="F15" s="32">
         <f>IF(COUNTIFS(34구역!F4:F43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"교회차2",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"교회차2",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!F4:F43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"교회차2",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"교회차2",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
-      <c r="G15">
+      <c r="G15" s="32">
         <f>IF(COUNTIFS(34구역!G4:G43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"교회차2",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"교회차2",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!G4:G43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"교회차2",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"교회차2",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
-      <c r="H15">
+      <c r="H15" s="32">
         <f>IF(COUNTIFS(34구역!F4:F43,"타교회",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"타교회",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!F4:F43,"타교회",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"타교회",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
-      <c r="I15">
+      <c r="I15" s="32">
         <f>IF(COUNTIFS(34구역!G4:G43,"타교회",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"타교회",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!G4:G43,"타교회",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"타교회",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
-      <c r="J15">
+      <c r="J15" s="32">
         <f>IF(COUNTIFS(34구역!F4:F43,"개인차",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!F4:F43,"개인차",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
-      <c r="K15">
+      <c r="K15" s="32">
         <f>IF(COUNTIFS(34구역!G4:G43,"개인차",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!G4:G43,"개인차",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
-      <c r="L15">
+      <c r="L15" s="32">
         <f>IF(COUNTIFS(34구역!F4:F43,"대중교통",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"대중교통",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!F4:F43,"대중교통",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"대중교통",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
-      <c r="M15">
+      <c r="M15" s="32">
         <f>IF(COUNTIFS(34구역!G4:G43,"대중교통",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"대중교통",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!G4:G43,"대중교통",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"대중교통",34구역!E4:E43,$B23))</f>
         <v/>
       </c>
@@ -8355,51 +8355,51 @@
           <t>합  계</t>
         </is>
       </c>
-      <c r="B16">
+      <c r="B16" s="32">
         <f>IF(SUM(B4:B15)=0,"",SUM(B4:B15))</f>
         <v/>
       </c>
-      <c r="C16">
+      <c r="C16" s="32">
         <f>IF(SUM(C4:C15)=0,"",SUM(C4:C15))</f>
         <v/>
       </c>
-      <c r="D16">
+      <c r="D16" s="32">
         <f>IF(SUM(D4:D15)=0,"",SUM(D4:D15))</f>
         <v/>
       </c>
-      <c r="E16">
+      <c r="E16" s="32">
         <f>IF(SUM(E4:E15)=0,"",SUM(E4:E15))</f>
         <v/>
       </c>
-      <c r="F16">
+      <c r="F16" s="32">
         <f>IF(SUM(F4:F15)=0,"",SUM(F4:F15))</f>
         <v/>
       </c>
-      <c r="G16">
+      <c r="G16" s="32">
         <f>IF(SUM(G4:G15)=0,"",SUM(G4:G15))</f>
         <v/>
       </c>
-      <c r="H16">
+      <c r="H16" s="32">
         <f>IF(SUM(H4:H15)=0,"",SUM(H4:H15))</f>
         <v/>
       </c>
-      <c r="I16">
+      <c r="I16" s="32">
         <f>IF(SUM(I4:I15)=0,"",SUM(I4:I15))</f>
         <v/>
       </c>
-      <c r="J16">
+      <c r="J16" s="32">
         <f>IF(SUM(J4:J15)=0,"",SUM(J4:J15))</f>
         <v/>
       </c>
-      <c r="K16">
+      <c r="K16" s="32">
         <f>IF(SUM(K4:K15)=0,"",SUM(K4:K15))</f>
         <v/>
       </c>
-      <c r="L16">
+      <c r="L16" s="32">
         <f>IF(SUM(L4:L15)=0,"",SUM(L4:L15))</f>
         <v/>
       </c>
-      <c r="M16">
+      <c r="M16" s="32">
         <f>IF(SUM(M4:M15)=0,"",SUM(M4:M15))</f>
         <v/>
       </c>
@@ -8436,107 +8436,107 @@
       <c r="M18" s="67" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>차수</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>1차</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="32" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>3차</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>4차</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>5차</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="32" t="inlineStr">
         <is>
           <t>6차</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="32" t="inlineStr">
         <is>
           <t>7차</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="32" t="inlineStr">
         <is>
           <t>8차</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="32" t="inlineStr">
         <is>
           <t>계</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>접수인원</t>
         </is>
       </c>
-      <c r="B20">
+      <c r="B20" s="32">
         <f>IF(COUNTIF(11구역!E4:E43,"1차")+COUNTIF(12구역!E4:E43,"1차")+COUNTIF(13구역!E4:E43,"1차")+COUNTIF(14구역!E4:E43,"1차")+COUNTIF(21구역!E4:E43,"1차")+COUNTIF(22구역!E4:E43,"1차")+COUNTIF(23구역!E4:E43,"1차")+COUNTIF(24구역!E4:E43,"1차")+COUNTIF(31구역!E4:E43,"1차")+COUNTIF(32구역!E4:E43,"1차")+COUNTIF(33구역!E4:E43,"1차")+COUNTIF(34구역!E4:E43,"1차")=0,"",COUNTIF(11구역!E4:E43,"1차")+COUNTIF(12구역!E4:E43,"1차")+COUNTIF(13구역!E4:E43,"1차")+COUNTIF(14구역!E4:E43,"1차")+COUNTIF(21구역!E4:E43,"1차")+COUNTIF(22구역!E4:E43,"1차")+COUNTIF(23구역!E4:E43,"1차")+COUNTIF(24구역!E4:E43,"1차")+COUNTIF(31구역!E4:E43,"1차")+COUNTIF(32구역!E4:E43,"1차")+COUNTIF(33구역!E4:E43,"1차")+COUNTIF(34구역!E4:E43,"1차"))</f>
         <v/>
       </c>
-      <c r="C20">
+      <c r="C20" s="32">
         <f>IF(COUNTIF(11구역!E4:E43,"2차")+COUNTIF(12구역!E4:E43,"2차")+COUNTIF(13구역!E4:E43,"2차")+COUNTIF(14구역!E4:E43,"2차")+COUNTIF(21구역!E4:E43,"2차")+COUNTIF(22구역!E4:E43,"2차")+COUNTIF(23구역!E4:E43,"2차")+COUNTIF(24구역!E4:E43,"2차")+COUNTIF(31구역!E4:E43,"2차")+COUNTIF(32구역!E4:E43,"2차")+COUNTIF(33구역!E4:E43,"2차")+COUNTIF(34구역!E4:E43,"2차")=0,"",COUNTIF(11구역!E4:E43,"2차")+COUNTIF(12구역!E4:E43,"2차")+COUNTIF(13구역!E4:E43,"2차")+COUNTIF(14구역!E4:E43,"2차")+COUNTIF(21구역!E4:E43,"2차")+COUNTIF(22구역!E4:E43,"2차")+COUNTIF(23구역!E4:E43,"2차")+COUNTIF(24구역!E4:E43,"2차")+COUNTIF(31구역!E4:E43,"2차")+COUNTIF(32구역!E4:E43,"2차")+COUNTIF(33구역!E4:E43,"2차")+COUNTIF(34구역!E4:E43,"2차"))</f>
         <v/>
       </c>
-      <c r="D20">
+      <c r="D20" s="32">
         <f>IF(COUNTIF(11구역!E4:E43,"3차")+COUNTIF(12구역!E4:E43,"3차")+COUNTIF(13구역!E4:E43,"3차")+COUNTIF(14구역!E4:E43,"3차")+COUNTIF(21구역!E4:E43,"3차")+COUNTIF(22구역!E4:E43,"3차")+COUNTIF(23구역!E4:E43,"3차")+COUNTIF(24구역!E4:E43,"3차")+COUNTIF(31구역!E4:E43,"3차")+COUNTIF(32구역!E4:E43,"3차")+COUNTIF(33구역!E4:E43,"3차")+COUNTIF(34구역!E4:E43,"3차")=0,"",COUNTIF(11구역!E4:E43,"3차")+COUNTIF(12구역!E4:E43,"3차")+COUNTIF(13구역!E4:E43,"3차")+COUNTIF(14구역!E4:E43,"3차")+COUNTIF(21구역!E4:E43,"3차")+COUNTIF(22구역!E4:E43,"3차")+COUNTIF(23구역!E4:E43,"3차")+COUNTIF(24구역!E4:E43,"3차")+COUNTIF(31구역!E4:E43,"3차")+COUNTIF(32구역!E4:E43,"3차")+COUNTIF(33구역!E4:E43,"3차")+COUNTIF(34구역!E4:E43,"3차"))</f>
         <v/>
       </c>
-      <c r="E20">
+      <c r="E20" s="32">
         <f>IF(COUNTIF(11구역!E4:E43,"4차")+COUNTIF(12구역!E4:E43,"4차")+COUNTIF(13구역!E4:E43,"4차")+COUNTIF(14구역!E4:E43,"4차")+COUNTIF(21구역!E4:E43,"4차")+COUNTIF(22구역!E4:E43,"4차")+COUNTIF(23구역!E4:E43,"4차")+COUNTIF(24구역!E4:E43,"4차")+COUNTIF(31구역!E4:E43,"4차")+COUNTIF(32구역!E4:E43,"4차")+COUNTIF(33구역!E4:E43,"4차")+COUNTIF(34구역!E4:E43,"4차")=0,"",COUNTIF(11구역!E4:E43,"4차")+COUNTIF(12구역!E4:E43,"4차")+COUNTIF(13구역!E4:E43,"4차")+COUNTIF(14구역!E4:E43,"4차")+COUNTIF(21구역!E4:E43,"4차")+COUNTIF(22구역!E4:E43,"4차")+COUNTIF(23구역!E4:E43,"4차")+COUNTIF(24구역!E4:E43,"4차")+COUNTIF(31구역!E4:E43,"4차")+COUNTIF(32구역!E4:E43,"4차")+COUNTIF(33구역!E4:E43,"4차")+COUNTIF(34구역!E4:E43,"4차"))</f>
         <v/>
       </c>
-      <c r="F20">
+      <c r="F20" s="32">
         <f>IF(COUNTIF(11구역!E4:E43,"5차")+COUNTIF(12구역!E4:E43,"5차")+COUNTIF(13구역!E4:E43,"5차")+COUNTIF(14구역!E4:E43,"5차")+COUNTIF(21구역!E4:E43,"5차")+COUNTIF(22구역!E4:E43,"5차")+COUNTIF(23구역!E4:E43,"5차")+COUNTIF(24구역!E4:E43,"5차")+COUNTIF(31구역!E4:E43,"5차")+COUNTIF(32구역!E4:E43,"5차")+COUNTIF(33구역!E4:E43,"5차")+COUNTIF(34구역!E4:E43,"5차")=0,"",COUNTIF(11구역!E4:E43,"5차")+COUNTIF(12구역!E4:E43,"5차")+COUNTIF(13구역!E4:E43,"5차")+COUNTIF(14구역!E4:E43,"5차")+COUNTIF(21구역!E4:E43,"5차")+COUNTIF(22구역!E4:E43,"5차")+COUNTIF(23구역!E4:E43,"5차")+COUNTIF(24구역!E4:E43,"5차")+COUNTIF(31구역!E4:E43,"5차")+COUNTIF(32구역!E4:E43,"5차")+COUNTIF(33구역!E4:E43,"5차")+COUNTIF(34구역!E4:E43,"5차"))</f>
         <v/>
       </c>
-      <c r="G20">
+      <c r="G20" s="32">
         <f>IF(COUNTIF(11구역!E4:E43,"6차")+COUNTIF(12구역!E4:E43,"6차")+COUNTIF(13구역!E4:E43,"6차")+COUNTIF(14구역!E4:E43,"6차")+COUNTIF(21구역!E4:E43,"6차")+COUNTIF(22구역!E4:E43,"6차")+COUNTIF(23구역!E4:E43,"6차")+COUNTIF(24구역!E4:E43,"6차")+COUNTIF(31구역!E4:E43,"6차")+COUNTIF(32구역!E4:E43,"6차")+COUNTIF(33구역!E4:E43,"6차")+COUNTIF(34구역!E4:E43,"6차")=0,"",COUNTIF(11구역!E4:E43,"6차")+COUNTIF(12구역!E4:E43,"6차")+COUNTIF(13구역!E4:E43,"6차")+COUNTIF(14구역!E4:E43,"6차")+COUNTIF(21구역!E4:E43,"6차")+COUNTIF(22구역!E4:E43,"6차")+COUNTIF(23구역!E4:E43,"6차")+COUNTIF(24구역!E4:E43,"6차")+COUNTIF(31구역!E4:E43,"6차")+COUNTIF(32구역!E4:E43,"6차")+COUNTIF(33구역!E4:E43,"6차")+COUNTIF(34구역!E4:E43,"6차"))</f>
         <v/>
       </c>
-      <c r="H20">
+      <c r="H20" s="32">
         <f>IF(COUNTIF(11구역!E4:E43,"7차")+COUNTIF(12구역!E4:E43,"7차")+COUNTIF(13구역!E4:E43,"7차")+COUNTIF(14구역!E4:E43,"7차")+COUNTIF(21구역!E4:E43,"7차")+COUNTIF(22구역!E4:E43,"7차")+COUNTIF(23구역!E4:E43,"7차")+COUNTIF(24구역!E4:E43,"7차")+COUNTIF(31구역!E4:E43,"7차")+COUNTIF(32구역!E4:E43,"7차")+COUNTIF(33구역!E4:E43,"7차")+COUNTIF(34구역!E4:E43,"7차")=0,"",COUNTIF(11구역!E4:E43,"7차")+COUNTIF(12구역!E4:E43,"7차")+COUNTIF(13구역!E4:E43,"7차")+COUNTIF(14구역!E4:E43,"7차")+COUNTIF(21구역!E4:E43,"7차")+COUNTIF(22구역!E4:E43,"7차")+COUNTIF(23구역!E4:E43,"7차")+COUNTIF(24구역!E4:E43,"7차")+COUNTIF(31구역!E4:E43,"7차")+COUNTIF(32구역!E4:E43,"7차")+COUNTIF(33구역!E4:E43,"7차")+COUNTIF(34구역!E4:E43,"7차"))</f>
         <v/>
       </c>
-      <c r="I20">
+      <c r="I20" s="32">
         <f>IF(COUNTIF(11구역!E4:E43,"8차")+COUNTIF(12구역!E4:E43,"8차")+COUNTIF(13구역!E4:E43,"8차")+COUNTIF(14구역!E4:E43,"8차")+COUNTIF(21구역!E4:E43,"8차")+COUNTIF(22구역!E4:E43,"8차")+COUNTIF(23구역!E4:E43,"8차")+COUNTIF(24구역!E4:E43,"8차")+COUNTIF(31구역!E4:E43,"8차")+COUNTIF(32구역!E4:E43,"8차")+COUNTIF(33구역!E4:E43,"8차")+COUNTIF(34구역!E4:E43,"8차")=0,"",COUNTIF(11구역!E4:E43,"8차")+COUNTIF(12구역!E4:E43,"8차")+COUNTIF(13구역!E4:E43,"8차")+COUNTIF(14구역!E4:E43,"8차")+COUNTIF(21구역!E4:E43,"8차")+COUNTIF(22구역!E4:E43,"8차")+COUNTIF(23구역!E4:E43,"8차")+COUNTIF(24구역!E4:E43,"8차")+COUNTIF(31구역!E4:E43,"8차")+COUNTIF(32구역!E4:E43,"8차")+COUNTIF(33구역!E4:E43,"8차")+COUNTIF(34구역!E4:E43,"8차"))</f>
         <v/>
       </c>
-      <c r="J20">
+      <c r="J20" s="32">
         <f>IF(SUM(B20:I20)=0,"",SUM(B20:I20))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>적용 차수</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/수양회_서식_template.xlsx
+++ b/수양회_서식_template.xlsx
@@ -375,7 +375,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -572,6 +572,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7582,8 +7583,6 @@
       <c r="I1" s="35" t="n"/>
       <c r="J1" s="35" t="n"/>
       <c r="K1" s="35" t="n"/>
-      <c r="L1" s="35" t="n"/>
-      <c r="M1" s="35" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1" s="33">
       <c r="A2" s="37" t="inlineStr">
@@ -7599,40 +7598,29 @@
       <c r="C2" s="35" t="n"/>
       <c r="D2" s="37" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
-        </is>
-      </c>
-      <c r="E2" s="37" t="inlineStr">
-        <is>
-          <t>기타
-하행</t>
-        </is>
-      </c>
+          <t>교회차</t>
+        </is>
+      </c>
+      <c r="E2" s="68" t="n"/>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교회차</t>
+          <t>타교회</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
       <c r="H2" s="38" t="inlineStr">
         <is>
-          <t>타교회</t>
+          <t>개인차량</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
       <c r="J2" s="38" t="inlineStr">
         <is>
-          <t>개인차량</t>
+          <t>대중교통</t>
         </is>
       </c>
       <c r="K2" s="35" t="n"/>
-      <c r="L2" s="38" t="inlineStr">
-        <is>
-          <t>대중교통</t>
-        </is>
-      </c>
-      <c r="M2" s="35" t="n"/>
+      <c r="L2" s="38" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="39" t="n"/>
@@ -7646,8 +7634,16 @@
           <t>하행</t>
         </is>
       </c>
-      <c r="D3" s="39" t="n"/>
-      <c r="E3" s="39" t="n"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>상행</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>하행</t>
+        </is>
+      </c>
       <c r="F3" s="40" t="inlineStr">
         <is>
           <t>상행</t>
@@ -7678,16 +7674,8 @@
           <t>하행</t>
         </is>
       </c>
-      <c r="L3" s="40" t="inlineStr">
-        <is>
-          <t>상행</t>
-        </is>
-      </c>
-      <c r="M3" s="40" t="inlineStr">
-        <is>
-          <t>하행</t>
-        </is>
-      </c>
+      <c r="L3" s="40" t="n"/>
+      <c r="M3" s="40" t="n"/>
     </row>
     <row r="4" ht="21.75" customHeight="1" s="33">
       <c r="A4" s="42" t="inlineStr">
@@ -7696,53 +7684,47 @@
         </is>
       </c>
       <c r="B4" s="42">
-        <f>IF(COUNTIFS(11구역!F4:F43,"1호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"2호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"3호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"4호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"5호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"6호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"7호차",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!F4:F43,"1호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"2호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"3호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"4호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"5호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"6호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"7호차",11구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(11구역!F4:F43,"1호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"2호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"3호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"4호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"5호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"6호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"7호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!F4:F43,"1호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"2호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"3호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"4호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"5호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"6호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"7호차",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C4" s="42">
-        <f>IF(COUNTIFS(11구역!G4:G43,"1호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"2호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"3호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"4호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"5호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"6호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"7호차",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!G4:G43,"1호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"2호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"3호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"4호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"5호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"6호차",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"7호차",11구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(11구역!G4:G43,"1호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"2호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"3호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"4호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"5호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"6호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"7호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!G4:G43,"1호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"2호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"3호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"4호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"5호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"6호차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"7호차",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D4" s="42">
-        <f>IF(COUNTIFS(11구역!H4:H43,"&lt;&gt;",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!H4:H43,"&lt;&gt;",11구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(11구역!F4:F43,"교회차1",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"교회차2",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!H4:H43,"*교회차*",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!F4:F43,"교회차1",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!F4:F43,"교회차2",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!H4:H43,"*교회차*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E4" s="42">
-        <f>IF(COUNTIFS(11구역!I4:I43,"&lt;&gt;",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!I4:I43,"&lt;&gt;",11구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(11구역!G4:G43,"교회차1",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"교회차2",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!I4:I43,"*교회차*",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!G4:G43,"교회차1",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!G4:G43,"교회차2",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!I4:I43,"*교회차*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F4" s="42">
-        <f>IF(COUNTIFS(11구역!F4:F43,"교회차1",11구역!E4:E43,$B23)+COUNTIFS(11구역!H4:H43,"교회차1",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"교회차2",11구역!E4:E43,$B23)+COUNTIFS(11구역!H4:H43,"교회차2",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!F4:F43,"교회차1",11구역!E4:E43,$B23)+COUNTIFS(11구역!H4:H43,"교회차1",11구역!E4:E43,$B23)+COUNTIFS(11구역!F4:F43,"교회차2",11구역!E4:E43,$B23)+COUNTIFS(11구역!H4:H43,"교회차2",11구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(11구역!F4:F43,"타교회",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!H4:H43,"*타교회*",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!F4:F43,"타교회",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!H4:H43,"*타교회*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G4" s="42">
-        <f>IF(COUNTIFS(11구역!G4:G43,"교회차1",11구역!E4:E43,$B23)+COUNTIFS(11구역!I4:I43,"교회차1",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"교회차2",11구역!E4:E43,$B23)+COUNTIFS(11구역!I4:I43,"교회차2",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!G4:G43,"교회차1",11구역!E4:E43,$B23)+COUNTIFS(11구역!I4:I43,"교회차1",11구역!E4:E43,$B23)+COUNTIFS(11구역!G4:G43,"교회차2",11구역!E4:E43,$B23)+COUNTIFS(11구역!I4:I43,"교회차2",11구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(11구역!G4:G43,"타교회",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!I4:I43,"*타교회*",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!G4:G43,"타교회",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!I4:I43,"*타교회*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H4" s="42">
-        <f>IF(COUNTIFS(11구역!F4:F43,"타교회",11구역!E4:E43,$B23)+COUNTIFS(11구역!H4:H43,"타교회",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!F4:F43,"타교회",11구역!E4:E43,$B23)+COUNTIFS(11구역!H4:H43,"타교회",11구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(11구역!F4:F43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!H4:H43,"*개인차*",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!F4:F43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!H4:H43,"*개인차*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I4" s="42">
-        <f>IF(COUNTIFS(11구역!G4:G43,"타교회",11구역!E4:E43,$B23)+COUNTIFS(11구역!I4:I43,"타교회",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!G4:G43,"타교회",11구역!E4:E43,$B23)+COUNTIFS(11구역!I4:I43,"타교회",11구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(11구역!G4:G43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!I4:I43,"*개인차*",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!G4:G43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!I4:I43,"*개인차*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J4" s="42">
-        <f>IF(COUNTIFS(11구역!F4:F43,"개인차",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!F4:F43,"개인차",11구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(11구역!F4:F43,"대중교통",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!H4:H43,"*대중교통*",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!F4:F43,"대중교통",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!H4:H43,"*대중교통*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K4" s="42">
-        <f>IF(COUNTIFS(11구역!G4:G43,"개인차",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!G4:G43,"개인차",11구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L4" s="42">
-        <f>IF(COUNTIFS(11구역!F4:F43,"대중교통",11구역!E4:E43,$B23)+COUNTIFS(11구역!H4:H43,"대중교통",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!F4:F43,"대중교통",11구역!E4:E43,$B23)+COUNTIFS(11구역!H4:H43,"대중교통",11구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M4" s="42">
-        <f>IF(COUNTIFS(11구역!G4:G43,"대중교통",11구역!E4:E43,$B23)+COUNTIFS(11구역!I4:I43,"대중교통",11구역!E4:E43,$B23)=0,"",COUNTIFS(11구역!G4:G43,"대중교통",11구역!E4:E43,$B23)+COUNTIFS(11구역!I4:I43,"대중교통",11구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(11구역!G4:G43,"대중교통",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!I4:I43,"*대중교통*",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!G4:G43,"대중교통",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!I4:I43,"*대중교통*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L4" s="42" t="n"/>
+      <c r="M4" s="42" t="n"/>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="33">
       <c r="A5" s="44" t="inlineStr">
@@ -7751,53 +7733,47 @@
         </is>
       </c>
       <c r="B5" s="44">
-        <f>IF(COUNTIFS(12구역!F4:F43,"1호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"2호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"3호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"4호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"5호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"6호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"7호차",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!F4:F43,"1호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"2호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"3호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"4호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"5호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"6호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"7호차",12구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(12구역!F4:F43,"1호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"2호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"3호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"4호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"5호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"6호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"7호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!F4:F43,"1호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"2호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"3호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"4호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"5호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"6호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"7호차",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C5" s="44">
-        <f>IF(COUNTIFS(12구역!G4:G43,"1호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"2호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"3호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"4호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"5호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"6호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"7호차",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!G4:G43,"1호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"2호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"3호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"4호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"5호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"6호차",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"7호차",12구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(12구역!G4:G43,"1호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"2호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"3호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"4호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"5호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"6호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"7호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!G4:G43,"1호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"2호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"3호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"4호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"5호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"6호차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"7호차",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D5" s="44">
-        <f>IF(COUNTIFS(12구역!H4:H43,"&lt;&gt;",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!H4:H43,"&lt;&gt;",12구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(12구역!F4:F43,"교회차1",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"교회차2",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!H4:H43,"*교회차*",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!F4:F43,"교회차1",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!F4:F43,"교회차2",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!H4:H43,"*교회차*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E5" s="44">
-        <f>IF(COUNTIFS(12구역!I4:I43,"&lt;&gt;",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!I4:I43,"&lt;&gt;",12구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(12구역!G4:G43,"교회차1",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"교회차2",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!I4:I43,"*교회차*",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!G4:G43,"교회차1",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!G4:G43,"교회차2",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!I4:I43,"*교회차*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F5" s="44">
-        <f>IF(COUNTIFS(12구역!F4:F43,"교회차1",12구역!E4:E43,$B23)+COUNTIFS(12구역!H4:H43,"교회차1",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"교회차2",12구역!E4:E43,$B23)+COUNTIFS(12구역!H4:H43,"교회차2",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!F4:F43,"교회차1",12구역!E4:E43,$B23)+COUNTIFS(12구역!H4:H43,"교회차1",12구역!E4:E43,$B23)+COUNTIFS(12구역!F4:F43,"교회차2",12구역!E4:E43,$B23)+COUNTIFS(12구역!H4:H43,"교회차2",12구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(12구역!F4:F43,"타교회",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!H4:H43,"*타교회*",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!F4:F43,"타교회",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!H4:H43,"*타교회*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G5" s="44">
-        <f>IF(COUNTIFS(12구역!G4:G43,"교회차1",12구역!E4:E43,$B23)+COUNTIFS(12구역!I4:I43,"교회차1",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"교회차2",12구역!E4:E43,$B23)+COUNTIFS(12구역!I4:I43,"교회차2",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!G4:G43,"교회차1",12구역!E4:E43,$B23)+COUNTIFS(12구역!I4:I43,"교회차1",12구역!E4:E43,$B23)+COUNTIFS(12구역!G4:G43,"교회차2",12구역!E4:E43,$B23)+COUNTIFS(12구역!I4:I43,"교회차2",12구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(12구역!G4:G43,"타교회",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!I4:I43,"*타교회*",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!G4:G43,"타교회",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!I4:I43,"*타교회*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H5" s="44">
-        <f>IF(COUNTIFS(12구역!F4:F43,"타교회",12구역!E4:E43,$B23)+COUNTIFS(12구역!H4:H43,"타교회",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!F4:F43,"타교회",12구역!E4:E43,$B23)+COUNTIFS(12구역!H4:H43,"타교회",12구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(12구역!F4:F43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!H4:H43,"*개인차*",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!F4:F43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!H4:H43,"*개인차*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I5" s="44">
-        <f>IF(COUNTIFS(12구역!G4:G43,"타교회",12구역!E4:E43,$B23)+COUNTIFS(12구역!I4:I43,"타교회",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!G4:G43,"타교회",12구역!E4:E43,$B23)+COUNTIFS(12구역!I4:I43,"타교회",12구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(12구역!G4:G43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!I4:I43,"*개인차*",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!G4:G43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!I4:I43,"*개인차*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J5" s="44">
-        <f>IF(COUNTIFS(12구역!F4:F43,"개인차",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!F4:F43,"개인차",12구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(12구역!F4:F43,"대중교통",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!H4:H43,"*대중교통*",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!F4:F43,"대중교통",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!H4:H43,"*대중교통*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K5" s="44">
-        <f>IF(COUNTIFS(12구역!G4:G43,"개인차",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!G4:G43,"개인차",12구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L5" s="44">
-        <f>IF(COUNTIFS(12구역!F4:F43,"대중교통",12구역!E4:E43,$B23)+COUNTIFS(12구역!H4:H43,"대중교통",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!F4:F43,"대중교통",12구역!E4:E43,$B23)+COUNTIFS(12구역!H4:H43,"대중교통",12구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M5" s="44">
-        <f>IF(COUNTIFS(12구역!G4:G43,"대중교통",12구역!E4:E43,$B23)+COUNTIFS(12구역!I4:I43,"대중교통",12구역!E4:E43,$B23)=0,"",COUNTIFS(12구역!G4:G43,"대중교통",12구역!E4:E43,$B23)+COUNTIFS(12구역!I4:I43,"대중교통",12구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(12구역!G4:G43,"대중교통",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!I4:I43,"*대중교통*",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!G4:G43,"대중교통",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!I4:I43,"*대중교통*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L5" s="44" t="n"/>
+      <c r="M5" s="44" t="n"/>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="33">
       <c r="A6" s="42" t="inlineStr">
@@ -7806,53 +7782,47 @@
         </is>
       </c>
       <c r="B6" s="42">
-        <f>IF(COUNTIFS(13구역!F4:F43,"1호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"2호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"3호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"4호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"5호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"6호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"7호차",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!F4:F43,"1호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"2호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"3호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"4호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"5호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"6호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"7호차",13구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(13구역!F4:F43,"1호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"2호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"3호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"4호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"5호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"6호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"7호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!F4:F43,"1호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"2호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"3호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"4호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"5호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"6호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"7호차",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C6" s="42">
-        <f>IF(COUNTIFS(13구역!G4:G43,"1호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"2호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"3호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"4호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"5호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"6호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"7호차",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!G4:G43,"1호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"2호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"3호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"4호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"5호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"6호차",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"7호차",13구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(13구역!G4:G43,"1호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"2호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"3호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"4호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"5호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"6호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"7호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!G4:G43,"1호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"2호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"3호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"4호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"5호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"6호차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"7호차",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D6" s="42">
-        <f>IF(COUNTIFS(13구역!H4:H43,"&lt;&gt;",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!H4:H43,"&lt;&gt;",13구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(13구역!F4:F43,"교회차1",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"교회차2",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!H4:H43,"*교회차*",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!F4:F43,"교회차1",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!F4:F43,"교회차2",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!H4:H43,"*교회차*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E6" s="42">
-        <f>IF(COUNTIFS(13구역!I4:I43,"&lt;&gt;",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!I4:I43,"&lt;&gt;",13구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(13구역!G4:G43,"교회차1",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"교회차2",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!I4:I43,"*교회차*",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!G4:G43,"교회차1",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!G4:G43,"교회차2",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!I4:I43,"*교회차*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F6" s="42">
-        <f>IF(COUNTIFS(13구역!F4:F43,"교회차1",13구역!E4:E43,$B23)+COUNTIFS(13구역!H4:H43,"교회차1",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"교회차2",13구역!E4:E43,$B23)+COUNTIFS(13구역!H4:H43,"교회차2",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!F4:F43,"교회차1",13구역!E4:E43,$B23)+COUNTIFS(13구역!H4:H43,"교회차1",13구역!E4:E43,$B23)+COUNTIFS(13구역!F4:F43,"교회차2",13구역!E4:E43,$B23)+COUNTIFS(13구역!H4:H43,"교회차2",13구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(13구역!F4:F43,"타교회",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!H4:H43,"*타교회*",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!F4:F43,"타교회",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!H4:H43,"*타교회*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G6" s="42">
-        <f>IF(COUNTIFS(13구역!G4:G43,"교회차1",13구역!E4:E43,$B23)+COUNTIFS(13구역!I4:I43,"교회차1",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"교회차2",13구역!E4:E43,$B23)+COUNTIFS(13구역!I4:I43,"교회차2",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!G4:G43,"교회차1",13구역!E4:E43,$B23)+COUNTIFS(13구역!I4:I43,"교회차1",13구역!E4:E43,$B23)+COUNTIFS(13구역!G4:G43,"교회차2",13구역!E4:E43,$B23)+COUNTIFS(13구역!I4:I43,"교회차2",13구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(13구역!G4:G43,"타교회",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!I4:I43,"*타교회*",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!G4:G43,"타교회",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!I4:I43,"*타교회*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H6" s="42">
-        <f>IF(COUNTIFS(13구역!F4:F43,"타교회",13구역!E4:E43,$B23)+COUNTIFS(13구역!H4:H43,"타교회",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!F4:F43,"타교회",13구역!E4:E43,$B23)+COUNTIFS(13구역!H4:H43,"타교회",13구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(13구역!F4:F43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!H4:H43,"*개인차*",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!F4:F43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!H4:H43,"*개인차*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I6" s="42">
-        <f>IF(COUNTIFS(13구역!G4:G43,"타교회",13구역!E4:E43,$B23)+COUNTIFS(13구역!I4:I43,"타교회",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!G4:G43,"타교회",13구역!E4:E43,$B23)+COUNTIFS(13구역!I4:I43,"타교회",13구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(13구역!G4:G43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!I4:I43,"*개인차*",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!G4:G43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!I4:I43,"*개인차*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J6" s="42">
-        <f>IF(COUNTIFS(13구역!F4:F43,"개인차",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!F4:F43,"개인차",13구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(13구역!F4:F43,"대중교통",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!H4:H43,"*대중교통*",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!F4:F43,"대중교통",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!H4:H43,"*대중교통*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K6" s="42">
-        <f>IF(COUNTIFS(13구역!G4:G43,"개인차",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!G4:G43,"개인차",13구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L6" s="42">
-        <f>IF(COUNTIFS(13구역!F4:F43,"대중교통",13구역!E4:E43,$B23)+COUNTIFS(13구역!H4:H43,"대중교통",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!F4:F43,"대중교통",13구역!E4:E43,$B23)+COUNTIFS(13구역!H4:H43,"대중교통",13구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M6" s="42">
-        <f>IF(COUNTIFS(13구역!G4:G43,"대중교통",13구역!E4:E43,$B23)+COUNTIFS(13구역!I4:I43,"대중교통",13구역!E4:E43,$B23)=0,"",COUNTIFS(13구역!G4:G43,"대중교통",13구역!E4:E43,$B23)+COUNTIFS(13구역!I4:I43,"대중교통",13구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(13구역!G4:G43,"대중교통",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!I4:I43,"*대중교통*",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!G4:G43,"대중교통",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!I4:I43,"*대중교통*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L6" s="42" t="n"/>
+      <c r="M6" s="42" t="n"/>
     </row>
     <row r="7" ht="21.75" customHeight="1" s="33">
       <c r="A7" s="44" t="inlineStr">
@@ -7861,53 +7831,47 @@
         </is>
       </c>
       <c r="B7" s="44">
-        <f>IF(COUNTIFS(14구역!F4:F43,"1호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"2호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"3호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"4호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"5호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"6호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"7호차",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!F4:F43,"1호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"2호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"3호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"4호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"5호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"6호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"7호차",14구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(14구역!F4:F43,"1호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"2호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"3호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"4호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"5호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"6호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"7호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!F4:F43,"1호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"2호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"3호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"4호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"5호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"6호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"7호차",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C7" s="44">
-        <f>IF(COUNTIFS(14구역!G4:G43,"1호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"2호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"3호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"4호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"5호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"6호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"7호차",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!G4:G43,"1호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"2호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"3호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"4호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"5호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"6호차",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"7호차",14구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(14구역!G4:G43,"1호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"2호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"3호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"4호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"5호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"6호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"7호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!G4:G43,"1호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"2호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"3호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"4호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"5호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"6호차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"7호차",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D7" s="44">
-        <f>IF(COUNTIFS(14구역!H4:H43,"&lt;&gt;",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!H4:H43,"&lt;&gt;",14구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(14구역!F4:F43,"교회차1",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"교회차2",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!H4:H43,"*교회차*",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!F4:F43,"교회차1",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!F4:F43,"교회차2",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!H4:H43,"*교회차*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E7" s="44">
-        <f>IF(COUNTIFS(14구역!I4:I43,"&lt;&gt;",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!I4:I43,"&lt;&gt;",14구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(14구역!G4:G43,"교회차1",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"교회차2",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!I4:I43,"*교회차*",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!G4:G43,"교회차1",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!G4:G43,"교회차2",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!I4:I43,"*교회차*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F7" s="44">
-        <f>IF(COUNTIFS(14구역!F4:F43,"교회차1",14구역!E4:E43,$B23)+COUNTIFS(14구역!H4:H43,"교회차1",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"교회차2",14구역!E4:E43,$B23)+COUNTIFS(14구역!H4:H43,"교회차2",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!F4:F43,"교회차1",14구역!E4:E43,$B23)+COUNTIFS(14구역!H4:H43,"교회차1",14구역!E4:E43,$B23)+COUNTIFS(14구역!F4:F43,"교회차2",14구역!E4:E43,$B23)+COUNTIFS(14구역!H4:H43,"교회차2",14구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(14구역!F4:F43,"타교회",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!H4:H43,"*타교회*",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!F4:F43,"타교회",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!H4:H43,"*타교회*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G7" s="44">
-        <f>IF(COUNTIFS(14구역!G4:G43,"교회차1",14구역!E4:E43,$B23)+COUNTIFS(14구역!I4:I43,"교회차1",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"교회차2",14구역!E4:E43,$B23)+COUNTIFS(14구역!I4:I43,"교회차2",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!G4:G43,"교회차1",14구역!E4:E43,$B23)+COUNTIFS(14구역!I4:I43,"교회차1",14구역!E4:E43,$B23)+COUNTIFS(14구역!G4:G43,"교회차2",14구역!E4:E43,$B23)+COUNTIFS(14구역!I4:I43,"교회차2",14구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(14구역!G4:G43,"타교회",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!I4:I43,"*타교회*",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!G4:G43,"타교회",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!I4:I43,"*타교회*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H7" s="44">
-        <f>IF(COUNTIFS(14구역!F4:F43,"타교회",14구역!E4:E43,$B23)+COUNTIFS(14구역!H4:H43,"타교회",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!F4:F43,"타교회",14구역!E4:E43,$B23)+COUNTIFS(14구역!H4:H43,"타교회",14구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(14구역!F4:F43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!H4:H43,"*개인차*",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!F4:F43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!H4:H43,"*개인차*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I7" s="44">
-        <f>IF(COUNTIFS(14구역!G4:G43,"타교회",14구역!E4:E43,$B23)+COUNTIFS(14구역!I4:I43,"타교회",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!G4:G43,"타교회",14구역!E4:E43,$B23)+COUNTIFS(14구역!I4:I43,"타교회",14구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(14구역!G4:G43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!I4:I43,"*개인차*",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!G4:G43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!I4:I43,"*개인차*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J7" s="44">
-        <f>IF(COUNTIFS(14구역!F4:F43,"개인차",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!F4:F43,"개인차",14구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(14구역!F4:F43,"대중교통",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!H4:H43,"*대중교통*",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!F4:F43,"대중교통",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!H4:H43,"*대중교통*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K7" s="44">
-        <f>IF(COUNTIFS(14구역!G4:G43,"개인차",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!G4:G43,"개인차",14구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L7" s="44">
-        <f>IF(COUNTIFS(14구역!F4:F43,"대중교통",14구역!E4:E43,$B23)+COUNTIFS(14구역!H4:H43,"대중교통",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!F4:F43,"대중교통",14구역!E4:E43,$B23)+COUNTIFS(14구역!H4:H43,"대중교통",14구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M7" s="44">
-        <f>IF(COUNTIFS(14구역!G4:G43,"대중교통",14구역!E4:E43,$B23)+COUNTIFS(14구역!I4:I43,"대중교통",14구역!E4:E43,$B23)=0,"",COUNTIFS(14구역!G4:G43,"대중교통",14구역!E4:E43,$B23)+COUNTIFS(14구역!I4:I43,"대중교통",14구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(14구역!G4:G43,"대중교통",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!I4:I43,"*대중교통*",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!G4:G43,"대중교통",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!I4:I43,"*대중교통*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L7" s="44" t="n"/>
+      <c r="M7" s="44" t="n"/>
     </row>
     <row r="8" ht="21.75" customHeight="1" s="33">
       <c r="A8" s="42" t="inlineStr">
@@ -7916,53 +7880,47 @@
         </is>
       </c>
       <c r="B8" s="42">
-        <f>IF(COUNTIFS(21구역!F4:F43,"1호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"2호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"3호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"4호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"5호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"6호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"7호차",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!F4:F43,"1호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"2호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"3호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"4호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"5호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"6호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"7호차",21구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(21구역!F4:F43,"1호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"2호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"3호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"4호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"5호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"6호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"7호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!F4:F43,"1호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"2호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"3호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"4호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"5호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"6호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"7호차",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C8" s="42">
-        <f>IF(COUNTIFS(21구역!G4:G43,"1호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"2호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"3호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"4호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"5호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"6호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"7호차",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!G4:G43,"1호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"2호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"3호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"4호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"5호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"6호차",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"7호차",21구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(21구역!G4:G43,"1호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"2호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"3호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"4호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"5호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"6호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"7호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!G4:G43,"1호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"2호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"3호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"4호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"5호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"6호차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"7호차",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D8" s="42">
-        <f>IF(COUNTIFS(21구역!H4:H43,"&lt;&gt;",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!H4:H43,"&lt;&gt;",21구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(21구역!F4:F43,"교회차1",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"교회차2",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!H4:H43,"*교회차*",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!F4:F43,"교회차1",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!F4:F43,"교회차2",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!H4:H43,"*교회차*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E8" s="42">
-        <f>IF(COUNTIFS(21구역!I4:I43,"&lt;&gt;",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!I4:I43,"&lt;&gt;",21구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(21구역!G4:G43,"교회차1",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"교회차2",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!I4:I43,"*교회차*",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!G4:G43,"교회차1",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!G4:G43,"교회차2",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!I4:I43,"*교회차*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F8" s="42">
-        <f>IF(COUNTIFS(21구역!F4:F43,"교회차1",21구역!E4:E43,$B23)+COUNTIFS(21구역!H4:H43,"교회차1",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"교회차2",21구역!E4:E43,$B23)+COUNTIFS(21구역!H4:H43,"교회차2",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!F4:F43,"교회차1",21구역!E4:E43,$B23)+COUNTIFS(21구역!H4:H43,"교회차1",21구역!E4:E43,$B23)+COUNTIFS(21구역!F4:F43,"교회차2",21구역!E4:E43,$B23)+COUNTIFS(21구역!H4:H43,"교회차2",21구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(21구역!F4:F43,"타교회",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!H4:H43,"*타교회*",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!F4:F43,"타교회",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!H4:H43,"*타교회*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G8" s="42">
-        <f>IF(COUNTIFS(21구역!G4:G43,"교회차1",21구역!E4:E43,$B23)+COUNTIFS(21구역!I4:I43,"교회차1",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"교회차2",21구역!E4:E43,$B23)+COUNTIFS(21구역!I4:I43,"교회차2",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!G4:G43,"교회차1",21구역!E4:E43,$B23)+COUNTIFS(21구역!I4:I43,"교회차1",21구역!E4:E43,$B23)+COUNTIFS(21구역!G4:G43,"교회차2",21구역!E4:E43,$B23)+COUNTIFS(21구역!I4:I43,"교회차2",21구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(21구역!G4:G43,"타교회",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!I4:I43,"*타교회*",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!G4:G43,"타교회",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!I4:I43,"*타교회*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H8" s="42">
-        <f>IF(COUNTIFS(21구역!F4:F43,"타교회",21구역!E4:E43,$B23)+COUNTIFS(21구역!H4:H43,"타교회",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!F4:F43,"타교회",21구역!E4:E43,$B23)+COUNTIFS(21구역!H4:H43,"타교회",21구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(21구역!F4:F43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!H4:H43,"*개인차*",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!F4:F43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!H4:H43,"*개인차*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I8" s="42">
-        <f>IF(COUNTIFS(21구역!G4:G43,"타교회",21구역!E4:E43,$B23)+COUNTIFS(21구역!I4:I43,"타교회",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!G4:G43,"타교회",21구역!E4:E43,$B23)+COUNTIFS(21구역!I4:I43,"타교회",21구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(21구역!G4:G43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!I4:I43,"*개인차*",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!G4:G43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!I4:I43,"*개인차*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J8" s="42">
-        <f>IF(COUNTIFS(21구역!F4:F43,"개인차",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!F4:F43,"개인차",21구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(21구역!F4:F43,"대중교통",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!H4:H43,"*대중교통*",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!F4:F43,"대중교통",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!H4:H43,"*대중교통*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K8" s="42">
-        <f>IF(COUNTIFS(21구역!G4:G43,"개인차",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!G4:G43,"개인차",21구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L8" s="42">
-        <f>IF(COUNTIFS(21구역!F4:F43,"대중교통",21구역!E4:E43,$B23)+COUNTIFS(21구역!H4:H43,"대중교통",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!F4:F43,"대중교통",21구역!E4:E43,$B23)+COUNTIFS(21구역!H4:H43,"대중교통",21구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M8" s="42">
-        <f>IF(COUNTIFS(21구역!G4:G43,"대중교통",21구역!E4:E43,$B23)+COUNTIFS(21구역!I4:I43,"대중교통",21구역!E4:E43,$B23)=0,"",COUNTIFS(21구역!G4:G43,"대중교통",21구역!E4:E43,$B23)+COUNTIFS(21구역!I4:I43,"대중교통",21구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(21구역!G4:G43,"대중교통",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!I4:I43,"*대중교통*",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!G4:G43,"대중교통",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!I4:I43,"*대중교통*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L8" s="42" t="n"/>
+      <c r="M8" s="42" t="n"/>
     </row>
     <row r="9" ht="21.75" customHeight="1" s="33">
       <c r="A9" s="44" t="inlineStr">
@@ -7971,53 +7929,47 @@
         </is>
       </c>
       <c r="B9" s="44">
-        <f>IF(COUNTIFS(22구역!F4:F43,"1호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"2호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"3호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"4호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"5호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"6호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"7호차",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!F4:F43,"1호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"2호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"3호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"4호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"5호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"6호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"7호차",22구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(22구역!F4:F43,"1호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"2호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"3호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"4호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"5호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"6호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"7호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!F4:F43,"1호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"2호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"3호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"4호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"5호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"6호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"7호차",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C9" s="44">
-        <f>IF(COUNTIFS(22구역!G4:G43,"1호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"2호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"3호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"4호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"5호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"6호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"7호차",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!G4:G43,"1호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"2호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"3호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"4호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"5호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"6호차",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"7호차",22구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(22구역!G4:G43,"1호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"2호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"3호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"4호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"5호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"6호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"7호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!G4:G43,"1호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"2호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"3호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"4호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"5호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"6호차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"7호차",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D9" s="44">
-        <f>IF(COUNTIFS(22구역!H4:H43,"&lt;&gt;",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!H4:H43,"&lt;&gt;",22구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(22구역!F4:F43,"교회차1",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"교회차2",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!H4:H43,"*교회차*",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!F4:F43,"교회차1",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!F4:F43,"교회차2",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!H4:H43,"*교회차*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E9" s="44">
-        <f>IF(COUNTIFS(22구역!I4:I43,"&lt;&gt;",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!I4:I43,"&lt;&gt;",22구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(22구역!G4:G43,"교회차1",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"교회차2",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!I4:I43,"*교회차*",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!G4:G43,"교회차1",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!G4:G43,"교회차2",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!I4:I43,"*교회차*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F9" s="44">
-        <f>IF(COUNTIFS(22구역!F4:F43,"교회차1",22구역!E4:E43,$B23)+COUNTIFS(22구역!H4:H43,"교회차1",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"교회차2",22구역!E4:E43,$B23)+COUNTIFS(22구역!H4:H43,"교회차2",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!F4:F43,"교회차1",22구역!E4:E43,$B23)+COUNTIFS(22구역!H4:H43,"교회차1",22구역!E4:E43,$B23)+COUNTIFS(22구역!F4:F43,"교회차2",22구역!E4:E43,$B23)+COUNTIFS(22구역!H4:H43,"교회차2",22구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(22구역!F4:F43,"타교회",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!H4:H43,"*타교회*",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!F4:F43,"타교회",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!H4:H43,"*타교회*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G9" s="44">
-        <f>IF(COUNTIFS(22구역!G4:G43,"교회차1",22구역!E4:E43,$B23)+COUNTIFS(22구역!I4:I43,"교회차1",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"교회차2",22구역!E4:E43,$B23)+COUNTIFS(22구역!I4:I43,"교회차2",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!G4:G43,"교회차1",22구역!E4:E43,$B23)+COUNTIFS(22구역!I4:I43,"교회차1",22구역!E4:E43,$B23)+COUNTIFS(22구역!G4:G43,"교회차2",22구역!E4:E43,$B23)+COUNTIFS(22구역!I4:I43,"교회차2",22구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(22구역!G4:G43,"타교회",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!I4:I43,"*타교회*",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!G4:G43,"타교회",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!I4:I43,"*타교회*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H9" s="44">
-        <f>IF(COUNTIFS(22구역!F4:F43,"타교회",22구역!E4:E43,$B23)+COUNTIFS(22구역!H4:H43,"타교회",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!F4:F43,"타교회",22구역!E4:E43,$B23)+COUNTIFS(22구역!H4:H43,"타교회",22구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(22구역!F4:F43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!H4:H43,"*개인차*",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!F4:F43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!H4:H43,"*개인차*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I9" s="44">
-        <f>IF(COUNTIFS(22구역!G4:G43,"타교회",22구역!E4:E43,$B23)+COUNTIFS(22구역!I4:I43,"타교회",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!G4:G43,"타교회",22구역!E4:E43,$B23)+COUNTIFS(22구역!I4:I43,"타교회",22구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(22구역!G4:G43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!I4:I43,"*개인차*",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!G4:G43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!I4:I43,"*개인차*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J9" s="44">
-        <f>IF(COUNTIFS(22구역!F4:F43,"개인차",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!F4:F43,"개인차",22구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(22구역!F4:F43,"대중교통",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!H4:H43,"*대중교통*",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!F4:F43,"대중교통",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!H4:H43,"*대중교통*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K9" s="44">
-        <f>IF(COUNTIFS(22구역!G4:G43,"개인차",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!G4:G43,"개인차",22구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L9" s="44">
-        <f>IF(COUNTIFS(22구역!F4:F43,"대중교통",22구역!E4:E43,$B23)+COUNTIFS(22구역!H4:H43,"대중교통",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!F4:F43,"대중교통",22구역!E4:E43,$B23)+COUNTIFS(22구역!H4:H43,"대중교통",22구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M9" s="44">
-        <f>IF(COUNTIFS(22구역!G4:G43,"대중교통",22구역!E4:E43,$B23)+COUNTIFS(22구역!I4:I43,"대중교통",22구역!E4:E43,$B23)=0,"",COUNTIFS(22구역!G4:G43,"대중교통",22구역!E4:E43,$B23)+COUNTIFS(22구역!I4:I43,"대중교통",22구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(22구역!G4:G43,"대중교통",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!I4:I43,"*대중교통*",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!G4:G43,"대중교통",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!I4:I43,"*대중교통*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L9" s="44" t="n"/>
+      <c r="M9" s="44" t="n"/>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="33">
       <c r="A10" s="42" t="inlineStr">
@@ -8026,53 +7978,47 @@
         </is>
       </c>
       <c r="B10" s="42">
-        <f>IF(COUNTIFS(23구역!F4:F43,"1호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"2호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"3호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"4호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"5호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"6호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"7호차",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!F4:F43,"1호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"2호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"3호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"4호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"5호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"6호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"7호차",23구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(23구역!F4:F43,"1호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"2호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"3호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"4호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"5호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"6호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"7호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!F4:F43,"1호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"2호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"3호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"4호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"5호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"6호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"7호차",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C10" s="42">
-        <f>IF(COUNTIFS(23구역!G4:G43,"1호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"2호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"3호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"4호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"5호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"6호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"7호차",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!G4:G43,"1호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"2호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"3호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"4호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"5호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"6호차",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"7호차",23구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(23구역!G4:G43,"1호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"2호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"3호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"4호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"5호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"6호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"7호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!G4:G43,"1호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"2호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"3호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"4호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"5호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"6호차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"7호차",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D10" s="42">
-        <f>IF(COUNTIFS(23구역!H4:H43,"&lt;&gt;",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!H4:H43,"&lt;&gt;",23구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(23구역!F4:F43,"교회차1",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"교회차2",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!H4:H43,"*교회차*",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!F4:F43,"교회차1",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!F4:F43,"교회차2",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!H4:H43,"*교회차*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E10" s="42">
-        <f>IF(COUNTIFS(23구역!I4:I43,"&lt;&gt;",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!I4:I43,"&lt;&gt;",23구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(23구역!G4:G43,"교회차1",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"교회차2",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!I4:I43,"*교회차*",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!G4:G43,"교회차1",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!G4:G43,"교회차2",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!I4:I43,"*교회차*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F10" s="42">
-        <f>IF(COUNTIFS(23구역!F4:F43,"교회차1",23구역!E4:E43,$B23)+COUNTIFS(23구역!H4:H43,"교회차1",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"교회차2",23구역!E4:E43,$B23)+COUNTIFS(23구역!H4:H43,"교회차2",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!F4:F43,"교회차1",23구역!E4:E43,$B23)+COUNTIFS(23구역!H4:H43,"교회차1",23구역!E4:E43,$B23)+COUNTIFS(23구역!F4:F43,"교회차2",23구역!E4:E43,$B23)+COUNTIFS(23구역!H4:H43,"교회차2",23구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(23구역!F4:F43,"타교회",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!H4:H43,"*타교회*",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!F4:F43,"타교회",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!H4:H43,"*타교회*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G10" s="42">
-        <f>IF(COUNTIFS(23구역!G4:G43,"교회차1",23구역!E4:E43,$B23)+COUNTIFS(23구역!I4:I43,"교회차1",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"교회차2",23구역!E4:E43,$B23)+COUNTIFS(23구역!I4:I43,"교회차2",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!G4:G43,"교회차1",23구역!E4:E43,$B23)+COUNTIFS(23구역!I4:I43,"교회차1",23구역!E4:E43,$B23)+COUNTIFS(23구역!G4:G43,"교회차2",23구역!E4:E43,$B23)+COUNTIFS(23구역!I4:I43,"교회차2",23구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(23구역!G4:G43,"타교회",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!I4:I43,"*타교회*",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!G4:G43,"타교회",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!I4:I43,"*타교회*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H10" s="42">
-        <f>IF(COUNTIFS(23구역!F4:F43,"타교회",23구역!E4:E43,$B23)+COUNTIFS(23구역!H4:H43,"타교회",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!F4:F43,"타교회",23구역!E4:E43,$B23)+COUNTIFS(23구역!H4:H43,"타교회",23구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(23구역!F4:F43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!H4:H43,"*개인차*",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!F4:F43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!H4:H43,"*개인차*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I10" s="42">
-        <f>IF(COUNTIFS(23구역!G4:G43,"타교회",23구역!E4:E43,$B23)+COUNTIFS(23구역!I4:I43,"타교회",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!G4:G43,"타교회",23구역!E4:E43,$B23)+COUNTIFS(23구역!I4:I43,"타교회",23구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(23구역!G4:G43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!I4:I43,"*개인차*",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!G4:G43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!I4:I43,"*개인차*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J10" s="42">
-        <f>IF(COUNTIFS(23구역!F4:F43,"개인차",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!F4:F43,"개인차",23구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(23구역!F4:F43,"대중교통",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!H4:H43,"*대중교통*",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!F4:F43,"대중교통",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!H4:H43,"*대중교통*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K10" s="42">
-        <f>IF(COUNTIFS(23구역!G4:G43,"개인차",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!G4:G43,"개인차",23구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L10" s="42">
-        <f>IF(COUNTIFS(23구역!F4:F43,"대중교통",23구역!E4:E43,$B23)+COUNTIFS(23구역!H4:H43,"대중교통",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!F4:F43,"대중교통",23구역!E4:E43,$B23)+COUNTIFS(23구역!H4:H43,"대중교통",23구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M10" s="42">
-        <f>IF(COUNTIFS(23구역!G4:G43,"대중교통",23구역!E4:E43,$B23)+COUNTIFS(23구역!I4:I43,"대중교통",23구역!E4:E43,$B23)=0,"",COUNTIFS(23구역!G4:G43,"대중교통",23구역!E4:E43,$B23)+COUNTIFS(23구역!I4:I43,"대중교통",23구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(23구역!G4:G43,"대중교통",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!I4:I43,"*대중교통*",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!G4:G43,"대중교통",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!I4:I43,"*대중교통*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L10" s="42" t="n"/>
+      <c r="M10" s="42" t="n"/>
     </row>
     <row r="11" ht="21.75" customHeight="1" s="33">
       <c r="A11" s="44" t="inlineStr">
@@ -8081,53 +8027,47 @@
         </is>
       </c>
       <c r="B11" s="44">
-        <f>IF(COUNTIFS(24구역!F4:F43,"1호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"2호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"3호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"4호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"5호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"6호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"7호차",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!F4:F43,"1호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"2호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"3호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"4호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"5호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"6호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"7호차",24구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(24구역!F4:F43,"1호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"2호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"3호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"4호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"5호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"6호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"7호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!F4:F43,"1호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"2호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"3호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"4호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"5호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"6호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"7호차",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C11" s="44">
-        <f>IF(COUNTIFS(24구역!G4:G43,"1호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"2호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"3호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"4호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"5호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"6호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"7호차",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!G4:G43,"1호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"2호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"3호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"4호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"5호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"6호차",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"7호차",24구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(24구역!G4:G43,"1호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"2호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"3호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"4호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"5호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"6호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"7호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!G4:G43,"1호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"2호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"3호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"4호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"5호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"6호차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"7호차",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D11" s="44">
-        <f>IF(COUNTIFS(24구역!H4:H43,"&lt;&gt;",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!H4:H43,"&lt;&gt;",24구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(24구역!F4:F43,"교회차1",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"교회차2",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!H4:H43,"*교회차*",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!F4:F43,"교회차1",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!F4:F43,"교회차2",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!H4:H43,"*교회차*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E11" s="44">
-        <f>IF(COUNTIFS(24구역!I4:I43,"&lt;&gt;",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!I4:I43,"&lt;&gt;",24구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(24구역!G4:G43,"교회차1",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"교회차2",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!I4:I43,"*교회차*",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!G4:G43,"교회차1",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!G4:G43,"교회차2",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!I4:I43,"*교회차*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F11" s="44">
-        <f>IF(COUNTIFS(24구역!F4:F43,"교회차1",24구역!E4:E43,$B23)+COUNTIFS(24구역!H4:H43,"교회차1",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"교회차2",24구역!E4:E43,$B23)+COUNTIFS(24구역!H4:H43,"교회차2",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!F4:F43,"교회차1",24구역!E4:E43,$B23)+COUNTIFS(24구역!H4:H43,"교회차1",24구역!E4:E43,$B23)+COUNTIFS(24구역!F4:F43,"교회차2",24구역!E4:E43,$B23)+COUNTIFS(24구역!H4:H43,"교회차2",24구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(24구역!F4:F43,"타교회",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!H4:H43,"*타교회*",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!F4:F43,"타교회",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!H4:H43,"*타교회*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G11" s="44">
-        <f>IF(COUNTIFS(24구역!G4:G43,"교회차1",24구역!E4:E43,$B23)+COUNTIFS(24구역!I4:I43,"교회차1",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"교회차2",24구역!E4:E43,$B23)+COUNTIFS(24구역!I4:I43,"교회차2",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!G4:G43,"교회차1",24구역!E4:E43,$B23)+COUNTIFS(24구역!I4:I43,"교회차1",24구역!E4:E43,$B23)+COUNTIFS(24구역!G4:G43,"교회차2",24구역!E4:E43,$B23)+COUNTIFS(24구역!I4:I43,"교회차2",24구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(24구역!G4:G43,"타교회",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!I4:I43,"*타교회*",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!G4:G43,"타교회",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!I4:I43,"*타교회*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H11" s="44">
-        <f>IF(COUNTIFS(24구역!F4:F43,"타교회",24구역!E4:E43,$B23)+COUNTIFS(24구역!H4:H43,"타교회",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!F4:F43,"타교회",24구역!E4:E43,$B23)+COUNTIFS(24구역!H4:H43,"타교회",24구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(24구역!F4:F43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!H4:H43,"*개인차*",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!F4:F43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!H4:H43,"*개인차*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I11" s="44">
-        <f>IF(COUNTIFS(24구역!G4:G43,"타교회",24구역!E4:E43,$B23)+COUNTIFS(24구역!I4:I43,"타교회",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!G4:G43,"타교회",24구역!E4:E43,$B23)+COUNTIFS(24구역!I4:I43,"타교회",24구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(24구역!G4:G43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!I4:I43,"*개인차*",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!G4:G43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!I4:I43,"*개인차*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J11" s="44">
-        <f>IF(COUNTIFS(24구역!F4:F43,"개인차",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!F4:F43,"개인차",24구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(24구역!F4:F43,"대중교통",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!H4:H43,"*대중교통*",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!F4:F43,"대중교통",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!H4:H43,"*대중교통*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K11" s="44">
-        <f>IF(COUNTIFS(24구역!G4:G43,"개인차",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!G4:G43,"개인차",24구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L11" s="44">
-        <f>IF(COUNTIFS(24구역!F4:F43,"대중교통",24구역!E4:E43,$B23)+COUNTIFS(24구역!H4:H43,"대중교통",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!F4:F43,"대중교통",24구역!E4:E43,$B23)+COUNTIFS(24구역!H4:H43,"대중교통",24구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M11" s="44">
-        <f>IF(COUNTIFS(24구역!G4:G43,"대중교통",24구역!E4:E43,$B23)+COUNTIFS(24구역!I4:I43,"대중교통",24구역!E4:E43,$B23)=0,"",COUNTIFS(24구역!G4:G43,"대중교통",24구역!E4:E43,$B23)+COUNTIFS(24구역!I4:I43,"대중교통",24구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(24구역!G4:G43,"대중교통",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!I4:I43,"*대중교통*",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!G4:G43,"대중교통",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!I4:I43,"*대중교통*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L11" s="44" t="n"/>
+      <c r="M11" s="44" t="n"/>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="33">
       <c r="A12" s="42" t="inlineStr">
@@ -8136,53 +8076,47 @@
         </is>
       </c>
       <c r="B12" s="42">
-        <f>IF(COUNTIFS(31구역!F4:F43,"1호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"2호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"3호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"4호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"5호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"6호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"7호차",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!F4:F43,"1호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"2호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"3호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"4호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"5호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"6호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"7호차",31구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(31구역!F4:F43,"1호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"2호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"3호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"4호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"5호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"6호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"7호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!F4:F43,"1호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"2호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"3호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"4호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"5호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"6호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"7호차",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C12" s="42">
-        <f>IF(COUNTIFS(31구역!G4:G43,"1호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"2호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"3호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"4호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"5호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"6호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"7호차",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!G4:G43,"1호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"2호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"3호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"4호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"5호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"6호차",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"7호차",31구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(31구역!G4:G43,"1호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"2호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"3호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"4호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"5호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"6호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"7호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!G4:G43,"1호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"2호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"3호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"4호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"5호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"6호차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"7호차",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D12" s="42">
-        <f>IF(COUNTIFS(31구역!H4:H43,"&lt;&gt;",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!H4:H43,"&lt;&gt;",31구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(31구역!F4:F43,"교회차1",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"교회차2",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!H4:H43,"*교회차*",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!F4:F43,"교회차1",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!F4:F43,"교회차2",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!H4:H43,"*교회차*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E12" s="42">
-        <f>IF(COUNTIFS(31구역!I4:I43,"&lt;&gt;",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!I4:I43,"&lt;&gt;",31구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(31구역!G4:G43,"교회차1",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"교회차2",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!I4:I43,"*교회차*",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!G4:G43,"교회차1",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!G4:G43,"교회차2",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!I4:I43,"*교회차*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F12" s="42">
-        <f>IF(COUNTIFS(31구역!F4:F43,"교회차1",31구역!E4:E43,$B23)+COUNTIFS(31구역!H4:H43,"교회차1",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"교회차2",31구역!E4:E43,$B23)+COUNTIFS(31구역!H4:H43,"교회차2",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!F4:F43,"교회차1",31구역!E4:E43,$B23)+COUNTIFS(31구역!H4:H43,"교회차1",31구역!E4:E43,$B23)+COUNTIFS(31구역!F4:F43,"교회차2",31구역!E4:E43,$B23)+COUNTIFS(31구역!H4:H43,"교회차2",31구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(31구역!F4:F43,"타교회",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!H4:H43,"*타교회*",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!F4:F43,"타교회",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!H4:H43,"*타교회*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G12" s="42">
-        <f>IF(COUNTIFS(31구역!G4:G43,"교회차1",31구역!E4:E43,$B23)+COUNTIFS(31구역!I4:I43,"교회차1",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"교회차2",31구역!E4:E43,$B23)+COUNTIFS(31구역!I4:I43,"교회차2",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!G4:G43,"교회차1",31구역!E4:E43,$B23)+COUNTIFS(31구역!I4:I43,"교회차1",31구역!E4:E43,$B23)+COUNTIFS(31구역!G4:G43,"교회차2",31구역!E4:E43,$B23)+COUNTIFS(31구역!I4:I43,"교회차2",31구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(31구역!G4:G43,"타교회",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!I4:I43,"*타교회*",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!G4:G43,"타교회",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!I4:I43,"*타교회*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H12" s="42">
-        <f>IF(COUNTIFS(31구역!F4:F43,"타교회",31구역!E4:E43,$B23)+COUNTIFS(31구역!H4:H43,"타교회",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!F4:F43,"타교회",31구역!E4:E43,$B23)+COUNTIFS(31구역!H4:H43,"타교회",31구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(31구역!F4:F43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!H4:H43,"*개인차*",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!F4:F43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!H4:H43,"*개인차*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I12" s="42">
-        <f>IF(COUNTIFS(31구역!G4:G43,"타교회",31구역!E4:E43,$B23)+COUNTIFS(31구역!I4:I43,"타교회",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!G4:G43,"타교회",31구역!E4:E43,$B23)+COUNTIFS(31구역!I4:I43,"타교회",31구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(31구역!G4:G43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!I4:I43,"*개인차*",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!G4:G43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!I4:I43,"*개인차*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J12" s="42">
-        <f>IF(COUNTIFS(31구역!F4:F43,"개인차",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!F4:F43,"개인차",31구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(31구역!F4:F43,"대중교통",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!H4:H43,"*대중교통*",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!F4:F43,"대중교통",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!H4:H43,"*대중교통*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K12" s="42">
-        <f>IF(COUNTIFS(31구역!G4:G43,"개인차",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!G4:G43,"개인차",31구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L12" s="42">
-        <f>IF(COUNTIFS(31구역!F4:F43,"대중교통",31구역!E4:E43,$B23)+COUNTIFS(31구역!H4:H43,"대중교통",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!F4:F43,"대중교통",31구역!E4:E43,$B23)+COUNTIFS(31구역!H4:H43,"대중교통",31구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M12" s="42">
-        <f>IF(COUNTIFS(31구역!G4:G43,"대중교통",31구역!E4:E43,$B23)+COUNTIFS(31구역!I4:I43,"대중교통",31구역!E4:E43,$B23)=0,"",COUNTIFS(31구역!G4:G43,"대중교통",31구역!E4:E43,$B23)+COUNTIFS(31구역!I4:I43,"대중교통",31구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(31구역!G4:G43,"대중교통",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!I4:I43,"*대중교통*",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!G4:G43,"대중교통",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!I4:I43,"*대중교통*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L12" s="42" t="n"/>
+      <c r="M12" s="42" t="n"/>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="33">
       <c r="A13" s="44" t="inlineStr">
@@ -8191,53 +8125,47 @@
         </is>
       </c>
       <c r="B13" s="44">
-        <f>IF(COUNTIFS(32구역!F4:F43,"1호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"2호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"3호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"4호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"5호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"6호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"7호차",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!F4:F43,"1호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"2호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"3호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"4호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"5호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"6호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"7호차",32구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(32구역!F4:F43,"1호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"2호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"3호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"4호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"5호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"6호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"7호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!F4:F43,"1호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"2호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"3호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"4호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"5호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"6호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"7호차",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C13" s="44">
-        <f>IF(COUNTIFS(32구역!G4:G43,"1호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"2호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"3호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"4호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"5호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"6호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"7호차",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!G4:G43,"1호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"2호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"3호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"4호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"5호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"6호차",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"7호차",32구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(32구역!G4:G43,"1호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"2호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"3호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"4호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"5호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"6호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"7호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!G4:G43,"1호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"2호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"3호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"4호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"5호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"6호차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"7호차",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D13" s="44">
-        <f>IF(COUNTIFS(32구역!H4:H43,"&lt;&gt;",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!H4:H43,"&lt;&gt;",32구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(32구역!F4:F43,"교회차1",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"교회차2",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!H4:H43,"*교회차*",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!F4:F43,"교회차1",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!F4:F43,"교회차2",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!H4:H43,"*교회차*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E13" s="44">
-        <f>IF(COUNTIFS(32구역!I4:I43,"&lt;&gt;",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!I4:I43,"&lt;&gt;",32구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(32구역!G4:G43,"교회차1",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"교회차2",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!I4:I43,"*교회차*",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!G4:G43,"교회차1",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!G4:G43,"교회차2",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!I4:I43,"*교회차*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F13" s="44">
-        <f>IF(COUNTIFS(32구역!F4:F43,"교회차1",32구역!E4:E43,$B23)+COUNTIFS(32구역!H4:H43,"교회차1",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"교회차2",32구역!E4:E43,$B23)+COUNTIFS(32구역!H4:H43,"교회차2",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!F4:F43,"교회차1",32구역!E4:E43,$B23)+COUNTIFS(32구역!H4:H43,"교회차1",32구역!E4:E43,$B23)+COUNTIFS(32구역!F4:F43,"교회차2",32구역!E4:E43,$B23)+COUNTIFS(32구역!H4:H43,"교회차2",32구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(32구역!F4:F43,"타교회",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!H4:H43,"*타교회*",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!F4:F43,"타교회",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!H4:H43,"*타교회*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G13" s="44">
-        <f>IF(COUNTIFS(32구역!G4:G43,"교회차1",32구역!E4:E43,$B23)+COUNTIFS(32구역!I4:I43,"교회차1",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"교회차2",32구역!E4:E43,$B23)+COUNTIFS(32구역!I4:I43,"교회차2",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!G4:G43,"교회차1",32구역!E4:E43,$B23)+COUNTIFS(32구역!I4:I43,"교회차1",32구역!E4:E43,$B23)+COUNTIFS(32구역!G4:G43,"교회차2",32구역!E4:E43,$B23)+COUNTIFS(32구역!I4:I43,"교회차2",32구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(32구역!G4:G43,"타교회",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!I4:I43,"*타교회*",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!G4:G43,"타교회",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!I4:I43,"*타교회*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H13" s="44">
-        <f>IF(COUNTIFS(32구역!F4:F43,"타교회",32구역!E4:E43,$B23)+COUNTIFS(32구역!H4:H43,"타교회",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!F4:F43,"타교회",32구역!E4:E43,$B23)+COUNTIFS(32구역!H4:H43,"타교회",32구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(32구역!F4:F43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!H4:H43,"*개인차*",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!F4:F43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!H4:H43,"*개인차*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I13" s="44">
-        <f>IF(COUNTIFS(32구역!G4:G43,"타교회",32구역!E4:E43,$B23)+COUNTIFS(32구역!I4:I43,"타교회",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!G4:G43,"타교회",32구역!E4:E43,$B23)+COUNTIFS(32구역!I4:I43,"타교회",32구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(32구역!G4:G43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!I4:I43,"*개인차*",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!G4:G43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!I4:I43,"*개인차*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J13" s="44">
-        <f>IF(COUNTIFS(32구역!F4:F43,"개인차",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!F4:F43,"개인차",32구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(32구역!F4:F43,"대중교통",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!H4:H43,"*대중교통*",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!F4:F43,"대중교통",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!H4:H43,"*대중교통*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K13" s="44">
-        <f>IF(COUNTIFS(32구역!G4:G43,"개인차",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!G4:G43,"개인차",32구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L13" s="44">
-        <f>IF(COUNTIFS(32구역!F4:F43,"대중교통",32구역!E4:E43,$B23)+COUNTIFS(32구역!H4:H43,"대중교통",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!F4:F43,"대중교통",32구역!E4:E43,$B23)+COUNTIFS(32구역!H4:H43,"대중교통",32구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M13" s="44">
-        <f>IF(COUNTIFS(32구역!G4:G43,"대중교통",32구역!E4:E43,$B23)+COUNTIFS(32구역!I4:I43,"대중교통",32구역!E4:E43,$B23)=0,"",COUNTIFS(32구역!G4:G43,"대중교통",32구역!E4:E43,$B23)+COUNTIFS(32구역!I4:I43,"대중교통",32구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(32구역!G4:G43,"대중교통",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!I4:I43,"*대중교통*",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!G4:G43,"대중교통",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!I4:I43,"*대중교통*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L13" s="44" t="n"/>
+      <c r="M13" s="44" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="33">
       <c r="A14" s="61" t="inlineStr">
@@ -8246,53 +8174,47 @@
         </is>
       </c>
       <c r="B14" s="61">
-        <f>IF(COUNTIFS(33구역!F4:F43,"1호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"2호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"3호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"4호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"5호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"6호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"7호차",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!F4:F43,"1호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"2호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"3호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"4호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"5호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"6호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"7호차",33구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(33구역!F4:F43,"1호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"2호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"3호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"4호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"5호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"6호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"7호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!F4:F43,"1호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"2호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"3호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"4호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"5호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"6호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"7호차",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C14" s="61">
-        <f>IF(COUNTIFS(33구역!G4:G43,"1호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"2호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"3호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"4호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"5호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"6호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"7호차",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!G4:G43,"1호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"2호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"3호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"4호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"5호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"6호차",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"7호차",33구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(33구역!G4:G43,"1호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"2호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"3호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"4호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"5호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"6호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"7호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!G4:G43,"1호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"2호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"3호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"4호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"5호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"6호차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"7호차",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D14" s="61">
-        <f>IF(COUNTIFS(33구역!H4:H43,"&lt;&gt;",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!H4:H43,"&lt;&gt;",33구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(33구역!F4:F43,"교회차1",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"교회차2",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!H4:H43,"*교회차*",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!F4:F43,"교회차1",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!F4:F43,"교회차2",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!H4:H43,"*교회차*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E14" s="61">
-        <f>IF(COUNTIFS(33구역!I4:I43,"&lt;&gt;",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!I4:I43,"&lt;&gt;",33구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(33구역!G4:G43,"교회차1",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"교회차2",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!I4:I43,"*교회차*",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!G4:G43,"교회차1",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!G4:G43,"교회차2",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!I4:I43,"*교회차*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F14" s="61">
-        <f>IF(COUNTIFS(33구역!F4:F43,"교회차1",33구역!E4:E43,$B23)+COUNTIFS(33구역!H4:H43,"교회차1",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"교회차2",33구역!E4:E43,$B23)+COUNTIFS(33구역!H4:H43,"교회차2",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!F4:F43,"교회차1",33구역!E4:E43,$B23)+COUNTIFS(33구역!H4:H43,"교회차1",33구역!E4:E43,$B23)+COUNTIFS(33구역!F4:F43,"교회차2",33구역!E4:E43,$B23)+COUNTIFS(33구역!H4:H43,"교회차2",33구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(33구역!F4:F43,"타교회",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!H4:H43,"*타교회*",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!F4:F43,"타교회",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!H4:H43,"*타교회*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G14" s="61">
-        <f>IF(COUNTIFS(33구역!G4:G43,"교회차1",33구역!E4:E43,$B23)+COUNTIFS(33구역!I4:I43,"교회차1",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"교회차2",33구역!E4:E43,$B23)+COUNTIFS(33구역!I4:I43,"교회차2",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!G4:G43,"교회차1",33구역!E4:E43,$B23)+COUNTIFS(33구역!I4:I43,"교회차1",33구역!E4:E43,$B23)+COUNTIFS(33구역!G4:G43,"교회차2",33구역!E4:E43,$B23)+COUNTIFS(33구역!I4:I43,"교회차2",33구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(33구역!G4:G43,"타교회",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!I4:I43,"*타교회*",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!G4:G43,"타교회",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!I4:I43,"*타교회*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H14" s="61">
-        <f>IF(COUNTIFS(33구역!F4:F43,"타교회",33구역!E4:E43,$B23)+COUNTIFS(33구역!H4:H43,"타교회",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!F4:F43,"타교회",33구역!E4:E43,$B23)+COUNTIFS(33구역!H4:H43,"타교회",33구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(33구역!F4:F43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!H4:H43,"*개인차*",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!F4:F43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!H4:H43,"*개인차*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I14" s="61">
-        <f>IF(COUNTIFS(33구역!G4:G43,"타교회",33구역!E4:E43,$B23)+COUNTIFS(33구역!I4:I43,"타교회",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!G4:G43,"타교회",33구역!E4:E43,$B23)+COUNTIFS(33구역!I4:I43,"타교회",33구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(33구역!G4:G43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!I4:I43,"*개인차*",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!G4:G43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!I4:I43,"*개인차*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J14" s="61">
-        <f>IF(COUNTIFS(33구역!F4:F43,"개인차",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!F4:F43,"개인차",33구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(33구역!F4:F43,"대중교통",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!H4:H43,"*대중교통*",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!F4:F43,"대중교통",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!H4:H43,"*대중교통*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K14" s="61">
-        <f>IF(COUNTIFS(33구역!G4:G43,"개인차",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!G4:G43,"개인차",33구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L14" s="61">
-        <f>IF(COUNTIFS(33구역!F4:F43,"대중교통",33구역!E4:E43,$B23)+COUNTIFS(33구역!H4:H43,"대중교통",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!F4:F43,"대중교통",33구역!E4:E43,$B23)+COUNTIFS(33구역!H4:H43,"대중교통",33구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M14" s="61">
-        <f>IF(COUNTIFS(33구역!G4:G43,"대중교통",33구역!E4:E43,$B23)+COUNTIFS(33구역!I4:I43,"대중교통",33구역!E4:E43,$B23)=0,"",COUNTIFS(33구역!G4:G43,"대중교통",33구역!E4:E43,$B23)+COUNTIFS(33구역!I4:I43,"대중교통",33구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(33구역!G4:G43,"대중교통",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!I4:I43,"*대중교통*",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!G4:G43,"대중교통",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!I4:I43,"*대중교통*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L14" s="61" t="n"/>
+      <c r="M14" s="61" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="32" t="inlineStr">
@@ -8301,53 +8223,47 @@
         </is>
       </c>
       <c r="B15" s="32">
-        <f>IF(COUNTIFS(34구역!F4:F43,"1호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"2호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"3호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"4호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"5호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"6호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"7호차",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!F4:F43,"1호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"2호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"3호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"4호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"5호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"6호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"7호차",34구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(34구역!F4:F43,"1호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"2호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"3호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"4호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"5호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"6호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"7호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!F4:F43,"1호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"2호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"3호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"4호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"5호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"6호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"7호차",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="C15" s="32">
-        <f>IF(COUNTIFS(34구역!G4:G43,"1호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"2호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"3호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"4호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"5호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"6호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"7호차",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!G4:G43,"1호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"2호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"3호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"4호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"5호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"6호차",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"7호차",34구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(34구역!G4:G43,"1호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"2호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"3호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"4호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"5호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"6호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"7호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!G4:G43,"1호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"2호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"3호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"4호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"5호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"6호차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"7호차",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="D15" s="32">
-        <f>IF(COUNTIFS(34구역!H4:H43,"&lt;&gt;",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!H4:H43,"&lt;&gt;",34구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(34구역!F4:F43,"교회차1",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"교회차2",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!H4:H43,"*교회차*",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!F4:F43,"교회차1",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!F4:F43,"교회차2",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!H4:H43,"*교회차*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="E15" s="32">
-        <f>IF(COUNTIFS(34구역!I4:I43,"&lt;&gt;",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!I4:I43,"&lt;&gt;",34구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(34구역!G4:G43,"교회차1",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"교회차2",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!I4:I43,"*교회차*",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!G4:G43,"교회차1",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!G4:G43,"교회차2",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!I4:I43,"*교회차*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="F15" s="32">
-        <f>IF(COUNTIFS(34구역!F4:F43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"교회차2",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"교회차2",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!F4:F43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!F4:F43,"교회차2",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"교회차2",34구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(34구역!F4:F43,"타교회",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!H4:H43,"*타교회*",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!F4:F43,"타교회",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!H4:H43,"*타교회*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="G15" s="32">
-        <f>IF(COUNTIFS(34구역!G4:G43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"교회차2",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"교회차2",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!G4:G43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"교회차1",34구역!E4:E43,$B23)+COUNTIFS(34구역!G4:G43,"교회차2",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"교회차2",34구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(34구역!G4:G43,"타교회",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!I4:I43,"*타교회*",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!G4:G43,"타교회",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!I4:I43,"*타교회*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="H15" s="32">
-        <f>IF(COUNTIFS(34구역!F4:F43,"타교회",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"타교회",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!F4:F43,"타교회",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"타교회",34구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(34구역!F4:F43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!H4:H43,"*개인차*",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!F4:F43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!H4:H43,"*개인차*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="I15" s="32">
-        <f>IF(COUNTIFS(34구역!G4:G43,"타교회",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"타교회",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!G4:G43,"타교회",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"타교회",34구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(34구역!G4:G43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!I4:I43,"*개인차*",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!G4:G43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!I4:I43,"*개인차*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="J15" s="32">
-        <f>IF(COUNTIFS(34구역!F4:F43,"개인차",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!F4:F43,"개인차",34구역!E4:E43,$B23))</f>
+        <f>IF(COUNTIFS(34구역!F4:F43,"대중교통",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!H4:H43,"*대중교통*",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!F4:F43,"대중교통",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!H4:H43,"*대중교통*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
         <v/>
       </c>
       <c r="K15" s="32">
-        <f>IF(COUNTIFS(34구역!G4:G43,"개인차",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!G4:G43,"개인차",34구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="L15" s="32">
-        <f>IF(COUNTIFS(34구역!F4:F43,"대중교통",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"대중교통",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!F4:F43,"대중교통",34구역!E4:E43,$B23)+COUNTIFS(34구역!H4:H43,"대중교통",34구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
-      <c r="M15" s="32">
-        <f>IF(COUNTIFS(34구역!G4:G43,"대중교통",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"대중교통",34구역!E4:E43,$B23)=0,"",COUNTIFS(34구역!G4:G43,"대중교통",34구역!E4:E43,$B23)+COUNTIFS(34구역!I4:I43,"대중교통",34구역!E4:E43,$B23))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTIFS(34구역!G4:G43,"대중교통",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!I4:I43,"*대중교통*",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!G4:G43,"대중교통",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!I4:I43,"*대중교통*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <v/>
+      </c>
+      <c r="L15" s="32" t="n"/>
+      <c r="M15" s="32" t="n"/>
     </row>
     <row r="16" ht="19.4" customHeight="1" s="33">
       <c r="A16" s="62" t="inlineStr">
@@ -8395,14 +8311,8 @@
         <f>IF(SUM(K4:K15)=0,"",SUM(K4:K15))</f>
         <v/>
       </c>
-      <c r="L16" s="32">
-        <f>IF(SUM(L4:L15)=0,"",SUM(L4:L15))</f>
-        <v/>
-      </c>
-      <c r="M16" s="32">
-        <f>IF(SUM(M4:M15)=0,"",SUM(M4:M15))</f>
-        <v/>
-      </c>
+      <c r="L16" s="32" t="n"/>
+      <c r="M16" s="32" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="33">
       <c r="A17" s="49" t="n"/>
@@ -8431,9 +8341,7 @@
       <c r="H18" s="35" t="n"/>
       <c r="I18" s="35" t="n"/>
       <c r="J18" s="35" t="n"/>
-      <c r="K18" s="35" t="n"/>
-      <c r="L18" s="35" t="n"/>
-      <c r="M18" s="67" t="n"/>
+      <c r="K18" s="67" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
@@ -8494,35 +8402,35 @@
         </is>
       </c>
       <c r="B20" s="32">
-        <f>IF(COUNTIF(11구역!E4:E43,"1차")+COUNTIF(12구역!E4:E43,"1차")+COUNTIF(13구역!E4:E43,"1차")+COUNTIF(14구역!E4:E43,"1차")+COUNTIF(21구역!E4:E43,"1차")+COUNTIF(22구역!E4:E43,"1차")+COUNTIF(23구역!E4:E43,"1차")+COUNTIF(24구역!E4:E43,"1차")+COUNTIF(31구역!E4:E43,"1차")+COUNTIF(32구역!E4:E43,"1차")+COUNTIF(33구역!E4:E43,"1차")+COUNTIF(34구역!E4:E43,"1차")=0,"",COUNTIF(11구역!E4:E43,"1차")+COUNTIF(12구역!E4:E43,"1차")+COUNTIF(13구역!E4:E43,"1차")+COUNTIF(14구역!E4:E43,"1차")+COUNTIF(21구역!E4:E43,"1차")+COUNTIF(22구역!E4:E43,"1차")+COUNTIF(23구역!E4:E43,"1차")+COUNTIF(24구역!E4:E43,"1차")+COUNTIF(31구역!E4:E43,"1차")+COUNTIF(32구역!E4:E43,"1차")+COUNTIF(33구역!E4:E43,"1차")+COUNTIF(34구역!E4:E43,"1차"))</f>
+        <f>IF(COUNTIF(11구역!E4:E43,"*1차*")+COUNTIF(12구역!E4:E43,"*1차*")+COUNTIF(13구역!E4:E43,"*1차*")+COUNTIF(14구역!E4:E43,"*1차*")+COUNTIF(21구역!E4:E43,"*1차*")+COUNTIF(22구역!E4:E43,"*1차*")+COUNTIF(23구역!E4:E43,"*1차*")+COUNTIF(24구역!E4:E43,"*1차*")+COUNTIF(31구역!E4:E43,"*1차*")+COUNTIF(32구역!E4:E43,"*1차*")+COUNTIF(33구역!E4:E43,"*1차*")+COUNTIF(34구역!E4:E43,"*1차*")=0,"",COUNTIF(11구역!E4:E43,"*1차*")+COUNTIF(12구역!E4:E43,"*1차*")+COUNTIF(13구역!E4:E43,"*1차*")+COUNTIF(14구역!E4:E43,"*1차*")+COUNTIF(21구역!E4:E43,"*1차*")+COUNTIF(22구역!E4:E43,"*1차*")+COUNTIF(23구역!E4:E43,"*1차*")+COUNTIF(24구역!E4:E43,"*1차*")+COUNTIF(31구역!E4:E43,"*1차*")+COUNTIF(32구역!E4:E43,"*1차*")+COUNTIF(33구역!E4:E43,"*1차*")+COUNTIF(34구역!E4:E43,"*1차*"))</f>
         <v/>
       </c>
       <c r="C20" s="32">
-        <f>IF(COUNTIF(11구역!E4:E43,"2차")+COUNTIF(12구역!E4:E43,"2차")+COUNTIF(13구역!E4:E43,"2차")+COUNTIF(14구역!E4:E43,"2차")+COUNTIF(21구역!E4:E43,"2차")+COUNTIF(22구역!E4:E43,"2차")+COUNTIF(23구역!E4:E43,"2차")+COUNTIF(24구역!E4:E43,"2차")+COUNTIF(31구역!E4:E43,"2차")+COUNTIF(32구역!E4:E43,"2차")+COUNTIF(33구역!E4:E43,"2차")+COUNTIF(34구역!E4:E43,"2차")=0,"",COUNTIF(11구역!E4:E43,"2차")+COUNTIF(12구역!E4:E43,"2차")+COUNTIF(13구역!E4:E43,"2차")+COUNTIF(14구역!E4:E43,"2차")+COUNTIF(21구역!E4:E43,"2차")+COUNTIF(22구역!E4:E43,"2차")+COUNTIF(23구역!E4:E43,"2차")+COUNTIF(24구역!E4:E43,"2차")+COUNTIF(31구역!E4:E43,"2차")+COUNTIF(32구역!E4:E43,"2차")+COUNTIF(33구역!E4:E43,"2차")+COUNTIF(34구역!E4:E43,"2차"))</f>
+        <f>IF(COUNTIF(11구역!E4:E43,"*2차*")+COUNTIF(12구역!E4:E43,"*2차*")+COUNTIF(13구역!E4:E43,"*2차*")+COUNTIF(14구역!E4:E43,"*2차*")+COUNTIF(21구역!E4:E43,"*2차*")+COUNTIF(22구역!E4:E43,"*2차*")+COUNTIF(23구역!E4:E43,"*2차*")+COUNTIF(24구역!E4:E43,"*2차*")+COUNTIF(31구역!E4:E43,"*2차*")+COUNTIF(32구역!E4:E43,"*2차*")+COUNTIF(33구역!E4:E43,"*2차*")+COUNTIF(34구역!E4:E43,"*2차*")=0,"",COUNTIF(11구역!E4:E43,"*2차*")+COUNTIF(12구역!E4:E43,"*2차*")+COUNTIF(13구역!E4:E43,"*2차*")+COUNTIF(14구역!E4:E43,"*2차*")+COUNTIF(21구역!E4:E43,"*2차*")+COUNTIF(22구역!E4:E43,"*2차*")+COUNTIF(23구역!E4:E43,"*2차*")+COUNTIF(24구역!E4:E43,"*2차*")+COUNTIF(31구역!E4:E43,"*2차*")+COUNTIF(32구역!E4:E43,"*2차*")+COUNTIF(33구역!E4:E43,"*2차*")+COUNTIF(34구역!E4:E43,"*2차*"))</f>
         <v/>
       </c>
       <c r="D20" s="32">
-        <f>IF(COUNTIF(11구역!E4:E43,"3차")+COUNTIF(12구역!E4:E43,"3차")+COUNTIF(13구역!E4:E43,"3차")+COUNTIF(14구역!E4:E43,"3차")+COUNTIF(21구역!E4:E43,"3차")+COUNTIF(22구역!E4:E43,"3차")+COUNTIF(23구역!E4:E43,"3차")+COUNTIF(24구역!E4:E43,"3차")+COUNTIF(31구역!E4:E43,"3차")+COUNTIF(32구역!E4:E43,"3차")+COUNTIF(33구역!E4:E43,"3차")+COUNTIF(34구역!E4:E43,"3차")=0,"",COUNTIF(11구역!E4:E43,"3차")+COUNTIF(12구역!E4:E43,"3차")+COUNTIF(13구역!E4:E43,"3차")+COUNTIF(14구역!E4:E43,"3차")+COUNTIF(21구역!E4:E43,"3차")+COUNTIF(22구역!E4:E43,"3차")+COUNTIF(23구역!E4:E43,"3차")+COUNTIF(24구역!E4:E43,"3차")+COUNTIF(31구역!E4:E43,"3차")+COUNTIF(32구역!E4:E43,"3차")+COUNTIF(33구역!E4:E43,"3차")+COUNTIF(34구역!E4:E43,"3차"))</f>
+        <f>IF(COUNTIF(11구역!E4:E43,"*3차*")+COUNTIF(12구역!E4:E43,"*3차*")+COUNTIF(13구역!E4:E43,"*3차*")+COUNTIF(14구역!E4:E43,"*3차*")+COUNTIF(21구역!E4:E43,"*3차*")+COUNTIF(22구역!E4:E43,"*3차*")+COUNTIF(23구역!E4:E43,"*3차*")+COUNTIF(24구역!E4:E43,"*3차*")+COUNTIF(31구역!E4:E43,"*3차*")+COUNTIF(32구역!E4:E43,"*3차*")+COUNTIF(33구역!E4:E43,"*3차*")+COUNTIF(34구역!E4:E43,"*3차*")=0,"",COUNTIF(11구역!E4:E43,"*3차*")+COUNTIF(12구역!E4:E43,"*3차*")+COUNTIF(13구역!E4:E43,"*3차*")+COUNTIF(14구역!E4:E43,"*3차*")+COUNTIF(21구역!E4:E43,"*3차*")+COUNTIF(22구역!E4:E43,"*3차*")+COUNTIF(23구역!E4:E43,"*3차*")+COUNTIF(24구역!E4:E43,"*3차*")+COUNTIF(31구역!E4:E43,"*3차*")+COUNTIF(32구역!E4:E43,"*3차*")+COUNTIF(33구역!E4:E43,"*3차*")+COUNTIF(34구역!E4:E43,"*3차*"))</f>
         <v/>
       </c>
       <c r="E20" s="32">
-        <f>IF(COUNTIF(11구역!E4:E43,"4차")+COUNTIF(12구역!E4:E43,"4차")+COUNTIF(13구역!E4:E43,"4차")+COUNTIF(14구역!E4:E43,"4차")+COUNTIF(21구역!E4:E43,"4차")+COUNTIF(22구역!E4:E43,"4차")+COUNTIF(23구역!E4:E43,"4차")+COUNTIF(24구역!E4:E43,"4차")+COUNTIF(31구역!E4:E43,"4차")+COUNTIF(32구역!E4:E43,"4차")+COUNTIF(33구역!E4:E43,"4차")+COUNTIF(34구역!E4:E43,"4차")=0,"",COUNTIF(11구역!E4:E43,"4차")+COUNTIF(12구역!E4:E43,"4차")+COUNTIF(13구역!E4:E43,"4차")+COUNTIF(14구역!E4:E43,"4차")+COUNTIF(21구역!E4:E43,"4차")+COUNTIF(22구역!E4:E43,"4차")+COUNTIF(23구역!E4:E43,"4차")+COUNTIF(24구역!E4:E43,"4차")+COUNTIF(31구역!E4:E43,"4차")+COUNTIF(32구역!E4:E43,"4차")+COUNTIF(33구역!E4:E43,"4차")+COUNTIF(34구역!E4:E43,"4차"))</f>
+        <f>IF(COUNTIF(11구역!E4:E43,"*4차*")+COUNTIF(12구역!E4:E43,"*4차*")+COUNTIF(13구역!E4:E43,"*4차*")+COUNTIF(14구역!E4:E43,"*4차*")+COUNTIF(21구역!E4:E43,"*4차*")+COUNTIF(22구역!E4:E43,"*4차*")+COUNTIF(23구역!E4:E43,"*4차*")+COUNTIF(24구역!E4:E43,"*4차*")+COUNTIF(31구역!E4:E43,"*4차*")+COUNTIF(32구역!E4:E43,"*4차*")+COUNTIF(33구역!E4:E43,"*4차*")+COUNTIF(34구역!E4:E43,"*4차*")=0,"",COUNTIF(11구역!E4:E43,"*4차*")+COUNTIF(12구역!E4:E43,"*4차*")+COUNTIF(13구역!E4:E43,"*4차*")+COUNTIF(14구역!E4:E43,"*4차*")+COUNTIF(21구역!E4:E43,"*4차*")+COUNTIF(22구역!E4:E43,"*4차*")+COUNTIF(23구역!E4:E43,"*4차*")+COUNTIF(24구역!E4:E43,"*4차*")+COUNTIF(31구역!E4:E43,"*4차*")+COUNTIF(32구역!E4:E43,"*4차*")+COUNTIF(33구역!E4:E43,"*4차*")+COUNTIF(34구역!E4:E43,"*4차*"))</f>
         <v/>
       </c>
       <c r="F20" s="32">
-        <f>IF(COUNTIF(11구역!E4:E43,"5차")+COUNTIF(12구역!E4:E43,"5차")+COUNTIF(13구역!E4:E43,"5차")+COUNTIF(14구역!E4:E43,"5차")+COUNTIF(21구역!E4:E43,"5차")+COUNTIF(22구역!E4:E43,"5차")+COUNTIF(23구역!E4:E43,"5차")+COUNTIF(24구역!E4:E43,"5차")+COUNTIF(31구역!E4:E43,"5차")+COUNTIF(32구역!E4:E43,"5차")+COUNTIF(33구역!E4:E43,"5차")+COUNTIF(34구역!E4:E43,"5차")=0,"",COUNTIF(11구역!E4:E43,"5차")+COUNTIF(12구역!E4:E43,"5차")+COUNTIF(13구역!E4:E43,"5차")+COUNTIF(14구역!E4:E43,"5차")+COUNTIF(21구역!E4:E43,"5차")+COUNTIF(22구역!E4:E43,"5차")+COUNTIF(23구역!E4:E43,"5차")+COUNTIF(24구역!E4:E43,"5차")+COUNTIF(31구역!E4:E43,"5차")+COUNTIF(32구역!E4:E43,"5차")+COUNTIF(33구역!E4:E43,"5차")+COUNTIF(34구역!E4:E43,"5차"))</f>
+        <f>IF(COUNTIF(11구역!E4:E43,"*5차*")+COUNTIF(12구역!E4:E43,"*5차*")+COUNTIF(13구역!E4:E43,"*5차*")+COUNTIF(14구역!E4:E43,"*5차*")+COUNTIF(21구역!E4:E43,"*5차*")+COUNTIF(22구역!E4:E43,"*5차*")+COUNTIF(23구역!E4:E43,"*5차*")+COUNTIF(24구역!E4:E43,"*5차*")+COUNTIF(31구역!E4:E43,"*5차*")+COUNTIF(32구역!E4:E43,"*5차*")+COUNTIF(33구역!E4:E43,"*5차*")+COUNTIF(34구역!E4:E43,"*5차*")=0,"",COUNTIF(11구역!E4:E43,"*5차*")+COUNTIF(12구역!E4:E43,"*5차*")+COUNTIF(13구역!E4:E43,"*5차*")+COUNTIF(14구역!E4:E43,"*5차*")+COUNTIF(21구역!E4:E43,"*5차*")+COUNTIF(22구역!E4:E43,"*5차*")+COUNTIF(23구역!E4:E43,"*5차*")+COUNTIF(24구역!E4:E43,"*5차*")+COUNTIF(31구역!E4:E43,"*5차*")+COUNTIF(32구역!E4:E43,"*5차*")+COUNTIF(33구역!E4:E43,"*5차*")+COUNTIF(34구역!E4:E43,"*5차*"))</f>
         <v/>
       </c>
       <c r="G20" s="32">
-        <f>IF(COUNTIF(11구역!E4:E43,"6차")+COUNTIF(12구역!E4:E43,"6차")+COUNTIF(13구역!E4:E43,"6차")+COUNTIF(14구역!E4:E43,"6차")+COUNTIF(21구역!E4:E43,"6차")+COUNTIF(22구역!E4:E43,"6차")+COUNTIF(23구역!E4:E43,"6차")+COUNTIF(24구역!E4:E43,"6차")+COUNTIF(31구역!E4:E43,"6차")+COUNTIF(32구역!E4:E43,"6차")+COUNTIF(33구역!E4:E43,"6차")+COUNTIF(34구역!E4:E43,"6차")=0,"",COUNTIF(11구역!E4:E43,"6차")+COUNTIF(12구역!E4:E43,"6차")+COUNTIF(13구역!E4:E43,"6차")+COUNTIF(14구역!E4:E43,"6차")+COUNTIF(21구역!E4:E43,"6차")+COUNTIF(22구역!E4:E43,"6차")+COUNTIF(23구역!E4:E43,"6차")+COUNTIF(24구역!E4:E43,"6차")+COUNTIF(31구역!E4:E43,"6차")+COUNTIF(32구역!E4:E43,"6차")+COUNTIF(33구역!E4:E43,"6차")+COUNTIF(34구역!E4:E43,"6차"))</f>
+        <f>IF(COUNTIF(11구역!E4:E43,"*6차*")+COUNTIF(12구역!E4:E43,"*6차*")+COUNTIF(13구역!E4:E43,"*6차*")+COUNTIF(14구역!E4:E43,"*6차*")+COUNTIF(21구역!E4:E43,"*6차*")+COUNTIF(22구역!E4:E43,"*6차*")+COUNTIF(23구역!E4:E43,"*6차*")+COUNTIF(24구역!E4:E43,"*6차*")+COUNTIF(31구역!E4:E43,"*6차*")+COUNTIF(32구역!E4:E43,"*6차*")+COUNTIF(33구역!E4:E43,"*6차*")+COUNTIF(34구역!E4:E43,"*6차*")=0,"",COUNTIF(11구역!E4:E43,"*6차*")+COUNTIF(12구역!E4:E43,"*6차*")+COUNTIF(13구역!E4:E43,"*6차*")+COUNTIF(14구역!E4:E43,"*6차*")+COUNTIF(21구역!E4:E43,"*6차*")+COUNTIF(22구역!E4:E43,"*6차*")+COUNTIF(23구역!E4:E43,"*6차*")+COUNTIF(24구역!E4:E43,"*6차*")+COUNTIF(31구역!E4:E43,"*6차*")+COUNTIF(32구역!E4:E43,"*6차*")+COUNTIF(33구역!E4:E43,"*6차*")+COUNTIF(34구역!E4:E43,"*6차*"))</f>
         <v/>
       </c>
       <c r="H20" s="32">
-        <f>IF(COUNTIF(11구역!E4:E43,"7차")+COUNTIF(12구역!E4:E43,"7차")+COUNTIF(13구역!E4:E43,"7차")+COUNTIF(14구역!E4:E43,"7차")+COUNTIF(21구역!E4:E43,"7차")+COUNTIF(22구역!E4:E43,"7차")+COUNTIF(23구역!E4:E43,"7차")+COUNTIF(24구역!E4:E43,"7차")+COUNTIF(31구역!E4:E43,"7차")+COUNTIF(32구역!E4:E43,"7차")+COUNTIF(33구역!E4:E43,"7차")+COUNTIF(34구역!E4:E43,"7차")=0,"",COUNTIF(11구역!E4:E43,"7차")+COUNTIF(12구역!E4:E43,"7차")+COUNTIF(13구역!E4:E43,"7차")+COUNTIF(14구역!E4:E43,"7차")+COUNTIF(21구역!E4:E43,"7차")+COUNTIF(22구역!E4:E43,"7차")+COUNTIF(23구역!E4:E43,"7차")+COUNTIF(24구역!E4:E43,"7차")+COUNTIF(31구역!E4:E43,"7차")+COUNTIF(32구역!E4:E43,"7차")+COUNTIF(33구역!E4:E43,"7차")+COUNTIF(34구역!E4:E43,"7차"))</f>
+        <f>IF(COUNTIF(11구역!E4:E43,"*7차*")+COUNTIF(12구역!E4:E43,"*7차*")+COUNTIF(13구역!E4:E43,"*7차*")+COUNTIF(14구역!E4:E43,"*7차*")+COUNTIF(21구역!E4:E43,"*7차*")+COUNTIF(22구역!E4:E43,"*7차*")+COUNTIF(23구역!E4:E43,"*7차*")+COUNTIF(24구역!E4:E43,"*7차*")+COUNTIF(31구역!E4:E43,"*7차*")+COUNTIF(32구역!E4:E43,"*7차*")+COUNTIF(33구역!E4:E43,"*7차*")+COUNTIF(34구역!E4:E43,"*7차*")=0,"",COUNTIF(11구역!E4:E43,"*7차*")+COUNTIF(12구역!E4:E43,"*7차*")+COUNTIF(13구역!E4:E43,"*7차*")+COUNTIF(14구역!E4:E43,"*7차*")+COUNTIF(21구역!E4:E43,"*7차*")+COUNTIF(22구역!E4:E43,"*7차*")+COUNTIF(23구역!E4:E43,"*7차*")+COUNTIF(24구역!E4:E43,"*7차*")+COUNTIF(31구역!E4:E43,"*7차*")+COUNTIF(32구역!E4:E43,"*7차*")+COUNTIF(33구역!E4:E43,"*7차*")+COUNTIF(34구역!E4:E43,"*7차*"))</f>
         <v/>
       </c>
       <c r="I20" s="32">
-        <f>IF(COUNTIF(11구역!E4:E43,"8차")+COUNTIF(12구역!E4:E43,"8차")+COUNTIF(13구역!E4:E43,"8차")+COUNTIF(14구역!E4:E43,"8차")+COUNTIF(21구역!E4:E43,"8차")+COUNTIF(22구역!E4:E43,"8차")+COUNTIF(23구역!E4:E43,"8차")+COUNTIF(24구역!E4:E43,"8차")+COUNTIF(31구역!E4:E43,"8차")+COUNTIF(32구역!E4:E43,"8차")+COUNTIF(33구역!E4:E43,"8차")+COUNTIF(34구역!E4:E43,"8차")=0,"",COUNTIF(11구역!E4:E43,"8차")+COUNTIF(12구역!E4:E43,"8차")+COUNTIF(13구역!E4:E43,"8차")+COUNTIF(14구역!E4:E43,"8차")+COUNTIF(21구역!E4:E43,"8차")+COUNTIF(22구역!E4:E43,"8차")+COUNTIF(23구역!E4:E43,"8차")+COUNTIF(24구역!E4:E43,"8차")+COUNTIF(31구역!E4:E43,"8차")+COUNTIF(32구역!E4:E43,"8차")+COUNTIF(33구역!E4:E43,"8차")+COUNTIF(34구역!E4:E43,"8차"))</f>
+        <f>IF(COUNTIF(11구역!E4:E43,"*8차*")+COUNTIF(12구역!E4:E43,"*8차*")+COUNTIF(13구역!E4:E43,"*8차*")+COUNTIF(14구역!E4:E43,"*8차*")+COUNTIF(21구역!E4:E43,"*8차*")+COUNTIF(22구역!E4:E43,"*8차*")+COUNTIF(23구역!E4:E43,"*8차*")+COUNTIF(24구역!E4:E43,"*8차*")+COUNTIF(31구역!E4:E43,"*8차*")+COUNTIF(32구역!E4:E43,"*8차*")+COUNTIF(33구역!E4:E43,"*8차*")+COUNTIF(34구역!E4:E43,"*8차*")=0,"",COUNTIF(11구역!E4:E43,"*8차*")+COUNTIF(12구역!E4:E43,"*8차*")+COUNTIF(13구역!E4:E43,"*8차*")+COUNTIF(14구역!E4:E43,"*8차*")+COUNTIF(21구역!E4:E43,"*8차*")+COUNTIF(22구역!E4:E43,"*8차*")+COUNTIF(23구역!E4:E43,"*8차*")+COUNTIF(24구역!E4:E43,"*8차*")+COUNTIF(31구역!E4:E43,"*8차*")+COUNTIF(32구역!E4:E43,"*8차*")+COUNTIF(33구역!E4:E43,"*8차*")+COUNTIF(34구역!E4:E43,"*8차*"))</f>
         <v/>
       </c>
       <c r="J20" s="32">
@@ -8539,17 +8447,15 @@
       <c r="B23" s="32" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="L2:M2"/>
+  <mergeCells count="8">
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A1:M1"/>
     <mergeCell ref="J2:K2"/>
-    <mergeCell ref="A18:M18"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/수양회_서식_template.xlsx
+++ b/수양회_서식_template.xlsx
@@ -7708,11 +7708,11 @@
         <v/>
       </c>
       <c r="H4" s="42">
-        <f>IF(COUNTIFS(11구역!F4:F43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!H4:H43,"*개인차*",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!F4:F43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!H4:H43,"*개인차*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(11구역!F4:F43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(11구역!H4:H43,"?*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!H4:H43,"*교회차*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!H4:H43,"*타교회*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!H4:H43,"*대중교통*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(11구역!F4:F43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(11구역!H4:H43,"?*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!H4:H43,"*교회차*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!H4:H43,"*타교회*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!H4:H43,"*대중교통*",11구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I4" s="42">
-        <f>IF(COUNTIFS(11구역!G4:G43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!I4:I43,"*개인차*",11구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(11구역!G4:G43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(11구역!I4:I43,"*개인차*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(11구역!G4:G43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(11구역!I4:I43,"?*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!I4:I43,"*교회차*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!I4:I43,"*타교회*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!I4:I43,"*대중교통*",11구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(11구역!G4:G43,"개인차",11구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(11구역!I4:I43,"?*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!I4:I43,"*교회차*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!I4:I43,"*타교회*",11구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(11구역!I4:I43,"*대중교통*",11구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J4" s="42">
@@ -7757,11 +7757,11 @@
         <v/>
       </c>
       <c r="H5" s="44">
-        <f>IF(COUNTIFS(12구역!F4:F43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!H4:H43,"*개인차*",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!F4:F43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!H4:H43,"*개인차*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(12구역!F4:F43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(12구역!H4:H43,"?*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!H4:H43,"*교회차*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!H4:H43,"*타교회*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!H4:H43,"*대중교통*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(12구역!F4:F43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(12구역!H4:H43,"?*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!H4:H43,"*교회차*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!H4:H43,"*타교회*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!H4:H43,"*대중교통*",12구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I5" s="44">
-        <f>IF(COUNTIFS(12구역!G4:G43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!I4:I43,"*개인차*",12구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(12구역!G4:G43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(12구역!I4:I43,"*개인차*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(12구역!G4:G43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(12구역!I4:I43,"?*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!I4:I43,"*교회차*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!I4:I43,"*타교회*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!I4:I43,"*대중교통*",12구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(12구역!G4:G43,"개인차",12구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(12구역!I4:I43,"?*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!I4:I43,"*교회차*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!I4:I43,"*타교회*",12구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(12구역!I4:I43,"*대중교통*",12구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J5" s="44">
@@ -7806,11 +7806,11 @@
         <v/>
       </c>
       <c r="H6" s="42">
-        <f>IF(COUNTIFS(13구역!F4:F43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!H4:H43,"*개인차*",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!F4:F43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!H4:H43,"*개인차*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(13구역!F4:F43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(13구역!H4:H43,"?*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!H4:H43,"*교회차*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!H4:H43,"*타교회*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!H4:H43,"*대중교통*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(13구역!F4:F43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(13구역!H4:H43,"?*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!H4:H43,"*교회차*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!H4:H43,"*타교회*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!H4:H43,"*대중교통*",13구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I6" s="42">
-        <f>IF(COUNTIFS(13구역!G4:G43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!I4:I43,"*개인차*",13구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(13구역!G4:G43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(13구역!I4:I43,"*개인차*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(13구역!G4:G43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(13구역!I4:I43,"?*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!I4:I43,"*교회차*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!I4:I43,"*타교회*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!I4:I43,"*대중교통*",13구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(13구역!G4:G43,"개인차",13구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(13구역!I4:I43,"?*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!I4:I43,"*교회차*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!I4:I43,"*타교회*",13구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(13구역!I4:I43,"*대중교통*",13구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J6" s="42">
@@ -7855,11 +7855,11 @@
         <v/>
       </c>
       <c r="H7" s="44">
-        <f>IF(COUNTIFS(14구역!F4:F43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!H4:H43,"*개인차*",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!F4:F43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!H4:H43,"*개인차*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(14구역!F4:F43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(14구역!H4:H43,"?*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!H4:H43,"*교회차*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!H4:H43,"*타교회*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!H4:H43,"*대중교통*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(14구역!F4:F43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(14구역!H4:H43,"?*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!H4:H43,"*교회차*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!H4:H43,"*타교회*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!H4:H43,"*대중교통*",14구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I7" s="44">
-        <f>IF(COUNTIFS(14구역!G4:G43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!I4:I43,"*개인차*",14구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(14구역!G4:G43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(14구역!I4:I43,"*개인차*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(14구역!G4:G43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(14구역!I4:I43,"?*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!I4:I43,"*교회차*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!I4:I43,"*타교회*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!I4:I43,"*대중교통*",14구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(14구역!G4:G43,"개인차",14구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(14구역!I4:I43,"?*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!I4:I43,"*교회차*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!I4:I43,"*타교회*",14구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(14구역!I4:I43,"*대중교통*",14구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J7" s="44">
@@ -7904,11 +7904,11 @@
         <v/>
       </c>
       <c r="H8" s="42">
-        <f>IF(COUNTIFS(21구역!F4:F43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!H4:H43,"*개인차*",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!F4:F43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!H4:H43,"*개인차*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(21구역!F4:F43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(21구역!H4:H43,"?*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!H4:H43,"*교회차*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!H4:H43,"*타교회*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!H4:H43,"*대중교통*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(21구역!F4:F43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(21구역!H4:H43,"?*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!H4:H43,"*교회차*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!H4:H43,"*타교회*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!H4:H43,"*대중교통*",21구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I8" s="42">
-        <f>IF(COUNTIFS(21구역!G4:G43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!I4:I43,"*개인차*",21구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(21구역!G4:G43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(21구역!I4:I43,"*개인차*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(21구역!G4:G43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(21구역!I4:I43,"?*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!I4:I43,"*교회차*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!I4:I43,"*타교회*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!I4:I43,"*대중교통*",21구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(21구역!G4:G43,"개인차",21구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(21구역!I4:I43,"?*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!I4:I43,"*교회차*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!I4:I43,"*타교회*",21구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(21구역!I4:I43,"*대중교통*",21구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J8" s="42">
@@ -7953,11 +7953,11 @@
         <v/>
       </c>
       <c r="H9" s="44">
-        <f>IF(COUNTIFS(22구역!F4:F43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!H4:H43,"*개인차*",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!F4:F43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!H4:H43,"*개인차*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(22구역!F4:F43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(22구역!H4:H43,"?*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!H4:H43,"*교회차*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!H4:H43,"*타교회*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!H4:H43,"*대중교통*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(22구역!F4:F43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(22구역!H4:H43,"?*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!H4:H43,"*교회차*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!H4:H43,"*타교회*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!H4:H43,"*대중교통*",22구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I9" s="44">
-        <f>IF(COUNTIFS(22구역!G4:G43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!I4:I43,"*개인차*",22구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(22구역!G4:G43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(22구역!I4:I43,"*개인차*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(22구역!G4:G43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(22구역!I4:I43,"?*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!I4:I43,"*교회차*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!I4:I43,"*타교회*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!I4:I43,"*대중교통*",22구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(22구역!G4:G43,"개인차",22구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(22구역!I4:I43,"?*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!I4:I43,"*교회차*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!I4:I43,"*타교회*",22구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(22구역!I4:I43,"*대중교통*",22구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J9" s="44">
@@ -8002,11 +8002,11 @@
         <v/>
       </c>
       <c r="H10" s="42">
-        <f>IF(COUNTIFS(23구역!F4:F43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!H4:H43,"*개인차*",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!F4:F43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!H4:H43,"*개인차*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(23구역!F4:F43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(23구역!H4:H43,"?*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!H4:H43,"*교회차*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!H4:H43,"*타교회*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!H4:H43,"*대중교통*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(23구역!F4:F43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(23구역!H4:H43,"?*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!H4:H43,"*교회차*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!H4:H43,"*타교회*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!H4:H43,"*대중교통*",23구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I10" s="42">
-        <f>IF(COUNTIFS(23구역!G4:G43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!I4:I43,"*개인차*",23구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(23구역!G4:G43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(23구역!I4:I43,"*개인차*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(23구역!G4:G43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(23구역!I4:I43,"?*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!I4:I43,"*교회차*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!I4:I43,"*타교회*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!I4:I43,"*대중교통*",23구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(23구역!G4:G43,"개인차",23구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(23구역!I4:I43,"?*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!I4:I43,"*교회차*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!I4:I43,"*타교회*",23구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(23구역!I4:I43,"*대중교통*",23구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J10" s="42">
@@ -8051,11 +8051,11 @@
         <v/>
       </c>
       <c r="H11" s="44">
-        <f>IF(COUNTIFS(24구역!F4:F43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!H4:H43,"*개인차*",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!F4:F43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!H4:H43,"*개인차*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(24구역!F4:F43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(24구역!H4:H43,"?*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!H4:H43,"*교회차*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!H4:H43,"*타교회*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!H4:H43,"*대중교통*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(24구역!F4:F43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(24구역!H4:H43,"?*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!H4:H43,"*교회차*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!H4:H43,"*타교회*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!H4:H43,"*대중교통*",24구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I11" s="44">
-        <f>IF(COUNTIFS(24구역!G4:G43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!I4:I43,"*개인차*",24구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(24구역!G4:G43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(24구역!I4:I43,"*개인차*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(24구역!G4:G43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(24구역!I4:I43,"?*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!I4:I43,"*교회차*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!I4:I43,"*타교회*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!I4:I43,"*대중교통*",24구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(24구역!G4:G43,"개인차",24구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(24구역!I4:I43,"?*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!I4:I43,"*교회차*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!I4:I43,"*타교회*",24구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(24구역!I4:I43,"*대중교통*",24구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J11" s="44">
@@ -8100,11 +8100,11 @@
         <v/>
       </c>
       <c r="H12" s="42">
-        <f>IF(COUNTIFS(31구역!F4:F43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!H4:H43,"*개인차*",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!F4:F43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!H4:H43,"*개인차*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(31구역!F4:F43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(31구역!H4:H43,"?*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!H4:H43,"*교회차*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!H4:H43,"*타교회*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!H4:H43,"*대중교통*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(31구역!F4:F43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(31구역!H4:H43,"?*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!H4:H43,"*교회차*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!H4:H43,"*타교회*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!H4:H43,"*대중교통*",31구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I12" s="42">
-        <f>IF(COUNTIFS(31구역!G4:G43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!I4:I43,"*개인차*",31구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(31구역!G4:G43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(31구역!I4:I43,"*개인차*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(31구역!G4:G43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(31구역!I4:I43,"?*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!I4:I43,"*교회차*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!I4:I43,"*타교회*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!I4:I43,"*대중교통*",31구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(31구역!G4:G43,"개인차",31구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(31구역!I4:I43,"?*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!I4:I43,"*교회차*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!I4:I43,"*타교회*",31구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(31구역!I4:I43,"*대중교통*",31구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J12" s="42">
@@ -8149,11 +8149,11 @@
         <v/>
       </c>
       <c r="H13" s="44">
-        <f>IF(COUNTIFS(32구역!F4:F43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!H4:H43,"*개인차*",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!F4:F43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!H4:H43,"*개인차*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(32구역!F4:F43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(32구역!H4:H43,"?*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!H4:H43,"*교회차*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!H4:H43,"*타교회*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!H4:H43,"*대중교통*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(32구역!F4:F43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(32구역!H4:H43,"?*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!H4:H43,"*교회차*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!H4:H43,"*타교회*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!H4:H43,"*대중교통*",32구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I13" s="44">
-        <f>IF(COUNTIFS(32구역!G4:G43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!I4:I43,"*개인차*",32구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(32구역!G4:G43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(32구역!I4:I43,"*개인차*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(32구역!G4:G43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(32구역!I4:I43,"?*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!I4:I43,"*교회차*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!I4:I43,"*타교회*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!I4:I43,"*대중교통*",32구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(32구역!G4:G43,"개인차",32구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(32구역!I4:I43,"?*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!I4:I43,"*교회차*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!I4:I43,"*타교회*",32구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(32구역!I4:I43,"*대중교통*",32구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J13" s="44">
@@ -8198,11 +8198,11 @@
         <v/>
       </c>
       <c r="H14" s="61">
-        <f>IF(COUNTIFS(33구역!F4:F43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!H4:H43,"*개인차*",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!F4:F43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!H4:H43,"*개인차*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(33구역!F4:F43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(33구역!H4:H43,"?*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!H4:H43,"*교회차*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!H4:H43,"*타교회*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!H4:H43,"*대중교통*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(33구역!F4:F43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(33구역!H4:H43,"?*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!H4:H43,"*교회차*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!H4:H43,"*타교회*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!H4:H43,"*대중교통*",33구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I14" s="61">
-        <f>IF(COUNTIFS(33구역!G4:G43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!I4:I43,"*개인차*",33구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(33구역!G4:G43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(33구역!I4:I43,"*개인차*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(33구역!G4:G43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(33구역!I4:I43,"?*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!I4:I43,"*교회차*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!I4:I43,"*타교회*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!I4:I43,"*대중교통*",33구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(33구역!G4:G43,"개인차",33구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(33구역!I4:I43,"?*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!I4:I43,"*교회차*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!I4:I43,"*타교회*",33구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(33구역!I4:I43,"*대중교통*",33구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J14" s="61">
@@ -8247,11 +8247,11 @@
         <v/>
       </c>
       <c r="H15" s="32">
-        <f>IF(COUNTIFS(34구역!F4:F43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!H4:H43,"*개인차*",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!F4:F43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!H4:H43,"*개인차*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(34구역!F4:F43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(34구역!H4:H43,"?*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!H4:H43,"*교회차*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!H4:H43,"*타교회*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!H4:H43,"*대중교통*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(34구역!F4:F43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(34구역!H4:H43,"?*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!H4:H43,"*교회차*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!H4:H43,"*타교회*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!H4:H43,"*대중교통*",34구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="I15" s="32">
-        <f>IF(COUNTIFS(34구역!G4:G43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!I4:I43,"*개인차*",34구역!E4:E43,"*"&amp;$B23&amp;"*")=0,"",COUNTIFS(34구역!G4:G43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+COUNTIFS(34구역!I4:I43,"*개인차*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))</f>
+        <f>IF(COUNTIFS(34구역!G4:G43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(34구역!I4:I43,"?*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!I4:I43,"*교회차*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!I4:I43,"*타교회*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!I4:I43,"*대중교통*",34구역!E4:E43,"*"&amp;$B23&amp;"*"))=0,"",COUNTIFS(34구역!G4:G43,"개인차",34구역!E4:E43,"*"&amp;$B23&amp;"*")+(COUNTIFS(34구역!I4:I43,"?*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!I4:I43,"*교회차*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!I4:I43,"*타교회*",34구역!E4:E43,"*"&amp;$B23&amp;"*")-COUNTIFS(34구역!I4:I43,"*대중교통*",34구역!E4:E43,"*"&amp;$B23&amp;"*")))</f>
         <v/>
       </c>
       <c r="J15" s="32">
@@ -16347,7 +16347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>

--- a/수양회_서식_template.xlsx
+++ b/수양회_서식_template.xlsx
@@ -941,24 +941,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -1788,24 +1786,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2635,24 +2631,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -3482,24 +3476,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -4329,24 +4321,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -5176,24 +5166,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -6023,24 +6011,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -6870,24 +6856,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -7717,24 +7701,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -8564,24 +8546,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -9411,24 +9391,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -10258,24 +10236,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -11105,24 +11081,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -20216,24 +20190,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -28822,8 +28794,8 @@
     <mergeCell ref="G176:K176"/>
     <mergeCell ref="A88:E88"/>
     <mergeCell ref="G132:K132"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A90:E90"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A133:K133"/>
@@ -35779,24 +35751,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -36626,24 +36596,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -37473,24 +37441,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -38320,24 +38286,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -39167,24 +39131,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -40014,24 +39976,22 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>기타
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
-          <t>기타
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="J3" s="40" t="inlineStr">
         <is>
-          <t>개인차 상행</t>
+          <t>합류</t>
         </is>
       </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>개인차 하행</t>
+          <t>귀가</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">

--- a/수양회_서식_template.xlsx
+++ b/수양회_서식_template.xlsx
@@ -901,14 +901,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -929,14 +930,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -946,17 +945,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -1656,15 +1655,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -1746,14 +1746,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -1774,14 +1775,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -1791,17 +1790,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2501,15 +2500,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -2591,14 +2591,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -2619,14 +2620,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -2636,17 +2635,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -3346,15 +3345,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -3436,14 +3436,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -3464,14 +3465,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -3481,17 +3480,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -4191,15 +4190,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -4281,14 +4281,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -4309,14 +4310,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -4326,17 +4325,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -5036,15 +5035,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -5126,14 +5126,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -5154,14 +5155,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -5171,17 +5170,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -5881,15 +5880,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -5971,14 +5971,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -5999,14 +6000,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -6016,17 +6015,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -6726,15 +6725,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -6816,14 +6816,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -6844,14 +6845,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -6861,17 +6860,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -7571,15 +7570,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -7661,14 +7661,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -7689,14 +7690,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -7706,17 +7705,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -8416,15 +8415,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -8506,14 +8506,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -8534,14 +8535,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -8551,17 +8550,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -9261,15 +9260,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -9351,14 +9351,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -9379,14 +9380,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -9396,17 +9395,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -10106,15 +10105,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -10196,14 +10196,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -10224,14 +10225,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -10241,17 +10240,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -10951,15 +10950,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -11041,14 +11041,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -11069,14 +11070,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -11086,17 +11085,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -11796,15 +11795,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -14262,7 +14262,7 @@
         <v/>
       </c>
       <c r="E4" s="42">
-        <f>IF(COUNTIFS(구역1!G4:G43,"교회차1",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차2",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차3",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차4",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차5",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!I4:I43,"*교회차*",구역1!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역1!G4:G43,"교회차1",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차2",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차3",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차4",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차5",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!I4:I43,"*교회차*",구역1!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역1!G4:G43,"교회차1",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차2",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차3",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차4",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차5",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!J4:J43,"*교회차*",구역1!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역1!G4:G43,"교회차1",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차2",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차3",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차4",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!G4:G43,"교회차5",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!J4:J43,"*교회차*",구역1!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F4" s="42">
@@ -14270,7 +14270,7 @@
         <v/>
       </c>
       <c r="G4" s="42">
-        <f>IF(COUNTIFS(구역1!G4:G43,"타교회",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!I4:I43,"*타교회*",구역1!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역1!G4:G43,"타교회",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!I4:I43,"*타교회*",구역1!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역1!G4:G43,"타교회",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!J4:J43,"*타교회*",구역1!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역1!G4:G43,"타교회",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!J4:J43,"*타교회*",구역1!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H4" s="42">
@@ -14278,7 +14278,7 @@
         <v/>
       </c>
       <c r="I4" s="42">
-        <f>IF(COUNTIFS(구역1!G4:G43,"개인차",구역1!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역1!I4:I43,"?*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!I4:I43,"*교회차*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!I4:I43,"*타교회*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!I4:I43,"*대중교통*",구역1!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역1!G4:G43,"개인차",구역1!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역1!I4:I43,"?*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!I4:I43,"*교회차*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!I4:I43,"*타교회*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!I4:I43,"*대중교통*",구역1!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역1!G4:G43,"개인차",구역1!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역1!J4:J43,"?*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!J4:J43,"*교회차*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!J4:J43,"*타교회*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!J4:J43,"*대중교통*",구역1!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역1!G4:G43,"개인차",구역1!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역1!J4:J43,"?*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!J4:J43,"*교회차*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!J4:J43,"*타교회*",구역1!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역1!J4:J43,"*대중교통*",구역1!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J4" s="42">
@@ -14286,7 +14286,7 @@
         <v/>
       </c>
       <c r="K4" s="42">
-        <f>IF(COUNTIFS(구역1!G4:G43,"대중교통",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!I4:I43,"*대중교통*",구역1!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역1!G4:G43,"대중교통",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!I4:I43,"*대중교통*",구역1!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역1!G4:G43,"대중교통",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!J4:J43,"*대중교통*",구역1!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역1!G4:G43,"대중교통",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!J4:J43,"*대중교통*",구역1!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L4" s="42" t="n"/>
@@ -14311,7 +14311,7 @@
         <v/>
       </c>
       <c r="E5" s="44">
-        <f>IF(COUNTIFS(구역2!G4:G43,"교회차1",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차2",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차3",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차4",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차5",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!I4:I43,"*교회차*",구역2!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역2!G4:G43,"교회차1",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차2",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차3",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차4",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차5",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!I4:I43,"*교회차*",구역2!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역2!G4:G43,"교회차1",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차2",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차3",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차4",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차5",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!J4:J43,"*교회차*",구역2!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역2!G4:G43,"교회차1",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차2",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차3",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차4",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!G4:G43,"교회차5",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!J4:J43,"*교회차*",구역2!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F5" s="44">
@@ -14319,7 +14319,7 @@
         <v/>
       </c>
       <c r="G5" s="44">
-        <f>IF(COUNTIFS(구역2!G4:G43,"타교회",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!I4:I43,"*타교회*",구역2!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역2!G4:G43,"타교회",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!I4:I43,"*타교회*",구역2!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역2!G4:G43,"타교회",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!J4:J43,"*타교회*",구역2!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역2!G4:G43,"타교회",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!J4:J43,"*타교회*",구역2!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H5" s="44">
@@ -14327,7 +14327,7 @@
         <v/>
       </c>
       <c r="I5" s="44">
-        <f>IF(COUNTIFS(구역2!G4:G43,"개인차",구역2!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역2!I4:I43,"?*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!I4:I43,"*교회차*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!I4:I43,"*타교회*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!I4:I43,"*대중교통*",구역2!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역2!G4:G43,"개인차",구역2!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역2!I4:I43,"?*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!I4:I43,"*교회차*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!I4:I43,"*타교회*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!I4:I43,"*대중교통*",구역2!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역2!G4:G43,"개인차",구역2!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역2!J4:J43,"?*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!J4:J43,"*교회차*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!J4:J43,"*타교회*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!J4:J43,"*대중교통*",구역2!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역2!G4:G43,"개인차",구역2!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역2!J4:J43,"?*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!J4:J43,"*교회차*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!J4:J43,"*타교회*",구역2!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역2!J4:J43,"*대중교통*",구역2!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J5" s="44">
@@ -14335,7 +14335,7 @@
         <v/>
       </c>
       <c r="K5" s="44">
-        <f>IF(COUNTIFS(구역2!G4:G43,"대중교통",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!I4:I43,"*대중교통*",구역2!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역2!G4:G43,"대중교통",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!I4:I43,"*대중교통*",구역2!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역2!G4:G43,"대중교통",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!J4:J43,"*대중교통*",구역2!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역2!G4:G43,"대중교통",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!J4:J43,"*대중교통*",구역2!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L5" s="44" t="n"/>
@@ -14360,7 +14360,7 @@
         <v/>
       </c>
       <c r="E6" s="42">
-        <f>IF(COUNTIFS(구역3!G4:G43,"교회차1",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차2",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차3",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차4",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차5",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!I4:I43,"*교회차*",구역3!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역3!G4:G43,"교회차1",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차2",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차3",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차4",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차5",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!I4:I43,"*교회차*",구역3!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역3!G4:G43,"교회차1",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차2",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차3",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차4",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차5",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!J4:J43,"*교회차*",구역3!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역3!G4:G43,"교회차1",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차2",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차3",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차4",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!G4:G43,"교회차5",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!J4:J43,"*교회차*",구역3!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F6" s="42">
@@ -14368,7 +14368,7 @@
         <v/>
       </c>
       <c r="G6" s="42">
-        <f>IF(COUNTIFS(구역3!G4:G43,"타교회",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!I4:I43,"*타교회*",구역3!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역3!G4:G43,"타교회",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!I4:I43,"*타교회*",구역3!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역3!G4:G43,"타교회",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!J4:J43,"*타교회*",구역3!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역3!G4:G43,"타교회",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!J4:J43,"*타교회*",구역3!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H6" s="42">
@@ -14376,7 +14376,7 @@
         <v/>
       </c>
       <c r="I6" s="42">
-        <f>IF(COUNTIFS(구역3!G4:G43,"개인차",구역3!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역3!I4:I43,"?*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!I4:I43,"*교회차*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!I4:I43,"*타교회*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!I4:I43,"*대중교통*",구역3!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역3!G4:G43,"개인차",구역3!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역3!I4:I43,"?*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!I4:I43,"*교회차*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!I4:I43,"*타교회*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!I4:I43,"*대중교통*",구역3!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역3!G4:G43,"개인차",구역3!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역3!J4:J43,"?*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!J4:J43,"*교회차*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!J4:J43,"*타교회*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!J4:J43,"*대중교통*",구역3!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역3!G4:G43,"개인차",구역3!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역3!J4:J43,"?*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!J4:J43,"*교회차*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!J4:J43,"*타교회*",구역3!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역3!J4:J43,"*대중교통*",구역3!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J6" s="42">
@@ -14384,7 +14384,7 @@
         <v/>
       </c>
       <c r="K6" s="42">
-        <f>IF(COUNTIFS(구역3!G4:G43,"대중교통",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!I4:I43,"*대중교통*",구역3!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역3!G4:G43,"대중교통",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!I4:I43,"*대중교통*",구역3!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역3!G4:G43,"대중교통",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!J4:J43,"*대중교통*",구역3!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역3!G4:G43,"대중교통",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!J4:J43,"*대중교통*",구역3!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L6" s="42" t="n"/>
@@ -14409,7 +14409,7 @@
         <v/>
       </c>
       <c r="E7" s="44">
-        <f>IF(COUNTIFS(구역4!G4:G43,"교회차1",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차2",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차3",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차4",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차5",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!I4:I43,"*교회차*",구역4!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역4!G4:G43,"교회차1",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차2",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차3",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차4",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차5",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!I4:I43,"*교회차*",구역4!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역4!G4:G43,"교회차1",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차2",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차3",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차4",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차5",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!J4:J43,"*교회차*",구역4!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역4!G4:G43,"교회차1",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차2",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차3",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차4",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!G4:G43,"교회차5",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!J4:J43,"*교회차*",구역4!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F7" s="44">
@@ -14417,7 +14417,7 @@
         <v/>
       </c>
       <c r="G7" s="44">
-        <f>IF(COUNTIFS(구역4!G4:G43,"타교회",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!I4:I43,"*타교회*",구역4!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역4!G4:G43,"타교회",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!I4:I43,"*타교회*",구역4!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역4!G4:G43,"타교회",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!J4:J43,"*타교회*",구역4!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역4!G4:G43,"타교회",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!J4:J43,"*타교회*",구역4!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H7" s="44">
@@ -14425,7 +14425,7 @@
         <v/>
       </c>
       <c r="I7" s="44">
-        <f>IF(COUNTIFS(구역4!G4:G43,"개인차",구역4!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역4!I4:I43,"?*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!I4:I43,"*교회차*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!I4:I43,"*타교회*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!I4:I43,"*대중교통*",구역4!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역4!G4:G43,"개인차",구역4!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역4!I4:I43,"?*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!I4:I43,"*교회차*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!I4:I43,"*타교회*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!I4:I43,"*대중교통*",구역4!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역4!G4:G43,"개인차",구역4!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역4!J4:J43,"?*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!J4:J43,"*교회차*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!J4:J43,"*타교회*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!J4:J43,"*대중교통*",구역4!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역4!G4:G43,"개인차",구역4!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역4!J4:J43,"?*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!J4:J43,"*교회차*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!J4:J43,"*타교회*",구역4!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역4!J4:J43,"*대중교통*",구역4!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J7" s="44">
@@ -14433,7 +14433,7 @@
         <v/>
       </c>
       <c r="K7" s="44">
-        <f>IF(COUNTIFS(구역4!G4:G43,"대중교통",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!I4:I43,"*대중교통*",구역4!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역4!G4:G43,"대중교통",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!I4:I43,"*대중교통*",구역4!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역4!G4:G43,"대중교통",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!J4:J43,"*대중교통*",구역4!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역4!G4:G43,"대중교통",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!J4:J43,"*대중교통*",구역4!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L7" s="44" t="n"/>
@@ -14458,7 +14458,7 @@
         <v/>
       </c>
       <c r="E8" s="42">
-        <f>IF(COUNTIFS(구역5!G4:G43,"교회차1",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차2",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차3",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차4",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차5",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!I4:I43,"*교회차*",구역5!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역5!G4:G43,"교회차1",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차2",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차3",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차4",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차5",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!I4:I43,"*교회차*",구역5!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역5!G4:G43,"교회차1",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차2",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차3",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차4",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차5",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!J4:J43,"*교회차*",구역5!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역5!G4:G43,"교회차1",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차2",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차3",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차4",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!G4:G43,"교회차5",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!J4:J43,"*교회차*",구역5!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F8" s="42">
@@ -14466,7 +14466,7 @@
         <v/>
       </c>
       <c r="G8" s="42">
-        <f>IF(COUNTIFS(구역5!G4:G43,"타교회",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!I4:I43,"*타교회*",구역5!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역5!G4:G43,"타교회",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!I4:I43,"*타교회*",구역5!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역5!G4:G43,"타교회",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!J4:J43,"*타교회*",구역5!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역5!G4:G43,"타교회",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!J4:J43,"*타교회*",구역5!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H8" s="42">
@@ -14474,7 +14474,7 @@
         <v/>
       </c>
       <c r="I8" s="42">
-        <f>IF(COUNTIFS(구역5!G4:G43,"개인차",구역5!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역5!I4:I43,"?*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!I4:I43,"*교회차*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!I4:I43,"*타교회*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!I4:I43,"*대중교통*",구역5!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역5!G4:G43,"개인차",구역5!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역5!I4:I43,"?*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!I4:I43,"*교회차*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!I4:I43,"*타교회*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!I4:I43,"*대중교통*",구역5!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역5!G4:G43,"개인차",구역5!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역5!J4:J43,"?*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!J4:J43,"*교회차*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!J4:J43,"*타교회*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!J4:J43,"*대중교통*",구역5!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역5!G4:G43,"개인차",구역5!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역5!J4:J43,"?*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!J4:J43,"*교회차*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!J4:J43,"*타교회*",구역5!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역5!J4:J43,"*대중교통*",구역5!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J8" s="42">
@@ -14482,7 +14482,7 @@
         <v/>
       </c>
       <c r="K8" s="42">
-        <f>IF(COUNTIFS(구역5!G4:G43,"대중교통",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!I4:I43,"*대중교통*",구역5!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역5!G4:G43,"대중교통",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!I4:I43,"*대중교통*",구역5!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역5!G4:G43,"대중교통",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!J4:J43,"*대중교통*",구역5!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역5!G4:G43,"대중교통",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!J4:J43,"*대중교통*",구역5!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L8" s="42" t="n"/>
@@ -14507,7 +14507,7 @@
         <v/>
       </c>
       <c r="E9" s="44">
-        <f>IF(COUNTIFS(구역6!G4:G43,"교회차1",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차2",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차3",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차4",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차5",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!I4:I43,"*교회차*",구역6!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역6!G4:G43,"교회차1",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차2",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차3",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차4",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차5",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!I4:I43,"*교회차*",구역6!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역6!G4:G43,"교회차1",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차2",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차3",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차4",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차5",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!J4:J43,"*교회차*",구역6!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역6!G4:G43,"교회차1",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차2",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차3",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차4",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!G4:G43,"교회차5",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!J4:J43,"*교회차*",구역6!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F9" s="44">
@@ -14515,7 +14515,7 @@
         <v/>
       </c>
       <c r="G9" s="44">
-        <f>IF(COUNTIFS(구역6!G4:G43,"타교회",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!I4:I43,"*타교회*",구역6!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역6!G4:G43,"타교회",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!I4:I43,"*타교회*",구역6!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역6!G4:G43,"타교회",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!J4:J43,"*타교회*",구역6!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역6!G4:G43,"타교회",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!J4:J43,"*타교회*",구역6!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H9" s="44">
@@ -14523,7 +14523,7 @@
         <v/>
       </c>
       <c r="I9" s="44">
-        <f>IF(COUNTIFS(구역6!G4:G43,"개인차",구역6!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역6!I4:I43,"?*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!I4:I43,"*교회차*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!I4:I43,"*타교회*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!I4:I43,"*대중교통*",구역6!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역6!G4:G43,"개인차",구역6!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역6!I4:I43,"?*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!I4:I43,"*교회차*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!I4:I43,"*타교회*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!I4:I43,"*대중교통*",구역6!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역6!G4:G43,"개인차",구역6!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역6!J4:J43,"?*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!J4:J43,"*교회차*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!J4:J43,"*타교회*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!J4:J43,"*대중교통*",구역6!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역6!G4:G43,"개인차",구역6!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역6!J4:J43,"?*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!J4:J43,"*교회차*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!J4:J43,"*타교회*",구역6!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역6!J4:J43,"*대중교통*",구역6!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J9" s="44">
@@ -14531,7 +14531,7 @@
         <v/>
       </c>
       <c r="K9" s="44">
-        <f>IF(COUNTIFS(구역6!G4:G43,"대중교통",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!I4:I43,"*대중교통*",구역6!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역6!G4:G43,"대중교통",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!I4:I43,"*대중교통*",구역6!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역6!G4:G43,"대중교통",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!J4:J43,"*대중교통*",구역6!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역6!G4:G43,"대중교통",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!J4:J43,"*대중교통*",구역6!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L9" s="44" t="n"/>
@@ -14556,7 +14556,7 @@
         <v/>
       </c>
       <c r="E10" s="42">
-        <f>IF(COUNTIFS(구역7!G4:G43,"교회차1",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차2",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차3",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차4",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차5",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!I4:I43,"*교회차*",구역7!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역7!G4:G43,"교회차1",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차2",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차3",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차4",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차5",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!I4:I43,"*교회차*",구역7!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역7!G4:G43,"교회차1",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차2",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차3",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차4",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차5",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!J4:J43,"*교회차*",구역7!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역7!G4:G43,"교회차1",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차2",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차3",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차4",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!G4:G43,"교회차5",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!J4:J43,"*교회차*",구역7!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F10" s="42">
@@ -14564,7 +14564,7 @@
         <v/>
       </c>
       <c r="G10" s="42">
-        <f>IF(COUNTIFS(구역7!G4:G43,"타교회",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!I4:I43,"*타교회*",구역7!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역7!G4:G43,"타교회",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!I4:I43,"*타교회*",구역7!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역7!G4:G43,"타교회",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!J4:J43,"*타교회*",구역7!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역7!G4:G43,"타교회",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!J4:J43,"*타교회*",구역7!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H10" s="42">
@@ -14572,7 +14572,7 @@
         <v/>
       </c>
       <c r="I10" s="42">
-        <f>IF(COUNTIFS(구역7!G4:G43,"개인차",구역7!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역7!I4:I43,"?*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!I4:I43,"*교회차*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!I4:I43,"*타교회*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!I4:I43,"*대중교통*",구역7!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역7!G4:G43,"개인차",구역7!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역7!I4:I43,"?*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!I4:I43,"*교회차*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!I4:I43,"*타교회*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!I4:I43,"*대중교통*",구역7!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역7!G4:G43,"개인차",구역7!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역7!J4:J43,"?*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!J4:J43,"*교회차*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!J4:J43,"*타교회*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!J4:J43,"*대중교통*",구역7!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역7!G4:G43,"개인차",구역7!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역7!J4:J43,"?*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!J4:J43,"*교회차*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!J4:J43,"*타교회*",구역7!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역7!J4:J43,"*대중교통*",구역7!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J10" s="42">
@@ -14580,7 +14580,7 @@
         <v/>
       </c>
       <c r="K10" s="42">
-        <f>IF(COUNTIFS(구역7!G4:G43,"대중교통",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!I4:I43,"*대중교통*",구역7!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역7!G4:G43,"대중교통",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!I4:I43,"*대중교통*",구역7!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역7!G4:G43,"대중교통",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!J4:J43,"*대중교통*",구역7!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역7!G4:G43,"대중교통",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!J4:J43,"*대중교통*",구역7!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L10" s="42" t="n"/>
@@ -14605,7 +14605,7 @@
         <v/>
       </c>
       <c r="E11" s="44">
-        <f>IF(COUNTIFS(구역8!G4:G43,"교회차1",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차2",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차3",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차4",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차5",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!I4:I43,"*교회차*",구역8!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역8!G4:G43,"교회차1",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차2",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차3",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차4",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차5",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!I4:I43,"*교회차*",구역8!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역8!G4:G43,"교회차1",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차2",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차3",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차4",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차5",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!J4:J43,"*교회차*",구역8!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역8!G4:G43,"교회차1",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차2",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차3",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차4",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!G4:G43,"교회차5",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!J4:J43,"*교회차*",구역8!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F11" s="44">
@@ -14613,7 +14613,7 @@
         <v/>
       </c>
       <c r="G11" s="44">
-        <f>IF(COUNTIFS(구역8!G4:G43,"타교회",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!I4:I43,"*타교회*",구역8!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역8!G4:G43,"타교회",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!I4:I43,"*타교회*",구역8!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역8!G4:G43,"타교회",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!J4:J43,"*타교회*",구역8!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역8!G4:G43,"타교회",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!J4:J43,"*타교회*",구역8!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H11" s="44">
@@ -14621,7 +14621,7 @@
         <v/>
       </c>
       <c r="I11" s="44">
-        <f>IF(COUNTIFS(구역8!G4:G43,"개인차",구역8!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역8!I4:I43,"?*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!I4:I43,"*교회차*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!I4:I43,"*타교회*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!I4:I43,"*대중교통*",구역8!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역8!G4:G43,"개인차",구역8!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역8!I4:I43,"?*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!I4:I43,"*교회차*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!I4:I43,"*타교회*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!I4:I43,"*대중교통*",구역8!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역8!G4:G43,"개인차",구역8!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역8!J4:J43,"?*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!J4:J43,"*교회차*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!J4:J43,"*타교회*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!J4:J43,"*대중교통*",구역8!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역8!G4:G43,"개인차",구역8!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역8!J4:J43,"?*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!J4:J43,"*교회차*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!J4:J43,"*타교회*",구역8!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역8!J4:J43,"*대중교통*",구역8!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J11" s="44">
@@ -14629,7 +14629,7 @@
         <v/>
       </c>
       <c r="K11" s="44">
-        <f>IF(COUNTIFS(구역8!G4:G43,"대중교통",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!I4:I43,"*대중교통*",구역8!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역8!G4:G43,"대중교통",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!I4:I43,"*대중교통*",구역8!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역8!G4:G43,"대중교통",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!J4:J43,"*대중교통*",구역8!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역8!G4:G43,"대중교통",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!J4:J43,"*대중교통*",구역8!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L11" s="44" t="n"/>
@@ -14654,7 +14654,7 @@
         <v/>
       </c>
       <c r="E12" s="42">
-        <f>IF(COUNTIFS(구역9!G4:G43,"교회차1",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차2",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차3",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차4",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차5",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!I4:I43,"*교회차*",구역9!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역9!G4:G43,"교회차1",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차2",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차3",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차4",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차5",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!I4:I43,"*교회차*",구역9!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역9!G4:G43,"교회차1",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차2",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차3",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차4",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차5",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!J4:J43,"*교회차*",구역9!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역9!G4:G43,"교회차1",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차2",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차3",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차4",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!G4:G43,"교회차5",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!J4:J43,"*교회차*",구역9!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F12" s="42">
@@ -14662,7 +14662,7 @@
         <v/>
       </c>
       <c r="G12" s="42">
-        <f>IF(COUNTIFS(구역9!G4:G43,"타교회",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!I4:I43,"*타교회*",구역9!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역9!G4:G43,"타교회",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!I4:I43,"*타교회*",구역9!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역9!G4:G43,"타교회",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!J4:J43,"*타교회*",구역9!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역9!G4:G43,"타교회",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!J4:J43,"*타교회*",구역9!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H12" s="42">
@@ -14670,7 +14670,7 @@
         <v/>
       </c>
       <c r="I12" s="42">
-        <f>IF(COUNTIFS(구역9!G4:G43,"개인차",구역9!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역9!I4:I43,"?*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!I4:I43,"*교회차*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!I4:I43,"*타교회*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!I4:I43,"*대중교통*",구역9!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역9!G4:G43,"개인차",구역9!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역9!I4:I43,"?*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!I4:I43,"*교회차*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!I4:I43,"*타교회*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!I4:I43,"*대중교통*",구역9!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역9!G4:G43,"개인차",구역9!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역9!J4:J43,"?*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!J4:J43,"*교회차*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!J4:J43,"*타교회*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!J4:J43,"*대중교통*",구역9!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역9!G4:G43,"개인차",구역9!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역9!J4:J43,"?*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!J4:J43,"*교회차*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!J4:J43,"*타교회*",구역9!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역9!J4:J43,"*대중교통*",구역9!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J12" s="42">
@@ -14678,7 +14678,7 @@
         <v/>
       </c>
       <c r="K12" s="42">
-        <f>IF(COUNTIFS(구역9!G4:G43,"대중교통",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!I4:I43,"*대중교통*",구역9!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역9!G4:G43,"대중교통",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!I4:I43,"*대중교통*",구역9!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역9!G4:G43,"대중교통",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!J4:J43,"*대중교통*",구역9!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역9!G4:G43,"대중교통",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!J4:J43,"*대중교통*",구역9!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L12" s="42" t="n"/>
@@ -14703,7 +14703,7 @@
         <v/>
       </c>
       <c r="E13" s="44">
-        <f>IF(COUNTIFS(구역10!G4:G43,"교회차1",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차2",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차3",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차4",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차5",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!I4:I43,"*교회차*",구역10!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역10!G4:G43,"교회차1",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차2",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차3",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차4",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차5",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!I4:I43,"*교회차*",구역10!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역10!G4:G43,"교회차1",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차2",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차3",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차4",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차5",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!J4:J43,"*교회차*",구역10!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역10!G4:G43,"교회차1",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차2",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차3",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차4",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!G4:G43,"교회차5",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!J4:J43,"*교회차*",구역10!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F13" s="44">
@@ -14711,7 +14711,7 @@
         <v/>
       </c>
       <c r="G13" s="44">
-        <f>IF(COUNTIFS(구역10!G4:G43,"타교회",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!I4:I43,"*타교회*",구역10!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역10!G4:G43,"타교회",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!I4:I43,"*타교회*",구역10!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역10!G4:G43,"타교회",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!J4:J43,"*타교회*",구역10!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역10!G4:G43,"타교회",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!J4:J43,"*타교회*",구역10!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H13" s="44">
@@ -14719,7 +14719,7 @@
         <v/>
       </c>
       <c r="I13" s="44">
-        <f>IF(COUNTIFS(구역10!G4:G43,"개인차",구역10!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역10!I4:I43,"?*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!I4:I43,"*교회차*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!I4:I43,"*타교회*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!I4:I43,"*대중교통*",구역10!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역10!G4:G43,"개인차",구역10!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역10!I4:I43,"?*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!I4:I43,"*교회차*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!I4:I43,"*타교회*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!I4:I43,"*대중교통*",구역10!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역10!G4:G43,"개인차",구역10!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역10!J4:J43,"?*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!J4:J43,"*교회차*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!J4:J43,"*타교회*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!J4:J43,"*대중교통*",구역10!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역10!G4:G43,"개인차",구역10!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역10!J4:J43,"?*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!J4:J43,"*교회차*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!J4:J43,"*타교회*",구역10!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역10!J4:J43,"*대중교통*",구역10!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J13" s="44">
@@ -14727,7 +14727,7 @@
         <v/>
       </c>
       <c r="K13" s="44">
-        <f>IF(COUNTIFS(구역10!G4:G43,"대중교통",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!I4:I43,"*대중교통*",구역10!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역10!G4:G43,"대중교통",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!I4:I43,"*대중교통*",구역10!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역10!G4:G43,"대중교통",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!J4:J43,"*대중교통*",구역10!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역10!G4:G43,"대중교통",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!J4:J43,"*대중교통*",구역10!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L13" s="44" t="n"/>
@@ -14752,7 +14752,7 @@
         <v/>
       </c>
       <c r="E14" s="61">
-        <f>IF(COUNTIFS(구역11!G4:G43,"교회차1",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차2",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차3",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차4",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차5",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!I4:I43,"*교회차*",구역11!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역11!G4:G43,"교회차1",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차2",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차3",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차4",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차5",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!I4:I43,"*교회차*",구역11!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역11!G4:G43,"교회차1",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차2",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차3",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차4",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차5",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!J4:J43,"*교회차*",구역11!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역11!G4:G43,"교회차1",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차2",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차3",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차4",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!G4:G43,"교회차5",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!J4:J43,"*교회차*",구역11!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F14" s="61">
@@ -14760,7 +14760,7 @@
         <v/>
       </c>
       <c r="G14" s="61">
-        <f>IF(COUNTIFS(구역11!G4:G43,"타교회",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!I4:I43,"*타교회*",구역11!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역11!G4:G43,"타교회",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!I4:I43,"*타교회*",구역11!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역11!G4:G43,"타교회",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!J4:J43,"*타교회*",구역11!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역11!G4:G43,"타교회",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!J4:J43,"*타교회*",구역11!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H14" s="61">
@@ -14768,7 +14768,7 @@
         <v/>
       </c>
       <c r="I14" s="61">
-        <f>IF(COUNTIFS(구역11!G4:G43,"개인차",구역11!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역11!I4:I43,"?*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!I4:I43,"*교회차*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!I4:I43,"*타교회*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!I4:I43,"*대중교통*",구역11!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역11!G4:G43,"개인차",구역11!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역11!I4:I43,"?*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!I4:I43,"*교회차*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!I4:I43,"*타교회*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!I4:I43,"*대중교통*",구역11!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역11!G4:G43,"개인차",구역11!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역11!J4:J43,"?*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!J4:J43,"*교회차*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!J4:J43,"*타교회*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!J4:J43,"*대중교통*",구역11!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역11!G4:G43,"개인차",구역11!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역11!J4:J43,"?*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!J4:J43,"*교회차*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!J4:J43,"*타교회*",구역11!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역11!J4:J43,"*대중교통*",구역11!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J14" s="61">
@@ -14776,7 +14776,7 @@
         <v/>
       </c>
       <c r="K14" s="61">
-        <f>IF(COUNTIFS(구역11!G4:G43,"대중교통",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!I4:I43,"*대중교통*",구역11!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역11!G4:G43,"대중교통",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!I4:I43,"*대중교통*",구역11!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역11!G4:G43,"대중교통",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!J4:J43,"*대중교통*",구역11!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역11!G4:G43,"대중교통",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!J4:J43,"*대중교통*",구역11!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L14" s="61" t="n"/>
@@ -14801,7 +14801,7 @@
         <v/>
       </c>
       <c r="E15" s="32">
-        <f>IF(COUNTIFS(구역12!G4:G43,"교회차1",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차2",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차3",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차4",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차5",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!I4:I43,"*교회차*",구역12!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역12!G4:G43,"교회차1",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차2",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차3",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차4",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차5",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!I4:I43,"*교회차*",구역12!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역12!G4:G43,"교회차1",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차2",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차3",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차4",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차5",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!J4:J43,"*교회차*",구역12!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역12!G4:G43,"교회차1",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차2",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차3",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차4",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!G4:G43,"교회차5",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!J4:J43,"*교회차*",구역12!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F15" s="32">
@@ -14809,7 +14809,7 @@
         <v/>
       </c>
       <c r="G15" s="32">
-        <f>IF(COUNTIFS(구역12!G4:G43,"타교회",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!I4:I43,"*타교회*",구역12!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역12!G4:G43,"타교회",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!I4:I43,"*타교회*",구역12!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역12!G4:G43,"타교회",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!J4:J43,"*타교회*",구역12!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역12!G4:G43,"타교회",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!J4:J43,"*타교회*",구역12!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H15" s="32">
@@ -14817,7 +14817,7 @@
         <v/>
       </c>
       <c r="I15" s="32">
-        <f>IF(COUNTIFS(구역12!G4:G43,"개인차",구역12!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역12!I4:I43,"?*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!I4:I43,"*교회차*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!I4:I43,"*타교회*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!I4:I43,"*대중교통*",구역12!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역12!G4:G43,"개인차",구역12!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역12!I4:I43,"?*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!I4:I43,"*교회차*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!I4:I43,"*타교회*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!I4:I43,"*대중교통*",구역12!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역12!G4:G43,"개인차",구역12!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역12!J4:J43,"?*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!J4:J43,"*교회차*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!J4:J43,"*타교회*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!J4:J43,"*대중교통*",구역12!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역12!G4:G43,"개인차",구역12!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역12!J4:J43,"?*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!J4:J43,"*교회차*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!J4:J43,"*타교회*",구역12!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역12!J4:J43,"*대중교통*",구역12!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J15" s="32">
@@ -14825,7 +14825,7 @@
         <v/>
       </c>
       <c r="K15" s="32">
-        <f>IF(COUNTIFS(구역12!G4:G43,"대중교통",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!I4:I43,"*대중교통*",구역12!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역12!G4:G43,"대중교통",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!I4:I43,"*대중교통*",구역12!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역12!G4:G43,"대중교통",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!J4:J43,"*대중교통*",구역12!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역12!G4:G43,"대중교통",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!J4:J43,"*대중교통*",구역12!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L15" s="32" t="n"/>
@@ -14850,7 +14850,7 @@
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>IF(COUNTIFS(구역13!G4:G43,"교회차1",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차2",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차3",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차4",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차5",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!I4:I43,"*교회차*",구역13!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역13!G4:G43,"교회차1",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차2",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차3",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차4",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차5",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!I4:I43,"*교회차*",구역13!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역13!G4:G43,"교회차1",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차2",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차3",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차4",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차5",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!J4:J43,"*교회차*",구역13!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역13!G4:G43,"교회차1",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차2",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차3",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차4",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!G4:G43,"교회차5",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!J4:J43,"*교회차*",구역13!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F16" s="32">
@@ -14858,7 +14858,7 @@
         <v/>
       </c>
       <c r="G16" s="32">
-        <f>IF(COUNTIFS(구역13!G4:G43,"타교회",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!I4:I43,"*타교회*",구역13!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역13!G4:G43,"타교회",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!I4:I43,"*타교회*",구역13!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역13!G4:G43,"타교회",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!J4:J43,"*타교회*",구역13!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역13!G4:G43,"타교회",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!J4:J43,"*타교회*",구역13!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H16" s="32">
@@ -14866,7 +14866,7 @@
         <v/>
       </c>
       <c r="I16" s="32">
-        <f>IF(COUNTIFS(구역13!G4:G43,"개인차",구역13!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역13!I4:I43,"?*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!I4:I43,"*교회차*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!I4:I43,"*타교회*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!I4:I43,"*대중교통*",구역13!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역13!G4:G43,"개인차",구역13!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역13!I4:I43,"?*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!I4:I43,"*교회차*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!I4:I43,"*타교회*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!I4:I43,"*대중교통*",구역13!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역13!G4:G43,"개인차",구역13!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역13!J4:J43,"?*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!J4:J43,"*교회차*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!J4:J43,"*타교회*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!J4:J43,"*대중교통*",구역13!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역13!G4:G43,"개인차",구역13!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역13!J4:J43,"?*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!J4:J43,"*교회차*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!J4:J43,"*타교회*",구역13!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역13!J4:J43,"*대중교통*",구역13!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J16" s="32">
@@ -14874,7 +14874,7 @@
         <v/>
       </c>
       <c r="K16" s="32">
-        <f>IF(COUNTIFS(구역13!G4:G43,"대중교통",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!I4:I43,"*대중교통*",구역13!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역13!G4:G43,"대중교통",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!I4:I43,"*대중교통*",구역13!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역13!G4:G43,"대중교통",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!J4:J43,"*대중교통*",구역13!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역13!G4:G43,"대중교통",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!J4:J43,"*대중교통*",구역13!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="L16" s="32" t="n"/>
@@ -14899,7 +14899,7 @@
         <v/>
       </c>
       <c r="E17" s="48">
-        <f>IF(COUNTIFS(구역14!G4:G43,"교회차1",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차2",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차3",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차4",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차5",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!I4:I43,"*교회차*",구역14!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역14!G4:G43,"교회차1",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차2",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차3",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차4",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차5",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!I4:I43,"*교회차*",구역14!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역14!G4:G43,"교회차1",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차2",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차3",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차4",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차5",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!J4:J43,"*교회차*",구역14!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역14!G4:G43,"교회차1",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차2",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차3",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차4",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!G4:G43,"교회차5",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!J4:J43,"*교회차*",구역14!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F17" s="48">
@@ -14907,7 +14907,7 @@
         <v/>
       </c>
       <c r="G17" s="48">
-        <f>IF(COUNTIFS(구역14!G4:G43,"타교회",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!I4:I43,"*타교회*",구역14!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역14!G4:G43,"타교회",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!I4:I43,"*타교회*",구역14!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역14!G4:G43,"타교회",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!J4:J43,"*타교회*",구역14!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역14!G4:G43,"타교회",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!J4:J43,"*타교회*",구역14!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H17" s="48">
@@ -14915,7 +14915,7 @@
         <v/>
       </c>
       <c r="I17" s="48">
-        <f>IF(COUNTIFS(구역14!G4:G43,"개인차",구역14!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역14!I4:I43,"?*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!I4:I43,"*교회차*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!I4:I43,"*타교회*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!I4:I43,"*대중교통*",구역14!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역14!G4:G43,"개인차",구역14!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역14!I4:I43,"?*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!I4:I43,"*교회차*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!I4:I43,"*타교회*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!I4:I43,"*대중교통*",구역14!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역14!G4:G43,"개인차",구역14!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역14!J4:J43,"?*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!J4:J43,"*교회차*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!J4:J43,"*타교회*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!J4:J43,"*대중교통*",구역14!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역14!G4:G43,"개인차",구역14!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역14!J4:J43,"?*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!J4:J43,"*교회차*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!J4:J43,"*타교회*",구역14!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역14!J4:J43,"*대중교통*",구역14!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J17" s="49">
@@ -14923,7 +14923,7 @@
         <v/>
       </c>
       <c r="K17" s="32">
-        <f>IF(COUNTIFS(구역14!G4:G43,"대중교통",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!I4:I43,"*대중교통*",구역14!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역14!G4:G43,"대중교통",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!I4:I43,"*대중교통*",구역14!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역14!G4:G43,"대중교통",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!J4:J43,"*대중교통*",구역14!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역14!G4:G43,"대중교통",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!J4:J43,"*대중교통*",구역14!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
     </row>
@@ -14946,7 +14946,7 @@
         <v/>
       </c>
       <c r="E18" s="32">
-        <f>IF(COUNTIFS(구역15!G4:G43,"교회차1",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차2",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차3",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차4",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차5",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!I4:I43,"*교회차*",구역15!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역15!G4:G43,"교회차1",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차2",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차3",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차4",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차5",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!I4:I43,"*교회차*",구역15!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역15!G4:G43,"교회차1",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차2",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차3",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차4",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차5",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!J4:J43,"*교회차*",구역15!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역15!G4:G43,"교회차1",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차2",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차3",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차4",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!G4:G43,"교회차5",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!J4:J43,"*교회차*",구역15!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F18" s="32">
@@ -14954,7 +14954,7 @@
         <v/>
       </c>
       <c r="G18" s="32">
-        <f>IF(COUNTIFS(구역15!G4:G43,"타교회",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!I4:I43,"*타교회*",구역15!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역15!G4:G43,"타교회",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!I4:I43,"*타교회*",구역15!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역15!G4:G43,"타교회",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!J4:J43,"*타교회*",구역15!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역15!G4:G43,"타교회",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!J4:J43,"*타교회*",구역15!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H18" s="32">
@@ -14962,7 +14962,7 @@
         <v/>
       </c>
       <c r="I18" s="32">
-        <f>IF(COUNTIFS(구역15!G4:G43,"개인차",구역15!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역15!I4:I43,"?*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!I4:I43,"*교회차*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!I4:I43,"*타교회*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!I4:I43,"*대중교통*",구역15!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역15!G4:G43,"개인차",구역15!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역15!I4:I43,"?*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!I4:I43,"*교회차*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!I4:I43,"*타교회*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!I4:I43,"*대중교통*",구역15!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역15!G4:G43,"개인차",구역15!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역15!J4:J43,"?*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!J4:J43,"*교회차*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!J4:J43,"*타교회*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!J4:J43,"*대중교통*",구역15!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역15!G4:G43,"개인차",구역15!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역15!J4:J43,"?*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!J4:J43,"*교회차*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!J4:J43,"*타교회*",구역15!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역15!J4:J43,"*대중교통*",구역15!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J18" s="32">
@@ -14970,7 +14970,7 @@
         <v/>
       </c>
       <c r="K18" s="32">
-        <f>IF(COUNTIFS(구역15!G4:G43,"대중교통",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!I4:I43,"*대중교통*",구역15!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역15!G4:G43,"대중교통",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!I4:I43,"*대중교통*",구역15!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역15!G4:G43,"대중교통",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!J4:J43,"*대중교통*",구역15!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역15!G4:G43,"대중교통",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!J4:J43,"*대중교통*",구역15!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
     </row>
@@ -14993,7 +14993,7 @@
         <v/>
       </c>
       <c r="E19" s="32">
-        <f>IF(COUNTIFS(구역16!G4:G43,"교회차1",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차2",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차3",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차4",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차5",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!I4:I43,"*교회차*",구역16!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역16!G4:G43,"교회차1",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차2",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차3",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차4",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차5",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!I4:I43,"*교회차*",구역16!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역16!G4:G43,"교회차1",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차2",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차3",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차4",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차5",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!J4:J43,"*교회차*",구역16!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역16!G4:G43,"교회차1",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차2",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차3",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차4",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!G4:G43,"교회차5",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!J4:J43,"*교회차*",구역16!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F19" s="32">
@@ -15001,7 +15001,7 @@
         <v/>
       </c>
       <c r="G19" s="32">
-        <f>IF(COUNTIFS(구역16!G4:G43,"타교회",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!I4:I43,"*타교회*",구역16!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역16!G4:G43,"타교회",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!I4:I43,"*타교회*",구역16!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역16!G4:G43,"타교회",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!J4:J43,"*타교회*",구역16!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역16!G4:G43,"타교회",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!J4:J43,"*타교회*",구역16!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H19" s="32">
@@ -15009,7 +15009,7 @@
         <v/>
       </c>
       <c r="I19" s="32">
-        <f>IF(COUNTIFS(구역16!G4:G43,"개인차",구역16!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역16!I4:I43,"?*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!I4:I43,"*교회차*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!I4:I43,"*타교회*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!I4:I43,"*대중교통*",구역16!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역16!G4:G43,"개인차",구역16!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역16!I4:I43,"?*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!I4:I43,"*교회차*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!I4:I43,"*타교회*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!I4:I43,"*대중교통*",구역16!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역16!G4:G43,"개인차",구역16!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역16!J4:J43,"?*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!J4:J43,"*교회차*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!J4:J43,"*타교회*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!J4:J43,"*대중교통*",구역16!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역16!G4:G43,"개인차",구역16!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역16!J4:J43,"?*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!J4:J43,"*교회차*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!J4:J43,"*타교회*",구역16!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역16!J4:J43,"*대중교통*",구역16!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J19" s="32">
@@ -15017,7 +15017,7 @@
         <v/>
       </c>
       <c r="K19" s="32">
-        <f>IF(COUNTIFS(구역16!G4:G43,"대중교통",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!I4:I43,"*대중교통*",구역16!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역16!G4:G43,"대중교통",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!I4:I43,"*대중교통*",구역16!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역16!G4:G43,"대중교통",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!J4:J43,"*대중교통*",구역16!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역16!G4:G43,"대중교통",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!J4:J43,"*대중교통*",구역16!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
     </row>
@@ -15040,7 +15040,7 @@
         <v/>
       </c>
       <c r="E20" s="32">
-        <f>IF(COUNTIFS(구역17!G4:G43,"교회차1",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차2",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차3",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차4",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차5",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!I4:I43,"*교회차*",구역17!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역17!G4:G43,"교회차1",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차2",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차3",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차4",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차5",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!I4:I43,"*교회차*",구역17!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역17!G4:G43,"교회차1",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차2",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차3",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차4",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차5",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!J4:J43,"*교회차*",구역17!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역17!G4:G43,"교회차1",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차2",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차3",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차4",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!G4:G43,"교회차5",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!J4:J43,"*교회차*",구역17!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F20" s="32">
@@ -15048,7 +15048,7 @@
         <v/>
       </c>
       <c r="G20" s="32">
-        <f>IF(COUNTIFS(구역17!G4:G43,"타교회",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!I4:I43,"*타교회*",구역17!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역17!G4:G43,"타교회",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!I4:I43,"*타교회*",구역17!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역17!G4:G43,"타교회",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!J4:J43,"*타교회*",구역17!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역17!G4:G43,"타교회",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!J4:J43,"*타교회*",구역17!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H20" s="32">
@@ -15056,7 +15056,7 @@
         <v/>
       </c>
       <c r="I20" s="32">
-        <f>IF(COUNTIFS(구역17!G4:G43,"개인차",구역17!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역17!I4:I43,"?*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!I4:I43,"*교회차*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!I4:I43,"*타교회*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!I4:I43,"*대중교통*",구역17!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역17!G4:G43,"개인차",구역17!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역17!I4:I43,"?*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!I4:I43,"*교회차*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!I4:I43,"*타교회*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!I4:I43,"*대중교통*",구역17!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역17!G4:G43,"개인차",구역17!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역17!J4:J43,"?*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!J4:J43,"*교회차*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!J4:J43,"*타교회*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!J4:J43,"*대중교통*",구역17!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역17!G4:G43,"개인차",구역17!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역17!J4:J43,"?*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!J4:J43,"*교회차*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!J4:J43,"*타교회*",구역17!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역17!J4:J43,"*대중교통*",구역17!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J20" s="32">
@@ -15064,7 +15064,7 @@
         <v/>
       </c>
       <c r="K20" s="32">
-        <f>IF(COUNTIFS(구역17!G4:G43,"대중교통",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!I4:I43,"*대중교통*",구역17!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역17!G4:G43,"대중교통",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!I4:I43,"*대중교통*",구역17!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역17!G4:G43,"대중교통",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!J4:J43,"*대중교통*",구역17!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역17!G4:G43,"대중교통",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!J4:J43,"*대중교통*",구역17!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
         <v/>
       </c>
       <c r="E21" s="32">
-        <f>IF(COUNTIFS(구역18!G4:G43,"교회차1",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차2",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차3",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차4",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차5",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!I4:I43,"*교회차*",구역18!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역18!G4:G43,"교회차1",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차2",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차3",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차4",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차5",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!I4:I43,"*교회차*",구역18!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역18!G4:G43,"교회차1",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차2",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차3",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차4",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차5",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!J4:J43,"*교회차*",구역18!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역18!G4:G43,"교회차1",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차2",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차3",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차4",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!G4:G43,"교회차5",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!J4:J43,"*교회차*",구역18!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F21" s="32">
@@ -15095,7 +15095,7 @@
         <v/>
       </c>
       <c r="G21" s="32">
-        <f>IF(COUNTIFS(구역18!G4:G43,"타교회",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!I4:I43,"*타교회*",구역18!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역18!G4:G43,"타교회",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!I4:I43,"*타교회*",구역18!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역18!G4:G43,"타교회",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!J4:J43,"*타교회*",구역18!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역18!G4:G43,"타교회",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!J4:J43,"*타교회*",구역18!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H21" s="32">
@@ -15103,7 +15103,7 @@
         <v/>
       </c>
       <c r="I21" s="32">
-        <f>IF(COUNTIFS(구역18!G4:G43,"개인차",구역18!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역18!I4:I43,"?*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!I4:I43,"*교회차*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!I4:I43,"*타교회*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!I4:I43,"*대중교통*",구역18!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역18!G4:G43,"개인차",구역18!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역18!I4:I43,"?*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!I4:I43,"*교회차*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!I4:I43,"*타교회*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!I4:I43,"*대중교통*",구역18!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역18!G4:G43,"개인차",구역18!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역18!J4:J43,"?*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!J4:J43,"*교회차*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!J4:J43,"*타교회*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!J4:J43,"*대중교통*",구역18!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역18!G4:G43,"개인차",구역18!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역18!J4:J43,"?*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!J4:J43,"*교회차*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!J4:J43,"*타교회*",구역18!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역18!J4:J43,"*대중교통*",구역18!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J21" s="32">
@@ -15111,7 +15111,7 @@
         <v/>
       </c>
       <c r="K21" s="32">
-        <f>IF(COUNTIFS(구역18!G4:G43,"대중교통",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!I4:I43,"*대중교통*",구역18!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역18!G4:G43,"대중교통",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!I4:I43,"*대중교통*",구역18!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역18!G4:G43,"대중교통",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!J4:J43,"*대중교통*",구역18!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역18!G4:G43,"대중교통",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!J4:J43,"*대중교통*",구역18!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
         <v/>
       </c>
       <c r="E22" s="32">
-        <f>IF(COUNTIFS(구역19!G4:G43,"교회차1",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차2",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차3",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차4",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차5",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!I4:I43,"*교회차*",구역19!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역19!G4:G43,"교회차1",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차2",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차3",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차4",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차5",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!I4:I43,"*교회차*",구역19!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역19!G4:G43,"교회차1",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차2",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차3",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차4",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차5",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!J4:J43,"*교회차*",구역19!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역19!G4:G43,"교회차1",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차2",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차3",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차4",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!G4:G43,"교회차5",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!J4:J43,"*교회차*",구역19!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F22" s="32">
@@ -15142,7 +15142,7 @@
         <v/>
       </c>
       <c r="G22" s="32">
-        <f>IF(COUNTIFS(구역19!G4:G43,"타교회",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!I4:I43,"*타교회*",구역19!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역19!G4:G43,"타교회",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!I4:I43,"*타교회*",구역19!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역19!G4:G43,"타교회",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!J4:J43,"*타교회*",구역19!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역19!G4:G43,"타교회",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!J4:J43,"*타교회*",구역19!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H22" s="32">
@@ -15150,7 +15150,7 @@
         <v/>
       </c>
       <c r="I22" s="32">
-        <f>IF(COUNTIFS(구역19!G4:G43,"개인차",구역19!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역19!I4:I43,"?*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!I4:I43,"*교회차*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!I4:I43,"*타교회*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!I4:I43,"*대중교통*",구역19!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역19!G4:G43,"개인차",구역19!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역19!I4:I43,"?*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!I4:I43,"*교회차*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!I4:I43,"*타교회*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!I4:I43,"*대중교통*",구역19!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역19!G4:G43,"개인차",구역19!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역19!J4:J43,"?*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!J4:J43,"*교회차*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!J4:J43,"*타교회*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!J4:J43,"*대중교통*",구역19!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역19!G4:G43,"개인차",구역19!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역19!J4:J43,"?*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!J4:J43,"*교회차*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!J4:J43,"*타교회*",구역19!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역19!J4:J43,"*대중교통*",구역19!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J22" s="32">
@@ -15158,7 +15158,7 @@
         <v/>
       </c>
       <c r="K22" s="32">
-        <f>IF(COUNTIFS(구역19!G4:G43,"대중교통",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!I4:I43,"*대중교통*",구역19!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역19!G4:G43,"대중교통",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!I4:I43,"*대중교통*",구역19!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역19!G4:G43,"대중교통",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!J4:J43,"*대중교통*",구역19!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역19!G4:G43,"대중교통",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!J4:J43,"*대중교통*",구역19!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
     </row>
@@ -15181,7 +15181,7 @@
         <v/>
       </c>
       <c r="E23" s="32">
-        <f>IF(COUNTIFS(구역20!G4:G43,"교회차1",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차2",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차3",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차4",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차5",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!I4:I43,"*교회차*",구역20!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역20!G4:G43,"교회차1",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차2",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차3",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차4",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차5",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!I4:I43,"*교회차*",구역20!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역20!G4:G43,"교회차1",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차2",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차3",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차4",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차5",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!J4:J43,"*교회차*",구역20!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역20!G4:G43,"교회차1",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차2",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차3",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차4",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!G4:G43,"교회차5",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!J4:J43,"*교회차*",구역20!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="F23" s="32">
@@ -15189,7 +15189,7 @@
         <v/>
       </c>
       <c r="G23" s="32">
-        <f>IF(COUNTIFS(구역20!G4:G43,"타교회",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!I4:I43,"*타교회*",구역20!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역20!G4:G43,"타교회",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!I4:I43,"*타교회*",구역20!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역20!G4:G43,"타교회",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!J4:J43,"*타교회*",구역20!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역20!G4:G43,"타교회",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!J4:J43,"*타교회*",구역20!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
       <c r="H23" s="32">
@@ -15197,7 +15197,7 @@
         <v/>
       </c>
       <c r="I23" s="32">
-        <f>IF(COUNTIFS(구역20!G4:G43,"개인차",구역20!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역20!I4:I43,"?*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!I4:I43,"*교회차*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!I4:I43,"*타교회*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!I4:I43,"*대중교통*",구역20!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역20!G4:G43,"개인차",구역20!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역20!I4:I43,"?*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!I4:I43,"*교회차*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!I4:I43,"*타교회*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!I4:I43,"*대중교통*",구역20!E4:E43,"*"&amp;$B31&amp;"*")))</f>
+        <f>IF(COUNTIFS(구역20!G4:G43,"개인차",구역20!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역20!J4:J43,"?*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!J4:J43,"*교회차*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!J4:J43,"*타교회*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!J4:J43,"*대중교통*",구역20!E4:E43,"*"&amp;$B31&amp;"*"))=0,"",COUNTIFS(구역20!G4:G43,"개인차",구역20!E4:E43,"*"&amp;$B31&amp;"*")+(COUNTIFS(구역20!J4:J43,"?*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!J4:J43,"*교회차*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!J4:J43,"*타교회*",구역20!E4:E43,"*"&amp;$B31&amp;"*")-COUNTIFS(구역20!J4:J43,"*대중교통*",구역20!E4:E43,"*"&amp;$B31&amp;"*")))</f>
         <v/>
       </c>
       <c r="J23" s="32">
@@ -15205,7 +15205,7 @@
         <v/>
       </c>
       <c r="K23" s="32">
-        <f>IF(COUNTIFS(구역20!G4:G43,"대중교통",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!I4:I43,"*대중교통*",구역20!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역20!G4:G43,"대중교통",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!I4:I43,"*대중교통*",구역20!E4:E43,"*"&amp;$B31&amp;"*"))</f>
+        <f>IF(COUNTIFS(구역20!G4:G43,"대중교통",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!J4:J43,"*대중교통*",구역20!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역20!G4:G43,"대중교통",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!J4:J43,"*대중교통*",구역20!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
     </row>
@@ -20150,14 +20150,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -20178,14 +20179,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -20195,17 +20194,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -20905,15 +20904,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -28794,8 +28794,8 @@
     <mergeCell ref="G176:K176"/>
     <mergeCell ref="A88:E88"/>
     <mergeCell ref="G132:K132"/>
+    <mergeCell ref="A45:K45"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A45:K45"/>
     <mergeCell ref="A90:E90"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A133:K133"/>
@@ -35711,14 +35711,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -35739,14 +35740,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -35756,17 +35755,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -36466,15 +36465,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -36556,14 +36556,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -36584,14 +36585,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -36601,17 +36600,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -37311,15 +37310,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -37401,14 +37401,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -37429,14 +37430,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -37446,17 +37445,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -38156,15 +38155,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -38246,14 +38246,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -38274,14 +38275,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -38291,17 +38290,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -39001,15 +39000,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -39091,14 +39091,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -39119,14 +39120,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -39136,17 +39135,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -39846,15 +39845,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>
@@ -39936,14 +39936,15 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>교 통 편</t>
+          <t>본대</t>
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -39964,14 +39965,12 @@
       <c r="E3" s="39" t="n"/>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>본대
-상행</t>
+          <t>상행</t>
         </is>
       </c>
       <c r="G3" s="40" t="inlineStr">
         <is>
-          <t>본대
-하행</t>
+          <t>하행</t>
         </is>
       </c>
       <c r="H3" s="40" t="inlineStr">
@@ -39981,17 +39980,17 @@
       </c>
       <c r="I3" s="40" t="inlineStr">
         <is>
+          <t>참석 시점</t>
+        </is>
+      </c>
+      <c r="J3" s="40" t="inlineStr">
+        <is>
           <t>하행</t>
         </is>
       </c>
-      <c r="J3" s="40" t="inlineStr">
-        <is>
-          <t>합류</t>
-        </is>
-      </c>
       <c r="K3" s="40" t="inlineStr">
         <is>
-          <t>귀가</t>
+          <t>귀가 시점</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -40691,15 +40690,16 @@
       <c r="N44" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:K2"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>

--- a/수양회_서식_template.xlsx
+++ b/수양회_서식_template.xlsx
@@ -384,7 +384,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -582,6 +582,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -905,11 +908,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -1750,11 +1756,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -2595,11 +2604,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -3440,11 +3452,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -4285,11 +4300,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -5130,11 +5148,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -5975,11 +5996,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -6820,11 +6844,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -7665,11 +7692,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -8510,11 +8540,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -9355,11 +9388,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -10200,11 +10236,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -11045,11 +11084,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -20154,11 +20196,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -28794,8 +28839,8 @@
     <mergeCell ref="G176:K176"/>
     <mergeCell ref="A88:E88"/>
     <mergeCell ref="G132:K132"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A90:E90"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A133:K133"/>
@@ -35715,11 +35760,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -36560,11 +36608,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -37405,11 +37456,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -38250,11 +38304,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -39095,11 +39152,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -39940,11 +40000,14 @@
         </is>
       </c>
       <c r="G2" s="35" t="n"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>

--- a/수양회_서식_template.xlsx
+++ b/수양회_서식_template.xlsx
@@ -53,7 +53,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -209,8 +209,24 @@
       <family val="0"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -259,8 +275,13 @@
         <bgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -373,6 +394,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDC3C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBDC3C7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -384,7 +464,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -584,6 +664,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -842,17 +962,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -913,9 +1035,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -1690,17 +1812,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -1761,9 +1885,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -2538,17 +2662,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -2609,9 +2735,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -3386,17 +3512,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -3457,9 +3585,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -4234,17 +4362,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -4305,9 +4435,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -5082,17 +5212,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -5153,9 +5285,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -5930,17 +6062,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -6001,9 +6135,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -6778,17 +6912,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -6849,9 +6985,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -7626,17 +7762,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -7697,9 +7835,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -8474,17 +8612,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -8545,9 +8685,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -9322,17 +9462,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -9393,9 +9535,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -10170,17 +10312,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -10241,9 +10385,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -11018,17 +11162,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -11089,9 +11235,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -12475,9 +12621,9 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="8" customWidth="1" style="32" min="3" max="3"/>
-    <col width="7.8" customWidth="1" style="32" min="4" max="4"/>
+    <col width="8.5" customWidth="1" style="32" min="4" max="4"/>
     <col width="8" customWidth="1" style="32" min="5" max="5"/>
     <col width="9" customWidth="1" style="32" min="6" max="6"/>
     <col width="8.5" customWidth="1" style="32" min="7" max="7"/>
@@ -12963,7 +13109,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="10" customWidth="1" style="32" min="5" max="5"/>
@@ -14167,12 +14313,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7.8" customWidth="1" style="32" min="1" max="1"/>
-    <col width="4.5" customWidth="1" style="32" min="2" max="2"/>
-    <col width="13" customWidth="1" style="32" min="3" max="13"/>
+    <col width="5.5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="5.5" customWidth="1" style="32" min="3" max="13"/>
+    <col width="5.5" customWidth="1" style="33" min="4" max="4"/>
+    <col width="5.5" customWidth="1" style="33" min="5" max="5"/>
+    <col width="5.5" customWidth="1" style="33" min="6" max="6"/>
+    <col width="5.5" customWidth="1" style="33" min="7" max="7"/>
+    <col width="5.5" customWidth="1" style="33" min="8" max="8"/>
+    <col width="5.5" customWidth="1" style="33" min="9" max="9"/>
+    <col width="5.5" customWidth="1" style="33" min="10" max="10"/>
+    <col width="5.5" customWidth="1" style="33" min="11" max="11"/>
+    <col width="5.5" customWidth="1" style="33" min="12" max="12"/>
+    <col width="8.43" customWidth="1" style="33" min="13" max="13"/>
+    <col width="8.43" customWidth="1" style="33" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -14191,6 +14348,9 @@
       <c r="I1" s="35" t="n"/>
       <c r="J1" s="35" t="n"/>
       <c r="K1" s="35" t="n"/>
+      <c r="L1" s="35" t="n"/>
+      <c r="M1" s="81" t="n"/>
+      <c r="N1" s="81" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1" s="33">
       <c r="A2" s="37" t="inlineStr">
@@ -14228,7 +14388,13 @@
         </is>
       </c>
       <c r="K2" s="35" t="n"/>
-      <c r="L2" s="38" t="n"/>
+      <c r="L2" s="38" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="M2" s="81" t="n"/>
+      <c r="N2" s="81" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="39" t="n"/>
@@ -14242,12 +14408,12 @@
           <t>하행</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="D3" s="40" t="inlineStr">
         <is>
           <t>상행</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="40" t="inlineStr">
         <is>
           <t>하행</t>
         </is>
@@ -14282,8 +14448,9 @@
           <t>하행</t>
         </is>
       </c>
-      <c r="L3" s="40" t="n"/>
-      <c r="M3" s="40" t="n"/>
+      <c r="L3" s="70" t="n"/>
+      <c r="M3" s="82" t="n"/>
+      <c r="N3" s="81" t="n"/>
     </row>
     <row r="4" ht="21.75" customHeight="1" s="33">
       <c r="A4" s="42" t="inlineStr">
@@ -14331,8 +14498,12 @@
         <f>IF(COUNTIFS(구역1!G4:G43,"대중교통",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!J4:J43,"*대중교통*",구역1!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역1!G4:G43,"대중교통",구역1!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역1!J4:J43,"*대중교통*",구역1!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L4" s="42" t="n"/>
-      <c r="M4" s="42" t="n"/>
+      <c r="L4" s="42">
+        <f>IF(SUM(B4,D4,F4,H4,J4)=0,"",SUM(B4,D4,F4,H4,J4))</f>
+        <v/>
+      </c>
+      <c r="M4" s="83" t="n"/>
+      <c r="N4" s="81" t="n"/>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="33">
       <c r="A5" s="44" t="inlineStr">
@@ -14380,8 +14551,12 @@
         <f>IF(COUNTIFS(구역2!G4:G43,"대중교통",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!J4:J43,"*대중교통*",구역2!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역2!G4:G43,"대중교통",구역2!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역2!J4:J43,"*대중교통*",구역2!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L5" s="44" t="n"/>
-      <c r="M5" s="44" t="n"/>
+      <c r="L5" s="42">
+        <f>IF(SUM(B5,D5,F5,H5,J5)=0,"",SUM(B5,D5,F5,H5,J5))</f>
+        <v/>
+      </c>
+      <c r="M5" s="83" t="n"/>
+      <c r="N5" s="81" t="n"/>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="33">
       <c r="A6" s="42" t="inlineStr">
@@ -14429,8 +14604,12 @@
         <f>IF(COUNTIFS(구역3!G4:G43,"대중교통",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!J4:J43,"*대중교통*",구역3!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역3!G4:G43,"대중교통",구역3!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역3!J4:J43,"*대중교통*",구역3!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L6" s="42" t="n"/>
-      <c r="M6" s="42" t="n"/>
+      <c r="L6" s="42">
+        <f>IF(SUM(B6,D6,F6,H6,J6)=0,"",SUM(B6,D6,F6,H6,J6))</f>
+        <v/>
+      </c>
+      <c r="M6" s="83" t="n"/>
+      <c r="N6" s="81" t="n"/>
     </row>
     <row r="7" ht="21.75" customHeight="1" s="33">
       <c r="A7" s="44" t="inlineStr">
@@ -14478,8 +14657,12 @@
         <f>IF(COUNTIFS(구역4!G4:G43,"대중교통",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!J4:J43,"*대중교통*",구역4!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역4!G4:G43,"대중교통",구역4!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역4!J4:J43,"*대중교통*",구역4!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L7" s="44" t="n"/>
-      <c r="M7" s="44" t="n"/>
+      <c r="L7" s="42">
+        <f>IF(SUM(B7,D7,F7,H7,J7)=0,"",SUM(B7,D7,F7,H7,J7))</f>
+        <v/>
+      </c>
+      <c r="M7" s="83" t="n"/>
+      <c r="N7" s="81" t="n"/>
     </row>
     <row r="8" ht="21.75" customHeight="1" s="33">
       <c r="A8" s="42" t="inlineStr">
@@ -14527,8 +14710,12 @@
         <f>IF(COUNTIFS(구역5!G4:G43,"대중교통",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!J4:J43,"*대중교통*",구역5!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역5!G4:G43,"대중교통",구역5!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역5!J4:J43,"*대중교통*",구역5!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L8" s="42" t="n"/>
-      <c r="M8" s="42" t="n"/>
+      <c r="L8" s="42">
+        <f>IF(SUM(B8,D8,F8,H8,J8)=0,"",SUM(B8,D8,F8,H8,J8))</f>
+        <v/>
+      </c>
+      <c r="M8" s="83" t="n"/>
+      <c r="N8" s="81" t="n"/>
     </row>
     <row r="9" ht="21.75" customHeight="1" s="33">
       <c r="A9" s="44" t="inlineStr">
@@ -14576,8 +14763,12 @@
         <f>IF(COUNTIFS(구역6!G4:G43,"대중교통",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!J4:J43,"*대중교통*",구역6!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역6!G4:G43,"대중교통",구역6!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역6!J4:J43,"*대중교통*",구역6!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L9" s="44" t="n"/>
-      <c r="M9" s="44" t="n"/>
+      <c r="L9" s="42">
+        <f>IF(SUM(B9,D9,F9,H9,J9)=0,"",SUM(B9,D9,F9,H9,J9))</f>
+        <v/>
+      </c>
+      <c r="M9" s="83" t="n"/>
+      <c r="N9" s="81" t="n"/>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="33">
       <c r="A10" s="42" t="inlineStr">
@@ -14625,8 +14816,12 @@
         <f>IF(COUNTIFS(구역7!G4:G43,"대중교통",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!J4:J43,"*대중교통*",구역7!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역7!G4:G43,"대중교통",구역7!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역7!J4:J43,"*대중교통*",구역7!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L10" s="42" t="n"/>
-      <c r="M10" s="42" t="n"/>
+      <c r="L10" s="42">
+        <f>IF(SUM(B10,D10,F10,H10,J10)=0,"",SUM(B10,D10,F10,H10,J10))</f>
+        <v/>
+      </c>
+      <c r="M10" s="83" t="n"/>
+      <c r="N10" s="81" t="n"/>
     </row>
     <row r="11" ht="21.75" customHeight="1" s="33">
       <c r="A11" s="44" t="inlineStr">
@@ -14674,8 +14869,12 @@
         <f>IF(COUNTIFS(구역8!G4:G43,"대중교통",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!J4:J43,"*대중교통*",구역8!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역8!G4:G43,"대중교통",구역8!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역8!J4:J43,"*대중교통*",구역8!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L11" s="44" t="n"/>
-      <c r="M11" s="44" t="n"/>
+      <c r="L11" s="42">
+        <f>IF(SUM(B11,D11,F11,H11,J11)=0,"",SUM(B11,D11,F11,H11,J11))</f>
+        <v/>
+      </c>
+      <c r="M11" s="83" t="n"/>
+      <c r="N11" s="81" t="n"/>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="33">
       <c r="A12" s="42" t="inlineStr">
@@ -14723,8 +14922,12 @@
         <f>IF(COUNTIFS(구역9!G4:G43,"대중교통",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!J4:J43,"*대중교통*",구역9!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역9!G4:G43,"대중교통",구역9!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역9!J4:J43,"*대중교통*",구역9!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="42" t="n"/>
+      <c r="L12" s="42">
+        <f>IF(SUM(B12,D12,F12,H12,J12)=0,"",SUM(B12,D12,F12,H12,J12))</f>
+        <v/>
+      </c>
+      <c r="M12" s="83" t="n"/>
+      <c r="N12" s="81" t="n"/>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="33">
       <c r="A13" s="44" t="inlineStr">
@@ -14772,8 +14975,12 @@
         <f>IF(COUNTIFS(구역10!G4:G43,"대중교통",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!J4:J43,"*대중교통*",구역10!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역10!G4:G43,"대중교통",구역10!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역10!J4:J43,"*대중교통*",구역10!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L13" s="44" t="n"/>
-      <c r="M13" s="44" t="n"/>
+      <c r="L13" s="42">
+        <f>IF(SUM(B13,D13,F13,H13,J13)=0,"",SUM(B13,D13,F13,H13,J13))</f>
+        <v/>
+      </c>
+      <c r="M13" s="83" t="n"/>
+      <c r="N13" s="81" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="33">
       <c r="A14" s="61" t="inlineStr">
@@ -14821,8 +15028,12 @@
         <f>IF(COUNTIFS(구역11!G4:G43,"대중교통",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!J4:J43,"*대중교통*",구역11!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역11!G4:G43,"대중교통",구역11!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역11!J4:J43,"*대중교통*",구역11!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L14" s="61" t="n"/>
-      <c r="M14" s="61" t="n"/>
+      <c r="L14" s="42">
+        <f>IF(SUM(B14,D14,F14,H14,J14)=0,"",SUM(B14,D14,F14,H14,J14))</f>
+        <v/>
+      </c>
+      <c r="M14" s="84" t="n"/>
+      <c r="N14" s="81" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="32" t="inlineStr">
@@ -14870,8 +15081,12 @@
         <f>IF(COUNTIFS(구역12!G4:G43,"대중교통",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!J4:J43,"*대중교통*",구역12!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역12!G4:G43,"대중교통",구역12!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역12!J4:J43,"*대중교통*",구역12!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L15" s="32" t="n"/>
-      <c r="M15" s="32" t="n"/>
+      <c r="L15" s="42">
+        <f>IF(SUM(B15,D15,F15,H15,J15)=0,"",SUM(B15,D15,F15,H15,J15))</f>
+        <v/>
+      </c>
+      <c r="M15" s="85" t="n"/>
+      <c r="N15" s="81" t="n"/>
     </row>
     <row r="16" ht="19.4" customHeight="1" s="33">
       <c r="A16" s="62" t="inlineStr">
@@ -14919,8 +15134,12 @@
         <f>IF(COUNTIFS(구역13!G4:G43,"대중교통",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!J4:J43,"*대중교통*",구역13!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역13!G4:G43,"대중교통",구역13!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역13!J4:J43,"*대중교통*",구역13!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="L16" s="32" t="n"/>
-      <c r="M16" s="32" t="n"/>
+      <c r="L16" s="42">
+        <f>IF(SUM(B16,D16,F16,H16,J16)=0,"",SUM(B16,D16,F16,H16,J16))</f>
+        <v/>
+      </c>
+      <c r="M16" s="85" t="n"/>
+      <c r="N16" s="81" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="33">
       <c r="A17" s="49" t="inlineStr">
@@ -14968,6 +15187,12 @@
         <f>IF(COUNTIFS(구역14!G4:G43,"대중교통",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!J4:J43,"*대중교통*",구역14!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역14!G4:G43,"대중교통",구역14!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역14!J4:J43,"*대중교통*",구역14!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
+      <c r="L17" s="42">
+        <f>IF(SUM(B17,D17,F17,H17,J17)=0,"",SUM(B17,D17,F17,H17,J17))</f>
+        <v/>
+      </c>
+      <c r="M17" s="81" t="n"/>
+      <c r="N17" s="81" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="33">
       <c r="A18" s="49" t="inlineStr">
@@ -15015,6 +15240,12 @@
         <f>IF(COUNTIFS(구역15!G4:G43,"대중교통",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!J4:J43,"*대중교통*",구역15!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역15!G4:G43,"대중교통",구역15!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역15!J4:J43,"*대중교통*",구역15!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
+      <c r="L18" s="42">
+        <f>IF(SUM(B18,D18,F18,H18,J18)=0,"",SUM(B18,D18,F18,H18,J18))</f>
+        <v/>
+      </c>
+      <c r="M18" s="81" t="n"/>
+      <c r="N18" s="81" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
@@ -15062,6 +15293,12 @@
         <f>IF(COUNTIFS(구역16!G4:G43,"대중교통",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!J4:J43,"*대중교통*",구역16!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역16!G4:G43,"대중교통",구역16!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역16!J4:J43,"*대중교통*",구역16!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
+      <c r="L19" s="42">
+        <f>IF(SUM(B19,D19,F19,H19,J19)=0,"",SUM(B19,D19,F19,H19,J19))</f>
+        <v/>
+      </c>
+      <c r="M19" s="81" t="n"/>
+      <c r="N19" s="81" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
@@ -15109,6 +15346,12 @@
         <f>IF(COUNTIFS(구역17!G4:G43,"대중교통",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!J4:J43,"*대중교통*",구역17!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역17!G4:G43,"대중교통",구역17!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역17!J4:J43,"*대중교통*",구역17!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
+      <c r="L20" s="42">
+        <f>IF(SUM(B20,D20,F20,H20,J20)=0,"",SUM(B20,D20,F20,H20,J20))</f>
+        <v/>
+      </c>
+      <c r="M20" s="81" t="n"/>
+      <c r="N20" s="81" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="32" t="inlineStr">
@@ -15156,6 +15399,12 @@
         <f>IF(COUNTIFS(구역18!G4:G43,"대중교통",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!J4:J43,"*대중교통*",구역18!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역18!G4:G43,"대중교통",구역18!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역18!J4:J43,"*대중교통*",구역18!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
+      <c r="L21" s="42">
+        <f>IF(SUM(B21,D21,F21,H21,J21)=0,"",SUM(B21,D21,F21,H21,J21))</f>
+        <v/>
+      </c>
+      <c r="M21" s="81" t="n"/>
+      <c r="N21" s="81" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="32" t="inlineStr">
@@ -15203,6 +15452,12 @@
         <f>IF(COUNTIFS(구역19!G4:G43,"대중교통",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!J4:J43,"*대중교통*",구역19!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역19!G4:G43,"대중교통",구역19!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역19!J4:J43,"*대중교통*",구역19!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
+      <c r="L22" s="42">
+        <f>IF(SUM(B22,D22,F22,H22,J22)=0,"",SUM(B22,D22,F22,H22,J22))</f>
+        <v/>
+      </c>
+      <c r="M22" s="81" t="n"/>
+      <c r="N22" s="81" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="32" t="inlineStr">
@@ -15250,6 +15505,12 @@
         <f>IF(COUNTIFS(구역20!G4:G43,"대중교통",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!J4:J43,"*대중교통*",구역20!E4:E43,"*"&amp;$B31&amp;"*")=0,"",COUNTIFS(구역20!G4:G43,"대중교통",구역20!E4:E43,"*"&amp;$B31&amp;"*")+COUNTIFS(구역20!J4:J43,"*대중교통*",구역20!E4:E43,"*"&amp;$B31&amp;"*"))</f>
         <v/>
       </c>
+      <c r="L23" s="42">
+        <f>IF(SUM(B23,D23,F23,H23,J23)=0,"",SUM(B23,D23,F23,H23,J23))</f>
+        <v/>
+      </c>
+      <c r="M23" s="81" t="n"/>
+      <c r="N23" s="81" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="32" t="inlineStr">
@@ -15297,127 +15558,168 @@
         <f>IF(SUM(K4:K23)=0,"",SUM(K4:K23))</f>
         <v/>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="L24" s="32">
+        <f>IF(SUM(L4:L23)=0,"",SUM(L4:L23))</f>
+        <v/>
+      </c>
+      <c r="M24" s="81" t="n"/>
+      <c r="N24" s="81" t="n"/>
+    </row>
+    <row r="25">
+      <c r="M25" s="81" t="n"/>
+      <c r="N25" s="81" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" s="33">
+      <c r="A26" s="71" t="inlineStr">
         <is>
           <t>차수별 접수인원</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="M26" s="81" t="n"/>
+      <c r="N26" s="81" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1" s="33">
+      <c r="A27" s="72" t="inlineStr">
         <is>
           <t>차수</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" s="72" t="inlineStr">
         <is>
           <t>1차</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
+      <c r="C27" s="72" t="inlineStr">
         <is>
           <t>2차</t>
         </is>
       </c>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="D27" s="72" t="inlineStr">
         <is>
           <t>3차</t>
         </is>
       </c>
-      <c r="E27" s="32" t="inlineStr">
+      <c r="E27" s="72" t="inlineStr">
         <is>
           <t>4차</t>
         </is>
       </c>
-      <c r="F27" s="32" t="inlineStr">
+      <c r="F27" s="72" t="inlineStr">
         <is>
           <t>5차</t>
         </is>
       </c>
-      <c r="G27" s="32" t="inlineStr">
+      <c r="G27" s="72" t="inlineStr">
         <is>
           <t>6차</t>
         </is>
       </c>
-      <c r="H27" s="32" t="inlineStr">
+      <c r="H27" s="72" t="inlineStr">
         <is>
           <t>7차</t>
         </is>
       </c>
-      <c r="I27" s="32" t="inlineStr">
+      <c r="I27" s="72" t="inlineStr">
         <is>
           <t>8차</t>
         </is>
       </c>
-      <c r="J27" s="32" t="inlineStr">
+      <c r="J27" s="72" t="inlineStr">
         <is>
           <t>계</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="M27" s="81" t="n"/>
+      <c r="N27" s="81" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" s="33">
+      <c r="A28" s="72" t="inlineStr">
         <is>
           <t>접수인원</t>
         </is>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="73">
         <f>IF(COUNTIF(구역1!E4:E43,"*1차*")+COUNTIF(구역2!E4:E43,"*1차*")+COUNTIF(구역3!E4:E43,"*1차*")+COUNTIF(구역4!E4:E43,"*1차*")+COUNTIF(구역5!E4:E43,"*1차*")+COUNTIF(구역6!E4:E43,"*1차*")+COUNTIF(구역7!E4:E43,"*1차*")+COUNTIF(구역8!E4:E43,"*1차*")+COUNTIF(구역9!E4:E43,"*1차*")+COUNTIF(구역10!E4:E43,"*1차*")+COUNTIF(구역11!E4:E43,"*1차*")+COUNTIF(구역12!E4:E43,"*1차*")+COUNTIF(구역13!E4:E43,"*1차*")+COUNTIF(구역14!E4:E43,"*1차*")+COUNTIF(구역15!E4:E43,"*1차*")+COUNTIF(구역16!E4:E43,"*1차*")+COUNTIF(구역17!E4:E43,"*1차*")+COUNTIF(구역18!E4:E43,"*1차*")+COUNTIF(구역19!E4:E43,"*1차*")+COUNTIF(구역20!E4:E43,"*1차*")=0,"",COUNTIF(구역1!E4:E43,"*1차*")+COUNTIF(구역2!E4:E43,"*1차*")+COUNTIF(구역3!E4:E43,"*1차*")+COUNTIF(구역4!E4:E43,"*1차*")+COUNTIF(구역5!E4:E43,"*1차*")+COUNTIF(구역6!E4:E43,"*1차*")+COUNTIF(구역7!E4:E43,"*1차*")+COUNTIF(구역8!E4:E43,"*1차*")+COUNTIF(구역9!E4:E43,"*1차*")+COUNTIF(구역10!E4:E43,"*1차*")+COUNTIF(구역11!E4:E43,"*1차*")+COUNTIF(구역12!E4:E43,"*1차*")+COUNTIF(구역13!E4:E43,"*1차*")+COUNTIF(구역14!E4:E43,"*1차*")+COUNTIF(구역15!E4:E43,"*1차*")+COUNTIF(구역16!E4:E43,"*1차*")+COUNTIF(구역17!E4:E43,"*1차*")+COUNTIF(구역18!E4:E43,"*1차*")+COUNTIF(구역19!E4:E43,"*1차*")+COUNTIF(구역20!E4:E43,"*1차*"))</f>
         <v/>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="73">
         <f>IF(COUNTIF(구역1!E4:E43,"*2차*")+COUNTIF(구역2!E4:E43,"*2차*")+COUNTIF(구역3!E4:E43,"*2차*")+COUNTIF(구역4!E4:E43,"*2차*")+COUNTIF(구역5!E4:E43,"*2차*")+COUNTIF(구역6!E4:E43,"*2차*")+COUNTIF(구역7!E4:E43,"*2차*")+COUNTIF(구역8!E4:E43,"*2차*")+COUNTIF(구역9!E4:E43,"*2차*")+COUNTIF(구역10!E4:E43,"*2차*")+COUNTIF(구역11!E4:E43,"*2차*")+COUNTIF(구역12!E4:E43,"*2차*")+COUNTIF(구역13!E4:E43,"*2차*")+COUNTIF(구역14!E4:E43,"*2차*")+COUNTIF(구역15!E4:E43,"*2차*")+COUNTIF(구역16!E4:E43,"*2차*")+COUNTIF(구역17!E4:E43,"*2차*")+COUNTIF(구역18!E4:E43,"*2차*")+COUNTIF(구역19!E4:E43,"*2차*")+COUNTIF(구역20!E4:E43,"*2차*")=0,"",COUNTIF(구역1!E4:E43,"*2차*")+COUNTIF(구역2!E4:E43,"*2차*")+COUNTIF(구역3!E4:E43,"*2차*")+COUNTIF(구역4!E4:E43,"*2차*")+COUNTIF(구역5!E4:E43,"*2차*")+COUNTIF(구역6!E4:E43,"*2차*")+COUNTIF(구역7!E4:E43,"*2차*")+COUNTIF(구역8!E4:E43,"*2차*")+COUNTIF(구역9!E4:E43,"*2차*")+COUNTIF(구역10!E4:E43,"*2차*")+COUNTIF(구역11!E4:E43,"*2차*")+COUNTIF(구역12!E4:E43,"*2차*")+COUNTIF(구역13!E4:E43,"*2차*")+COUNTIF(구역14!E4:E43,"*2차*")+COUNTIF(구역15!E4:E43,"*2차*")+COUNTIF(구역16!E4:E43,"*2차*")+COUNTIF(구역17!E4:E43,"*2차*")+COUNTIF(구역18!E4:E43,"*2차*")+COUNTIF(구역19!E4:E43,"*2차*")+COUNTIF(구역20!E4:E43,"*2차*"))</f>
         <v/>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="73">
         <f>IF(COUNTIF(구역1!E4:E43,"*3차*")+COUNTIF(구역2!E4:E43,"*3차*")+COUNTIF(구역3!E4:E43,"*3차*")+COUNTIF(구역4!E4:E43,"*3차*")+COUNTIF(구역5!E4:E43,"*3차*")+COUNTIF(구역6!E4:E43,"*3차*")+COUNTIF(구역7!E4:E43,"*3차*")+COUNTIF(구역8!E4:E43,"*3차*")+COUNTIF(구역9!E4:E43,"*3차*")+COUNTIF(구역10!E4:E43,"*3차*")+COUNTIF(구역11!E4:E43,"*3차*")+COUNTIF(구역12!E4:E43,"*3차*")+COUNTIF(구역13!E4:E43,"*3차*")+COUNTIF(구역14!E4:E43,"*3차*")+COUNTIF(구역15!E4:E43,"*3차*")+COUNTIF(구역16!E4:E43,"*3차*")+COUNTIF(구역17!E4:E43,"*3차*")+COUNTIF(구역18!E4:E43,"*3차*")+COUNTIF(구역19!E4:E43,"*3차*")+COUNTIF(구역20!E4:E43,"*3차*")=0,"",COUNTIF(구역1!E4:E43,"*3차*")+COUNTIF(구역2!E4:E43,"*3차*")+COUNTIF(구역3!E4:E43,"*3차*")+COUNTIF(구역4!E4:E43,"*3차*")+COUNTIF(구역5!E4:E43,"*3차*")+COUNTIF(구역6!E4:E43,"*3차*")+COUNTIF(구역7!E4:E43,"*3차*")+COUNTIF(구역8!E4:E43,"*3차*")+COUNTIF(구역9!E4:E43,"*3차*")+COUNTIF(구역10!E4:E43,"*3차*")+COUNTIF(구역11!E4:E43,"*3차*")+COUNTIF(구역12!E4:E43,"*3차*")+COUNTIF(구역13!E4:E43,"*3차*")+COUNTIF(구역14!E4:E43,"*3차*")+COUNTIF(구역15!E4:E43,"*3차*")+COUNTIF(구역16!E4:E43,"*3차*")+COUNTIF(구역17!E4:E43,"*3차*")+COUNTIF(구역18!E4:E43,"*3차*")+COUNTIF(구역19!E4:E43,"*3차*")+COUNTIF(구역20!E4:E43,"*3차*"))</f>
         <v/>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="73">
         <f>IF(COUNTIF(구역1!E4:E43,"*4차*")+COUNTIF(구역2!E4:E43,"*4차*")+COUNTIF(구역3!E4:E43,"*4차*")+COUNTIF(구역4!E4:E43,"*4차*")+COUNTIF(구역5!E4:E43,"*4차*")+COUNTIF(구역6!E4:E43,"*4차*")+COUNTIF(구역7!E4:E43,"*4차*")+COUNTIF(구역8!E4:E43,"*4차*")+COUNTIF(구역9!E4:E43,"*4차*")+COUNTIF(구역10!E4:E43,"*4차*")+COUNTIF(구역11!E4:E43,"*4차*")+COUNTIF(구역12!E4:E43,"*4차*")+COUNTIF(구역13!E4:E43,"*4차*")+COUNTIF(구역14!E4:E43,"*4차*")+COUNTIF(구역15!E4:E43,"*4차*")+COUNTIF(구역16!E4:E43,"*4차*")+COUNTIF(구역17!E4:E43,"*4차*")+COUNTIF(구역18!E4:E43,"*4차*")+COUNTIF(구역19!E4:E43,"*4차*")+COUNTIF(구역20!E4:E43,"*4차*")=0,"",COUNTIF(구역1!E4:E43,"*4차*")+COUNTIF(구역2!E4:E43,"*4차*")+COUNTIF(구역3!E4:E43,"*4차*")+COUNTIF(구역4!E4:E43,"*4차*")+COUNTIF(구역5!E4:E43,"*4차*")+COUNTIF(구역6!E4:E43,"*4차*")+COUNTIF(구역7!E4:E43,"*4차*")+COUNTIF(구역8!E4:E43,"*4차*")+COUNTIF(구역9!E4:E43,"*4차*")+COUNTIF(구역10!E4:E43,"*4차*")+COUNTIF(구역11!E4:E43,"*4차*")+COUNTIF(구역12!E4:E43,"*4차*")+COUNTIF(구역13!E4:E43,"*4차*")+COUNTIF(구역14!E4:E43,"*4차*")+COUNTIF(구역15!E4:E43,"*4차*")+COUNTIF(구역16!E4:E43,"*4차*")+COUNTIF(구역17!E4:E43,"*4차*")+COUNTIF(구역18!E4:E43,"*4차*")+COUNTIF(구역19!E4:E43,"*4차*")+COUNTIF(구역20!E4:E43,"*4차*"))</f>
         <v/>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="73">
         <f>IF(COUNTIF(구역1!E4:E43,"*5차*")+COUNTIF(구역2!E4:E43,"*5차*")+COUNTIF(구역3!E4:E43,"*5차*")+COUNTIF(구역4!E4:E43,"*5차*")+COUNTIF(구역5!E4:E43,"*5차*")+COUNTIF(구역6!E4:E43,"*5차*")+COUNTIF(구역7!E4:E43,"*5차*")+COUNTIF(구역8!E4:E43,"*5차*")+COUNTIF(구역9!E4:E43,"*5차*")+COUNTIF(구역10!E4:E43,"*5차*")+COUNTIF(구역11!E4:E43,"*5차*")+COUNTIF(구역12!E4:E43,"*5차*")+COUNTIF(구역13!E4:E43,"*5차*")+COUNTIF(구역14!E4:E43,"*5차*")+COUNTIF(구역15!E4:E43,"*5차*")+COUNTIF(구역16!E4:E43,"*5차*")+COUNTIF(구역17!E4:E43,"*5차*")+COUNTIF(구역18!E4:E43,"*5차*")+COUNTIF(구역19!E4:E43,"*5차*")+COUNTIF(구역20!E4:E43,"*5차*")=0,"",COUNTIF(구역1!E4:E43,"*5차*")+COUNTIF(구역2!E4:E43,"*5차*")+COUNTIF(구역3!E4:E43,"*5차*")+COUNTIF(구역4!E4:E43,"*5차*")+COUNTIF(구역5!E4:E43,"*5차*")+COUNTIF(구역6!E4:E43,"*5차*")+COUNTIF(구역7!E4:E43,"*5차*")+COUNTIF(구역8!E4:E43,"*5차*")+COUNTIF(구역9!E4:E43,"*5차*")+COUNTIF(구역10!E4:E43,"*5차*")+COUNTIF(구역11!E4:E43,"*5차*")+COUNTIF(구역12!E4:E43,"*5차*")+COUNTIF(구역13!E4:E43,"*5차*")+COUNTIF(구역14!E4:E43,"*5차*")+COUNTIF(구역15!E4:E43,"*5차*")+COUNTIF(구역16!E4:E43,"*5차*")+COUNTIF(구역17!E4:E43,"*5차*")+COUNTIF(구역18!E4:E43,"*5차*")+COUNTIF(구역19!E4:E43,"*5차*")+COUNTIF(구역20!E4:E43,"*5차*"))</f>
         <v/>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="73">
         <f>IF(COUNTIF(구역1!E4:E43,"*6차*")+COUNTIF(구역2!E4:E43,"*6차*")+COUNTIF(구역3!E4:E43,"*6차*")+COUNTIF(구역4!E4:E43,"*6차*")+COUNTIF(구역5!E4:E43,"*6차*")+COUNTIF(구역6!E4:E43,"*6차*")+COUNTIF(구역7!E4:E43,"*6차*")+COUNTIF(구역8!E4:E43,"*6차*")+COUNTIF(구역9!E4:E43,"*6차*")+COUNTIF(구역10!E4:E43,"*6차*")+COUNTIF(구역11!E4:E43,"*6차*")+COUNTIF(구역12!E4:E43,"*6차*")+COUNTIF(구역13!E4:E43,"*6차*")+COUNTIF(구역14!E4:E43,"*6차*")+COUNTIF(구역15!E4:E43,"*6차*")+COUNTIF(구역16!E4:E43,"*6차*")+COUNTIF(구역17!E4:E43,"*6차*")+COUNTIF(구역18!E4:E43,"*6차*")+COUNTIF(구역19!E4:E43,"*6차*")+COUNTIF(구역20!E4:E43,"*6차*")=0,"",COUNTIF(구역1!E4:E43,"*6차*")+COUNTIF(구역2!E4:E43,"*6차*")+COUNTIF(구역3!E4:E43,"*6차*")+COUNTIF(구역4!E4:E43,"*6차*")+COUNTIF(구역5!E4:E43,"*6차*")+COUNTIF(구역6!E4:E43,"*6차*")+COUNTIF(구역7!E4:E43,"*6차*")+COUNTIF(구역8!E4:E43,"*6차*")+COUNTIF(구역9!E4:E43,"*6차*")+COUNTIF(구역10!E4:E43,"*6차*")+COUNTIF(구역11!E4:E43,"*6차*")+COUNTIF(구역12!E4:E43,"*6차*")+COUNTIF(구역13!E4:E43,"*6차*")+COUNTIF(구역14!E4:E43,"*6차*")+COUNTIF(구역15!E4:E43,"*6차*")+COUNTIF(구역16!E4:E43,"*6차*")+COUNTIF(구역17!E4:E43,"*6차*")+COUNTIF(구역18!E4:E43,"*6차*")+COUNTIF(구역19!E4:E43,"*6차*")+COUNTIF(구역20!E4:E43,"*6차*"))</f>
         <v/>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="73">
         <f>IF(COUNTIF(구역1!E4:E43,"*7차*")+COUNTIF(구역2!E4:E43,"*7차*")+COUNTIF(구역3!E4:E43,"*7차*")+COUNTIF(구역4!E4:E43,"*7차*")+COUNTIF(구역5!E4:E43,"*7차*")+COUNTIF(구역6!E4:E43,"*7차*")+COUNTIF(구역7!E4:E43,"*7차*")+COUNTIF(구역8!E4:E43,"*7차*")+COUNTIF(구역9!E4:E43,"*7차*")+COUNTIF(구역10!E4:E43,"*7차*")+COUNTIF(구역11!E4:E43,"*7차*")+COUNTIF(구역12!E4:E43,"*7차*")+COUNTIF(구역13!E4:E43,"*7차*")+COUNTIF(구역14!E4:E43,"*7차*")+COUNTIF(구역15!E4:E43,"*7차*")+COUNTIF(구역16!E4:E43,"*7차*")+COUNTIF(구역17!E4:E43,"*7차*")+COUNTIF(구역18!E4:E43,"*7차*")+COUNTIF(구역19!E4:E43,"*7차*")+COUNTIF(구역20!E4:E43,"*7차*")=0,"",COUNTIF(구역1!E4:E43,"*7차*")+COUNTIF(구역2!E4:E43,"*7차*")+COUNTIF(구역3!E4:E43,"*7차*")+COUNTIF(구역4!E4:E43,"*7차*")+COUNTIF(구역5!E4:E43,"*7차*")+COUNTIF(구역6!E4:E43,"*7차*")+COUNTIF(구역7!E4:E43,"*7차*")+COUNTIF(구역8!E4:E43,"*7차*")+COUNTIF(구역9!E4:E43,"*7차*")+COUNTIF(구역10!E4:E43,"*7차*")+COUNTIF(구역11!E4:E43,"*7차*")+COUNTIF(구역12!E4:E43,"*7차*")+COUNTIF(구역13!E4:E43,"*7차*")+COUNTIF(구역14!E4:E43,"*7차*")+COUNTIF(구역15!E4:E43,"*7차*")+COUNTIF(구역16!E4:E43,"*7차*")+COUNTIF(구역17!E4:E43,"*7차*")+COUNTIF(구역18!E4:E43,"*7차*")+COUNTIF(구역19!E4:E43,"*7차*")+COUNTIF(구역20!E4:E43,"*7차*"))</f>
         <v/>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="73">
         <f>IF(COUNTIF(구역1!E4:E43,"*8차*")+COUNTIF(구역2!E4:E43,"*8차*")+COUNTIF(구역3!E4:E43,"*8차*")+COUNTIF(구역4!E4:E43,"*8차*")+COUNTIF(구역5!E4:E43,"*8차*")+COUNTIF(구역6!E4:E43,"*8차*")+COUNTIF(구역7!E4:E43,"*8차*")+COUNTIF(구역8!E4:E43,"*8차*")+COUNTIF(구역9!E4:E43,"*8차*")+COUNTIF(구역10!E4:E43,"*8차*")+COUNTIF(구역11!E4:E43,"*8차*")+COUNTIF(구역12!E4:E43,"*8차*")+COUNTIF(구역13!E4:E43,"*8차*")+COUNTIF(구역14!E4:E43,"*8차*")+COUNTIF(구역15!E4:E43,"*8차*")+COUNTIF(구역16!E4:E43,"*8차*")+COUNTIF(구역17!E4:E43,"*8차*")+COUNTIF(구역18!E4:E43,"*8차*")+COUNTIF(구역19!E4:E43,"*8차*")+COUNTIF(구역20!E4:E43,"*8차*")=0,"",COUNTIF(구역1!E4:E43,"*8차*")+COUNTIF(구역2!E4:E43,"*8차*")+COUNTIF(구역3!E4:E43,"*8차*")+COUNTIF(구역4!E4:E43,"*8차*")+COUNTIF(구역5!E4:E43,"*8차*")+COUNTIF(구역6!E4:E43,"*8차*")+COUNTIF(구역7!E4:E43,"*8차*")+COUNTIF(구역8!E4:E43,"*8차*")+COUNTIF(구역9!E4:E43,"*8차*")+COUNTIF(구역10!E4:E43,"*8차*")+COUNTIF(구역11!E4:E43,"*8차*")+COUNTIF(구역12!E4:E43,"*8차*")+COUNTIF(구역13!E4:E43,"*8차*")+COUNTIF(구역14!E4:E43,"*8차*")+COUNTIF(구역15!E4:E43,"*8차*")+COUNTIF(구역16!E4:E43,"*8차*")+COUNTIF(구역17!E4:E43,"*8차*")+COUNTIF(구역18!E4:E43,"*8차*")+COUNTIF(구역19!E4:E43,"*8차*")+COUNTIF(구역20!E4:E43,"*8차*"))</f>
         <v/>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="73">
         <f>IF(SUM(B28:I28)=0,"",SUM(B28:I28))</f>
         <v/>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="M28" s="81" t="n"/>
+      <c r="N28" s="81" t="n"/>
+    </row>
+    <row r="29">
+      <c r="M29" s="81" t="n"/>
+      <c r="N29" s="81" t="n"/>
+    </row>
+    <row r="30">
+      <c r="M30" s="81" t="n"/>
+      <c r="N30" s="81" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1" s="33">
+      <c r="A31" s="74" t="inlineStr">
         <is>
           <t>적용 차수</t>
         </is>
       </c>
-      <c r="B31" s="32" t="inlineStr"/>
+      <c r="B31" s="75" t="inlineStr"/>
+      <c r="C31" s="77" t="n"/>
+      <c r="M31" s="81" t="n"/>
+      <c r="N31" s="81" t="n"/>
+    </row>
+    <row r="32">
+      <c r="M32" s="81" t="n"/>
+      <c r="N32" s="81" t="n"/>
+    </row>
+    <row r="33">
+      <c r="M33" s="81" t="n"/>
+      <c r="N33" s="81" t="n"/>
+    </row>
+    <row r="34">
+      <c r="M34" s="81" t="n"/>
+      <c r="N34" s="81" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="A26:L26"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A26:K26"/>
     <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="L2:L3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -15435,14 +15737,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="13" customWidth="1" style="32" min="5" max="5"/>
     <col width="12.61" customWidth="1" style="32" min="6" max="6"/>
     <col width="2" customWidth="1" style="32" min="7" max="7"/>
     <col width="4" customWidth="1" style="32" min="8" max="8"/>
-    <col width="5.51" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="9" customWidth="1" style="32" min="10" max="10"/>
     <col width="8" customWidth="1" style="32" min="11" max="11"/>
     <col width="13" customWidth="1" style="32" min="12" max="12"/>
@@ -16374,14 +16676,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="13" customWidth="1" style="32" min="5" max="5"/>
     <col width="12.61" customWidth="1" style="32" min="6" max="6"/>
     <col width="2" customWidth="1" style="32" min="7" max="7"/>
     <col width="4" customWidth="1" style="32" min="8" max="8"/>
-    <col width="5.51" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="9" customWidth="1" style="32" min="10" max="10"/>
     <col width="8" customWidth="1" style="32" min="11" max="11"/>
     <col width="13" customWidth="1" style="32" min="12" max="12"/>
@@ -17313,14 +17615,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="13" customWidth="1" style="32" min="5" max="5"/>
     <col width="12.61" customWidth="1" style="32" min="6" max="6"/>
     <col width="2" customWidth="1" style="32" min="7" max="7"/>
     <col width="4" customWidth="1" style="32" min="8" max="8"/>
-    <col width="5.51" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="9" customWidth="1" style="32" min="10" max="10"/>
     <col width="8" customWidth="1" style="32" min="11" max="11"/>
     <col width="13" customWidth="1" style="32" min="12" max="12"/>
@@ -18252,14 +18554,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="13" customWidth="1" style="32" min="5" max="5"/>
     <col width="12.61" customWidth="1" style="32" min="6" max="6"/>
     <col width="2" customWidth="1" style="32" min="7" max="7"/>
     <col width="4" customWidth="1" style="32" min="8" max="8"/>
-    <col width="5.51" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="9" customWidth="1" style="32" min="10" max="10"/>
     <col width="8" customWidth="1" style="32" min="11" max="11"/>
     <col width="13" customWidth="1" style="32" min="12" max="12"/>
@@ -19191,14 +19493,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="13" customWidth="1" style="32" min="5" max="5"/>
     <col width="12.61" customWidth="1" style="32" min="6" max="6"/>
     <col width="2" customWidth="1" style="32" min="7" max="7"/>
     <col width="4" customWidth="1" style="32" min="8" max="8"/>
-    <col width="5.51" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="9" customWidth="1" style="32" min="10" max="10"/>
     <col width="8" customWidth="1" style="32" min="11" max="11"/>
     <col width="13" customWidth="1" style="32" min="12" max="12"/>
@@ -20130,17 +20432,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -20201,9 +20505,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -20978,14 +21282,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="13" customWidth="1" style="32" min="5" max="5"/>
     <col width="12.61" customWidth="1" style="32" min="6" max="6"/>
     <col width="2" customWidth="1" style="32" min="7" max="7"/>
     <col width="4" customWidth="1" style="32" min="8" max="8"/>
-    <col width="5.51" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="9" customWidth="1" style="32" min="10" max="10"/>
     <col width="8" customWidth="1" style="32" min="11" max="11"/>
     <col width="13" customWidth="1" style="32" min="12" max="12"/>
@@ -21917,14 +22221,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="13" customWidth="1" style="32" min="5" max="5"/>
     <col width="12.61" customWidth="1" style="32" min="6" max="6"/>
     <col width="2" customWidth="1" style="32" min="7" max="7"/>
     <col width="4" customWidth="1" style="32" min="8" max="8"/>
-    <col width="5.51" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="9" customWidth="1" style="32" min="10" max="10"/>
     <col width="8" customWidth="1" style="32" min="11" max="11"/>
     <col width="13" customWidth="1" style="32" min="12" max="12"/>
@@ -22856,14 +23160,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="13" customWidth="1" style="32" min="5" max="5"/>
     <col width="12.61" customWidth="1" style="32" min="6" max="6"/>
     <col width="2" customWidth="1" style="32" min="7" max="7"/>
     <col width="4" customWidth="1" style="32" min="8" max="8"/>
-    <col width="5.51" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="9" customWidth="1" style="32" min="10" max="10"/>
     <col width="8" customWidth="1" style="32" min="11" max="11"/>
     <col width="13" customWidth="1" style="32" min="12" max="12"/>
@@ -23795,14 +24099,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="13" customWidth="1" style="32" min="5" max="5"/>
     <col width="12.61" customWidth="1" style="32" min="6" max="6"/>
     <col width="2" customWidth="1" style="32" min="7" max="7"/>
     <col width="4" customWidth="1" style="32" min="8" max="8"/>
-    <col width="5.51" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="9" customWidth="1" style="32" min="10" max="10"/>
     <col width="8" customWidth="1" style="32" min="11" max="11"/>
     <col width="13" customWidth="1" style="32" min="12" max="12"/>
@@ -24734,14 +25038,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="13" customWidth="1" style="32" min="5" max="5"/>
     <col width="12.61" customWidth="1" style="32" min="6" max="6"/>
     <col width="2" customWidth="1" style="32" min="7" max="7"/>
     <col width="4" customWidth="1" style="32" min="8" max="8"/>
-    <col width="5.51" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="9" customWidth="1" style="32" min="10" max="10"/>
     <col width="8" customWidth="1" style="32" min="11" max="11"/>
     <col width="13" customWidth="1" style="32" min="12" max="12"/>
@@ -25673,14 +25977,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="14.6" customWidth="1" style="32" min="5" max="5"/>
     <col width="2" customWidth="1" style="32" min="6" max="6"/>
     <col width="4" customWidth="1" style="32" min="7" max="7"/>
     <col width="5.51" customWidth="1" style="32" min="8" max="8"/>
-    <col width="9" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="8" customWidth="1" style="32" min="10" max="10"/>
     <col width="14.6" customWidth="1" style="32" min="11" max="11"/>
   </cols>
@@ -28874,14 +29178,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="14.6" customWidth="1" style="32" min="5" max="5"/>
     <col width="2" customWidth="1" style="32" min="6" max="6"/>
     <col width="4" customWidth="1" style="32" min="7" max="7"/>
     <col width="5.51" customWidth="1" style="32" min="8" max="8"/>
-    <col width="9" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="8" customWidth="1" style="32" min="10" max="10"/>
     <col width="14.6" customWidth="1" style="32" min="11" max="11"/>
   </cols>
@@ -34395,14 +34699,14 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5.51" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
     <col width="14.6" customWidth="1" style="32" min="5" max="5"/>
     <col width="2" customWidth="1" style="32" min="6" max="6"/>
     <col width="4" customWidth="1" style="32" min="7" max="7"/>
     <col width="5.51" customWidth="1" style="32" min="8" max="8"/>
-    <col width="9" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="9" max="9"/>
     <col width="8" customWidth="1" style="32" min="10" max="10"/>
     <col width="14.6" customWidth="1" style="32" min="11" max="11"/>
   </cols>
@@ -35694,17 +35998,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -35765,9 +36071,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -36542,17 +36848,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -36613,9 +36921,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -37390,17 +37698,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -37461,9 +37771,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -38238,17 +38548,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -38309,9 +38621,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -39086,17 +39398,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -39157,9 +39471,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>
@@ -39934,17 +40248,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.5" customWidth="1" style="32" min="1" max="1"/>
-    <col width="5" customWidth="1" style="32" min="2" max="2"/>
+    <col width="7" customWidth="1" style="32" min="2" max="2"/>
     <col width="9" customWidth="1" style="32" min="3" max="3"/>
     <col width="8" customWidth="1" style="32" min="4" max="4"/>
-    <col width="5.51" customWidth="1" style="32" min="5" max="5"/>
-    <col width="7.5" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13" customWidth="1" style="32" min="7" max="9"/>
-    <col width="6" customWidth="1" style="32" min="10" max="10"/>
-    <col width="13" customWidth="1" style="32" min="11" max="11"/>
+    <col width="8.5" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8" customWidth="1" style="32" min="7" max="9"/>
+    <col width="8" customWidth="1" style="33" min="8" max="8"/>
+    <col width="9" customWidth="1" style="33" min="9" max="9"/>
+    <col width="8" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="32" min="11" max="11"/>
     <col width="8" customWidth="1" style="32" min="12" max="12"/>
     <col width="6" customWidth="1" style="32" min="13" max="13"/>
-    <col width="9" customWidth="1" style="32" min="14" max="14"/>
+    <col width="13" customWidth="1" style="32" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="33">
@@ -40005,9 +40321,9 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
+      <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="38" t="inlineStr">
         <is>
           <t>인 도 자</t>

--- a/수양회_서식_template.xlsx
+++ b/수양회_서식_template.xlsx
@@ -53,7 +53,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -224,6 +224,12 @@
       <b val="1"/>
       <color rgb="FF1F4E79"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -464,7 +470,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -704,6 +710,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -15512,53 +15521,53 @@
       <c r="M23" s="81" t="n"/>
       <c r="N23" s="81" t="n"/>
     </row>
-    <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+    <row r="24" ht="20" customHeight="1" s="33">
+      <c r="A24" s="86" t="inlineStr">
         <is>
           <t>합  계</t>
         </is>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="86">
         <f>IF(SUM(B4:B23)=0,"",SUM(B4:B23))</f>
         <v/>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="86">
         <f>IF(SUM(C4:C23)=0,"",SUM(C4:C23))</f>
         <v/>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="86">
         <f>IF(SUM(D4:D23)=0,"",SUM(D4:D23))</f>
         <v/>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="86">
         <f>IF(SUM(E4:E23)=0,"",SUM(E4:E23))</f>
         <v/>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="86">
         <f>IF(SUM(F4:F23)=0,"",SUM(F4:F23))</f>
         <v/>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="86">
         <f>IF(SUM(G4:G23)=0,"",SUM(G4:G23))</f>
         <v/>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="86">
         <f>IF(SUM(H4:H23)=0,"",SUM(H4:H23))</f>
         <v/>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="86">
         <f>IF(SUM(I4:I23)=0,"",SUM(I4:I23))</f>
         <v/>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="86">
         <f>IF(SUM(J4:J23)=0,"",SUM(J4:J23))</f>
         <v/>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="86">
         <f>IF(SUM(K4:K23)=0,"",SUM(K4:K23))</f>
         <v/>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="86">
         <f>IF(SUM(L4:L23)=0,"",SUM(L4:L23))</f>
         <v/>
       </c>
@@ -25983,8 +25992,8 @@
     <col width="14.6" customWidth="1" style="32" min="5" max="5"/>
     <col width="2" customWidth="1" style="32" min="6" max="6"/>
     <col width="4" customWidth="1" style="32" min="7" max="7"/>
-    <col width="5.51" customWidth="1" style="32" min="8" max="8"/>
-    <col width="7" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="8" max="8"/>
+    <col width="9" customWidth="1" style="32" min="9" max="9"/>
     <col width="8" customWidth="1" style="32" min="10" max="10"/>
     <col width="14.6" customWidth="1" style="32" min="11" max="11"/>
   </cols>
@@ -29184,8 +29193,8 @@
     <col width="14.6" customWidth="1" style="32" min="5" max="5"/>
     <col width="2" customWidth="1" style="32" min="6" max="6"/>
     <col width="4" customWidth="1" style="32" min="7" max="7"/>
-    <col width="5.51" customWidth="1" style="32" min="8" max="8"/>
-    <col width="7" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="8" max="8"/>
+    <col width="9" customWidth="1" style="32" min="9" max="9"/>
     <col width="8" customWidth="1" style="32" min="10" max="10"/>
     <col width="14.6" customWidth="1" style="32" min="11" max="11"/>
   </cols>
@@ -34705,8 +34714,8 @@
     <col width="14.6" customWidth="1" style="32" min="5" max="5"/>
     <col width="2" customWidth="1" style="32" min="6" max="6"/>
     <col width="4" customWidth="1" style="32" min="7" max="7"/>
-    <col width="5.51" customWidth="1" style="32" min="8" max="8"/>
-    <col width="7" customWidth="1" style="32" min="9" max="9"/>
+    <col width="7" customWidth="1" style="32" min="8" max="8"/>
+    <col width="9" customWidth="1" style="32" min="9" max="9"/>
     <col width="8" customWidth="1" style="32" min="10" max="10"/>
     <col width="14.6" customWidth="1" style="32" min="11" max="11"/>
   </cols>

--- a/수양회_서식_template.xlsx
+++ b/수양회_서식_template.xlsx
@@ -22029,12 +22029,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
+      <c r="C2" s="35" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -22996,12 +22998,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
+      <c r="C2" s="35" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -23963,12 +23967,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
+      <c r="C2" s="35" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -24930,12 +24936,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
+      <c r="C2" s="35" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -25897,12 +25905,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
+      <c r="C2" s="35" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -28194,12 +28204,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
+      <c r="C2" s="35" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -29161,12 +29173,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
+      <c r="C2" s="35" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -30128,12 +30142,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
+      <c r="C2" s="35" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -31095,12 +31111,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
+      <c r="C2" s="35" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -32062,12 +32080,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
+      <c r="C2" s="35" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
+      <c r="J2" s="35" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">

--- a/수양회_서식_template.xlsx
+++ b/수양회_서식_template.xlsx
@@ -470,7 +470,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -712,6 +712,9 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -18866,7 +18869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I203"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
@@ -19327,16 +19330,1831 @@
       <c r="H37" s="42" t="n"/>
       <c r="I37" s="42" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1" s="33">
-      <c r="A38" s="45" t="n"/>
-      <c r="B38" s="32" t="n"/>
-      <c r="C38" s="32" t="n"/>
-      <c r="D38" s="32" t="n"/>
-      <c r="E38" s="32" t="n"/>
-      <c r="F38" s="32" t="n"/>
-      <c r="G38" s="46" t="n"/>
-      <c r="H38" s="46" t="n"/>
-      <c r="I38" s="46" t="n"/>
+    <row r="38" ht="19.5" customHeight="1" s="33">
+      <c r="A38" s="43" t="n"/>
+      <c r="B38" s="44" t="n"/>
+      <c r="C38" s="44" t="n"/>
+      <c r="D38" s="44" t="n"/>
+      <c r="E38" s="44" t="n"/>
+      <c r="F38" s="44" t="n"/>
+      <c r="G38" s="44" t="n"/>
+      <c r="H38" s="44" t="n"/>
+      <c r="I38" s="44" t="n"/>
+    </row>
+    <row r="39" ht="19.5" customHeight="1" s="33">
+      <c r="A39" s="41" t="n"/>
+      <c r="B39" s="42" t="n"/>
+      <c r="C39" s="42" t="n"/>
+      <c r="D39" s="42" t="n"/>
+      <c r="E39" s="42" t="n"/>
+      <c r="F39" s="42" t="n"/>
+      <c r="G39" s="42" t="n"/>
+      <c r="H39" s="42" t="n"/>
+      <c r="I39" s="42" t="n"/>
+    </row>
+    <row r="40" ht="19.5" customHeight="1" s="33">
+      <c r="A40" s="43" t="n"/>
+      <c r="B40" s="44" t="n"/>
+      <c r="C40" s="44" t="n"/>
+      <c r="D40" s="44" t="n"/>
+      <c r="E40" s="44" t="n"/>
+      <c r="F40" s="44" t="n"/>
+      <c r="G40" s="44" t="n"/>
+      <c r="H40" s="44" t="n"/>
+      <c r="I40" s="44" t="n"/>
+    </row>
+    <row r="41" ht="19.5" customHeight="1" s="33">
+      <c r="A41" s="41" t="n"/>
+      <c r="B41" s="42" t="n"/>
+      <c r="C41" s="42" t="n"/>
+      <c r="D41" s="42" t="n"/>
+      <c r="E41" s="42" t="n"/>
+      <c r="F41" s="42" t="n"/>
+      <c r="G41" s="42" t="n"/>
+      <c r="H41" s="42" t="n"/>
+      <c r="I41" s="42" t="n"/>
+    </row>
+    <row r="42" ht="19.5" customHeight="1" s="33">
+      <c r="A42" s="43" t="n"/>
+      <c r="B42" s="44" t="n"/>
+      <c r="C42" s="44" t="n"/>
+      <c r="D42" s="44" t="n"/>
+      <c r="E42" s="44" t="n"/>
+      <c r="F42" s="44" t="n"/>
+      <c r="G42" s="44" t="n"/>
+      <c r="H42" s="44" t="n"/>
+      <c r="I42" s="44" t="n"/>
+    </row>
+    <row r="43" ht="19.5" customHeight="1" s="33">
+      <c r="A43" s="41" t="n"/>
+      <c r="B43" s="42" t="n"/>
+      <c r="C43" s="42" t="n"/>
+      <c r="D43" s="42" t="n"/>
+      <c r="E43" s="42" t="n"/>
+      <c r="F43" s="42" t="n"/>
+      <c r="G43" s="42" t="n"/>
+      <c r="H43" s="42" t="n"/>
+      <c r="I43" s="42" t="n"/>
+    </row>
+    <row r="44" ht="19.5" customHeight="1" s="33">
+      <c r="A44" s="43" t="n"/>
+      <c r="B44" s="44" t="n"/>
+      <c r="C44" s="44" t="n"/>
+      <c r="D44" s="44" t="n"/>
+      <c r="E44" s="44" t="n"/>
+      <c r="F44" s="44" t="n"/>
+      <c r="G44" s="44" t="n"/>
+      <c r="H44" s="44" t="n"/>
+      <c r="I44" s="44" t="n"/>
+    </row>
+    <row r="45" ht="19.5" customHeight="1" s="33">
+      <c r="A45" s="41" t="n"/>
+      <c r="B45" s="42" t="n"/>
+      <c r="C45" s="42" t="n"/>
+      <c r="D45" s="42" t="n"/>
+      <c r="E45" s="42" t="n"/>
+      <c r="F45" s="42" t="n"/>
+      <c r="G45" s="42" t="n"/>
+      <c r="H45" s="42" t="n"/>
+      <c r="I45" s="42" t="n"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="1" s="33">
+      <c r="A46" s="43" t="n"/>
+      <c r="B46" s="44" t="n"/>
+      <c r="C46" s="44" t="n"/>
+      <c r="D46" s="44" t="n"/>
+      <c r="E46" s="44" t="n"/>
+      <c r="F46" s="44" t="n"/>
+      <c r="G46" s="44" t="n"/>
+      <c r="H46" s="44" t="n"/>
+      <c r="I46" s="44" t="n"/>
+    </row>
+    <row r="47" ht="19.5" customHeight="1" s="33">
+      <c r="A47" s="41" t="n"/>
+      <c r="B47" s="42" t="n"/>
+      <c r="C47" s="42" t="n"/>
+      <c r="D47" s="42" t="n"/>
+      <c r="E47" s="42" t="n"/>
+      <c r="F47" s="42" t="n"/>
+      <c r="G47" s="42" t="n"/>
+      <c r="H47" s="42" t="n"/>
+      <c r="I47" s="42" t="n"/>
+    </row>
+    <row r="48" ht="19.5" customHeight="1" s="33">
+      <c r="A48" s="43" t="n"/>
+      <c r="B48" s="44" t="n"/>
+      <c r="C48" s="44" t="n"/>
+      <c r="D48" s="44" t="n"/>
+      <c r="E48" s="44" t="n"/>
+      <c r="F48" s="44" t="n"/>
+      <c r="G48" s="44" t="n"/>
+      <c r="H48" s="44" t="n"/>
+      <c r="I48" s="44" t="n"/>
+    </row>
+    <row r="49" ht="19.5" customHeight="1" s="33">
+      <c r="A49" s="41" t="n"/>
+      <c r="B49" s="42" t="n"/>
+      <c r="C49" s="42" t="n"/>
+      <c r="D49" s="42" t="n"/>
+      <c r="E49" s="42" t="n"/>
+      <c r="F49" s="42" t="n"/>
+      <c r="G49" s="42" t="n"/>
+      <c r="H49" s="42" t="n"/>
+      <c r="I49" s="42" t="n"/>
+    </row>
+    <row r="50" ht="19.5" customHeight="1" s="33">
+      <c r="A50" s="43" t="n"/>
+      <c r="B50" s="44" t="n"/>
+      <c r="C50" s="44" t="n"/>
+      <c r="D50" s="44" t="n"/>
+      <c r="E50" s="44" t="n"/>
+      <c r="F50" s="44" t="n"/>
+      <c r="G50" s="44" t="n"/>
+      <c r="H50" s="44" t="n"/>
+      <c r="I50" s="44" t="n"/>
+    </row>
+    <row r="51" ht="19.5" customHeight="1" s="33">
+      <c r="A51" s="41" t="n"/>
+      <c r="B51" s="42" t="n"/>
+      <c r="C51" s="42" t="n"/>
+      <c r="D51" s="42" t="n"/>
+      <c r="E51" s="42" t="n"/>
+      <c r="F51" s="42" t="n"/>
+      <c r="G51" s="42" t="n"/>
+      <c r="H51" s="42" t="n"/>
+      <c r="I51" s="42" t="n"/>
+    </row>
+    <row r="52" ht="19.5" customHeight="1" s="33">
+      <c r="A52" s="43" t="n"/>
+      <c r="B52" s="44" t="n"/>
+      <c r="C52" s="44" t="n"/>
+      <c r="D52" s="44" t="n"/>
+      <c r="E52" s="44" t="n"/>
+      <c r="F52" s="44" t="n"/>
+      <c r="G52" s="44" t="n"/>
+      <c r="H52" s="44" t="n"/>
+      <c r="I52" s="44" t="n"/>
+    </row>
+    <row r="53" ht="19.5" customHeight="1" s="33">
+      <c r="A53" s="41" t="n"/>
+      <c r="B53" s="42" t="n"/>
+      <c r="C53" s="42" t="n"/>
+      <c r="D53" s="42" t="n"/>
+      <c r="E53" s="42" t="n"/>
+      <c r="F53" s="42" t="n"/>
+      <c r="G53" s="42" t="n"/>
+      <c r="H53" s="42" t="n"/>
+      <c r="I53" s="42" t="n"/>
+    </row>
+    <row r="54" ht="19.5" customHeight="1" s="33">
+      <c r="A54" s="43" t="n"/>
+      <c r="B54" s="44" t="n"/>
+      <c r="C54" s="44" t="n"/>
+      <c r="D54" s="44" t="n"/>
+      <c r="E54" s="44" t="n"/>
+      <c r="F54" s="44" t="n"/>
+      <c r="G54" s="44" t="n"/>
+      <c r="H54" s="44" t="n"/>
+      <c r="I54" s="44" t="n"/>
+    </row>
+    <row r="55" ht="19.5" customHeight="1" s="33">
+      <c r="A55" s="41" t="n"/>
+      <c r="B55" s="42" t="n"/>
+      <c r="C55" s="42" t="n"/>
+      <c r="D55" s="42" t="n"/>
+      <c r="E55" s="42" t="n"/>
+      <c r="F55" s="42" t="n"/>
+      <c r="G55" s="42" t="n"/>
+      <c r="H55" s="42" t="n"/>
+      <c r="I55" s="42" t="n"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="1" s="33">
+      <c r="A56" s="43" t="n"/>
+      <c r="B56" s="44" t="n"/>
+      <c r="C56" s="44" t="n"/>
+      <c r="D56" s="44" t="n"/>
+      <c r="E56" s="44" t="n"/>
+      <c r="F56" s="44" t="n"/>
+      <c r="G56" s="44" t="n"/>
+      <c r="H56" s="44" t="n"/>
+      <c r="I56" s="44" t="n"/>
+    </row>
+    <row r="57" ht="19.5" customHeight="1" s="33">
+      <c r="A57" s="41" t="n"/>
+      <c r="B57" s="42" t="n"/>
+      <c r="C57" s="42" t="n"/>
+      <c r="D57" s="42" t="n"/>
+      <c r="E57" s="42" t="n"/>
+      <c r="F57" s="42" t="n"/>
+      <c r="G57" s="42" t="n"/>
+      <c r="H57" s="42" t="n"/>
+      <c r="I57" s="42" t="n"/>
+    </row>
+    <row r="58" ht="19.5" customHeight="1" s="33">
+      <c r="A58" s="43" t="n"/>
+      <c r="B58" s="44" t="n"/>
+      <c r="C58" s="44" t="n"/>
+      <c r="D58" s="44" t="n"/>
+      <c r="E58" s="44" t="n"/>
+      <c r="F58" s="44" t="n"/>
+      <c r="G58" s="44" t="n"/>
+      <c r="H58" s="44" t="n"/>
+      <c r="I58" s="44" t="n"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1" s="33">
+      <c r="A59" s="41" t="n"/>
+      <c r="B59" s="42" t="n"/>
+      <c r="C59" s="42" t="n"/>
+      <c r="D59" s="42" t="n"/>
+      <c r="E59" s="42" t="n"/>
+      <c r="F59" s="42" t="n"/>
+      <c r="G59" s="42" t="n"/>
+      <c r="H59" s="42" t="n"/>
+      <c r="I59" s="42" t="n"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="1" s="33">
+      <c r="A60" s="43" t="n"/>
+      <c r="B60" s="44" t="n"/>
+      <c r="C60" s="44" t="n"/>
+      <c r="D60" s="44" t="n"/>
+      <c r="E60" s="44" t="n"/>
+      <c r="F60" s="44" t="n"/>
+      <c r="G60" s="44" t="n"/>
+      <c r="H60" s="44" t="n"/>
+      <c r="I60" s="44" t="n"/>
+    </row>
+    <row r="61" ht="19.5" customHeight="1" s="33">
+      <c r="A61" s="41" t="n"/>
+      <c r="B61" s="42" t="n"/>
+      <c r="C61" s="42" t="n"/>
+      <c r="D61" s="42" t="n"/>
+      <c r="E61" s="42" t="n"/>
+      <c r="F61" s="42" t="n"/>
+      <c r="G61" s="42" t="n"/>
+      <c r="H61" s="42" t="n"/>
+      <c r="I61" s="42" t="n"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1" s="33">
+      <c r="A62" s="43" t="n"/>
+      <c r="B62" s="44" t="n"/>
+      <c r="C62" s="44" t="n"/>
+      <c r="D62" s="44" t="n"/>
+      <c r="E62" s="44" t="n"/>
+      <c r="F62" s="44" t="n"/>
+      <c r="G62" s="44" t="n"/>
+      <c r="H62" s="44" t="n"/>
+      <c r="I62" s="44" t="n"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1" s="33">
+      <c r="A63" s="41" t="n"/>
+      <c r="B63" s="42" t="n"/>
+      <c r="C63" s="42" t="n"/>
+      <c r="D63" s="42" t="n"/>
+      <c r="E63" s="42" t="n"/>
+      <c r="F63" s="42" t="n"/>
+      <c r="G63" s="42" t="n"/>
+      <c r="H63" s="42" t="n"/>
+      <c r="I63" s="42" t="n"/>
+    </row>
+    <row r="64" ht="19.5" customHeight="1" s="33">
+      <c r="A64" s="43" t="n"/>
+      <c r="B64" s="44" t="n"/>
+      <c r="C64" s="44" t="n"/>
+      <c r="D64" s="44" t="n"/>
+      <c r="E64" s="44" t="n"/>
+      <c r="F64" s="44" t="n"/>
+      <c r="G64" s="44" t="n"/>
+      <c r="H64" s="44" t="n"/>
+      <c r="I64" s="44" t="n"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="1" s="33">
+      <c r="A65" s="41" t="n"/>
+      <c r="B65" s="42" t="n"/>
+      <c r="C65" s="42" t="n"/>
+      <c r="D65" s="42" t="n"/>
+      <c r="E65" s="42" t="n"/>
+      <c r="F65" s="42" t="n"/>
+      <c r="G65" s="42" t="n"/>
+      <c r="H65" s="42" t="n"/>
+      <c r="I65" s="42" t="n"/>
+    </row>
+    <row r="66" ht="19.5" customHeight="1" s="33">
+      <c r="A66" s="43" t="n"/>
+      <c r="B66" s="44" t="n"/>
+      <c r="C66" s="44" t="n"/>
+      <c r="D66" s="44" t="n"/>
+      <c r="E66" s="44" t="n"/>
+      <c r="F66" s="44" t="n"/>
+      <c r="G66" s="44" t="n"/>
+      <c r="H66" s="44" t="n"/>
+      <c r="I66" s="44" t="n"/>
+    </row>
+    <row r="67" ht="19.5" customHeight="1" s="33">
+      <c r="A67" s="41" t="n"/>
+      <c r="B67" s="42" t="n"/>
+      <c r="C67" s="42" t="n"/>
+      <c r="D67" s="42" t="n"/>
+      <c r="E67" s="42" t="n"/>
+      <c r="F67" s="42" t="n"/>
+      <c r="G67" s="42" t="n"/>
+      <c r="H67" s="42" t="n"/>
+      <c r="I67" s="42" t="n"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="1" s="33">
+      <c r="A68" s="43" t="n"/>
+      <c r="B68" s="44" t="n"/>
+      <c r="C68" s="44" t="n"/>
+      <c r="D68" s="44" t="n"/>
+      <c r="E68" s="44" t="n"/>
+      <c r="F68" s="44" t="n"/>
+      <c r="G68" s="44" t="n"/>
+      <c r="H68" s="44" t="n"/>
+      <c r="I68" s="44" t="n"/>
+    </row>
+    <row r="69" ht="19.5" customHeight="1" s="33">
+      <c r="A69" s="41" t="n"/>
+      <c r="B69" s="42" t="n"/>
+      <c r="C69" s="42" t="n"/>
+      <c r="D69" s="42" t="n"/>
+      <c r="E69" s="42" t="n"/>
+      <c r="F69" s="42" t="n"/>
+      <c r="G69" s="42" t="n"/>
+      <c r="H69" s="42" t="n"/>
+      <c r="I69" s="42" t="n"/>
+    </row>
+    <row r="70" ht="19.5" customHeight="1" s="33">
+      <c r="A70" s="43" t="n"/>
+      <c r="B70" s="44" t="n"/>
+      <c r="C70" s="44" t="n"/>
+      <c r="D70" s="44" t="n"/>
+      <c r="E70" s="44" t="n"/>
+      <c r="F70" s="44" t="n"/>
+      <c r="G70" s="44" t="n"/>
+      <c r="H70" s="44" t="n"/>
+      <c r="I70" s="44" t="n"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="1" s="33">
+      <c r="A71" s="41" t="n"/>
+      <c r="B71" s="42" t="n"/>
+      <c r="C71" s="42" t="n"/>
+      <c r="D71" s="42" t="n"/>
+      <c r="E71" s="42" t="n"/>
+      <c r="F71" s="42" t="n"/>
+      <c r="G71" s="42" t="n"/>
+      <c r="H71" s="42" t="n"/>
+      <c r="I71" s="42" t="n"/>
+    </row>
+    <row r="72" ht="19.5" customHeight="1" s="33">
+      <c r="A72" s="43" t="n"/>
+      <c r="B72" s="44" t="n"/>
+      <c r="C72" s="44" t="n"/>
+      <c r="D72" s="44" t="n"/>
+      <c r="E72" s="44" t="n"/>
+      <c r="F72" s="44" t="n"/>
+      <c r="G72" s="44" t="n"/>
+      <c r="H72" s="44" t="n"/>
+      <c r="I72" s="44" t="n"/>
+    </row>
+    <row r="73" ht="19.5" customHeight="1" s="33">
+      <c r="A73" s="41" t="n"/>
+      <c r="B73" s="42" t="n"/>
+      <c r="C73" s="42" t="n"/>
+      <c r="D73" s="42" t="n"/>
+      <c r="E73" s="42" t="n"/>
+      <c r="F73" s="42" t="n"/>
+      <c r="G73" s="42" t="n"/>
+      <c r="H73" s="42" t="n"/>
+      <c r="I73" s="42" t="n"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1" s="33">
+      <c r="A74" s="43" t="n"/>
+      <c r="B74" s="44" t="n"/>
+      <c r="C74" s="44" t="n"/>
+      <c r="D74" s="44" t="n"/>
+      <c r="E74" s="44" t="n"/>
+      <c r="F74" s="44" t="n"/>
+      <c r="G74" s="44" t="n"/>
+      <c r="H74" s="44" t="n"/>
+      <c r="I74" s="44" t="n"/>
+    </row>
+    <row r="75" ht="19.5" customHeight="1" s="33">
+      <c r="A75" s="41" t="n"/>
+      <c r="B75" s="42" t="n"/>
+      <c r="C75" s="42" t="n"/>
+      <c r="D75" s="42" t="n"/>
+      <c r="E75" s="42" t="n"/>
+      <c r="F75" s="42" t="n"/>
+      <c r="G75" s="42" t="n"/>
+      <c r="H75" s="42" t="n"/>
+      <c r="I75" s="42" t="n"/>
+    </row>
+    <row r="76" ht="19.5" customHeight="1" s="33">
+      <c r="A76" s="43" t="n"/>
+      <c r="B76" s="44" t="n"/>
+      <c r="C76" s="44" t="n"/>
+      <c r="D76" s="44" t="n"/>
+      <c r="E76" s="44" t="n"/>
+      <c r="F76" s="44" t="n"/>
+      <c r="G76" s="44" t="n"/>
+      <c r="H76" s="44" t="n"/>
+      <c r="I76" s="44" t="n"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="1" s="33">
+      <c r="A77" s="41" t="n"/>
+      <c r="B77" s="42" t="n"/>
+      <c r="C77" s="42" t="n"/>
+      <c r="D77" s="42" t="n"/>
+      <c r="E77" s="42" t="n"/>
+      <c r="F77" s="42" t="n"/>
+      <c r="G77" s="42" t="n"/>
+      <c r="H77" s="42" t="n"/>
+      <c r="I77" s="42" t="n"/>
+    </row>
+    <row r="78" ht="19.5" customHeight="1" s="33">
+      <c r="A78" s="43" t="n"/>
+      <c r="B78" s="44" t="n"/>
+      <c r="C78" s="44" t="n"/>
+      <c r="D78" s="44" t="n"/>
+      <c r="E78" s="44" t="n"/>
+      <c r="F78" s="44" t="n"/>
+      <c r="G78" s="44" t="n"/>
+      <c r="H78" s="44" t="n"/>
+      <c r="I78" s="44" t="n"/>
+    </row>
+    <row r="79" ht="19.5" customHeight="1" s="33">
+      <c r="A79" s="41" t="n"/>
+      <c r="B79" s="42" t="n"/>
+      <c r="C79" s="42" t="n"/>
+      <c r="D79" s="42" t="n"/>
+      <c r="E79" s="42" t="n"/>
+      <c r="F79" s="42" t="n"/>
+      <c r="G79" s="42" t="n"/>
+      <c r="H79" s="42" t="n"/>
+      <c r="I79" s="42" t="n"/>
+    </row>
+    <row r="80" ht="19.5" customHeight="1" s="33">
+      <c r="A80" s="43" t="n"/>
+      <c r="B80" s="44" t="n"/>
+      <c r="C80" s="44" t="n"/>
+      <c r="D80" s="44" t="n"/>
+      <c r="E80" s="44" t="n"/>
+      <c r="F80" s="44" t="n"/>
+      <c r="G80" s="44" t="n"/>
+      <c r="H80" s="44" t="n"/>
+      <c r="I80" s="44" t="n"/>
+    </row>
+    <row r="81" ht="19.5" customHeight="1" s="33">
+      <c r="A81" s="41" t="n"/>
+      <c r="B81" s="42" t="n"/>
+      <c r="C81" s="42" t="n"/>
+      <c r="D81" s="42" t="n"/>
+      <c r="E81" s="42" t="n"/>
+      <c r="F81" s="42" t="n"/>
+      <c r="G81" s="42" t="n"/>
+      <c r="H81" s="42" t="n"/>
+      <c r="I81" s="42" t="n"/>
+    </row>
+    <row r="82" ht="19.5" customHeight="1" s="33">
+      <c r="A82" s="43" t="n"/>
+      <c r="B82" s="44" t="n"/>
+      <c r="C82" s="44" t="n"/>
+      <c r="D82" s="44" t="n"/>
+      <c r="E82" s="44" t="n"/>
+      <c r="F82" s="44" t="n"/>
+      <c r="G82" s="44" t="n"/>
+      <c r="H82" s="44" t="n"/>
+      <c r="I82" s="44" t="n"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1" s="33">
+      <c r="A83" s="41" t="n"/>
+      <c r="B83" s="42" t="n"/>
+      <c r="C83" s="42" t="n"/>
+      <c r="D83" s="42" t="n"/>
+      <c r="E83" s="42" t="n"/>
+      <c r="F83" s="42" t="n"/>
+      <c r="G83" s="42" t="n"/>
+      <c r="H83" s="42" t="n"/>
+      <c r="I83" s="42" t="n"/>
+    </row>
+    <row r="84" ht="19.5" customHeight="1" s="33">
+      <c r="A84" s="43" t="n"/>
+      <c r="B84" s="44" t="n"/>
+      <c r="C84" s="44" t="n"/>
+      <c r="D84" s="44" t="n"/>
+      <c r="E84" s="44" t="n"/>
+      <c r="F84" s="44" t="n"/>
+      <c r="G84" s="44" t="n"/>
+      <c r="H84" s="44" t="n"/>
+      <c r="I84" s="44" t="n"/>
+    </row>
+    <row r="85" ht="19.5" customHeight="1" s="33">
+      <c r="A85" s="41" t="n"/>
+      <c r="B85" s="42" t="n"/>
+      <c r="C85" s="42" t="n"/>
+      <c r="D85" s="42" t="n"/>
+      <c r="E85" s="42" t="n"/>
+      <c r="F85" s="42" t="n"/>
+      <c r="G85" s="42" t="n"/>
+      <c r="H85" s="42" t="n"/>
+      <c r="I85" s="42" t="n"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="1" s="33">
+      <c r="A86" s="43" t="n"/>
+      <c r="B86" s="44" t="n"/>
+      <c r="C86" s="44" t="n"/>
+      <c r="D86" s="44" t="n"/>
+      <c r="E86" s="44" t="n"/>
+      <c r="F86" s="44" t="n"/>
+      <c r="G86" s="44" t="n"/>
+      <c r="H86" s="44" t="n"/>
+      <c r="I86" s="44" t="n"/>
+    </row>
+    <row r="87" ht="19.5" customHeight="1" s="33">
+      <c r="A87" s="41" t="n"/>
+      <c r="B87" s="42" t="n"/>
+      <c r="C87" s="42" t="n"/>
+      <c r="D87" s="42" t="n"/>
+      <c r="E87" s="42" t="n"/>
+      <c r="F87" s="42" t="n"/>
+      <c r="G87" s="42" t="n"/>
+      <c r="H87" s="42" t="n"/>
+      <c r="I87" s="42" t="n"/>
+    </row>
+    <row r="88" ht="19.5" customHeight="1" s="33">
+      <c r="A88" s="43" t="n"/>
+      <c r="B88" s="44" t="n"/>
+      <c r="C88" s="44" t="n"/>
+      <c r="D88" s="44" t="n"/>
+      <c r="E88" s="44" t="n"/>
+      <c r="F88" s="44" t="n"/>
+      <c r="G88" s="44" t="n"/>
+      <c r="H88" s="44" t="n"/>
+      <c r="I88" s="44" t="n"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1" s="33">
+      <c r="A89" s="41" t="n"/>
+      <c r="B89" s="42" t="n"/>
+      <c r="C89" s="42" t="n"/>
+      <c r="D89" s="42" t="n"/>
+      <c r="E89" s="42" t="n"/>
+      <c r="F89" s="42" t="n"/>
+      <c r="G89" s="42" t="n"/>
+      <c r="H89" s="42" t="n"/>
+      <c r="I89" s="42" t="n"/>
+    </row>
+    <row r="90" ht="19.5" customHeight="1" s="33">
+      <c r="A90" s="43" t="n"/>
+      <c r="B90" s="44" t="n"/>
+      <c r="C90" s="44" t="n"/>
+      <c r="D90" s="44" t="n"/>
+      <c r="E90" s="44" t="n"/>
+      <c r="F90" s="44" t="n"/>
+      <c r="G90" s="44" t="n"/>
+      <c r="H90" s="44" t="n"/>
+      <c r="I90" s="44" t="n"/>
+    </row>
+    <row r="91" ht="19.5" customHeight="1" s="33">
+      <c r="A91" s="41" t="n"/>
+      <c r="B91" s="42" t="n"/>
+      <c r="C91" s="42" t="n"/>
+      <c r="D91" s="42" t="n"/>
+      <c r="E91" s="42" t="n"/>
+      <c r="F91" s="42" t="n"/>
+      <c r="G91" s="42" t="n"/>
+      <c r="H91" s="42" t="n"/>
+      <c r="I91" s="42" t="n"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1" s="33">
+      <c r="A92" s="43" t="n"/>
+      <c r="B92" s="44" t="n"/>
+      <c r="C92" s="44" t="n"/>
+      <c r="D92" s="44" t="n"/>
+      <c r="E92" s="44" t="n"/>
+      <c r="F92" s="44" t="n"/>
+      <c r="G92" s="44" t="n"/>
+      <c r="H92" s="44" t="n"/>
+      <c r="I92" s="44" t="n"/>
+    </row>
+    <row r="93" ht="19.5" customHeight="1" s="33">
+      <c r="A93" s="41" t="n"/>
+      <c r="B93" s="42" t="n"/>
+      <c r="C93" s="42" t="n"/>
+      <c r="D93" s="42" t="n"/>
+      <c r="E93" s="42" t="n"/>
+      <c r="F93" s="42" t="n"/>
+      <c r="G93" s="42" t="n"/>
+      <c r="H93" s="42" t="n"/>
+      <c r="I93" s="42" t="n"/>
+    </row>
+    <row r="94" ht="19.5" customHeight="1" s="33">
+      <c r="A94" s="43" t="n"/>
+      <c r="B94" s="44" t="n"/>
+      <c r="C94" s="44" t="n"/>
+      <c r="D94" s="44" t="n"/>
+      <c r="E94" s="44" t="n"/>
+      <c r="F94" s="44" t="n"/>
+      <c r="G94" s="44" t="n"/>
+      <c r="H94" s="44" t="n"/>
+      <c r="I94" s="44" t="n"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1" s="33">
+      <c r="A95" s="41" t="n"/>
+      <c r="B95" s="42" t="n"/>
+      <c r="C95" s="42" t="n"/>
+      <c r="D95" s="42" t="n"/>
+      <c r="E95" s="42" t="n"/>
+      <c r="F95" s="42" t="n"/>
+      <c r="G95" s="42" t="n"/>
+      <c r="H95" s="42" t="n"/>
+      <c r="I95" s="42" t="n"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1" s="33">
+      <c r="A96" s="43" t="n"/>
+      <c r="B96" s="44" t="n"/>
+      <c r="C96" s="44" t="n"/>
+      <c r="D96" s="44" t="n"/>
+      <c r="E96" s="44" t="n"/>
+      <c r="F96" s="44" t="n"/>
+      <c r="G96" s="44" t="n"/>
+      <c r="H96" s="44" t="n"/>
+      <c r="I96" s="44" t="n"/>
+    </row>
+    <row r="97" ht="19.5" customHeight="1" s="33">
+      <c r="A97" s="41" t="n"/>
+      <c r="B97" s="42" t="n"/>
+      <c r="C97" s="42" t="n"/>
+      <c r="D97" s="42" t="n"/>
+      <c r="E97" s="42" t="n"/>
+      <c r="F97" s="42" t="n"/>
+      <c r="G97" s="42" t="n"/>
+      <c r="H97" s="42" t="n"/>
+      <c r="I97" s="42" t="n"/>
+    </row>
+    <row r="98" ht="19.5" customHeight="1" s="33">
+      <c r="A98" s="43" t="n"/>
+      <c r="B98" s="44" t="n"/>
+      <c r="C98" s="44" t="n"/>
+      <c r="D98" s="44" t="n"/>
+      <c r="E98" s="44" t="n"/>
+      <c r="F98" s="44" t="n"/>
+      <c r="G98" s="44" t="n"/>
+      <c r="H98" s="44" t="n"/>
+      <c r="I98" s="44" t="n"/>
+    </row>
+    <row r="99" ht="19.5" customHeight="1" s="33">
+      <c r="A99" s="41" t="n"/>
+      <c r="B99" s="42" t="n"/>
+      <c r="C99" s="42" t="n"/>
+      <c r="D99" s="42" t="n"/>
+      <c r="E99" s="42" t="n"/>
+      <c r="F99" s="42" t="n"/>
+      <c r="G99" s="42" t="n"/>
+      <c r="H99" s="42" t="n"/>
+      <c r="I99" s="42" t="n"/>
+    </row>
+    <row r="100" ht="19.5" customHeight="1" s="33">
+      <c r="A100" s="43" t="n"/>
+      <c r="B100" s="44" t="n"/>
+      <c r="C100" s="44" t="n"/>
+      <c r="D100" s="44" t="n"/>
+      <c r="E100" s="44" t="n"/>
+      <c r="F100" s="44" t="n"/>
+      <c r="G100" s="44" t="n"/>
+      <c r="H100" s="44" t="n"/>
+      <c r="I100" s="44" t="n"/>
+    </row>
+    <row r="101" ht="19.5" customHeight="1" s="33">
+      <c r="A101" s="41" t="n"/>
+      <c r="B101" s="42" t="n"/>
+      <c r="C101" s="42" t="n"/>
+      <c r="D101" s="42" t="n"/>
+      <c r="E101" s="42" t="n"/>
+      <c r="F101" s="42" t="n"/>
+      <c r="G101" s="42" t="n"/>
+      <c r="H101" s="42" t="n"/>
+      <c r="I101" s="42" t="n"/>
+    </row>
+    <row r="102" ht="19.5" customHeight="1" s="33">
+      <c r="A102" s="43" t="n"/>
+      <c r="B102" s="44" t="n"/>
+      <c r="C102" s="44" t="n"/>
+      <c r="D102" s="44" t="n"/>
+      <c r="E102" s="44" t="n"/>
+      <c r="F102" s="44" t="n"/>
+      <c r="G102" s="44" t="n"/>
+      <c r="H102" s="44" t="n"/>
+      <c r="I102" s="44" t="n"/>
+    </row>
+    <row r="103" ht="19.5" customHeight="1" s="33">
+      <c r="A103" s="41" t="n"/>
+      <c r="B103" s="42" t="n"/>
+      <c r="C103" s="42" t="n"/>
+      <c r="D103" s="42" t="n"/>
+      <c r="E103" s="42" t="n"/>
+      <c r="F103" s="42" t="n"/>
+      <c r="G103" s="42" t="n"/>
+      <c r="H103" s="42" t="n"/>
+      <c r="I103" s="42" t="n"/>
+    </row>
+    <row r="104" ht="19.5" customHeight="1" s="33">
+      <c r="A104" s="43" t="n"/>
+      <c r="B104" s="44" t="n"/>
+      <c r="C104" s="44" t="n"/>
+      <c r="D104" s="44" t="n"/>
+      <c r="E104" s="44" t="n"/>
+      <c r="F104" s="44" t="n"/>
+      <c r="G104" s="44" t="n"/>
+      <c r="H104" s="44" t="n"/>
+      <c r="I104" s="44" t="n"/>
+    </row>
+    <row r="105" ht="19.5" customHeight="1" s="33">
+      <c r="A105" s="41" t="n"/>
+      <c r="B105" s="42" t="n"/>
+      <c r="C105" s="42" t="n"/>
+      <c r="D105" s="42" t="n"/>
+      <c r="E105" s="42" t="n"/>
+      <c r="F105" s="42" t="n"/>
+      <c r="G105" s="42" t="n"/>
+      <c r="H105" s="42" t="n"/>
+      <c r="I105" s="42" t="n"/>
+    </row>
+    <row r="106" ht="19.5" customHeight="1" s="33">
+      <c r="A106" s="43" t="n"/>
+      <c r="B106" s="44" t="n"/>
+      <c r="C106" s="44" t="n"/>
+      <c r="D106" s="44" t="n"/>
+      <c r="E106" s="44" t="n"/>
+      <c r="F106" s="44" t="n"/>
+      <c r="G106" s="44" t="n"/>
+      <c r="H106" s="44" t="n"/>
+      <c r="I106" s="44" t="n"/>
+    </row>
+    <row r="107" ht="19.5" customHeight="1" s="33">
+      <c r="A107" s="41" t="n"/>
+      <c r="B107" s="42" t="n"/>
+      <c r="C107" s="42" t="n"/>
+      <c r="D107" s="42" t="n"/>
+      <c r="E107" s="42" t="n"/>
+      <c r="F107" s="42" t="n"/>
+      <c r="G107" s="42" t="n"/>
+      <c r="H107" s="42" t="n"/>
+      <c r="I107" s="42" t="n"/>
+    </row>
+    <row r="108" ht="19.5" customHeight="1" s="33">
+      <c r="A108" s="43" t="n"/>
+      <c r="B108" s="44" t="n"/>
+      <c r="C108" s="44" t="n"/>
+      <c r="D108" s="44" t="n"/>
+      <c r="E108" s="44" t="n"/>
+      <c r="F108" s="44" t="n"/>
+      <c r="G108" s="44" t="n"/>
+      <c r="H108" s="44" t="n"/>
+      <c r="I108" s="44" t="n"/>
+    </row>
+    <row r="109" ht="19.5" customHeight="1" s="33">
+      <c r="A109" s="41" t="n"/>
+      <c r="B109" s="42" t="n"/>
+      <c r="C109" s="42" t="n"/>
+      <c r="D109" s="42" t="n"/>
+      <c r="E109" s="42" t="n"/>
+      <c r="F109" s="42" t="n"/>
+      <c r="G109" s="42" t="n"/>
+      <c r="H109" s="42" t="n"/>
+      <c r="I109" s="42" t="n"/>
+    </row>
+    <row r="110" ht="19.5" customHeight="1" s="33">
+      <c r="A110" s="43" t="n"/>
+      <c r="B110" s="44" t="n"/>
+      <c r="C110" s="44" t="n"/>
+      <c r="D110" s="44" t="n"/>
+      <c r="E110" s="44" t="n"/>
+      <c r="F110" s="44" t="n"/>
+      <c r="G110" s="44" t="n"/>
+      <c r="H110" s="44" t="n"/>
+      <c r="I110" s="44" t="n"/>
+    </row>
+    <row r="111" ht="19.5" customHeight="1" s="33">
+      <c r="A111" s="41" t="n"/>
+      <c r="B111" s="42" t="n"/>
+      <c r="C111" s="42" t="n"/>
+      <c r="D111" s="42" t="n"/>
+      <c r="E111" s="42" t="n"/>
+      <c r="F111" s="42" t="n"/>
+      <c r="G111" s="42" t="n"/>
+      <c r="H111" s="42" t="n"/>
+      <c r="I111" s="42" t="n"/>
+    </row>
+    <row r="112" ht="19.5" customHeight="1" s="33">
+      <c r="A112" s="43" t="n"/>
+      <c r="B112" s="44" t="n"/>
+      <c r="C112" s="44" t="n"/>
+      <c r="D112" s="44" t="n"/>
+      <c r="E112" s="44" t="n"/>
+      <c r="F112" s="44" t="n"/>
+      <c r="G112" s="44" t="n"/>
+      <c r="H112" s="44" t="n"/>
+      <c r="I112" s="44" t="n"/>
+    </row>
+    <row r="113" ht="19.5" customHeight="1" s="33">
+      <c r="A113" s="41" t="n"/>
+      <c r="B113" s="42" t="n"/>
+      <c r="C113" s="42" t="n"/>
+      <c r="D113" s="42" t="n"/>
+      <c r="E113" s="42" t="n"/>
+      <c r="F113" s="42" t="n"/>
+      <c r="G113" s="42" t="n"/>
+      <c r="H113" s="42" t="n"/>
+      <c r="I113" s="42" t="n"/>
+    </row>
+    <row r="114" ht="19.5" customHeight="1" s="33">
+      <c r="A114" s="43" t="n"/>
+      <c r="B114" s="44" t="n"/>
+      <c r="C114" s="44" t="n"/>
+      <c r="D114" s="44" t="n"/>
+      <c r="E114" s="44" t="n"/>
+      <c r="F114" s="44" t="n"/>
+      <c r="G114" s="44" t="n"/>
+      <c r="H114" s="44" t="n"/>
+      <c r="I114" s="44" t="n"/>
+    </row>
+    <row r="115" ht="19.5" customHeight="1" s="33">
+      <c r="A115" s="41" t="n"/>
+      <c r="B115" s="42" t="n"/>
+      <c r="C115" s="42" t="n"/>
+      <c r="D115" s="42" t="n"/>
+      <c r="E115" s="42" t="n"/>
+      <c r="F115" s="42" t="n"/>
+      <c r="G115" s="42" t="n"/>
+      <c r="H115" s="42" t="n"/>
+      <c r="I115" s="42" t="n"/>
+    </row>
+    <row r="116" ht="19.5" customHeight="1" s="33">
+      <c r="A116" s="43" t="n"/>
+      <c r="B116" s="44" t="n"/>
+      <c r="C116" s="44" t="n"/>
+      <c r="D116" s="44" t="n"/>
+      <c r="E116" s="44" t="n"/>
+      <c r="F116" s="44" t="n"/>
+      <c r="G116" s="44" t="n"/>
+      <c r="H116" s="44" t="n"/>
+      <c r="I116" s="44" t="n"/>
+    </row>
+    <row r="117" ht="19.5" customHeight="1" s="33">
+      <c r="A117" s="41" t="n"/>
+      <c r="B117" s="42" t="n"/>
+      <c r="C117" s="42" t="n"/>
+      <c r="D117" s="42" t="n"/>
+      <c r="E117" s="42" t="n"/>
+      <c r="F117" s="42" t="n"/>
+      <c r="G117" s="42" t="n"/>
+      <c r="H117" s="42" t="n"/>
+      <c r="I117" s="42" t="n"/>
+    </row>
+    <row r="118" ht="19.5" customHeight="1" s="33">
+      <c r="A118" s="43" t="n"/>
+      <c r="B118" s="44" t="n"/>
+      <c r="C118" s="44" t="n"/>
+      <c r="D118" s="44" t="n"/>
+      <c r="E118" s="44" t="n"/>
+      <c r="F118" s="44" t="n"/>
+      <c r="G118" s="44" t="n"/>
+      <c r="H118" s="44" t="n"/>
+      <c r="I118" s="44" t="n"/>
+    </row>
+    <row r="119" ht="19.5" customHeight="1" s="33">
+      <c r="A119" s="41" t="n"/>
+      <c r="B119" s="42" t="n"/>
+      <c r="C119" s="42" t="n"/>
+      <c r="D119" s="42" t="n"/>
+      <c r="E119" s="42" t="n"/>
+      <c r="F119" s="42" t="n"/>
+      <c r="G119" s="42" t="n"/>
+      <c r="H119" s="42" t="n"/>
+      <c r="I119" s="42" t="n"/>
+    </row>
+    <row r="120" ht="19.5" customHeight="1" s="33">
+      <c r="A120" s="43" t="n"/>
+      <c r="B120" s="44" t="n"/>
+      <c r="C120" s="44" t="n"/>
+      <c r="D120" s="44" t="n"/>
+      <c r="E120" s="44" t="n"/>
+      <c r="F120" s="44" t="n"/>
+      <c r="G120" s="44" t="n"/>
+      <c r="H120" s="44" t="n"/>
+      <c r="I120" s="44" t="n"/>
+    </row>
+    <row r="121" ht="19.5" customHeight="1" s="33">
+      <c r="A121" s="41" t="n"/>
+      <c r="B121" s="42" t="n"/>
+      <c r="C121" s="42" t="n"/>
+      <c r="D121" s="42" t="n"/>
+      <c r="E121" s="42" t="n"/>
+      <c r="F121" s="42" t="n"/>
+      <c r="G121" s="42" t="n"/>
+      <c r="H121" s="42" t="n"/>
+      <c r="I121" s="42" t="n"/>
+    </row>
+    <row r="122" ht="19.5" customHeight="1" s="33">
+      <c r="A122" s="43" t="n"/>
+      <c r="B122" s="44" t="n"/>
+      <c r="C122" s="44" t="n"/>
+      <c r="D122" s="44" t="n"/>
+      <c r="E122" s="44" t="n"/>
+      <c r="F122" s="44" t="n"/>
+      <c r="G122" s="44" t="n"/>
+      <c r="H122" s="44" t="n"/>
+      <c r="I122" s="44" t="n"/>
+    </row>
+    <row r="123" ht="19.5" customHeight="1" s="33">
+      <c r="A123" s="41" t="n"/>
+      <c r="B123" s="42" t="n"/>
+      <c r="C123" s="42" t="n"/>
+      <c r="D123" s="42" t="n"/>
+      <c r="E123" s="42" t="n"/>
+      <c r="F123" s="42" t="n"/>
+      <c r="G123" s="42" t="n"/>
+      <c r="H123" s="42" t="n"/>
+      <c r="I123" s="42" t="n"/>
+    </row>
+    <row r="124" ht="19.5" customHeight="1" s="33">
+      <c r="A124" s="43" t="n"/>
+      <c r="B124" s="44" t="n"/>
+      <c r="C124" s="44" t="n"/>
+      <c r="D124" s="44" t="n"/>
+      <c r="E124" s="44" t="n"/>
+      <c r="F124" s="44" t="n"/>
+      <c r="G124" s="44" t="n"/>
+      <c r="H124" s="44" t="n"/>
+      <c r="I124" s="44" t="n"/>
+    </row>
+    <row r="125" ht="19.5" customHeight="1" s="33">
+      <c r="A125" s="41" t="n"/>
+      <c r="B125" s="42" t="n"/>
+      <c r="C125" s="42" t="n"/>
+      <c r="D125" s="42" t="n"/>
+      <c r="E125" s="42" t="n"/>
+      <c r="F125" s="42" t="n"/>
+      <c r="G125" s="42" t="n"/>
+      <c r="H125" s="42" t="n"/>
+      <c r="I125" s="42" t="n"/>
+    </row>
+    <row r="126" ht="19.5" customHeight="1" s="33">
+      <c r="A126" s="43" t="n"/>
+      <c r="B126" s="44" t="n"/>
+      <c r="C126" s="44" t="n"/>
+      <c r="D126" s="44" t="n"/>
+      <c r="E126" s="44" t="n"/>
+      <c r="F126" s="44" t="n"/>
+      <c r="G126" s="44" t="n"/>
+      <c r="H126" s="44" t="n"/>
+      <c r="I126" s="44" t="n"/>
+    </row>
+    <row r="127" ht="19.5" customHeight="1" s="33">
+      <c r="A127" s="41" t="n"/>
+      <c r="B127" s="42" t="n"/>
+      <c r="C127" s="42" t="n"/>
+      <c r="D127" s="42" t="n"/>
+      <c r="E127" s="42" t="n"/>
+      <c r="F127" s="42" t="n"/>
+      <c r="G127" s="42" t="n"/>
+      <c r="H127" s="42" t="n"/>
+      <c r="I127" s="42" t="n"/>
+    </row>
+    <row r="128" ht="19.5" customHeight="1" s="33">
+      <c r="A128" s="43" t="n"/>
+      <c r="B128" s="44" t="n"/>
+      <c r="C128" s="44" t="n"/>
+      <c r="D128" s="44" t="n"/>
+      <c r="E128" s="44" t="n"/>
+      <c r="F128" s="44" t="n"/>
+      <c r="G128" s="44" t="n"/>
+      <c r="H128" s="44" t="n"/>
+      <c r="I128" s="44" t="n"/>
+    </row>
+    <row r="129" ht="19.5" customHeight="1" s="33">
+      <c r="A129" s="41" t="n"/>
+      <c r="B129" s="42" t="n"/>
+      <c r="C129" s="42" t="n"/>
+      <c r="D129" s="42" t="n"/>
+      <c r="E129" s="42" t="n"/>
+      <c r="F129" s="42" t="n"/>
+      <c r="G129" s="42" t="n"/>
+      <c r="H129" s="42" t="n"/>
+      <c r="I129" s="42" t="n"/>
+    </row>
+    <row r="130" ht="19.5" customHeight="1" s="33">
+      <c r="A130" s="43" t="n"/>
+      <c r="B130" s="44" t="n"/>
+      <c r="C130" s="44" t="n"/>
+      <c r="D130" s="44" t="n"/>
+      <c r="E130" s="44" t="n"/>
+      <c r="F130" s="44" t="n"/>
+      <c r="G130" s="44" t="n"/>
+      <c r="H130" s="44" t="n"/>
+      <c r="I130" s="44" t="n"/>
+    </row>
+    <row r="131" ht="19.5" customHeight="1" s="33">
+      <c r="A131" s="41" t="n"/>
+      <c r="B131" s="42" t="n"/>
+      <c r="C131" s="42" t="n"/>
+      <c r="D131" s="42" t="n"/>
+      <c r="E131" s="42" t="n"/>
+      <c r="F131" s="42" t="n"/>
+      <c r="G131" s="42" t="n"/>
+      <c r="H131" s="42" t="n"/>
+      <c r="I131" s="42" t="n"/>
+    </row>
+    <row r="132" ht="19.5" customHeight="1" s="33">
+      <c r="A132" s="43" t="n"/>
+      <c r="B132" s="44" t="n"/>
+      <c r="C132" s="44" t="n"/>
+      <c r="D132" s="44" t="n"/>
+      <c r="E132" s="44" t="n"/>
+      <c r="F132" s="44" t="n"/>
+      <c r="G132" s="44" t="n"/>
+      <c r="H132" s="44" t="n"/>
+      <c r="I132" s="44" t="n"/>
+    </row>
+    <row r="133" ht="19.5" customHeight="1" s="33">
+      <c r="A133" s="41" t="n"/>
+      <c r="B133" s="42" t="n"/>
+      <c r="C133" s="42" t="n"/>
+      <c r="D133" s="42" t="n"/>
+      <c r="E133" s="42" t="n"/>
+      <c r="F133" s="42" t="n"/>
+      <c r="G133" s="42" t="n"/>
+      <c r="H133" s="42" t="n"/>
+      <c r="I133" s="42" t="n"/>
+    </row>
+    <row r="134" ht="19.5" customHeight="1" s="33">
+      <c r="A134" s="43" t="n"/>
+      <c r="B134" s="44" t="n"/>
+      <c r="C134" s="44" t="n"/>
+      <c r="D134" s="44" t="n"/>
+      <c r="E134" s="44" t="n"/>
+      <c r="F134" s="44" t="n"/>
+      <c r="G134" s="44" t="n"/>
+      <c r="H134" s="44" t="n"/>
+      <c r="I134" s="44" t="n"/>
+    </row>
+    <row r="135" ht="19.5" customHeight="1" s="33">
+      <c r="A135" s="41" t="n"/>
+      <c r="B135" s="42" t="n"/>
+      <c r="C135" s="42" t="n"/>
+      <c r="D135" s="42" t="n"/>
+      <c r="E135" s="42" t="n"/>
+      <c r="F135" s="42" t="n"/>
+      <c r="G135" s="42" t="n"/>
+      <c r="H135" s="42" t="n"/>
+      <c r="I135" s="42" t="n"/>
+    </row>
+    <row r="136" ht="19.5" customHeight="1" s="33">
+      <c r="A136" s="43" t="n"/>
+      <c r="B136" s="44" t="n"/>
+      <c r="C136" s="44" t="n"/>
+      <c r="D136" s="44" t="n"/>
+      <c r="E136" s="44" t="n"/>
+      <c r="F136" s="44" t="n"/>
+      <c r="G136" s="44" t="n"/>
+      <c r="H136" s="44" t="n"/>
+      <c r="I136" s="44" t="n"/>
+    </row>
+    <row r="137" ht="19.5" customHeight="1" s="33">
+      <c r="A137" s="41" t="n"/>
+      <c r="B137" s="42" t="n"/>
+      <c r="C137" s="42" t="n"/>
+      <c r="D137" s="42" t="n"/>
+      <c r="E137" s="42" t="n"/>
+      <c r="F137" s="42" t="n"/>
+      <c r="G137" s="42" t="n"/>
+      <c r="H137" s="42" t="n"/>
+      <c r="I137" s="42" t="n"/>
+    </row>
+    <row r="138" ht="19.5" customHeight="1" s="33">
+      <c r="A138" s="43" t="n"/>
+      <c r="B138" s="44" t="n"/>
+      <c r="C138" s="44" t="n"/>
+      <c r="D138" s="44" t="n"/>
+      <c r="E138" s="44" t="n"/>
+      <c r="F138" s="44" t="n"/>
+      <c r="G138" s="44" t="n"/>
+      <c r="H138" s="44" t="n"/>
+      <c r="I138" s="44" t="n"/>
+    </row>
+    <row r="139" ht="19.5" customHeight="1" s="33">
+      <c r="A139" s="41" t="n"/>
+      <c r="B139" s="42" t="n"/>
+      <c r="C139" s="42" t="n"/>
+      <c r="D139" s="42" t="n"/>
+      <c r="E139" s="42" t="n"/>
+      <c r="F139" s="42" t="n"/>
+      <c r="G139" s="42" t="n"/>
+      <c r="H139" s="42" t="n"/>
+      <c r="I139" s="42" t="n"/>
+    </row>
+    <row r="140" ht="19.5" customHeight="1" s="33">
+      <c r="A140" s="43" t="n"/>
+      <c r="B140" s="44" t="n"/>
+      <c r="C140" s="44" t="n"/>
+      <c r="D140" s="44" t="n"/>
+      <c r="E140" s="44" t="n"/>
+      <c r="F140" s="44" t="n"/>
+      <c r="G140" s="44" t="n"/>
+      <c r="H140" s="44" t="n"/>
+      <c r="I140" s="44" t="n"/>
+    </row>
+    <row r="141" ht="19.5" customHeight="1" s="33">
+      <c r="A141" s="41" t="n"/>
+      <c r="B141" s="42" t="n"/>
+      <c r="C141" s="42" t="n"/>
+      <c r="D141" s="42" t="n"/>
+      <c r="E141" s="42" t="n"/>
+      <c r="F141" s="42" t="n"/>
+      <c r="G141" s="42" t="n"/>
+      <c r="H141" s="42" t="n"/>
+      <c r="I141" s="42" t="n"/>
+    </row>
+    <row r="142" ht="19.5" customHeight="1" s="33">
+      <c r="A142" s="43" t="n"/>
+      <c r="B142" s="44" t="n"/>
+      <c r="C142" s="44" t="n"/>
+      <c r="D142" s="44" t="n"/>
+      <c r="E142" s="44" t="n"/>
+      <c r="F142" s="44" t="n"/>
+      <c r="G142" s="44" t="n"/>
+      <c r="H142" s="44" t="n"/>
+      <c r="I142" s="44" t="n"/>
+    </row>
+    <row r="143" ht="19.5" customHeight="1" s="33">
+      <c r="A143" s="41" t="n"/>
+      <c r="B143" s="42" t="n"/>
+      <c r="C143" s="42" t="n"/>
+      <c r="D143" s="42" t="n"/>
+      <c r="E143" s="42" t="n"/>
+      <c r="F143" s="42" t="n"/>
+      <c r="G143" s="42" t="n"/>
+      <c r="H143" s="42" t="n"/>
+      <c r="I143" s="42" t="n"/>
+    </row>
+    <row r="144" ht="19.5" customHeight="1" s="33">
+      <c r="A144" s="43" t="n"/>
+      <c r="B144" s="44" t="n"/>
+      <c r="C144" s="44" t="n"/>
+      <c r="D144" s="44" t="n"/>
+      <c r="E144" s="44" t="n"/>
+      <c r="F144" s="44" t="n"/>
+      <c r="G144" s="44" t="n"/>
+      <c r="H144" s="44" t="n"/>
+      <c r="I144" s="44" t="n"/>
+    </row>
+    <row r="145" ht="19.5" customHeight="1" s="33">
+      <c r="A145" s="41" t="n"/>
+      <c r="B145" s="42" t="n"/>
+      <c r="C145" s="42" t="n"/>
+      <c r="D145" s="42" t="n"/>
+      <c r="E145" s="42" t="n"/>
+      <c r="F145" s="42" t="n"/>
+      <c r="G145" s="42" t="n"/>
+      <c r="H145" s="42" t="n"/>
+      <c r="I145" s="42" t="n"/>
+    </row>
+    <row r="146" ht="19.5" customHeight="1" s="33">
+      <c r="A146" s="43" t="n"/>
+      <c r="B146" s="44" t="n"/>
+      <c r="C146" s="44" t="n"/>
+      <c r="D146" s="44" t="n"/>
+      <c r="E146" s="44" t="n"/>
+      <c r="F146" s="44" t="n"/>
+      <c r="G146" s="44" t="n"/>
+      <c r="H146" s="44" t="n"/>
+      <c r="I146" s="44" t="n"/>
+    </row>
+    <row r="147" ht="19.5" customHeight="1" s="33">
+      <c r="A147" s="41" t="n"/>
+      <c r="B147" s="42" t="n"/>
+      <c r="C147" s="42" t="n"/>
+      <c r="D147" s="42" t="n"/>
+      <c r="E147" s="42" t="n"/>
+      <c r="F147" s="42" t="n"/>
+      <c r="G147" s="42" t="n"/>
+      <c r="H147" s="42" t="n"/>
+      <c r="I147" s="42" t="n"/>
+    </row>
+    <row r="148" ht="19.5" customHeight="1" s="33">
+      <c r="A148" s="43" t="n"/>
+      <c r="B148" s="44" t="n"/>
+      <c r="C148" s="44" t="n"/>
+      <c r="D148" s="44" t="n"/>
+      <c r="E148" s="44" t="n"/>
+      <c r="F148" s="44" t="n"/>
+      <c r="G148" s="44" t="n"/>
+      <c r="H148" s="44" t="n"/>
+      <c r="I148" s="44" t="n"/>
+    </row>
+    <row r="149" ht="19.5" customHeight="1" s="33">
+      <c r="A149" s="41" t="n"/>
+      <c r="B149" s="42" t="n"/>
+      <c r="C149" s="42" t="n"/>
+      <c r="D149" s="42" t="n"/>
+      <c r="E149" s="42" t="n"/>
+      <c r="F149" s="42" t="n"/>
+      <c r="G149" s="42" t="n"/>
+      <c r="H149" s="42" t="n"/>
+      <c r="I149" s="42" t="n"/>
+    </row>
+    <row r="150" ht="19.5" customHeight="1" s="33">
+      <c r="A150" s="43" t="n"/>
+      <c r="B150" s="44" t="n"/>
+      <c r="C150" s="44" t="n"/>
+      <c r="D150" s="44" t="n"/>
+      <c r="E150" s="44" t="n"/>
+      <c r="F150" s="44" t="n"/>
+      <c r="G150" s="44" t="n"/>
+      <c r="H150" s="44" t="n"/>
+      <c r="I150" s="44" t="n"/>
+    </row>
+    <row r="151" ht="19.5" customHeight="1" s="33">
+      <c r="A151" s="41" t="n"/>
+      <c r="B151" s="42" t="n"/>
+      <c r="C151" s="42" t="n"/>
+      <c r="D151" s="42" t="n"/>
+      <c r="E151" s="42" t="n"/>
+      <c r="F151" s="42" t="n"/>
+      <c r="G151" s="42" t="n"/>
+      <c r="H151" s="42" t="n"/>
+      <c r="I151" s="42" t="n"/>
+    </row>
+    <row r="152" ht="19.5" customHeight="1" s="33">
+      <c r="A152" s="43" t="n"/>
+      <c r="B152" s="44" t="n"/>
+      <c r="C152" s="44" t="n"/>
+      <c r="D152" s="44" t="n"/>
+      <c r="E152" s="44" t="n"/>
+      <c r="F152" s="44" t="n"/>
+      <c r="G152" s="44" t="n"/>
+      <c r="H152" s="44" t="n"/>
+      <c r="I152" s="44" t="n"/>
+    </row>
+    <row r="153" ht="19.5" customHeight="1" s="33">
+      <c r="A153" s="41" t="n"/>
+      <c r="B153" s="42" t="n"/>
+      <c r="C153" s="42" t="n"/>
+      <c r="D153" s="42" t="n"/>
+      <c r="E153" s="42" t="n"/>
+      <c r="F153" s="42" t="n"/>
+      <c r="G153" s="42" t="n"/>
+      <c r="H153" s="42" t="n"/>
+      <c r="I153" s="42" t="n"/>
+    </row>
+    <row r="154" ht="19.5" customHeight="1" s="33">
+      <c r="A154" s="43" t="n"/>
+      <c r="B154" s="44" t="n"/>
+      <c r="C154" s="44" t="n"/>
+      <c r="D154" s="44" t="n"/>
+      <c r="E154" s="44" t="n"/>
+      <c r="F154" s="44" t="n"/>
+      <c r="G154" s="44" t="n"/>
+      <c r="H154" s="44" t="n"/>
+      <c r="I154" s="44" t="n"/>
+    </row>
+    <row r="155" ht="19.5" customHeight="1" s="33">
+      <c r="A155" s="41" t="n"/>
+      <c r="B155" s="42" t="n"/>
+      <c r="C155" s="42" t="n"/>
+      <c r="D155" s="42" t="n"/>
+      <c r="E155" s="42" t="n"/>
+      <c r="F155" s="42" t="n"/>
+      <c r="G155" s="42" t="n"/>
+      <c r="H155" s="42" t="n"/>
+      <c r="I155" s="42" t="n"/>
+    </row>
+    <row r="156" ht="19.5" customHeight="1" s="33">
+      <c r="A156" s="43" t="n"/>
+      <c r="B156" s="44" t="n"/>
+      <c r="C156" s="44" t="n"/>
+      <c r="D156" s="44" t="n"/>
+      <c r="E156" s="44" t="n"/>
+      <c r="F156" s="44" t="n"/>
+      <c r="G156" s="44" t="n"/>
+      <c r="H156" s="44" t="n"/>
+      <c r="I156" s="44" t="n"/>
+    </row>
+    <row r="157" ht="19.5" customHeight="1" s="33">
+      <c r="A157" s="41" t="n"/>
+      <c r="B157" s="42" t="n"/>
+      <c r="C157" s="42" t="n"/>
+      <c r="D157" s="42" t="n"/>
+      <c r="E157" s="42" t="n"/>
+      <c r="F157" s="42" t="n"/>
+      <c r="G157" s="42" t="n"/>
+      <c r="H157" s="42" t="n"/>
+      <c r="I157" s="42" t="n"/>
+    </row>
+    <row r="158" ht="19.5" customHeight="1" s="33">
+      <c r="A158" s="43" t="n"/>
+      <c r="B158" s="44" t="n"/>
+      <c r="C158" s="44" t="n"/>
+      <c r="D158" s="44" t="n"/>
+      <c r="E158" s="44" t="n"/>
+      <c r="F158" s="44" t="n"/>
+      <c r="G158" s="44" t="n"/>
+      <c r="H158" s="44" t="n"/>
+      <c r="I158" s="44" t="n"/>
+    </row>
+    <row r="159" ht="19.5" customHeight="1" s="33">
+      <c r="A159" s="41" t="n"/>
+      <c r="B159" s="42" t="n"/>
+      <c r="C159" s="42" t="n"/>
+      <c r="D159" s="42" t="n"/>
+      <c r="E159" s="42" t="n"/>
+      <c r="F159" s="42" t="n"/>
+      <c r="G159" s="42" t="n"/>
+      <c r="H159" s="42" t="n"/>
+      <c r="I159" s="42" t="n"/>
+    </row>
+    <row r="160" ht="19.5" customHeight="1" s="33">
+      <c r="A160" s="43" t="n"/>
+      <c r="B160" s="44" t="n"/>
+      <c r="C160" s="44" t="n"/>
+      <c r="D160" s="44" t="n"/>
+      <c r="E160" s="44" t="n"/>
+      <c r="F160" s="44" t="n"/>
+      <c r="G160" s="44" t="n"/>
+      <c r="H160" s="44" t="n"/>
+      <c r="I160" s="44" t="n"/>
+    </row>
+    <row r="161" ht="19.5" customHeight="1" s="33">
+      <c r="A161" s="41" t="n"/>
+      <c r="B161" s="42" t="n"/>
+      <c r="C161" s="42" t="n"/>
+      <c r="D161" s="42" t="n"/>
+      <c r="E161" s="42" t="n"/>
+      <c r="F161" s="42" t="n"/>
+      <c r="G161" s="42" t="n"/>
+      <c r="H161" s="42" t="n"/>
+      <c r="I161" s="42" t="n"/>
+    </row>
+    <row r="162" ht="19.5" customHeight="1" s="33">
+      <c r="A162" s="43" t="n"/>
+      <c r="B162" s="44" t="n"/>
+      <c r="C162" s="44" t="n"/>
+      <c r="D162" s="44" t="n"/>
+      <c r="E162" s="44" t="n"/>
+      <c r="F162" s="44" t="n"/>
+      <c r="G162" s="44" t="n"/>
+      <c r="H162" s="44" t="n"/>
+      <c r="I162" s="44" t="n"/>
+    </row>
+    <row r="163" ht="19.5" customHeight="1" s="33">
+      <c r="A163" s="41" t="n"/>
+      <c r="B163" s="42" t="n"/>
+      <c r="C163" s="42" t="n"/>
+      <c r="D163" s="42" t="n"/>
+      <c r="E163" s="42" t="n"/>
+      <c r="F163" s="42" t="n"/>
+      <c r="G163" s="42" t="n"/>
+      <c r="H163" s="42" t="n"/>
+      <c r="I163" s="42" t="n"/>
+    </row>
+    <row r="164" ht="19.5" customHeight="1" s="33">
+      <c r="A164" s="43" t="n"/>
+      <c r="B164" s="44" t="n"/>
+      <c r="C164" s="44" t="n"/>
+      <c r="D164" s="44" t="n"/>
+      <c r="E164" s="44" t="n"/>
+      <c r="F164" s="44" t="n"/>
+      <c r="G164" s="44" t="n"/>
+      <c r="H164" s="44" t="n"/>
+      <c r="I164" s="44" t="n"/>
+    </row>
+    <row r="165" ht="19.5" customHeight="1" s="33">
+      <c r="A165" s="41" t="n"/>
+      <c r="B165" s="42" t="n"/>
+      <c r="C165" s="42" t="n"/>
+      <c r="D165" s="42" t="n"/>
+      <c r="E165" s="42" t="n"/>
+      <c r="F165" s="42" t="n"/>
+      <c r="G165" s="42" t="n"/>
+      <c r="H165" s="42" t="n"/>
+      <c r="I165" s="42" t="n"/>
+    </row>
+    <row r="166" ht="19.5" customHeight="1" s="33">
+      <c r="A166" s="43" t="n"/>
+      <c r="B166" s="44" t="n"/>
+      <c r="C166" s="44" t="n"/>
+      <c r="D166" s="44" t="n"/>
+      <c r="E166" s="44" t="n"/>
+      <c r="F166" s="44" t="n"/>
+      <c r="G166" s="44" t="n"/>
+      <c r="H166" s="44" t="n"/>
+      <c r="I166" s="44" t="n"/>
+    </row>
+    <row r="167" ht="19.5" customHeight="1" s="33">
+      <c r="A167" s="41" t="n"/>
+      <c r="B167" s="42" t="n"/>
+      <c r="C167" s="42" t="n"/>
+      <c r="D167" s="42" t="n"/>
+      <c r="E167" s="42" t="n"/>
+      <c r="F167" s="42" t="n"/>
+      <c r="G167" s="42" t="n"/>
+      <c r="H167" s="42" t="n"/>
+      <c r="I167" s="42" t="n"/>
+    </row>
+    <row r="168" ht="19.5" customHeight="1" s="33">
+      <c r="A168" s="43" t="n"/>
+      <c r="B168" s="44" t="n"/>
+      <c r="C168" s="44" t="n"/>
+      <c r="D168" s="44" t="n"/>
+      <c r="E168" s="44" t="n"/>
+      <c r="F168" s="44" t="n"/>
+      <c r="G168" s="44" t="n"/>
+      <c r="H168" s="44" t="n"/>
+      <c r="I168" s="44" t="n"/>
+    </row>
+    <row r="169" ht="19.5" customHeight="1" s="33">
+      <c r="A169" s="41" t="n"/>
+      <c r="B169" s="42" t="n"/>
+      <c r="C169" s="42" t="n"/>
+      <c r="D169" s="42" t="n"/>
+      <c r="E169" s="42" t="n"/>
+      <c r="F169" s="42" t="n"/>
+      <c r="G169" s="42" t="n"/>
+      <c r="H169" s="42" t="n"/>
+      <c r="I169" s="42" t="n"/>
+    </row>
+    <row r="170" ht="19.5" customHeight="1" s="33">
+      <c r="A170" s="43" t="n"/>
+      <c r="B170" s="44" t="n"/>
+      <c r="C170" s="44" t="n"/>
+      <c r="D170" s="44" t="n"/>
+      <c r="E170" s="44" t="n"/>
+      <c r="F170" s="44" t="n"/>
+      <c r="G170" s="44" t="n"/>
+      <c r="H170" s="44" t="n"/>
+      <c r="I170" s="44" t="n"/>
+    </row>
+    <row r="171" ht="19.5" customHeight="1" s="33">
+      <c r="A171" s="41" t="n"/>
+      <c r="B171" s="42" t="n"/>
+      <c r="C171" s="42" t="n"/>
+      <c r="D171" s="42" t="n"/>
+      <c r="E171" s="42" t="n"/>
+      <c r="F171" s="42" t="n"/>
+      <c r="G171" s="42" t="n"/>
+      <c r="H171" s="42" t="n"/>
+      <c r="I171" s="42" t="n"/>
+    </row>
+    <row r="172" ht="19.5" customHeight="1" s="33">
+      <c r="A172" s="43" t="n"/>
+      <c r="B172" s="44" t="n"/>
+      <c r="C172" s="44" t="n"/>
+      <c r="D172" s="44" t="n"/>
+      <c r="E172" s="44" t="n"/>
+      <c r="F172" s="44" t="n"/>
+      <c r="G172" s="44" t="n"/>
+      <c r="H172" s="44" t="n"/>
+      <c r="I172" s="44" t="n"/>
+    </row>
+    <row r="173" ht="19.5" customHeight="1" s="33">
+      <c r="A173" s="41" t="n"/>
+      <c r="B173" s="42" t="n"/>
+      <c r="C173" s="42" t="n"/>
+      <c r="D173" s="42" t="n"/>
+      <c r="E173" s="42" t="n"/>
+      <c r="F173" s="42" t="n"/>
+      <c r="G173" s="42" t="n"/>
+      <c r="H173" s="42" t="n"/>
+      <c r="I173" s="42" t="n"/>
+    </row>
+    <row r="174" ht="19.5" customHeight="1" s="33">
+      <c r="A174" s="43" t="n"/>
+      <c r="B174" s="44" t="n"/>
+      <c r="C174" s="44" t="n"/>
+      <c r="D174" s="44" t="n"/>
+      <c r="E174" s="44" t="n"/>
+      <c r="F174" s="44" t="n"/>
+      <c r="G174" s="44" t="n"/>
+      <c r="H174" s="44" t="n"/>
+      <c r="I174" s="44" t="n"/>
+    </row>
+    <row r="175" ht="19.5" customHeight="1" s="33">
+      <c r="A175" s="41" t="n"/>
+      <c r="B175" s="42" t="n"/>
+      <c r="C175" s="42" t="n"/>
+      <c r="D175" s="42" t="n"/>
+      <c r="E175" s="42" t="n"/>
+      <c r="F175" s="42" t="n"/>
+      <c r="G175" s="42" t="n"/>
+      <c r="H175" s="42" t="n"/>
+      <c r="I175" s="42" t="n"/>
+    </row>
+    <row r="176" ht="19.5" customHeight="1" s="33">
+      <c r="A176" s="43" t="n"/>
+      <c r="B176" s="44" t="n"/>
+      <c r="C176" s="44" t="n"/>
+      <c r="D176" s="44" t="n"/>
+      <c r="E176" s="44" t="n"/>
+      <c r="F176" s="44" t="n"/>
+      <c r="G176" s="44" t="n"/>
+      <c r="H176" s="44" t="n"/>
+      <c r="I176" s="44" t="n"/>
+    </row>
+    <row r="177" ht="19.5" customHeight="1" s="33">
+      <c r="A177" s="41" t="n"/>
+      <c r="B177" s="42" t="n"/>
+      <c r="C177" s="42" t="n"/>
+      <c r="D177" s="42" t="n"/>
+      <c r="E177" s="42" t="n"/>
+      <c r="F177" s="42" t="n"/>
+      <c r="G177" s="42" t="n"/>
+      <c r="H177" s="42" t="n"/>
+      <c r="I177" s="42" t="n"/>
+    </row>
+    <row r="178" ht="19.5" customHeight="1" s="33">
+      <c r="A178" s="43" t="n"/>
+      <c r="B178" s="44" t="n"/>
+      <c r="C178" s="44" t="n"/>
+      <c r="D178" s="44" t="n"/>
+      <c r="E178" s="44" t="n"/>
+      <c r="F178" s="44" t="n"/>
+      <c r="G178" s="44" t="n"/>
+      <c r="H178" s="44" t="n"/>
+      <c r="I178" s="44" t="n"/>
+    </row>
+    <row r="179" ht="19.5" customHeight="1" s="33">
+      <c r="A179" s="41" t="n"/>
+      <c r="B179" s="42" t="n"/>
+      <c r="C179" s="42" t="n"/>
+      <c r="D179" s="42" t="n"/>
+      <c r="E179" s="42" t="n"/>
+      <c r="F179" s="42" t="n"/>
+      <c r="G179" s="42" t="n"/>
+      <c r="H179" s="42" t="n"/>
+      <c r="I179" s="42" t="n"/>
+    </row>
+    <row r="180" ht="19.5" customHeight="1" s="33">
+      <c r="A180" s="43" t="n"/>
+      <c r="B180" s="44" t="n"/>
+      <c r="C180" s="44" t="n"/>
+      <c r="D180" s="44" t="n"/>
+      <c r="E180" s="44" t="n"/>
+      <c r="F180" s="44" t="n"/>
+      <c r="G180" s="44" t="n"/>
+      <c r="H180" s="44" t="n"/>
+      <c r="I180" s="44" t="n"/>
+    </row>
+    <row r="181" ht="19.5" customHeight="1" s="33">
+      <c r="A181" s="41" t="n"/>
+      <c r="B181" s="42" t="n"/>
+      <c r="C181" s="42" t="n"/>
+      <c r="D181" s="42" t="n"/>
+      <c r="E181" s="42" t="n"/>
+      <c r="F181" s="42" t="n"/>
+      <c r="G181" s="42" t="n"/>
+      <c r="H181" s="42" t="n"/>
+      <c r="I181" s="42" t="n"/>
+    </row>
+    <row r="182" ht="19.5" customHeight="1" s="33">
+      <c r="A182" s="43" t="n"/>
+      <c r="B182" s="44" t="n"/>
+      <c r="C182" s="44" t="n"/>
+      <c r="D182" s="44" t="n"/>
+      <c r="E182" s="44" t="n"/>
+      <c r="F182" s="44" t="n"/>
+      <c r="G182" s="44" t="n"/>
+      <c r="H182" s="44" t="n"/>
+      <c r="I182" s="44" t="n"/>
+    </row>
+    <row r="183" ht="19.5" customHeight="1" s="33">
+      <c r="A183" s="41" t="n"/>
+      <c r="B183" s="42" t="n"/>
+      <c r="C183" s="42" t="n"/>
+      <c r="D183" s="42" t="n"/>
+      <c r="E183" s="42" t="n"/>
+      <c r="F183" s="42" t="n"/>
+      <c r="G183" s="42" t="n"/>
+      <c r="H183" s="42" t="n"/>
+      <c r="I183" s="42" t="n"/>
+    </row>
+    <row r="184" ht="19.5" customHeight="1" s="33">
+      <c r="A184" s="43" t="n"/>
+      <c r="B184" s="44" t="n"/>
+      <c r="C184" s="44" t="n"/>
+      <c r="D184" s="44" t="n"/>
+      <c r="E184" s="44" t="n"/>
+      <c r="F184" s="44" t="n"/>
+      <c r="G184" s="44" t="n"/>
+      <c r="H184" s="44" t="n"/>
+      <c r="I184" s="44" t="n"/>
+    </row>
+    <row r="185" ht="19.5" customHeight="1" s="33">
+      <c r="A185" s="41" t="n"/>
+      <c r="B185" s="42" t="n"/>
+      <c r="C185" s="42" t="n"/>
+      <c r="D185" s="42" t="n"/>
+      <c r="E185" s="42" t="n"/>
+      <c r="F185" s="42" t="n"/>
+      <c r="G185" s="42" t="n"/>
+      <c r="H185" s="42" t="n"/>
+      <c r="I185" s="42" t="n"/>
+    </row>
+    <row r="186" ht="19.5" customHeight="1" s="33">
+      <c r="A186" s="43" t="n"/>
+      <c r="B186" s="44" t="n"/>
+      <c r="C186" s="44" t="n"/>
+      <c r="D186" s="44" t="n"/>
+      <c r="E186" s="44" t="n"/>
+      <c r="F186" s="44" t="n"/>
+      <c r="G186" s="44" t="n"/>
+      <c r="H186" s="44" t="n"/>
+      <c r="I186" s="44" t="n"/>
+    </row>
+    <row r="187" ht="19.5" customHeight="1" s="33">
+      <c r="A187" s="41" t="n"/>
+      <c r="B187" s="42" t="n"/>
+      <c r="C187" s="42" t="n"/>
+      <c r="D187" s="42" t="n"/>
+      <c r="E187" s="42" t="n"/>
+      <c r="F187" s="42" t="n"/>
+      <c r="G187" s="42" t="n"/>
+      <c r="H187" s="42" t="n"/>
+      <c r="I187" s="42" t="n"/>
+    </row>
+    <row r="188" ht="19.5" customHeight="1" s="33">
+      <c r="A188" s="43" t="n"/>
+      <c r="B188" s="44" t="n"/>
+      <c r="C188" s="44" t="n"/>
+      <c r="D188" s="44" t="n"/>
+      <c r="E188" s="44" t="n"/>
+      <c r="F188" s="44" t="n"/>
+      <c r="G188" s="44" t="n"/>
+      <c r="H188" s="44" t="n"/>
+      <c r="I188" s="44" t="n"/>
+    </row>
+    <row r="189" ht="19.5" customHeight="1" s="33">
+      <c r="A189" s="41" t="n"/>
+      <c r="B189" s="42" t="n"/>
+      <c r="C189" s="42" t="n"/>
+      <c r="D189" s="42" t="n"/>
+      <c r="E189" s="42" t="n"/>
+      <c r="F189" s="42" t="n"/>
+      <c r="G189" s="42" t="n"/>
+      <c r="H189" s="42" t="n"/>
+      <c r="I189" s="42" t="n"/>
+    </row>
+    <row r="190" ht="19.5" customHeight="1" s="33">
+      <c r="A190" s="43" t="n"/>
+      <c r="B190" s="44" t="n"/>
+      <c r="C190" s="44" t="n"/>
+      <c r="D190" s="44" t="n"/>
+      <c r="E190" s="44" t="n"/>
+      <c r="F190" s="44" t="n"/>
+      <c r="G190" s="44" t="n"/>
+      <c r="H190" s="44" t="n"/>
+      <c r="I190" s="44" t="n"/>
+    </row>
+    <row r="191" ht="19.5" customHeight="1" s="33">
+      <c r="A191" s="41" t="n"/>
+      <c r="B191" s="42" t="n"/>
+      <c r="C191" s="42" t="n"/>
+      <c r="D191" s="42" t="n"/>
+      <c r="E191" s="42" t="n"/>
+      <c r="F191" s="42" t="n"/>
+      <c r="G191" s="42" t="n"/>
+      <c r="H191" s="42" t="n"/>
+      <c r="I191" s="42" t="n"/>
+    </row>
+    <row r="192" ht="19.5" customHeight="1" s="33">
+      <c r="A192" s="43" t="n"/>
+      <c r="B192" s="44" t="n"/>
+      <c r="C192" s="44" t="n"/>
+      <c r="D192" s="44" t="n"/>
+      <c r="E192" s="44" t="n"/>
+      <c r="F192" s="44" t="n"/>
+      <c r="G192" s="44" t="n"/>
+      <c r="H192" s="44" t="n"/>
+      <c r="I192" s="44" t="n"/>
+    </row>
+    <row r="193" ht="19.5" customHeight="1" s="33">
+      <c r="A193" s="41" t="n"/>
+      <c r="B193" s="42" t="n"/>
+      <c r="C193" s="42" t="n"/>
+      <c r="D193" s="42" t="n"/>
+      <c r="E193" s="42" t="n"/>
+      <c r="F193" s="42" t="n"/>
+      <c r="G193" s="42" t="n"/>
+      <c r="H193" s="42" t="n"/>
+      <c r="I193" s="42" t="n"/>
+    </row>
+    <row r="194" ht="19.5" customHeight="1" s="33">
+      <c r="A194" s="43" t="n"/>
+      <c r="B194" s="44" t="n"/>
+      <c r="C194" s="44" t="n"/>
+      <c r="D194" s="44" t="n"/>
+      <c r="E194" s="44" t="n"/>
+      <c r="F194" s="44" t="n"/>
+      <c r="G194" s="44" t="n"/>
+      <c r="H194" s="44" t="n"/>
+      <c r="I194" s="44" t="n"/>
+    </row>
+    <row r="195" ht="19.5" customHeight="1" s="33">
+      <c r="A195" s="41" t="n"/>
+      <c r="B195" s="42" t="n"/>
+      <c r="C195" s="42" t="n"/>
+      <c r="D195" s="42" t="n"/>
+      <c r="E195" s="42" t="n"/>
+      <c r="F195" s="42" t="n"/>
+      <c r="G195" s="42" t="n"/>
+      <c r="H195" s="42" t="n"/>
+      <c r="I195" s="42" t="n"/>
+    </row>
+    <row r="196" ht="19.5" customHeight="1" s="33">
+      <c r="A196" s="43" t="n"/>
+      <c r="B196" s="44" t="n"/>
+      <c r="C196" s="44" t="n"/>
+      <c r="D196" s="44" t="n"/>
+      <c r="E196" s="44" t="n"/>
+      <c r="F196" s="44" t="n"/>
+      <c r="G196" s="44" t="n"/>
+      <c r="H196" s="44" t="n"/>
+      <c r="I196" s="44" t="n"/>
+    </row>
+    <row r="197" ht="19.5" customHeight="1" s="33">
+      <c r="A197" s="41" t="n"/>
+      <c r="B197" s="42" t="n"/>
+      <c r="C197" s="42" t="n"/>
+      <c r="D197" s="42" t="n"/>
+      <c r="E197" s="42" t="n"/>
+      <c r="F197" s="42" t="n"/>
+      <c r="G197" s="42" t="n"/>
+      <c r="H197" s="42" t="n"/>
+      <c r="I197" s="42" t="n"/>
+    </row>
+    <row r="198" ht="19.5" customHeight="1" s="33">
+      <c r="A198" s="43" t="n"/>
+      <c r="B198" s="44" t="n"/>
+      <c r="C198" s="44" t="n"/>
+      <c r="D198" s="44" t="n"/>
+      <c r="E198" s="44" t="n"/>
+      <c r="F198" s="44" t="n"/>
+      <c r="G198" s="44" t="n"/>
+      <c r="H198" s="44" t="n"/>
+      <c r="I198" s="44" t="n"/>
+    </row>
+    <row r="199" ht="19.5" customHeight="1" s="33">
+      <c r="A199" s="41" t="n"/>
+      <c r="B199" s="42" t="n"/>
+      <c r="C199" s="42" t="n"/>
+      <c r="D199" s="42" t="n"/>
+      <c r="E199" s="42" t="n"/>
+      <c r="F199" s="42" t="n"/>
+      <c r="G199" s="42" t="n"/>
+      <c r="H199" s="42" t="n"/>
+      <c r="I199" s="42" t="n"/>
+    </row>
+    <row r="200" ht="19.5" customHeight="1" s="33">
+      <c r="A200" s="43" t="n"/>
+      <c r="B200" s="44" t="n"/>
+      <c r="C200" s="44" t="n"/>
+      <c r="D200" s="44" t="n"/>
+      <c r="E200" s="44" t="n"/>
+      <c r="F200" s="44" t="n"/>
+      <c r="G200" s="44" t="n"/>
+      <c r="H200" s="44" t="n"/>
+      <c r="I200" s="44" t="n"/>
+    </row>
+    <row r="201" ht="19.5" customHeight="1" s="33">
+      <c r="A201" s="41" t="n"/>
+      <c r="B201" s="42" t="n"/>
+      <c r="C201" s="42" t="n"/>
+      <c r="D201" s="42" t="n"/>
+      <c r="E201" s="42" t="n"/>
+      <c r="F201" s="42" t="n"/>
+      <c r="G201" s="42" t="n"/>
+      <c r="H201" s="42" t="n"/>
+      <c r="I201" s="42" t="n"/>
+    </row>
+    <row r="202" ht="19.5" customHeight="1" s="33">
+      <c r="A202" s="43" t="n"/>
+      <c r="B202" s="44" t="n"/>
+      <c r="C202" s="44" t="n"/>
+      <c r="D202" s="44" t="n"/>
+      <c r="E202" s="44" t="n"/>
+      <c r="F202" s="44" t="n"/>
+      <c r="G202" s="44" t="n"/>
+      <c r="H202" s="44" t="n"/>
+      <c r="I202" s="44" t="n"/>
+    </row>
+    <row r="203" ht="15" customHeight="1" s="33">
+      <c r="A203" s="45" t="n"/>
+      <c r="B203" s="32" t="n"/>
+      <c r="C203" s="32" t="n"/>
+      <c r="D203" s="32" t="n"/>
+      <c r="E203" s="32" t="n"/>
+      <c r="F203" s="32" t="n"/>
+      <c r="G203" s="46" t="n"/>
+      <c r="H203" s="46" t="n"/>
+      <c r="I203" s="46" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -19354,7 +21172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="32" min="1" max="1"/>
@@ -20530,23 +22348,793 @@
       <c r="F82" s="44" t="n"/>
     </row>
     <row r="83" ht="15" customHeight="1" s="33">
-      <c r="A83" s="58" t="inlineStr">
+      <c r="A83" s="41" t="n"/>
+      <c r="B83" s="42" t="n"/>
+      <c r="C83" s="42" t="n"/>
+      <c r="D83" s="42" t="n"/>
+      <c r="E83" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F83" s="42" t="n"/>
+    </row>
+    <row r="84" ht="15" customHeight="1" s="33">
+      <c r="A84" s="43" t="n"/>
+      <c r="B84" s="44" t="n"/>
+      <c r="C84" s="44" t="n"/>
+      <c r="D84" s="44" t="n"/>
+      <c r="E84" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F84" s="44" t="n"/>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="33">
+      <c r="A85" s="41" t="n"/>
+      <c r="B85" s="42" t="n"/>
+      <c r="C85" s="42" t="n"/>
+      <c r="D85" s="42" t="n"/>
+      <c r="E85" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F85" s="42" t="n"/>
+    </row>
+    <row r="86" ht="15" customHeight="1" s="33">
+      <c r="A86" s="43" t="n"/>
+      <c r="B86" s="44" t="n"/>
+      <c r="C86" s="44" t="n"/>
+      <c r="D86" s="44" t="n"/>
+      <c r="E86" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F86" s="44" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="33">
+      <c r="A87" s="41" t="n"/>
+      <c r="B87" s="42" t="n"/>
+      <c r="C87" s="42" t="n"/>
+      <c r="D87" s="42" t="n"/>
+      <c r="E87" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F87" s="42" t="n"/>
+    </row>
+    <row r="88" ht="15" customHeight="1" s="33">
+      <c r="A88" s="43" t="n"/>
+      <c r="B88" s="44" t="n"/>
+      <c r="C88" s="44" t="n"/>
+      <c r="D88" s="44" t="n"/>
+      <c r="E88" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F88" s="44" t="n"/>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="33">
+      <c r="A89" s="41" t="n"/>
+      <c r="B89" s="42" t="n"/>
+      <c r="C89" s="42" t="n"/>
+      <c r="D89" s="42" t="n"/>
+      <c r="E89" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F89" s="42" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="33">
+      <c r="A90" s="43" t="n"/>
+      <c r="B90" s="44" t="n"/>
+      <c r="C90" s="44" t="n"/>
+      <c r="D90" s="44" t="n"/>
+      <c r="E90" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F90" s="44" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1" s="33">
+      <c r="A91" s="41" t="n"/>
+      <c r="B91" s="42" t="n"/>
+      <c r="C91" s="42" t="n"/>
+      <c r="D91" s="42" t="n"/>
+      <c r="E91" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F91" s="42" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1" s="33">
+      <c r="A92" s="43" t="n"/>
+      <c r="B92" s="44" t="n"/>
+      <c r="C92" s="44" t="n"/>
+      <c r="D92" s="44" t="n"/>
+      <c r="E92" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F92" s="44" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1" s="33">
+      <c r="A93" s="41" t="n"/>
+      <c r="B93" s="42" t="n"/>
+      <c r="C93" s="42" t="n"/>
+      <c r="D93" s="42" t="n"/>
+      <c r="E93" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F93" s="42" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1" s="33">
+      <c r="A94" s="43" t="n"/>
+      <c r="B94" s="44" t="n"/>
+      <c r="C94" s="44" t="n"/>
+      <c r="D94" s="44" t="n"/>
+      <c r="E94" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F94" s="44" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="33">
+      <c r="A95" s="41" t="n"/>
+      <c r="B95" s="42" t="n"/>
+      <c r="C95" s="42" t="n"/>
+      <c r="D95" s="42" t="n"/>
+      <c r="E95" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F95" s="42" t="n"/>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="33">
+      <c r="A96" s="43" t="n"/>
+      <c r="B96" s="44" t="n"/>
+      <c r="C96" s="44" t="n"/>
+      <c r="D96" s="44" t="n"/>
+      <c r="E96" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F96" s="44" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="33">
+      <c r="A97" s="41" t="n"/>
+      <c r="B97" s="42" t="n"/>
+      <c r="C97" s="42" t="n"/>
+      <c r="D97" s="42" t="n"/>
+      <c r="E97" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F97" s="42" t="n"/>
+    </row>
+    <row r="98" ht="15" customHeight="1" s="33">
+      <c r="A98" s="43" t="n"/>
+      <c r="B98" s="44" t="n"/>
+      <c r="C98" s="44" t="n"/>
+      <c r="D98" s="44" t="n"/>
+      <c r="E98" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F98" s="44" t="n"/>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="33">
+      <c r="A99" s="41" t="n"/>
+      <c r="B99" s="42" t="n"/>
+      <c r="C99" s="42" t="n"/>
+      <c r="D99" s="42" t="n"/>
+      <c r="E99" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F99" s="42" t="n"/>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="33">
+      <c r="A100" s="43" t="n"/>
+      <c r="B100" s="44" t="n"/>
+      <c r="C100" s="44" t="n"/>
+      <c r="D100" s="44" t="n"/>
+      <c r="E100" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F100" s="44" t="n"/>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="33">
+      <c r="A101" s="41" t="n"/>
+      <c r="B101" s="42" t="n"/>
+      <c r="C101" s="42" t="n"/>
+      <c r="D101" s="42" t="n"/>
+      <c r="E101" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F101" s="42" t="n"/>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="33">
+      <c r="A102" s="43" t="n"/>
+      <c r="B102" s="44" t="n"/>
+      <c r="C102" s="44" t="n"/>
+      <c r="D102" s="44" t="n"/>
+      <c r="E102" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F102" s="44" t="n"/>
+    </row>
+    <row r="103" ht="15" customHeight="1" s="33">
+      <c r="A103" s="41" t="n"/>
+      <c r="B103" s="42" t="n"/>
+      <c r="C103" s="42" t="n"/>
+      <c r="D103" s="42" t="n"/>
+      <c r="E103" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F103" s="42" t="n"/>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="33">
+      <c r="A104" s="43" t="n"/>
+      <c r="B104" s="44" t="n"/>
+      <c r="C104" s="44" t="n"/>
+      <c r="D104" s="44" t="n"/>
+      <c r="E104" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F104" s="44" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1" s="33">
+      <c r="A105" s="41" t="n"/>
+      <c r="B105" s="42" t="n"/>
+      <c r="C105" s="42" t="n"/>
+      <c r="D105" s="42" t="n"/>
+      <c r="E105" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F105" s="42" t="n"/>
+    </row>
+    <row r="106" ht="15" customHeight="1" s="33">
+      <c r="A106" s="43" t="n"/>
+      <c r="B106" s="44" t="n"/>
+      <c r="C106" s="44" t="n"/>
+      <c r="D106" s="44" t="n"/>
+      <c r="E106" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F106" s="44" t="n"/>
+    </row>
+    <row r="107" ht="15" customHeight="1" s="33">
+      <c r="A107" s="41" t="n"/>
+      <c r="B107" s="42" t="n"/>
+      <c r="C107" s="42" t="n"/>
+      <c r="D107" s="42" t="n"/>
+      <c r="E107" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F107" s="42" t="n"/>
+    </row>
+    <row r="108" ht="15" customHeight="1" s="33">
+      <c r="A108" s="43" t="n"/>
+      <c r="B108" s="44" t="n"/>
+      <c r="C108" s="44" t="n"/>
+      <c r="D108" s="44" t="n"/>
+      <c r="E108" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F108" s="44" t="n"/>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="33">
+      <c r="A109" s="41" t="n"/>
+      <c r="B109" s="42" t="n"/>
+      <c r="C109" s="42" t="n"/>
+      <c r="D109" s="42" t="n"/>
+      <c r="E109" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F109" s="42" t="n"/>
+    </row>
+    <row r="110" ht="15" customHeight="1" s="33">
+      <c r="A110" s="43" t="n"/>
+      <c r="B110" s="44" t="n"/>
+      <c r="C110" s="44" t="n"/>
+      <c r="D110" s="44" t="n"/>
+      <c r="E110" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F110" s="44" t="n"/>
+    </row>
+    <row r="111" ht="15" customHeight="1" s="33">
+      <c r="A111" s="41" t="n"/>
+      <c r="B111" s="42" t="n"/>
+      <c r="C111" s="42" t="n"/>
+      <c r="D111" s="42" t="n"/>
+      <c r="E111" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F111" s="42" t="n"/>
+    </row>
+    <row r="112" ht="15" customHeight="1" s="33">
+      <c r="A112" s="43" t="n"/>
+      <c r="B112" s="44" t="n"/>
+      <c r="C112" s="44" t="n"/>
+      <c r="D112" s="44" t="n"/>
+      <c r="E112" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F112" s="44" t="n"/>
+    </row>
+    <row r="113" ht="15" customHeight="1" s="33">
+      <c r="A113" s="41" t="n"/>
+      <c r="B113" s="42" t="n"/>
+      <c r="C113" s="42" t="n"/>
+      <c r="D113" s="42" t="n"/>
+      <c r="E113" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F113" s="42" t="n"/>
+    </row>
+    <row r="114" ht="15" customHeight="1" s="33">
+      <c r="A114" s="43" t="n"/>
+      <c r="B114" s="44" t="n"/>
+      <c r="C114" s="44" t="n"/>
+      <c r="D114" s="44" t="n"/>
+      <c r="E114" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F114" s="44" t="n"/>
+    </row>
+    <row r="115" ht="15" customHeight="1" s="33">
+      <c r="A115" s="41" t="n"/>
+      <c r="B115" s="42" t="n"/>
+      <c r="C115" s="42" t="n"/>
+      <c r="D115" s="42" t="n"/>
+      <c r="E115" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F115" s="42" t="n"/>
+    </row>
+    <row r="116" ht="15" customHeight="1" s="33">
+      <c r="A116" s="43" t="n"/>
+      <c r="B116" s="44" t="n"/>
+      <c r="C116" s="44" t="n"/>
+      <c r="D116" s="44" t="n"/>
+      <c r="E116" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F116" s="44" t="n"/>
+    </row>
+    <row r="117" ht="15" customHeight="1" s="33">
+      <c r="A117" s="41" t="n"/>
+      <c r="B117" s="42" t="n"/>
+      <c r="C117" s="42" t="n"/>
+      <c r="D117" s="42" t="n"/>
+      <c r="E117" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F117" s="42" t="n"/>
+    </row>
+    <row r="118" ht="15" customHeight="1" s="33">
+      <c r="A118" s="43" t="n"/>
+      <c r="B118" s="44" t="n"/>
+      <c r="C118" s="44" t="n"/>
+      <c r="D118" s="44" t="n"/>
+      <c r="E118" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F118" s="44" t="n"/>
+    </row>
+    <row r="119" ht="15" customHeight="1" s="33">
+      <c r="A119" s="41" t="n"/>
+      <c r="B119" s="42" t="n"/>
+      <c r="C119" s="42" t="n"/>
+      <c r="D119" s="42" t="n"/>
+      <c r="E119" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F119" s="42" t="n"/>
+    </row>
+    <row r="120" ht="15" customHeight="1" s="33">
+      <c r="A120" s="43" t="n"/>
+      <c r="B120" s="44" t="n"/>
+      <c r="C120" s="44" t="n"/>
+      <c r="D120" s="44" t="n"/>
+      <c r="E120" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F120" s="44" t="n"/>
+    </row>
+    <row r="121" ht="15" customHeight="1" s="33">
+      <c r="A121" s="41" t="n"/>
+      <c r="B121" s="42" t="n"/>
+      <c r="C121" s="42" t="n"/>
+      <c r="D121" s="42" t="n"/>
+      <c r="E121" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F121" s="42" t="n"/>
+    </row>
+    <row r="122" ht="15" customHeight="1" s="33">
+      <c r="A122" s="43" t="n"/>
+      <c r="B122" s="44" t="n"/>
+      <c r="C122" s="44" t="n"/>
+      <c r="D122" s="44" t="n"/>
+      <c r="E122" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F122" s="44" t="n"/>
+    </row>
+    <row r="123" ht="15" customHeight="1" s="33">
+      <c r="A123" s="41" t="n"/>
+      <c r="B123" s="42" t="n"/>
+      <c r="C123" s="42" t="n"/>
+      <c r="D123" s="42" t="n"/>
+      <c r="E123" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F123" s="42" t="n"/>
+    </row>
+    <row r="124" ht="15" customHeight="1" s="33">
+      <c r="A124" s="43" t="n"/>
+      <c r="B124" s="44" t="n"/>
+      <c r="C124" s="44" t="n"/>
+      <c r="D124" s="44" t="n"/>
+      <c r="E124" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F124" s="44" t="n"/>
+    </row>
+    <row r="125" ht="15" customHeight="1" s="33">
+      <c r="A125" s="41" t="n"/>
+      <c r="B125" s="42" t="n"/>
+      <c r="C125" s="42" t="n"/>
+      <c r="D125" s="42" t="n"/>
+      <c r="E125" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F125" s="42" t="n"/>
+    </row>
+    <row r="126" ht="15" customHeight="1" s="33">
+      <c r="A126" s="43" t="n"/>
+      <c r="B126" s="44" t="n"/>
+      <c r="C126" s="44" t="n"/>
+      <c r="D126" s="44" t="n"/>
+      <c r="E126" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F126" s="44" t="n"/>
+    </row>
+    <row r="127" ht="15" customHeight="1" s="33">
+      <c r="A127" s="41" t="n"/>
+      <c r="B127" s="42" t="n"/>
+      <c r="C127" s="42" t="n"/>
+      <c r="D127" s="42" t="n"/>
+      <c r="E127" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F127" s="42" t="n"/>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="33">
+      <c r="A128" s="43" t="n"/>
+      <c r="B128" s="44" t="n"/>
+      <c r="C128" s="44" t="n"/>
+      <c r="D128" s="44" t="n"/>
+      <c r="E128" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F128" s="44" t="n"/>
+    </row>
+    <row r="129" ht="15" customHeight="1" s="33">
+      <c r="A129" s="41" t="n"/>
+      <c r="B129" s="42" t="n"/>
+      <c r="C129" s="42" t="n"/>
+      <c r="D129" s="42" t="n"/>
+      <c r="E129" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F129" s="42" t="n"/>
+    </row>
+    <row r="130" ht="15" customHeight="1" s="33">
+      <c r="A130" s="43" t="n"/>
+      <c r="B130" s="44" t="n"/>
+      <c r="C130" s="44" t="n"/>
+      <c r="D130" s="44" t="n"/>
+      <c r="E130" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F130" s="44" t="n"/>
+    </row>
+    <row r="131" ht="15" customHeight="1" s="33">
+      <c r="A131" s="41" t="n"/>
+      <c r="B131" s="42" t="n"/>
+      <c r="C131" s="42" t="n"/>
+      <c r="D131" s="42" t="n"/>
+      <c r="E131" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F131" s="42" t="n"/>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="33">
+      <c r="A132" s="43" t="n"/>
+      <c r="B132" s="44" t="n"/>
+      <c r="C132" s="44" t="n"/>
+      <c r="D132" s="44" t="n"/>
+      <c r="E132" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F132" s="44" t="n"/>
+    </row>
+    <row r="133" ht="15" customHeight="1" s="33">
+      <c r="A133" s="41" t="n"/>
+      <c r="B133" s="42" t="n"/>
+      <c r="C133" s="42" t="n"/>
+      <c r="D133" s="42" t="n"/>
+      <c r="E133" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F133" s="42" t="n"/>
+    </row>
+    <row r="134" ht="15" customHeight="1" s="33">
+      <c r="A134" s="43" t="n"/>
+      <c r="B134" s="44" t="n"/>
+      <c r="C134" s="44" t="n"/>
+      <c r="D134" s="44" t="n"/>
+      <c r="E134" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F134" s="44" t="n"/>
+    </row>
+    <row r="135" ht="15" customHeight="1" s="33">
+      <c r="A135" s="41" t="n"/>
+      <c r="B135" s="42" t="n"/>
+      <c r="C135" s="42" t="n"/>
+      <c r="D135" s="42" t="n"/>
+      <c r="E135" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F135" s="42" t="n"/>
+    </row>
+    <row r="136" ht="15" customHeight="1" s="33">
+      <c r="A136" s="43" t="n"/>
+      <c r="B136" s="44" t="n"/>
+      <c r="C136" s="44" t="n"/>
+      <c r="D136" s="44" t="n"/>
+      <c r="E136" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F136" s="44" t="n"/>
+    </row>
+    <row r="137" ht="15" customHeight="1" s="33">
+      <c r="A137" s="41" t="n"/>
+      <c r="B137" s="42" t="n"/>
+      <c r="C137" s="42" t="n"/>
+      <c r="D137" s="42" t="n"/>
+      <c r="E137" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F137" s="42" t="n"/>
+    </row>
+    <row r="138" ht="15" customHeight="1" s="33">
+      <c r="A138" s="43" t="n"/>
+      <c r="B138" s="44" t="n"/>
+      <c r="C138" s="44" t="n"/>
+      <c r="D138" s="44" t="n"/>
+      <c r="E138" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F138" s="44" t="n"/>
+    </row>
+    <row r="139" ht="15" customHeight="1" s="33">
+      <c r="A139" s="41" t="n"/>
+      <c r="B139" s="42" t="n"/>
+      <c r="C139" s="42" t="n"/>
+      <c r="D139" s="42" t="n"/>
+      <c r="E139" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F139" s="42" t="n"/>
+    </row>
+    <row r="140" ht="15" customHeight="1" s="33">
+      <c r="A140" s="43" t="n"/>
+      <c r="B140" s="44" t="n"/>
+      <c r="C140" s="44" t="n"/>
+      <c r="D140" s="44" t="n"/>
+      <c r="E140" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F140" s="44" t="n"/>
+    </row>
+    <row r="141" ht="15" customHeight="1" s="33">
+      <c r="A141" s="41" t="n"/>
+      <c r="B141" s="42" t="n"/>
+      <c r="C141" s="42" t="n"/>
+      <c r="D141" s="42" t="n"/>
+      <c r="E141" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F141" s="42" t="n"/>
+    </row>
+    <row r="142" ht="15" customHeight="1" s="33">
+      <c r="A142" s="43" t="n"/>
+      <c r="B142" s="44" t="n"/>
+      <c r="C142" s="44" t="n"/>
+      <c r="D142" s="44" t="n"/>
+      <c r="E142" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F142" s="44" t="n"/>
+    </row>
+    <row r="143" ht="15" customHeight="1" s="33">
+      <c r="A143" s="41" t="n"/>
+      <c r="B143" s="42" t="n"/>
+      <c r="C143" s="42" t="n"/>
+      <c r="D143" s="42" t="n"/>
+      <c r="E143" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F143" s="42" t="n"/>
+    </row>
+    <row r="144" ht="15" customHeight="1" s="33">
+      <c r="A144" s="43" t="n"/>
+      <c r="B144" s="44" t="n"/>
+      <c r="C144" s="44" t="n"/>
+      <c r="D144" s="44" t="n"/>
+      <c r="E144" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F144" s="44" t="n"/>
+    </row>
+    <row r="145" ht="15" customHeight="1" s="33">
+      <c r="A145" s="41" t="n"/>
+      <c r="B145" s="42" t="n"/>
+      <c r="C145" s="42" t="n"/>
+      <c r="D145" s="42" t="n"/>
+      <c r="E145" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F145" s="42" t="n"/>
+    </row>
+    <row r="146" ht="15" customHeight="1" s="33">
+      <c r="A146" s="43" t="n"/>
+      <c r="B146" s="44" t="n"/>
+      <c r="C146" s="44" t="n"/>
+      <c r="D146" s="44" t="n"/>
+      <c r="E146" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F146" s="44" t="n"/>
+    </row>
+    <row r="147" ht="15" customHeight="1" s="33">
+      <c r="A147" s="41" t="n"/>
+      <c r="B147" s="42" t="n"/>
+      <c r="C147" s="42" t="n"/>
+      <c r="D147" s="42" t="n"/>
+      <c r="E147" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F147" s="42" t="n"/>
+    </row>
+    <row r="148" ht="15" customHeight="1" s="33">
+      <c r="A148" s="43" t="n"/>
+      <c r="B148" s="44" t="n"/>
+      <c r="C148" s="44" t="n"/>
+      <c r="D148" s="44" t="n"/>
+      <c r="E148" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F148" s="44" t="n"/>
+    </row>
+    <row r="149" ht="15" customHeight="1" s="33">
+      <c r="A149" s="41" t="n"/>
+      <c r="B149" s="42" t="n"/>
+      <c r="C149" s="42" t="n"/>
+      <c r="D149" s="42" t="n"/>
+      <c r="E149" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F149" s="42" t="n"/>
+    </row>
+    <row r="150" ht="15" customHeight="1" s="33">
+      <c r="A150" s="43" t="n"/>
+      <c r="B150" s="44" t="n"/>
+      <c r="C150" s="44" t="n"/>
+      <c r="D150" s="44" t="n"/>
+      <c r="E150" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F150" s="44" t="n"/>
+    </row>
+    <row r="151" ht="15" customHeight="1" s="33">
+      <c r="A151" s="41" t="n"/>
+      <c r="B151" s="42" t="n"/>
+      <c r="C151" s="42" t="n"/>
+      <c r="D151" s="42" t="n"/>
+      <c r="E151" s="54">
+        <f>IF(C81="","",VLOOKUP(C81,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F151" s="42" t="n"/>
+    </row>
+    <row r="152" ht="15" customHeight="1" s="33">
+      <c r="A152" s="43" t="n"/>
+      <c r="B152" s="44" t="n"/>
+      <c r="C152" s="44" t="n"/>
+      <c r="D152" s="44" t="n"/>
+      <c r="E152" s="57">
+        <f>IF(C82="","",VLOOKUP(C82,$J$3:$K$11,2,0))</f>
+        <v/>
+      </c>
+      <c r="F152" s="44" t="n"/>
+    </row>
+    <row r="153" ht="15" customHeight="1" s="33">
+      <c r="A153" s="58" t="inlineStr">
         <is>
           <t>합  계</t>
         </is>
       </c>
-      <c r="B83" s="35" t="n"/>
-      <c r="C83" s="35" t="n"/>
-      <c r="D83" s="35" t="n"/>
-      <c r="E83" s="59">
-        <f>IF(SUM(E3:E82)=0,"",SUM(E3:E82))</f>
-        <v/>
-      </c>
-      <c r="F83" s="60" t="n"/>
+      <c r="B153" s="35" t="n"/>
+      <c r="C153" s="35" t="n"/>
+      <c r="D153" s="35" t="n"/>
+      <c r="E153" s="59">
+        <f>IF(SUM(E3:E152)=0,"",SUM(E3:E152))</f>
+        <v/>
+      </c>
+      <c r="F153" s="60" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="A153:D153"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -22029,14 +24617,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
+      <c r="C2" s="87" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
+      <c r="J2" s="87" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -22829,7 +25417,7 @@
       <c r="D44" s="42" t="n"/>
       <c r="E44" s="42" t="n"/>
       <c r="F44" s="42" t="n"/>
-      <c r="H44" s="42" t="n">
+      <c r="H44" s="41" t="n">
         <v>41</v>
       </c>
       <c r="I44" s="42" t="n"/>
@@ -22847,7 +25435,7 @@
       <c r="D45" s="44" t="n"/>
       <c r="E45" s="44" t="n"/>
       <c r="F45" s="44" t="n"/>
-      <c r="H45" s="44" t="n">
+      <c r="H45" s="43" t="n">
         <v>42</v>
       </c>
       <c r="I45" s="44" t="n"/>
@@ -22865,7 +25453,7 @@
       <c r="D46" s="42" t="n"/>
       <c r="E46" s="42" t="n"/>
       <c r="F46" s="42" t="n"/>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="41" t="n">
         <v>43</v>
       </c>
       <c r="I46" s="42" t="n"/>
@@ -22875,13 +25463,17 @@
       <c r="M46" s="42" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="33">
-      <c r="A47" s="43" t="n"/>
+      <c r="A47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="B47" s="44" t="n"/>
       <c r="C47" s="44" t="n"/>
       <c r="D47" s="44" t="n"/>
       <c r="E47" s="44" t="n"/>
       <c r="F47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
+      <c r="H47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="I47" s="44" t="n"/>
       <c r="J47" s="44" t="n"/>
       <c r="K47" s="44" t="n"/>
@@ -22889,13 +25481,17 @@
       <c r="M47" s="44" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="33">
-      <c r="A48" s="41" t="n"/>
+      <c r="A48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="B48" s="42" t="n"/>
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
       <c r="F48" s="42" t="n"/>
-      <c r="H48" s="42" t="n"/>
+      <c r="H48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
       <c r="K48" s="42" t="n"/>
@@ -22998,14 +25594,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
+      <c r="C2" s="87" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
+      <c r="J2" s="87" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -23798,7 +26394,7 @@
       <c r="D44" s="42" t="n"/>
       <c r="E44" s="42" t="n"/>
       <c r="F44" s="42" t="n"/>
-      <c r="H44" s="42" t="n">
+      <c r="H44" s="41" t="n">
         <v>41</v>
       </c>
       <c r="I44" s="42" t="n"/>
@@ -23816,7 +26412,7 @@
       <c r="D45" s="44" t="n"/>
       <c r="E45" s="44" t="n"/>
       <c r="F45" s="44" t="n"/>
-      <c r="H45" s="44" t="n">
+      <c r="H45" s="43" t="n">
         <v>42</v>
       </c>
       <c r="I45" s="44" t="n"/>
@@ -23834,7 +26430,7 @@
       <c r="D46" s="42" t="n"/>
       <c r="E46" s="42" t="n"/>
       <c r="F46" s="42" t="n"/>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="41" t="n">
         <v>43</v>
       </c>
       <c r="I46" s="42" t="n"/>
@@ -23844,13 +26440,17 @@
       <c r="M46" s="42" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="33">
-      <c r="A47" s="43" t="n"/>
+      <c r="A47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="B47" s="44" t="n"/>
       <c r="C47" s="44" t="n"/>
       <c r="D47" s="44" t="n"/>
       <c r="E47" s="44" t="n"/>
       <c r="F47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
+      <c r="H47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="I47" s="44" t="n"/>
       <c r="J47" s="44" t="n"/>
       <c r="K47" s="44" t="n"/>
@@ -23858,13 +26458,17 @@
       <c r="M47" s="44" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="33">
-      <c r="A48" s="41" t="n"/>
+      <c r="A48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="B48" s="42" t="n"/>
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
       <c r="F48" s="42" t="n"/>
-      <c r="H48" s="42" t="n"/>
+      <c r="H48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
       <c r="K48" s="42" t="n"/>
@@ -23967,14 +26571,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
+      <c r="C2" s="87" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
+      <c r="J2" s="87" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -24767,7 +27371,7 @@
       <c r="D44" s="42" t="n"/>
       <c r="E44" s="42" t="n"/>
       <c r="F44" s="42" t="n"/>
-      <c r="H44" s="42" t="n">
+      <c r="H44" s="41" t="n">
         <v>41</v>
       </c>
       <c r="I44" s="42" t="n"/>
@@ -24785,7 +27389,7 @@
       <c r="D45" s="44" t="n"/>
       <c r="E45" s="44" t="n"/>
       <c r="F45" s="44" t="n"/>
-      <c r="H45" s="44" t="n">
+      <c r="H45" s="43" t="n">
         <v>42</v>
       </c>
       <c r="I45" s="44" t="n"/>
@@ -24803,7 +27407,7 @@
       <c r="D46" s="42" t="n"/>
       <c r="E46" s="42" t="n"/>
       <c r="F46" s="42" t="n"/>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="41" t="n">
         <v>43</v>
       </c>
       <c r="I46" s="42" t="n"/>
@@ -24813,13 +27417,17 @@
       <c r="M46" s="42" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="33">
-      <c r="A47" s="43" t="n"/>
+      <c r="A47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="B47" s="44" t="n"/>
       <c r="C47" s="44" t="n"/>
       <c r="D47" s="44" t="n"/>
       <c r="E47" s="44" t="n"/>
       <c r="F47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
+      <c r="H47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="I47" s="44" t="n"/>
       <c r="J47" s="44" t="n"/>
       <c r="K47" s="44" t="n"/>
@@ -24827,13 +27435,17 @@
       <c r="M47" s="44" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="33">
-      <c r="A48" s="41" t="n"/>
+      <c r="A48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="B48" s="42" t="n"/>
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
       <c r="F48" s="42" t="n"/>
-      <c r="H48" s="42" t="n"/>
+      <c r="H48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
       <c r="K48" s="42" t="n"/>
@@ -24936,14 +27548,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
+      <c r="C2" s="87" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
+      <c r="J2" s="87" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -25736,7 +28348,7 @@
       <c r="D44" s="42" t="n"/>
       <c r="E44" s="42" t="n"/>
       <c r="F44" s="42" t="n"/>
-      <c r="H44" s="42" t="n">
+      <c r="H44" s="41" t="n">
         <v>41</v>
       </c>
       <c r="I44" s="42" t="n"/>
@@ -25754,7 +28366,7 @@
       <c r="D45" s="44" t="n"/>
       <c r="E45" s="44" t="n"/>
       <c r="F45" s="44" t="n"/>
-      <c r="H45" s="44" t="n">
+      <c r="H45" s="43" t="n">
         <v>42</v>
       </c>
       <c r="I45" s="44" t="n"/>
@@ -25772,7 +28384,7 @@
       <c r="D46" s="42" t="n"/>
       <c r="E46" s="42" t="n"/>
       <c r="F46" s="42" t="n"/>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="41" t="n">
         <v>43</v>
       </c>
       <c r="I46" s="42" t="n"/>
@@ -25782,13 +28394,17 @@
       <c r="M46" s="42" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="33">
-      <c r="A47" s="43" t="n"/>
+      <c r="A47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="B47" s="44" t="n"/>
       <c r="C47" s="44" t="n"/>
       <c r="D47" s="44" t="n"/>
       <c r="E47" s="44" t="n"/>
       <c r="F47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
+      <c r="H47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="I47" s="44" t="n"/>
       <c r="J47" s="44" t="n"/>
       <c r="K47" s="44" t="n"/>
@@ -25796,13 +28412,17 @@
       <c r="M47" s="44" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="33">
-      <c r="A48" s="41" t="n"/>
+      <c r="A48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="B48" s="42" t="n"/>
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
       <c r="F48" s="42" t="n"/>
-      <c r="H48" s="42" t="n"/>
+      <c r="H48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
       <c r="K48" s="42" t="n"/>
@@ -25905,14 +28525,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
+      <c r="C2" s="87" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
+      <c r="J2" s="87" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -26705,7 +29325,7 @@
       <c r="D44" s="42" t="n"/>
       <c r="E44" s="42" t="n"/>
       <c r="F44" s="42" t="n"/>
-      <c r="H44" s="42" t="n">
+      <c r="H44" s="41" t="n">
         <v>41</v>
       </c>
       <c r="I44" s="42" t="n"/>
@@ -26723,7 +29343,7 @@
       <c r="D45" s="44" t="n"/>
       <c r="E45" s="44" t="n"/>
       <c r="F45" s="44" t="n"/>
-      <c r="H45" s="44" t="n">
+      <c r="H45" s="43" t="n">
         <v>42</v>
       </c>
       <c r="I45" s="44" t="n"/>
@@ -26741,7 +29361,7 @@
       <c r="D46" s="42" t="n"/>
       <c r="E46" s="42" t="n"/>
       <c r="F46" s="42" t="n"/>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="41" t="n">
         <v>43</v>
       </c>
       <c r="I46" s="42" t="n"/>
@@ -26751,13 +29371,17 @@
       <c r="M46" s="42" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="33">
-      <c r="A47" s="43" t="n"/>
+      <c r="A47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="B47" s="44" t="n"/>
       <c r="C47" s="44" t="n"/>
       <c r="D47" s="44" t="n"/>
       <c r="E47" s="44" t="n"/>
       <c r="F47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
+      <c r="H47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="I47" s="44" t="n"/>
       <c r="J47" s="44" t="n"/>
       <c r="K47" s="44" t="n"/>
@@ -26765,13 +29389,17 @@
       <c r="M47" s="44" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="33">
-      <c r="A48" s="41" t="n"/>
+      <c r="A48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="B48" s="42" t="n"/>
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
       <c r="F48" s="42" t="n"/>
-      <c r="H48" s="42" t="n"/>
+      <c r="H48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
       <c r="K48" s="42" t="n"/>
@@ -28204,14 +30832,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
+      <c r="C2" s="87" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
+      <c r="J2" s="87" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -29004,7 +31632,7 @@
       <c r="D44" s="42" t="n"/>
       <c r="E44" s="42" t="n"/>
       <c r="F44" s="42" t="n"/>
-      <c r="H44" s="42" t="n">
+      <c r="H44" s="41" t="n">
         <v>41</v>
       </c>
       <c r="I44" s="42" t="n"/>
@@ -29022,7 +31650,7 @@
       <c r="D45" s="44" t="n"/>
       <c r="E45" s="44" t="n"/>
       <c r="F45" s="44" t="n"/>
-      <c r="H45" s="44" t="n">
+      <c r="H45" s="43" t="n">
         <v>42</v>
       </c>
       <c r="I45" s="44" t="n"/>
@@ -29040,7 +31668,7 @@
       <c r="D46" s="42" t="n"/>
       <c r="E46" s="42" t="n"/>
       <c r="F46" s="42" t="n"/>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="41" t="n">
         <v>43</v>
       </c>
       <c r="I46" s="42" t="n"/>
@@ -29050,13 +31678,17 @@
       <c r="M46" s="42" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="33">
-      <c r="A47" s="43" t="n"/>
+      <c r="A47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="B47" s="44" t="n"/>
       <c r="C47" s="44" t="n"/>
       <c r="D47" s="44" t="n"/>
       <c r="E47" s="44" t="n"/>
       <c r="F47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
+      <c r="H47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="I47" s="44" t="n"/>
       <c r="J47" s="44" t="n"/>
       <c r="K47" s="44" t="n"/>
@@ -29064,13 +31696,17 @@
       <c r="M47" s="44" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="33">
-      <c r="A48" s="41" t="n"/>
+      <c r="A48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="B48" s="42" t="n"/>
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
       <c r="F48" s="42" t="n"/>
-      <c r="H48" s="42" t="n"/>
+      <c r="H48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
       <c r="K48" s="42" t="n"/>
@@ -29173,14 +31809,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
+      <c r="C2" s="87" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
+      <c r="J2" s="87" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -29973,7 +32609,7 @@
       <c r="D44" s="42" t="n"/>
       <c r="E44" s="42" t="n"/>
       <c r="F44" s="42" t="n"/>
-      <c r="H44" s="42" t="n">
+      <c r="H44" s="41" t="n">
         <v>41</v>
       </c>
       <c r="I44" s="42" t="n"/>
@@ -29991,7 +32627,7 @@
       <c r="D45" s="44" t="n"/>
       <c r="E45" s="44" t="n"/>
       <c r="F45" s="44" t="n"/>
-      <c r="H45" s="44" t="n">
+      <c r="H45" s="43" t="n">
         <v>42</v>
       </c>
       <c r="I45" s="44" t="n"/>
@@ -30009,7 +32645,7 @@
       <c r="D46" s="42" t="n"/>
       <c r="E46" s="42" t="n"/>
       <c r="F46" s="42" t="n"/>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="41" t="n">
         <v>43</v>
       </c>
       <c r="I46" s="42" t="n"/>
@@ -30019,13 +32655,17 @@
       <c r="M46" s="42" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="33">
-      <c r="A47" s="43" t="n"/>
+      <c r="A47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="B47" s="44" t="n"/>
       <c r="C47" s="44" t="n"/>
       <c r="D47" s="44" t="n"/>
       <c r="E47" s="44" t="n"/>
       <c r="F47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
+      <c r="H47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="I47" s="44" t="n"/>
       <c r="J47" s="44" t="n"/>
       <c r="K47" s="44" t="n"/>
@@ -30033,13 +32673,17 @@
       <c r="M47" s="44" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="33">
-      <c r="A48" s="41" t="n"/>
+      <c r="A48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="B48" s="42" t="n"/>
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
       <c r="F48" s="42" t="n"/>
-      <c r="H48" s="42" t="n"/>
+      <c r="H48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
       <c r="K48" s="42" t="n"/>
@@ -30142,14 +32786,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
+      <c r="C2" s="87" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
+      <c r="J2" s="87" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -30942,7 +33586,7 @@
       <c r="D44" s="42" t="n"/>
       <c r="E44" s="42" t="n"/>
       <c r="F44" s="42" t="n"/>
-      <c r="H44" s="42" t="n">
+      <c r="H44" s="41" t="n">
         <v>41</v>
       </c>
       <c r="I44" s="42" t="n"/>
@@ -30960,7 +33604,7 @@
       <c r="D45" s="44" t="n"/>
       <c r="E45" s="44" t="n"/>
       <c r="F45" s="44" t="n"/>
-      <c r="H45" s="44" t="n">
+      <c r="H45" s="43" t="n">
         <v>42</v>
       </c>
       <c r="I45" s="44" t="n"/>
@@ -30978,7 +33622,7 @@
       <c r="D46" s="42" t="n"/>
       <c r="E46" s="42" t="n"/>
       <c r="F46" s="42" t="n"/>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="41" t="n">
         <v>43</v>
       </c>
       <c r="I46" s="42" t="n"/>
@@ -30988,13 +33632,17 @@
       <c r="M46" s="42" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="33">
-      <c r="A47" s="43" t="n"/>
+      <c r="A47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="B47" s="44" t="n"/>
       <c r="C47" s="44" t="n"/>
       <c r="D47" s="44" t="n"/>
       <c r="E47" s="44" t="n"/>
       <c r="F47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
+      <c r="H47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="I47" s="44" t="n"/>
       <c r="J47" s="44" t="n"/>
       <c r="K47" s="44" t="n"/>
@@ -31002,13 +33650,17 @@
       <c r="M47" s="44" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="33">
-      <c r="A48" s="41" t="n"/>
+      <c r="A48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="B48" s="42" t="n"/>
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
       <c r="F48" s="42" t="n"/>
-      <c r="H48" s="42" t="n"/>
+      <c r="H48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
       <c r="K48" s="42" t="n"/>
@@ -31111,14 +33763,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
+      <c r="C2" s="87" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
+      <c r="J2" s="87" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -31911,7 +34563,7 @@
       <c r="D44" s="42" t="n"/>
       <c r="E44" s="42" t="n"/>
       <c r="F44" s="42" t="n"/>
-      <c r="H44" s="42" t="n">
+      <c r="H44" s="41" t="n">
         <v>41</v>
       </c>
       <c r="I44" s="42" t="n"/>
@@ -31929,7 +34581,7 @@
       <c r="D45" s="44" t="n"/>
       <c r="E45" s="44" t="n"/>
       <c r="F45" s="44" t="n"/>
-      <c r="H45" s="44" t="n">
+      <c r="H45" s="43" t="n">
         <v>42</v>
       </c>
       <c r="I45" s="44" t="n"/>
@@ -31947,7 +34599,7 @@
       <c r="D46" s="42" t="n"/>
       <c r="E46" s="42" t="n"/>
       <c r="F46" s="42" t="n"/>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="41" t="n">
         <v>43</v>
       </c>
       <c r="I46" s="42" t="n"/>
@@ -31957,13 +34609,17 @@
       <c r="M46" s="42" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="33">
-      <c r="A47" s="43" t="n"/>
+      <c r="A47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="B47" s="44" t="n"/>
       <c r="C47" s="44" t="n"/>
       <c r="D47" s="44" t="n"/>
       <c r="E47" s="44" t="n"/>
       <c r="F47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
+      <c r="H47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="I47" s="44" t="n"/>
       <c r="J47" s="44" t="n"/>
       <c r="K47" s="44" t="n"/>
@@ -31971,13 +34627,17 @@
       <c r="M47" s="44" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="33">
-      <c r="A48" s="41" t="n"/>
+      <c r="A48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="B48" s="42" t="n"/>
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
       <c r="F48" s="42" t="n"/>
-      <c r="H48" s="42" t="n"/>
+      <c r="H48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
       <c r="K48" s="42" t="n"/>
@@ -32080,14 +34740,14 @@
         </is>
       </c>
       <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
+      <c r="C2" s="87" t="n"/>
       <c r="H2" s="63" t="inlineStr">
         <is>
           <t>선탑자:</t>
         </is>
       </c>
       <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
+      <c r="J2" s="87" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1" s="33">
       <c r="A3" s="48" t="inlineStr">
@@ -32880,7 +35540,7 @@
       <c r="D44" s="42" t="n"/>
       <c r="E44" s="42" t="n"/>
       <c r="F44" s="42" t="n"/>
-      <c r="H44" s="42" t="n">
+      <c r="H44" s="41" t="n">
         <v>41</v>
       </c>
       <c r="I44" s="42" t="n"/>
@@ -32898,7 +35558,7 @@
       <c r="D45" s="44" t="n"/>
       <c r="E45" s="44" t="n"/>
       <c r="F45" s="44" t="n"/>
-      <c r="H45" s="44" t="n">
+      <c r="H45" s="43" t="n">
         <v>42</v>
       </c>
       <c r="I45" s="44" t="n"/>
@@ -32916,7 +35576,7 @@
       <c r="D46" s="42" t="n"/>
       <c r="E46" s="42" t="n"/>
       <c r="F46" s="42" t="n"/>
-      <c r="H46" s="42" t="n">
+      <c r="H46" s="41" t="n">
         <v>43</v>
       </c>
       <c r="I46" s="42" t="n"/>
@@ -32926,13 +35586,17 @@
       <c r="M46" s="42" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="33">
-      <c r="A47" s="43" t="n"/>
+      <c r="A47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="B47" s="44" t="n"/>
       <c r="C47" s="44" t="n"/>
       <c r="D47" s="44" t="n"/>
       <c r="E47" s="44" t="n"/>
       <c r="F47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
+      <c r="H47" s="43" t="n">
+        <v>44</v>
+      </c>
       <c r="I47" s="44" t="n"/>
       <c r="J47" s="44" t="n"/>
       <c r="K47" s="44" t="n"/>
@@ -32940,13 +35604,17 @@
       <c r="M47" s="44" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="33">
-      <c r="A48" s="41" t="n"/>
+      <c r="A48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="B48" s="42" t="n"/>
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
       <c r="F48" s="42" t="n"/>
-      <c r="H48" s="42" t="n"/>
+      <c r="H48" s="41" t="n">
+        <v>45</v>
+      </c>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
       <c r="K48" s="42" t="n"/>
@@ -33115,6 +35783,9 @@
       <c r="C4" s="42" t="n"/>
       <c r="D4" s="42" t="n"/>
       <c r="E4" s="42" t="n"/>
+      <c r="G4" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H4" s="42" t="n"/>
       <c r="I4" s="42" t="n"/>
       <c r="J4" s="42" t="n"/>
@@ -33128,6 +35799,9 @@
       <c r="C5" s="44" t="n"/>
       <c r="D5" s="44" t="n"/>
       <c r="E5" s="44" t="n"/>
+      <c r="G5" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H5" s="44" t="n"/>
       <c r="I5" s="44" t="n"/>
       <c r="J5" s="44" t="n"/>
@@ -33141,6 +35815,9 @@
       <c r="C6" s="42" t="n"/>
       <c r="D6" s="42" t="n"/>
       <c r="E6" s="42" t="n"/>
+      <c r="G6" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H6" s="42" t="n"/>
       <c r="I6" s="42" t="n"/>
       <c r="J6" s="42" t="n"/>
@@ -33154,6 +35831,9 @@
       <c r="C7" s="44" t="n"/>
       <c r="D7" s="44" t="n"/>
       <c r="E7" s="44" t="n"/>
+      <c r="G7" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H7" s="44" t="n"/>
       <c r="I7" s="44" t="n"/>
       <c r="J7" s="44" t="n"/>
@@ -33167,6 +35847,9 @@
       <c r="C8" s="42" t="n"/>
       <c r="D8" s="42" t="n"/>
       <c r="E8" s="42" t="n"/>
+      <c r="G8" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H8" s="42" t="n"/>
       <c r="I8" s="42" t="n"/>
       <c r="J8" s="42" t="n"/>
@@ -33180,6 +35863,9 @@
       <c r="C9" s="44" t="n"/>
       <c r="D9" s="44" t="n"/>
       <c r="E9" s="44" t="n"/>
+      <c r="G9" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H9" s="44" t="n"/>
       <c r="I9" s="44" t="n"/>
       <c r="J9" s="44" t="n"/>
@@ -33193,6 +35879,9 @@
       <c r="C10" s="42" t="n"/>
       <c r="D10" s="42" t="n"/>
       <c r="E10" s="42" t="n"/>
+      <c r="G10" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H10" s="42" t="n"/>
       <c r="I10" s="42" t="n"/>
       <c r="J10" s="42" t="n"/>
@@ -33206,6 +35895,9 @@
       <c r="C11" s="44" t="n"/>
       <c r="D11" s="44" t="n"/>
       <c r="E11" s="44" t="n"/>
+      <c r="G11" s="43" t="n">
+        <v>8</v>
+      </c>
       <c r="H11" s="44" t="n"/>
       <c r="I11" s="44" t="n"/>
       <c r="J11" s="44" t="n"/>
@@ -33219,6 +35911,9 @@
       <c r="C12" s="42" t="n"/>
       <c r="D12" s="42" t="n"/>
       <c r="E12" s="42" t="n"/>
+      <c r="G12" s="41" t="n">
+        <v>9</v>
+      </c>
       <c r="H12" s="42" t="n"/>
       <c r="I12" s="42" t="n"/>
       <c r="J12" s="42" t="n"/>
@@ -33232,6 +35927,9 @@
       <c r="C13" s="44" t="n"/>
       <c r="D13" s="44" t="n"/>
       <c r="E13" s="44" t="n"/>
+      <c r="G13" s="43" t="n">
+        <v>10</v>
+      </c>
       <c r="H13" s="44" t="n"/>
       <c r="I13" s="44" t="n"/>
       <c r="J13" s="44" t="n"/>
@@ -33245,6 +35943,9 @@
       <c r="C14" s="42" t="n"/>
       <c r="D14" s="42" t="n"/>
       <c r="E14" s="42" t="n"/>
+      <c r="G14" s="41" t="n">
+        <v>11</v>
+      </c>
       <c r="H14" s="42" t="n"/>
       <c r="I14" s="42" t="n"/>
       <c r="J14" s="42" t="n"/>
@@ -33258,6 +35959,9 @@
       <c r="C15" s="44" t="n"/>
       <c r="D15" s="44" t="n"/>
       <c r="E15" s="44" t="n"/>
+      <c r="G15" s="43" t="n">
+        <v>12</v>
+      </c>
       <c r="H15" s="44" t="n"/>
       <c r="I15" s="44" t="n"/>
       <c r="J15" s="44" t="n"/>
@@ -33271,6 +35975,9 @@
       <c r="C16" s="42" t="n"/>
       <c r="D16" s="42" t="n"/>
       <c r="E16" s="42" t="n"/>
+      <c r="G16" s="41" t="n">
+        <v>13</v>
+      </c>
       <c r="H16" s="42" t="n"/>
       <c r="I16" s="42" t="n"/>
       <c r="J16" s="42" t="n"/>
@@ -33284,6 +35991,9 @@
       <c r="C17" s="44" t="n"/>
       <c r="D17" s="44" t="n"/>
       <c r="E17" s="44" t="n"/>
+      <c r="G17" s="43" t="n">
+        <v>14</v>
+      </c>
       <c r="H17" s="44" t="n"/>
       <c r="I17" s="44" t="n"/>
       <c r="J17" s="44" t="n"/>
@@ -33297,6 +36007,9 @@
       <c r="C18" s="42" t="n"/>
       <c r="D18" s="42" t="n"/>
       <c r="E18" s="42" t="n"/>
+      <c r="G18" s="41" t="n">
+        <v>15</v>
+      </c>
       <c r="H18" s="42" t="n"/>
       <c r="I18" s="42" t="n"/>
       <c r="J18" s="42" t="n"/>
@@ -33310,6 +36023,9 @@
       <c r="C19" s="44" t="n"/>
       <c r="D19" s="44" t="n"/>
       <c r="E19" s="44" t="n"/>
+      <c r="G19" s="43" t="n">
+        <v>16</v>
+      </c>
       <c r="H19" s="44" t="n"/>
       <c r="I19" s="44" t="n"/>
       <c r="J19" s="44" t="n"/>
@@ -33323,6 +36039,9 @@
       <c r="C20" s="42" t="n"/>
       <c r="D20" s="42" t="n"/>
       <c r="E20" s="42" t="n"/>
+      <c r="G20" s="41" t="n">
+        <v>17</v>
+      </c>
       <c r="H20" s="42" t="n"/>
       <c r="I20" s="42" t="n"/>
       <c r="J20" s="42" t="n"/>
@@ -33336,6 +36055,9 @@
       <c r="C21" s="44" t="n"/>
       <c r="D21" s="44" t="n"/>
       <c r="E21" s="44" t="n"/>
+      <c r="G21" s="43" t="n">
+        <v>18</v>
+      </c>
       <c r="H21" s="44" t="n"/>
       <c r="I21" s="44" t="n"/>
       <c r="J21" s="44" t="n"/>
@@ -33349,6 +36071,9 @@
       <c r="C22" s="42" t="n"/>
       <c r="D22" s="42" t="n"/>
       <c r="E22" s="42" t="n"/>
+      <c r="G22" s="41" t="n">
+        <v>19</v>
+      </c>
       <c r="H22" s="42" t="n"/>
       <c r="I22" s="42" t="n"/>
       <c r="J22" s="42" t="n"/>
@@ -33362,6 +36087,9 @@
       <c r="C23" s="44" t="n"/>
       <c r="D23" s="44" t="n"/>
       <c r="E23" s="44" t="n"/>
+      <c r="G23" s="43" t="n">
+        <v>20</v>
+      </c>
       <c r="H23" s="44" t="n"/>
       <c r="I23" s="44" t="n"/>
       <c r="J23" s="44" t="n"/>
@@ -33375,6 +36103,9 @@
       <c r="C24" s="42" t="n"/>
       <c r="D24" s="42" t="n"/>
       <c r="E24" s="42" t="n"/>
+      <c r="G24" s="41" t="n">
+        <v>21</v>
+      </c>
       <c r="H24" s="42" t="n"/>
       <c r="I24" s="42" t="n"/>
       <c r="J24" s="42" t="n"/>
@@ -33388,6 +36119,9 @@
       <c r="C25" s="44" t="n"/>
       <c r="D25" s="44" t="n"/>
       <c r="E25" s="44" t="n"/>
+      <c r="G25" s="43" t="n">
+        <v>22</v>
+      </c>
       <c r="H25" s="44" t="n"/>
       <c r="I25" s="44" t="n"/>
       <c r="J25" s="44" t="n"/>
@@ -33401,6 +36135,9 @@
       <c r="C26" s="42" t="n"/>
       <c r="D26" s="42" t="n"/>
       <c r="E26" s="42" t="n"/>
+      <c r="G26" s="41" t="n">
+        <v>23</v>
+      </c>
       <c r="H26" s="42" t="n"/>
       <c r="I26" s="42" t="n"/>
       <c r="J26" s="42" t="n"/>
@@ -33414,6 +36151,9 @@
       <c r="C27" s="44" t="n"/>
       <c r="D27" s="44" t="n"/>
       <c r="E27" s="44" t="n"/>
+      <c r="G27" s="43" t="n">
+        <v>24</v>
+      </c>
       <c r="H27" s="44" t="n"/>
       <c r="I27" s="44" t="n"/>
       <c r="J27" s="44" t="n"/>
@@ -33427,6 +36167,9 @@
       <c r="C28" s="42" t="n"/>
       <c r="D28" s="42" t="n"/>
       <c r="E28" s="42" t="n"/>
+      <c r="G28" s="41" t="n">
+        <v>25</v>
+      </c>
       <c r="H28" s="42" t="n"/>
       <c r="I28" s="42" t="n"/>
       <c r="J28" s="42" t="n"/>
@@ -33440,6 +36183,9 @@
       <c r="C29" s="44" t="n"/>
       <c r="D29" s="44" t="n"/>
       <c r="E29" s="44" t="n"/>
+      <c r="G29" s="43" t="n">
+        <v>26</v>
+      </c>
       <c r="H29" s="44" t="n"/>
       <c r="I29" s="44" t="n"/>
       <c r="J29" s="44" t="n"/>
@@ -33453,6 +36199,9 @@
       <c r="C30" s="42" t="n"/>
       <c r="D30" s="42" t="n"/>
       <c r="E30" s="42" t="n"/>
+      <c r="G30" s="41" t="n">
+        <v>27</v>
+      </c>
       <c r="H30" s="42" t="n"/>
       <c r="I30" s="42" t="n"/>
       <c r="J30" s="42" t="n"/>
@@ -33466,6 +36215,9 @@
       <c r="C31" s="44" t="n"/>
       <c r="D31" s="44" t="n"/>
       <c r="E31" s="44" t="n"/>
+      <c r="G31" s="43" t="n">
+        <v>28</v>
+      </c>
       <c r="H31" s="44" t="n"/>
       <c r="I31" s="44" t="n"/>
       <c r="J31" s="44" t="n"/>
@@ -33479,6 +36231,9 @@
       <c r="C32" s="42" t="n"/>
       <c r="D32" s="42" t="n"/>
       <c r="E32" s="42" t="n"/>
+      <c r="G32" s="41" t="n">
+        <v>29</v>
+      </c>
       <c r="H32" s="42" t="n"/>
       <c r="I32" s="42" t="n"/>
       <c r="J32" s="42" t="n"/>
@@ -33492,6 +36247,9 @@
       <c r="C33" s="44" t="n"/>
       <c r="D33" s="44" t="n"/>
       <c r="E33" s="44" t="n"/>
+      <c r="G33" s="43" t="n">
+        <v>30</v>
+      </c>
       <c r="H33" s="44" t="n"/>
       <c r="I33" s="44" t="n"/>
       <c r="J33" s="44" t="n"/>
@@ -33505,6 +36263,9 @@
       <c r="C34" s="42" t="n"/>
       <c r="D34" s="42" t="n"/>
       <c r="E34" s="42" t="n"/>
+      <c r="G34" s="41" t="n">
+        <v>31</v>
+      </c>
       <c r="H34" s="42" t="n"/>
       <c r="I34" s="42" t="n"/>
       <c r="J34" s="42" t="n"/>
@@ -33518,6 +36279,9 @@
       <c r="C35" s="44" t="n"/>
       <c r="D35" s="44" t="n"/>
       <c r="E35" s="44" t="n"/>
+      <c r="G35" s="43" t="n">
+        <v>32</v>
+      </c>
       <c r="H35" s="44" t="n"/>
       <c r="I35" s="44" t="n"/>
       <c r="J35" s="44" t="n"/>
@@ -33531,6 +36295,9 @@
       <c r="C36" s="42" t="n"/>
       <c r="D36" s="42" t="n"/>
       <c r="E36" s="42" t="n"/>
+      <c r="G36" s="41" t="n">
+        <v>33</v>
+      </c>
       <c r="H36" s="42" t="n"/>
       <c r="I36" s="42" t="n"/>
       <c r="J36" s="42" t="n"/>
@@ -33544,6 +36311,9 @@
       <c r="C37" s="44" t="n"/>
       <c r="D37" s="44" t="n"/>
       <c r="E37" s="44" t="n"/>
+      <c r="G37" s="43" t="n">
+        <v>34</v>
+      </c>
       <c r="H37" s="44" t="n"/>
       <c r="I37" s="44" t="n"/>
       <c r="J37" s="44" t="n"/>
@@ -33557,6 +36327,9 @@
       <c r="C38" s="42" t="n"/>
       <c r="D38" s="42" t="n"/>
       <c r="E38" s="42" t="n"/>
+      <c r="G38" s="41" t="n">
+        <v>35</v>
+      </c>
       <c r="H38" s="42" t="n"/>
       <c r="I38" s="42" t="n"/>
       <c r="J38" s="42" t="n"/>
@@ -33570,6 +36343,9 @@
       <c r="C39" s="44" t="n"/>
       <c r="D39" s="44" t="n"/>
       <c r="E39" s="44" t="n"/>
+      <c r="G39" s="43" t="n">
+        <v>36</v>
+      </c>
       <c r="H39" s="44" t="n"/>
       <c r="I39" s="44" t="n"/>
       <c r="J39" s="44" t="n"/>
@@ -33583,6 +36359,9 @@
       <c r="C40" s="42" t="n"/>
       <c r="D40" s="42" t="n"/>
       <c r="E40" s="42" t="n"/>
+      <c r="G40" s="41" t="n">
+        <v>37</v>
+      </c>
       <c r="H40" s="42" t="n"/>
       <c r="I40" s="42" t="n"/>
       <c r="J40" s="42" t="n"/>
@@ -33596,6 +36375,9 @@
       <c r="C41" s="44" t="n"/>
       <c r="D41" s="44" t="n"/>
       <c r="E41" s="44" t="n"/>
+      <c r="G41" s="43" t="n">
+        <v>38</v>
+      </c>
       <c r="H41" s="44" t="n"/>
       <c r="I41" s="44" t="n"/>
       <c r="J41" s="44" t="n"/>
@@ -33609,6 +36391,9 @@
       <c r="C42" s="42" t="n"/>
       <c r="D42" s="42" t="n"/>
       <c r="E42" s="42" t="n"/>
+      <c r="G42" s="41" t="n">
+        <v>39</v>
+      </c>
       <c r="H42" s="42" t="n"/>
       <c r="I42" s="42" t="n"/>
       <c r="J42" s="42" t="n"/>
@@ -33622,6 +36407,9 @@
       <c r="C43" s="44" t="n"/>
       <c r="D43" s="44" t="n"/>
       <c r="E43" s="44" t="n"/>
+      <c r="G43" s="43" t="n">
+        <v>40</v>
+      </c>
       <c r="H43" s="44" t="n"/>
       <c r="I43" s="44" t="n"/>
       <c r="J43" s="44" t="n"/>
@@ -33744,6 +36532,9 @@
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
+      <c r="G48" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H48" s="42" t="n"/>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
@@ -33757,6 +36548,9 @@
       <c r="C49" s="44" t="n"/>
       <c r="D49" s="44" t="n"/>
       <c r="E49" s="44" t="n"/>
+      <c r="G49" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H49" s="44" t="n"/>
       <c r="I49" s="44" t="n"/>
       <c r="J49" s="44" t="n"/>
@@ -33770,6 +36564,9 @@
       <c r="C50" s="42" t="n"/>
       <c r="D50" s="42" t="n"/>
       <c r="E50" s="42" t="n"/>
+      <c r="G50" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H50" s="42" t="n"/>
       <c r="I50" s="42" t="n"/>
       <c r="J50" s="42" t="n"/>
@@ -33783,6 +36580,9 @@
       <c r="C51" s="44" t="n"/>
       <c r="D51" s="44" t="n"/>
       <c r="E51" s="44" t="n"/>
+      <c r="G51" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H51" s="44" t="n"/>
       <c r="I51" s="44" t="n"/>
       <c r="J51" s="44" t="n"/>
@@ -33796,6 +36596,9 @@
       <c r="C52" s="42" t="n"/>
       <c r="D52" s="42" t="n"/>
       <c r="E52" s="42" t="n"/>
+      <c r="G52" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H52" s="42" t="n"/>
       <c r="I52" s="42" t="n"/>
       <c r="J52" s="42" t="n"/>
@@ -33809,6 +36612,9 @@
       <c r="C53" s="44" t="n"/>
       <c r="D53" s="44" t="n"/>
       <c r="E53" s="44" t="n"/>
+      <c r="G53" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H53" s="44" t="n"/>
       <c r="I53" s="44" t="n"/>
       <c r="J53" s="44" t="n"/>
@@ -33822,6 +36628,9 @@
       <c r="C54" s="42" t="n"/>
       <c r="D54" s="42" t="n"/>
       <c r="E54" s="42" t="n"/>
+      <c r="G54" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H54" s="42" t="n"/>
       <c r="I54" s="42" t="n"/>
       <c r="J54" s="42" t="n"/>
@@ -33835,6 +36644,9 @@
       <c r="C55" s="44" t="n"/>
       <c r="D55" s="44" t="n"/>
       <c r="E55" s="44" t="n"/>
+      <c r="G55" s="43" t="n">
+        <v>8</v>
+      </c>
       <c r="H55" s="44" t="n"/>
       <c r="I55" s="44" t="n"/>
       <c r="J55" s="44" t="n"/>
@@ -33848,6 +36660,9 @@
       <c r="C56" s="42" t="n"/>
       <c r="D56" s="42" t="n"/>
       <c r="E56" s="42" t="n"/>
+      <c r="G56" s="41" t="n">
+        <v>9</v>
+      </c>
       <c r="H56" s="42" t="n"/>
       <c r="I56" s="42" t="n"/>
       <c r="J56" s="42" t="n"/>
@@ -33861,6 +36676,9 @@
       <c r="C57" s="44" t="n"/>
       <c r="D57" s="44" t="n"/>
       <c r="E57" s="44" t="n"/>
+      <c r="G57" s="43" t="n">
+        <v>10</v>
+      </c>
       <c r="H57" s="44" t="n"/>
       <c r="I57" s="44" t="n"/>
       <c r="J57" s="44" t="n"/>
@@ -33874,6 +36692,9 @@
       <c r="C58" s="42" t="n"/>
       <c r="D58" s="42" t="n"/>
       <c r="E58" s="42" t="n"/>
+      <c r="G58" s="41" t="n">
+        <v>11</v>
+      </c>
       <c r="H58" s="42" t="n"/>
       <c r="I58" s="42" t="n"/>
       <c r="J58" s="42" t="n"/>
@@ -33887,6 +36708,9 @@
       <c r="C59" s="44" t="n"/>
       <c r="D59" s="44" t="n"/>
       <c r="E59" s="44" t="n"/>
+      <c r="G59" s="43" t="n">
+        <v>12</v>
+      </c>
       <c r="H59" s="44" t="n"/>
       <c r="I59" s="44" t="n"/>
       <c r="J59" s="44" t="n"/>
@@ -33900,6 +36724,9 @@
       <c r="C60" s="42" t="n"/>
       <c r="D60" s="42" t="n"/>
       <c r="E60" s="42" t="n"/>
+      <c r="G60" s="41" t="n">
+        <v>13</v>
+      </c>
       <c r="H60" s="42" t="n"/>
       <c r="I60" s="42" t="n"/>
       <c r="J60" s="42" t="n"/>
@@ -33913,6 +36740,9 @@
       <c r="C61" s="44" t="n"/>
       <c r="D61" s="44" t="n"/>
       <c r="E61" s="44" t="n"/>
+      <c r="G61" s="43" t="n">
+        <v>14</v>
+      </c>
       <c r="H61" s="44" t="n"/>
       <c r="I61" s="44" t="n"/>
       <c r="J61" s="44" t="n"/>
@@ -33926,6 +36756,9 @@
       <c r="C62" s="42" t="n"/>
       <c r="D62" s="42" t="n"/>
       <c r="E62" s="42" t="n"/>
+      <c r="G62" s="41" t="n">
+        <v>15</v>
+      </c>
       <c r="H62" s="42" t="n"/>
       <c r="I62" s="42" t="n"/>
       <c r="J62" s="42" t="n"/>
@@ -33939,6 +36772,9 @@
       <c r="C63" s="44" t="n"/>
       <c r="D63" s="44" t="n"/>
       <c r="E63" s="44" t="n"/>
+      <c r="G63" s="43" t="n">
+        <v>16</v>
+      </c>
       <c r="H63" s="44" t="n"/>
       <c r="I63" s="44" t="n"/>
       <c r="J63" s="44" t="n"/>
@@ -33952,6 +36788,9 @@
       <c r="C64" s="42" t="n"/>
       <c r="D64" s="42" t="n"/>
       <c r="E64" s="42" t="n"/>
+      <c r="G64" s="41" t="n">
+        <v>17</v>
+      </c>
       <c r="H64" s="42" t="n"/>
       <c r="I64" s="42" t="n"/>
       <c r="J64" s="42" t="n"/>
@@ -33965,6 +36804,9 @@
       <c r="C65" s="44" t="n"/>
       <c r="D65" s="44" t="n"/>
       <c r="E65" s="44" t="n"/>
+      <c r="G65" s="43" t="n">
+        <v>18</v>
+      </c>
       <c r="H65" s="44" t="n"/>
       <c r="I65" s="44" t="n"/>
       <c r="J65" s="44" t="n"/>
@@ -33978,6 +36820,9 @@
       <c r="C66" s="42" t="n"/>
       <c r="D66" s="42" t="n"/>
       <c r="E66" s="42" t="n"/>
+      <c r="G66" s="41" t="n">
+        <v>19</v>
+      </c>
       <c r="H66" s="42" t="n"/>
       <c r="I66" s="42" t="n"/>
       <c r="J66" s="42" t="n"/>
@@ -33991,6 +36836,9 @@
       <c r="C67" s="44" t="n"/>
       <c r="D67" s="44" t="n"/>
       <c r="E67" s="44" t="n"/>
+      <c r="G67" s="43" t="n">
+        <v>20</v>
+      </c>
       <c r="H67" s="44" t="n"/>
       <c r="I67" s="44" t="n"/>
       <c r="J67" s="44" t="n"/>
@@ -34004,6 +36852,9 @@
       <c r="C68" s="42" t="n"/>
       <c r="D68" s="42" t="n"/>
       <c r="E68" s="42" t="n"/>
+      <c r="G68" s="41" t="n">
+        <v>21</v>
+      </c>
       <c r="H68" s="42" t="n"/>
       <c r="I68" s="42" t="n"/>
       <c r="J68" s="42" t="n"/>
@@ -34017,6 +36868,9 @@
       <c r="C69" s="44" t="n"/>
       <c r="D69" s="44" t="n"/>
       <c r="E69" s="44" t="n"/>
+      <c r="G69" s="43" t="n">
+        <v>22</v>
+      </c>
       <c r="H69" s="44" t="n"/>
       <c r="I69" s="44" t="n"/>
       <c r="J69" s="44" t="n"/>
@@ -34030,6 +36884,9 @@
       <c r="C70" s="42" t="n"/>
       <c r="D70" s="42" t="n"/>
       <c r="E70" s="42" t="n"/>
+      <c r="G70" s="41" t="n">
+        <v>23</v>
+      </c>
       <c r="H70" s="42" t="n"/>
       <c r="I70" s="42" t="n"/>
       <c r="J70" s="42" t="n"/>
@@ -34043,6 +36900,9 @@
       <c r="C71" s="44" t="n"/>
       <c r="D71" s="44" t="n"/>
       <c r="E71" s="44" t="n"/>
+      <c r="G71" s="43" t="n">
+        <v>24</v>
+      </c>
       <c r="H71" s="44" t="n"/>
       <c r="I71" s="44" t="n"/>
       <c r="J71" s="44" t="n"/>
@@ -34056,6 +36916,9 @@
       <c r="C72" s="42" t="n"/>
       <c r="D72" s="42" t="n"/>
       <c r="E72" s="42" t="n"/>
+      <c r="G72" s="41" t="n">
+        <v>25</v>
+      </c>
       <c r="H72" s="42" t="n"/>
       <c r="I72" s="42" t="n"/>
       <c r="J72" s="42" t="n"/>
@@ -34069,6 +36932,9 @@
       <c r="C73" s="44" t="n"/>
       <c r="D73" s="44" t="n"/>
       <c r="E73" s="44" t="n"/>
+      <c r="G73" s="43" t="n">
+        <v>26</v>
+      </c>
       <c r="H73" s="44" t="n"/>
       <c r="I73" s="44" t="n"/>
       <c r="J73" s="44" t="n"/>
@@ -34082,6 +36948,9 @@
       <c r="C74" s="42" t="n"/>
       <c r="D74" s="42" t="n"/>
       <c r="E74" s="42" t="n"/>
+      <c r="G74" s="41" t="n">
+        <v>27</v>
+      </c>
       <c r="H74" s="42" t="n"/>
       <c r="I74" s="42" t="n"/>
       <c r="J74" s="42" t="n"/>
@@ -34095,6 +36964,9 @@
       <c r="C75" s="44" t="n"/>
       <c r="D75" s="44" t="n"/>
       <c r="E75" s="44" t="n"/>
+      <c r="G75" s="43" t="n">
+        <v>28</v>
+      </c>
       <c r="H75" s="44" t="n"/>
       <c r="I75" s="44" t="n"/>
       <c r="J75" s="44" t="n"/>
@@ -34108,6 +36980,9 @@
       <c r="C76" s="42" t="n"/>
       <c r="D76" s="42" t="n"/>
       <c r="E76" s="42" t="n"/>
+      <c r="G76" s="41" t="n">
+        <v>29</v>
+      </c>
       <c r="H76" s="42" t="n"/>
       <c r="I76" s="42" t="n"/>
       <c r="J76" s="42" t="n"/>
@@ -34121,6 +36996,9 @@
       <c r="C77" s="44" t="n"/>
       <c r="D77" s="44" t="n"/>
       <c r="E77" s="44" t="n"/>
+      <c r="G77" s="43" t="n">
+        <v>30</v>
+      </c>
       <c r="H77" s="44" t="n"/>
       <c r="I77" s="44" t="n"/>
       <c r="J77" s="44" t="n"/>
@@ -34134,6 +37012,9 @@
       <c r="C78" s="42" t="n"/>
       <c r="D78" s="42" t="n"/>
       <c r="E78" s="42" t="n"/>
+      <c r="G78" s="41" t="n">
+        <v>31</v>
+      </c>
       <c r="H78" s="42" t="n"/>
       <c r="I78" s="42" t="n"/>
       <c r="J78" s="42" t="n"/>
@@ -34147,6 +37028,9 @@
       <c r="C79" s="44" t="n"/>
       <c r="D79" s="44" t="n"/>
       <c r="E79" s="44" t="n"/>
+      <c r="G79" s="43" t="n">
+        <v>32</v>
+      </c>
       <c r="H79" s="44" t="n"/>
       <c r="I79" s="44" t="n"/>
       <c r="J79" s="44" t="n"/>
@@ -34160,6 +37044,9 @@
       <c r="C80" s="42" t="n"/>
       <c r="D80" s="42" t="n"/>
       <c r="E80" s="42" t="n"/>
+      <c r="G80" s="41" t="n">
+        <v>33</v>
+      </c>
       <c r="H80" s="42" t="n"/>
       <c r="I80" s="42" t="n"/>
       <c r="J80" s="42" t="n"/>
@@ -34173,6 +37060,9 @@
       <c r="C81" s="44" t="n"/>
       <c r="D81" s="44" t="n"/>
       <c r="E81" s="44" t="n"/>
+      <c r="G81" s="43" t="n">
+        <v>34</v>
+      </c>
       <c r="H81" s="44" t="n"/>
       <c r="I81" s="44" t="n"/>
       <c r="J81" s="44" t="n"/>
@@ -34186,6 +37076,9 @@
       <c r="C82" s="42" t="n"/>
       <c r="D82" s="42" t="n"/>
       <c r="E82" s="42" t="n"/>
+      <c r="G82" s="41" t="n">
+        <v>35</v>
+      </c>
       <c r="H82" s="42" t="n"/>
       <c r="I82" s="42" t="n"/>
       <c r="J82" s="42" t="n"/>
@@ -34199,6 +37092,9 @@
       <c r="C83" s="44" t="n"/>
       <c r="D83" s="44" t="n"/>
       <c r="E83" s="44" t="n"/>
+      <c r="G83" s="43" t="n">
+        <v>36</v>
+      </c>
       <c r="H83" s="44" t="n"/>
       <c r="I83" s="44" t="n"/>
       <c r="J83" s="44" t="n"/>
@@ -34212,6 +37108,9 @@
       <c r="C84" s="42" t="n"/>
       <c r="D84" s="42" t="n"/>
       <c r="E84" s="42" t="n"/>
+      <c r="G84" s="41" t="n">
+        <v>37</v>
+      </c>
       <c r="H84" s="42" t="n"/>
       <c r="I84" s="42" t="n"/>
       <c r="J84" s="42" t="n"/>
@@ -34225,6 +37124,9 @@
       <c r="C85" s="44" t="n"/>
       <c r="D85" s="44" t="n"/>
       <c r="E85" s="44" t="n"/>
+      <c r="G85" s="43" t="n">
+        <v>38</v>
+      </c>
       <c r="H85" s="44" t="n"/>
       <c r="I85" s="44" t="n"/>
       <c r="J85" s="44" t="n"/>
@@ -34238,6 +37140,9 @@
       <c r="C86" s="42" t="n"/>
       <c r="D86" s="42" t="n"/>
       <c r="E86" s="42" t="n"/>
+      <c r="G86" s="41" t="n">
+        <v>39</v>
+      </c>
       <c r="H86" s="42" t="n"/>
       <c r="I86" s="42" t="n"/>
       <c r="J86" s="42" t="n"/>
@@ -34251,6 +37156,9 @@
       <c r="C87" s="44" t="n"/>
       <c r="D87" s="44" t="n"/>
       <c r="E87" s="44" t="n"/>
+      <c r="G87" s="43" t="n">
+        <v>40</v>
+      </c>
       <c r="H87" s="44" t="n"/>
       <c r="I87" s="44" t="n"/>
       <c r="J87" s="44" t="n"/>
@@ -34373,6 +37281,9 @@
       <c r="C92" s="42" t="n"/>
       <c r="D92" s="42" t="n"/>
       <c r="E92" s="42" t="n"/>
+      <c r="G92" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H92" s="42" t="n"/>
       <c r="I92" s="42" t="n"/>
       <c r="J92" s="42" t="n"/>
@@ -34386,6 +37297,9 @@
       <c r="C93" s="44" t="n"/>
       <c r="D93" s="44" t="n"/>
       <c r="E93" s="44" t="n"/>
+      <c r="G93" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H93" s="44" t="n"/>
       <c r="I93" s="44" t="n"/>
       <c r="J93" s="44" t="n"/>
@@ -34399,6 +37313,9 @@
       <c r="C94" s="42" t="n"/>
       <c r="D94" s="42" t="n"/>
       <c r="E94" s="42" t="n"/>
+      <c r="G94" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H94" s="42" t="n"/>
       <c r="I94" s="42" t="n"/>
       <c r="J94" s="42" t="n"/>
@@ -34412,6 +37329,9 @@
       <c r="C95" s="44" t="n"/>
       <c r="D95" s="44" t="n"/>
       <c r="E95" s="44" t="n"/>
+      <c r="G95" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H95" s="44" t="n"/>
       <c r="I95" s="44" t="n"/>
       <c r="J95" s="44" t="n"/>
@@ -34425,6 +37345,9 @@
       <c r="C96" s="42" t="n"/>
       <c r="D96" s="42" t="n"/>
       <c r="E96" s="42" t="n"/>
+      <c r="G96" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H96" s="42" t="n"/>
       <c r="I96" s="42" t="n"/>
       <c r="J96" s="42" t="n"/>
@@ -34438,6 +37361,9 @@
       <c r="C97" s="44" t="n"/>
       <c r="D97" s="44" t="n"/>
       <c r="E97" s="44" t="n"/>
+      <c r="G97" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H97" s="44" t="n"/>
       <c r="I97" s="44" t="n"/>
       <c r="J97" s="44" t="n"/>
@@ -34451,6 +37377,9 @@
       <c r="C98" s="42" t="n"/>
       <c r="D98" s="42" t="n"/>
       <c r="E98" s="42" t="n"/>
+      <c r="G98" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H98" s="42" t="n"/>
       <c r="I98" s="42" t="n"/>
       <c r="J98" s="42" t="n"/>
@@ -34464,6 +37393,9 @@
       <c r="C99" s="44" t="n"/>
       <c r="D99" s="44" t="n"/>
       <c r="E99" s="44" t="n"/>
+      <c r="G99" s="43" t="n">
+        <v>8</v>
+      </c>
       <c r="H99" s="44" t="n"/>
       <c r="I99" s="44" t="n"/>
       <c r="J99" s="44" t="n"/>
@@ -34477,6 +37409,9 @@
       <c r="C100" s="42" t="n"/>
       <c r="D100" s="42" t="n"/>
       <c r="E100" s="42" t="n"/>
+      <c r="G100" s="41" t="n">
+        <v>9</v>
+      </c>
       <c r="H100" s="42" t="n"/>
       <c r="I100" s="42" t="n"/>
       <c r="J100" s="42" t="n"/>
@@ -34490,6 +37425,9 @@
       <c r="C101" s="44" t="n"/>
       <c r="D101" s="44" t="n"/>
       <c r="E101" s="44" t="n"/>
+      <c r="G101" s="43" t="n">
+        <v>10</v>
+      </c>
       <c r="H101" s="44" t="n"/>
       <c r="I101" s="44" t="n"/>
       <c r="J101" s="44" t="n"/>
@@ -34503,6 +37441,9 @@
       <c r="C102" s="42" t="n"/>
       <c r="D102" s="42" t="n"/>
       <c r="E102" s="42" t="n"/>
+      <c r="G102" s="41" t="n">
+        <v>11</v>
+      </c>
       <c r="H102" s="42" t="n"/>
       <c r="I102" s="42" t="n"/>
       <c r="J102" s="42" t="n"/>
@@ -34516,6 +37457,9 @@
       <c r="C103" s="44" t="n"/>
       <c r="D103" s="44" t="n"/>
       <c r="E103" s="44" t="n"/>
+      <c r="G103" s="43" t="n">
+        <v>12</v>
+      </c>
       <c r="H103" s="44" t="n"/>
       <c r="I103" s="44" t="n"/>
       <c r="J103" s="44" t="n"/>
@@ -34529,6 +37473,9 @@
       <c r="C104" s="42" t="n"/>
       <c r="D104" s="42" t="n"/>
       <c r="E104" s="42" t="n"/>
+      <c r="G104" s="41" t="n">
+        <v>13</v>
+      </c>
       <c r="H104" s="42" t="n"/>
       <c r="I104" s="42" t="n"/>
       <c r="J104" s="42" t="n"/>
@@ -34542,6 +37489,9 @@
       <c r="C105" s="44" t="n"/>
       <c r="D105" s="44" t="n"/>
       <c r="E105" s="44" t="n"/>
+      <c r="G105" s="43" t="n">
+        <v>14</v>
+      </c>
       <c r="H105" s="44" t="n"/>
       <c r="I105" s="44" t="n"/>
       <c r="J105" s="44" t="n"/>
@@ -34555,6 +37505,9 @@
       <c r="C106" s="42" t="n"/>
       <c r="D106" s="42" t="n"/>
       <c r="E106" s="42" t="n"/>
+      <c r="G106" s="41" t="n">
+        <v>15</v>
+      </c>
       <c r="H106" s="42" t="n"/>
       <c r="I106" s="42" t="n"/>
       <c r="J106" s="42" t="n"/>
@@ -34568,6 +37521,9 @@
       <c r="C107" s="44" t="n"/>
       <c r="D107" s="44" t="n"/>
       <c r="E107" s="44" t="n"/>
+      <c r="G107" s="43" t="n">
+        <v>16</v>
+      </c>
       <c r="H107" s="44" t="n"/>
       <c r="I107" s="44" t="n"/>
       <c r="J107" s="44" t="n"/>
@@ -34581,6 +37537,9 @@
       <c r="C108" s="42" t="n"/>
       <c r="D108" s="42" t="n"/>
       <c r="E108" s="42" t="n"/>
+      <c r="G108" s="41" t="n">
+        <v>17</v>
+      </c>
       <c r="H108" s="42" t="n"/>
       <c r="I108" s="42" t="n"/>
       <c r="J108" s="42" t="n"/>
@@ -34594,6 +37553,9 @@
       <c r="C109" s="44" t="n"/>
       <c r="D109" s="44" t="n"/>
       <c r="E109" s="44" t="n"/>
+      <c r="G109" s="43" t="n">
+        <v>18</v>
+      </c>
       <c r="H109" s="44" t="n"/>
       <c r="I109" s="44" t="n"/>
       <c r="J109" s="44" t="n"/>
@@ -34607,6 +37569,9 @@
       <c r="C110" s="42" t="n"/>
       <c r="D110" s="42" t="n"/>
       <c r="E110" s="42" t="n"/>
+      <c r="G110" s="41" t="n">
+        <v>19</v>
+      </c>
       <c r="H110" s="42" t="n"/>
       <c r="I110" s="42" t="n"/>
       <c r="J110" s="42" t="n"/>
@@ -34620,6 +37585,9 @@
       <c r="C111" s="44" t="n"/>
       <c r="D111" s="44" t="n"/>
       <c r="E111" s="44" t="n"/>
+      <c r="G111" s="43" t="n">
+        <v>20</v>
+      </c>
       <c r="H111" s="44" t="n"/>
       <c r="I111" s="44" t="n"/>
       <c r="J111" s="44" t="n"/>
@@ -34633,6 +37601,9 @@
       <c r="C112" s="42" t="n"/>
       <c r="D112" s="42" t="n"/>
       <c r="E112" s="42" t="n"/>
+      <c r="G112" s="41" t="n">
+        <v>21</v>
+      </c>
       <c r="H112" s="42" t="n"/>
       <c r="I112" s="42" t="n"/>
       <c r="J112" s="42" t="n"/>
@@ -34646,6 +37617,9 @@
       <c r="C113" s="44" t="n"/>
       <c r="D113" s="44" t="n"/>
       <c r="E113" s="44" t="n"/>
+      <c r="G113" s="43" t="n">
+        <v>22</v>
+      </c>
       <c r="H113" s="44" t="n"/>
       <c r="I113" s="44" t="n"/>
       <c r="J113" s="44" t="n"/>
@@ -34659,6 +37633,9 @@
       <c r="C114" s="42" t="n"/>
       <c r="D114" s="42" t="n"/>
       <c r="E114" s="42" t="n"/>
+      <c r="G114" s="41" t="n">
+        <v>23</v>
+      </c>
       <c r="H114" s="42" t="n"/>
       <c r="I114" s="42" t="n"/>
       <c r="J114" s="42" t="n"/>
@@ -34672,6 +37649,9 @@
       <c r="C115" s="44" t="n"/>
       <c r="D115" s="44" t="n"/>
       <c r="E115" s="44" t="n"/>
+      <c r="G115" s="43" t="n">
+        <v>24</v>
+      </c>
       <c r="H115" s="44" t="n"/>
       <c r="I115" s="44" t="n"/>
       <c r="J115" s="44" t="n"/>
@@ -34685,6 +37665,9 @@
       <c r="C116" s="42" t="n"/>
       <c r="D116" s="42" t="n"/>
       <c r="E116" s="42" t="n"/>
+      <c r="G116" s="41" t="n">
+        <v>25</v>
+      </c>
       <c r="H116" s="42" t="n"/>
       <c r="I116" s="42" t="n"/>
       <c r="J116" s="42" t="n"/>
@@ -34698,6 +37681,9 @@
       <c r="C117" s="44" t="n"/>
       <c r="D117" s="44" t="n"/>
       <c r="E117" s="44" t="n"/>
+      <c r="G117" s="43" t="n">
+        <v>26</v>
+      </c>
       <c r="H117" s="44" t="n"/>
       <c r="I117" s="44" t="n"/>
       <c r="J117" s="44" t="n"/>
@@ -34711,6 +37697,9 @@
       <c r="C118" s="42" t="n"/>
       <c r="D118" s="42" t="n"/>
       <c r="E118" s="42" t="n"/>
+      <c r="G118" s="41" t="n">
+        <v>27</v>
+      </c>
       <c r="H118" s="42" t="n"/>
       <c r="I118" s="42" t="n"/>
       <c r="J118" s="42" t="n"/>
@@ -34724,6 +37713,9 @@
       <c r="C119" s="44" t="n"/>
       <c r="D119" s="44" t="n"/>
       <c r="E119" s="44" t="n"/>
+      <c r="G119" s="43" t="n">
+        <v>28</v>
+      </c>
       <c r="H119" s="44" t="n"/>
       <c r="I119" s="44" t="n"/>
       <c r="J119" s="44" t="n"/>
@@ -34737,6 +37729,9 @@
       <c r="C120" s="42" t="n"/>
       <c r="D120" s="42" t="n"/>
       <c r="E120" s="42" t="n"/>
+      <c r="G120" s="41" t="n">
+        <v>29</v>
+      </c>
       <c r="H120" s="42" t="n"/>
       <c r="I120" s="42" t="n"/>
       <c r="J120" s="42" t="n"/>
@@ -34750,6 +37745,9 @@
       <c r="C121" s="44" t="n"/>
       <c r="D121" s="44" t="n"/>
       <c r="E121" s="44" t="n"/>
+      <c r="G121" s="43" t="n">
+        <v>30</v>
+      </c>
       <c r="H121" s="44" t="n"/>
       <c r="I121" s="44" t="n"/>
       <c r="J121" s="44" t="n"/>
@@ -34763,6 +37761,9 @@
       <c r="C122" s="42" t="n"/>
       <c r="D122" s="42" t="n"/>
       <c r="E122" s="42" t="n"/>
+      <c r="G122" s="41" t="n">
+        <v>31</v>
+      </c>
       <c r="H122" s="42" t="n"/>
       <c r="I122" s="42" t="n"/>
       <c r="J122" s="42" t="n"/>
@@ -34776,6 +37777,9 @@
       <c r="C123" s="44" t="n"/>
       <c r="D123" s="44" t="n"/>
       <c r="E123" s="44" t="n"/>
+      <c r="G123" s="43" t="n">
+        <v>32</v>
+      </c>
       <c r="H123" s="44" t="n"/>
       <c r="I123" s="44" t="n"/>
       <c r="J123" s="44" t="n"/>
@@ -34789,6 +37793,9 @@
       <c r="C124" s="42" t="n"/>
       <c r="D124" s="42" t="n"/>
       <c r="E124" s="42" t="n"/>
+      <c r="G124" s="41" t="n">
+        <v>33</v>
+      </c>
       <c r="H124" s="42" t="n"/>
       <c r="I124" s="42" t="n"/>
       <c r="J124" s="42" t="n"/>
@@ -34802,6 +37809,9 @@
       <c r="C125" s="44" t="n"/>
       <c r="D125" s="44" t="n"/>
       <c r="E125" s="44" t="n"/>
+      <c r="G125" s="43" t="n">
+        <v>34</v>
+      </c>
       <c r="H125" s="44" t="n"/>
       <c r="I125" s="44" t="n"/>
       <c r="J125" s="44" t="n"/>
@@ -34815,6 +37825,9 @@
       <c r="C126" s="42" t="n"/>
       <c r="D126" s="42" t="n"/>
       <c r="E126" s="42" t="n"/>
+      <c r="G126" s="41" t="n">
+        <v>35</v>
+      </c>
       <c r="H126" s="42" t="n"/>
       <c r="I126" s="42" t="n"/>
       <c r="J126" s="42" t="n"/>
@@ -34828,6 +37841,9 @@
       <c r="C127" s="44" t="n"/>
       <c r="D127" s="44" t="n"/>
       <c r="E127" s="44" t="n"/>
+      <c r="G127" s="43" t="n">
+        <v>36</v>
+      </c>
       <c r="H127" s="44" t="n"/>
       <c r="I127" s="44" t="n"/>
       <c r="J127" s="44" t="n"/>
@@ -34841,6 +37857,9 @@
       <c r="C128" s="42" t="n"/>
       <c r="D128" s="42" t="n"/>
       <c r="E128" s="42" t="n"/>
+      <c r="G128" s="41" t="n">
+        <v>37</v>
+      </c>
       <c r="H128" s="42" t="n"/>
       <c r="I128" s="42" t="n"/>
       <c r="J128" s="42" t="n"/>
@@ -34854,6 +37873,9 @@
       <c r="C129" s="44" t="n"/>
       <c r="D129" s="44" t="n"/>
       <c r="E129" s="44" t="n"/>
+      <c r="G129" s="43" t="n">
+        <v>38</v>
+      </c>
       <c r="H129" s="44" t="n"/>
       <c r="I129" s="44" t="n"/>
       <c r="J129" s="44" t="n"/>
@@ -34867,6 +37889,9 @@
       <c r="C130" s="42" t="n"/>
       <c r="D130" s="42" t="n"/>
       <c r="E130" s="42" t="n"/>
+      <c r="G130" s="41" t="n">
+        <v>39</v>
+      </c>
       <c r="H130" s="42" t="n"/>
       <c r="I130" s="42" t="n"/>
       <c r="J130" s="42" t="n"/>
@@ -34880,6 +37905,9 @@
       <c r="C131" s="44" t="n"/>
       <c r="D131" s="44" t="n"/>
       <c r="E131" s="44" t="n"/>
+      <c r="G131" s="43" t="n">
+        <v>40</v>
+      </c>
       <c r="H131" s="44" t="n"/>
       <c r="I131" s="44" t="n"/>
       <c r="J131" s="44" t="n"/>
@@ -35002,6 +38030,9 @@
       <c r="C136" s="42" t="n"/>
       <c r="D136" s="42" t="n"/>
       <c r="E136" s="42" t="n"/>
+      <c r="G136" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H136" s="42" t="n"/>
       <c r="I136" s="42" t="n"/>
       <c r="J136" s="42" t="n"/>
@@ -35015,6 +38046,9 @@
       <c r="C137" s="44" t="n"/>
       <c r="D137" s="44" t="n"/>
       <c r="E137" s="44" t="n"/>
+      <c r="G137" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H137" s="44" t="n"/>
       <c r="I137" s="44" t="n"/>
       <c r="J137" s="44" t="n"/>
@@ -35028,6 +38062,9 @@
       <c r="C138" s="42" t="n"/>
       <c r="D138" s="42" t="n"/>
       <c r="E138" s="42" t="n"/>
+      <c r="G138" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H138" s="42" t="n"/>
       <c r="I138" s="42" t="n"/>
       <c r="J138" s="42" t="n"/>
@@ -35041,6 +38078,9 @@
       <c r="C139" s="44" t="n"/>
       <c r="D139" s="44" t="n"/>
       <c r="E139" s="44" t="n"/>
+      <c r="G139" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H139" s="44" t="n"/>
       <c r="I139" s="44" t="n"/>
       <c r="J139" s="44" t="n"/>
@@ -35054,6 +38094,9 @@
       <c r="C140" s="42" t="n"/>
       <c r="D140" s="42" t="n"/>
       <c r="E140" s="42" t="n"/>
+      <c r="G140" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H140" s="42" t="n"/>
       <c r="I140" s="42" t="n"/>
       <c r="J140" s="42" t="n"/>
@@ -35067,6 +38110,9 @@
       <c r="C141" s="44" t="n"/>
       <c r="D141" s="44" t="n"/>
       <c r="E141" s="44" t="n"/>
+      <c r="G141" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H141" s="44" t="n"/>
       <c r="I141" s="44" t="n"/>
       <c r="J141" s="44" t="n"/>
@@ -35080,6 +38126,9 @@
       <c r="C142" s="42" t="n"/>
       <c r="D142" s="42" t="n"/>
       <c r="E142" s="42" t="n"/>
+      <c r="G142" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H142" s="42" t="n"/>
       <c r="I142" s="42" t="n"/>
       <c r="J142" s="42" t="n"/>
@@ -35093,6 +38142,9 @@
       <c r="C143" s="44" t="n"/>
       <c r="D143" s="44" t="n"/>
       <c r="E143" s="44" t="n"/>
+      <c r="G143" s="43" t="n">
+        <v>8</v>
+      </c>
       <c r="H143" s="44" t="n"/>
       <c r="I143" s="44" t="n"/>
       <c r="J143" s="44" t="n"/>
@@ -35106,6 +38158,9 @@
       <c r="C144" s="42" t="n"/>
       <c r="D144" s="42" t="n"/>
       <c r="E144" s="42" t="n"/>
+      <c r="G144" s="41" t="n">
+        <v>9</v>
+      </c>
       <c r="H144" s="42" t="n"/>
       <c r="I144" s="42" t="n"/>
       <c r="J144" s="42" t="n"/>
@@ -35119,6 +38174,9 @@
       <c r="C145" s="44" t="n"/>
       <c r="D145" s="44" t="n"/>
       <c r="E145" s="44" t="n"/>
+      <c r="G145" s="43" t="n">
+        <v>10</v>
+      </c>
       <c r="H145" s="44" t="n"/>
       <c r="I145" s="44" t="n"/>
       <c r="J145" s="44" t="n"/>
@@ -35132,6 +38190,9 @@
       <c r="C146" s="42" t="n"/>
       <c r="D146" s="42" t="n"/>
       <c r="E146" s="42" t="n"/>
+      <c r="G146" s="41" t="n">
+        <v>11</v>
+      </c>
       <c r="H146" s="42" t="n"/>
       <c r="I146" s="42" t="n"/>
       <c r="J146" s="42" t="n"/>
@@ -35145,6 +38206,9 @@
       <c r="C147" s="44" t="n"/>
       <c r="D147" s="44" t="n"/>
       <c r="E147" s="44" t="n"/>
+      <c r="G147" s="43" t="n">
+        <v>12</v>
+      </c>
       <c r="H147" s="44" t="n"/>
       <c r="I147" s="44" t="n"/>
       <c r="J147" s="44" t="n"/>
@@ -35158,6 +38222,9 @@
       <c r="C148" s="42" t="n"/>
       <c r="D148" s="42" t="n"/>
       <c r="E148" s="42" t="n"/>
+      <c r="G148" s="41" t="n">
+        <v>13</v>
+      </c>
       <c r="H148" s="42" t="n"/>
       <c r="I148" s="42" t="n"/>
       <c r="J148" s="42" t="n"/>
@@ -35171,6 +38238,9 @@
       <c r="C149" s="44" t="n"/>
       <c r="D149" s="44" t="n"/>
       <c r="E149" s="44" t="n"/>
+      <c r="G149" s="43" t="n">
+        <v>14</v>
+      </c>
       <c r="H149" s="44" t="n"/>
       <c r="I149" s="44" t="n"/>
       <c r="J149" s="44" t="n"/>
@@ -35184,6 +38254,9 @@
       <c r="C150" s="42" t="n"/>
       <c r="D150" s="42" t="n"/>
       <c r="E150" s="42" t="n"/>
+      <c r="G150" s="41" t="n">
+        <v>15</v>
+      </c>
       <c r="H150" s="42" t="n"/>
       <c r="I150" s="42" t="n"/>
       <c r="J150" s="42" t="n"/>
@@ -35197,6 +38270,9 @@
       <c r="C151" s="44" t="n"/>
       <c r="D151" s="44" t="n"/>
       <c r="E151" s="44" t="n"/>
+      <c r="G151" s="43" t="n">
+        <v>16</v>
+      </c>
       <c r="H151" s="44" t="n"/>
       <c r="I151" s="44" t="n"/>
       <c r="J151" s="44" t="n"/>
@@ -35210,6 +38286,9 @@
       <c r="C152" s="42" t="n"/>
       <c r="D152" s="42" t="n"/>
       <c r="E152" s="42" t="n"/>
+      <c r="G152" s="41" t="n">
+        <v>17</v>
+      </c>
       <c r="H152" s="42" t="n"/>
       <c r="I152" s="42" t="n"/>
       <c r="J152" s="42" t="n"/>
@@ -35223,6 +38302,9 @@
       <c r="C153" s="44" t="n"/>
       <c r="D153" s="44" t="n"/>
       <c r="E153" s="44" t="n"/>
+      <c r="G153" s="43" t="n">
+        <v>18</v>
+      </c>
       <c r="H153" s="44" t="n"/>
       <c r="I153" s="44" t="n"/>
       <c r="J153" s="44" t="n"/>
@@ -35236,6 +38318,9 @@
       <c r="C154" s="42" t="n"/>
       <c r="D154" s="42" t="n"/>
       <c r="E154" s="42" t="n"/>
+      <c r="G154" s="41" t="n">
+        <v>19</v>
+      </c>
       <c r="H154" s="42" t="n"/>
       <c r="I154" s="42" t="n"/>
       <c r="J154" s="42" t="n"/>
@@ -35249,6 +38334,9 @@
       <c r="C155" s="44" t="n"/>
       <c r="D155" s="44" t="n"/>
       <c r="E155" s="44" t="n"/>
+      <c r="G155" s="43" t="n">
+        <v>20</v>
+      </c>
       <c r="H155" s="44" t="n"/>
       <c r="I155" s="44" t="n"/>
       <c r="J155" s="44" t="n"/>
@@ -35262,6 +38350,9 @@
       <c r="C156" s="42" t="n"/>
       <c r="D156" s="42" t="n"/>
       <c r="E156" s="42" t="n"/>
+      <c r="G156" s="41" t="n">
+        <v>21</v>
+      </c>
       <c r="H156" s="42" t="n"/>
       <c r="I156" s="42" t="n"/>
       <c r="J156" s="42" t="n"/>
@@ -35275,6 +38366,9 @@
       <c r="C157" s="44" t="n"/>
       <c r="D157" s="44" t="n"/>
       <c r="E157" s="44" t="n"/>
+      <c r="G157" s="43" t="n">
+        <v>22</v>
+      </c>
       <c r="H157" s="44" t="n"/>
       <c r="I157" s="44" t="n"/>
       <c r="J157" s="44" t="n"/>
@@ -35288,6 +38382,9 @@
       <c r="C158" s="42" t="n"/>
       <c r="D158" s="42" t="n"/>
       <c r="E158" s="42" t="n"/>
+      <c r="G158" s="41" t="n">
+        <v>23</v>
+      </c>
       <c r="H158" s="42" t="n"/>
       <c r="I158" s="42" t="n"/>
       <c r="J158" s="42" t="n"/>
@@ -35301,6 +38398,9 @@
       <c r="C159" s="44" t="n"/>
       <c r="D159" s="44" t="n"/>
       <c r="E159" s="44" t="n"/>
+      <c r="G159" s="43" t="n">
+        <v>24</v>
+      </c>
       <c r="H159" s="44" t="n"/>
       <c r="I159" s="44" t="n"/>
       <c r="J159" s="44" t="n"/>
@@ -35314,6 +38414,9 @@
       <c r="C160" s="42" t="n"/>
       <c r="D160" s="42" t="n"/>
       <c r="E160" s="42" t="n"/>
+      <c r="G160" s="41" t="n">
+        <v>25</v>
+      </c>
       <c r="H160" s="42" t="n"/>
       <c r="I160" s="42" t="n"/>
       <c r="J160" s="42" t="n"/>
@@ -35327,6 +38430,9 @@
       <c r="C161" s="44" t="n"/>
       <c r="D161" s="44" t="n"/>
       <c r="E161" s="44" t="n"/>
+      <c r="G161" s="43" t="n">
+        <v>26</v>
+      </c>
       <c r="H161" s="44" t="n"/>
       <c r="I161" s="44" t="n"/>
       <c r="J161" s="44" t="n"/>
@@ -35340,6 +38446,9 @@
       <c r="C162" s="42" t="n"/>
       <c r="D162" s="42" t="n"/>
       <c r="E162" s="42" t="n"/>
+      <c r="G162" s="41" t="n">
+        <v>27</v>
+      </c>
       <c r="H162" s="42" t="n"/>
       <c r="I162" s="42" t="n"/>
       <c r="J162" s="42" t="n"/>
@@ -35353,6 +38462,9 @@
       <c r="C163" s="44" t="n"/>
       <c r="D163" s="44" t="n"/>
       <c r="E163" s="44" t="n"/>
+      <c r="G163" s="43" t="n">
+        <v>28</v>
+      </c>
       <c r="H163" s="44" t="n"/>
       <c r="I163" s="44" t="n"/>
       <c r="J163" s="44" t="n"/>
@@ -35366,6 +38478,9 @@
       <c r="C164" s="42" t="n"/>
       <c r="D164" s="42" t="n"/>
       <c r="E164" s="42" t="n"/>
+      <c r="G164" s="41" t="n">
+        <v>29</v>
+      </c>
       <c r="H164" s="42" t="n"/>
       <c r="I164" s="42" t="n"/>
       <c r="J164" s="42" t="n"/>
@@ -35379,6 +38494,9 @@
       <c r="C165" s="44" t="n"/>
       <c r="D165" s="44" t="n"/>
       <c r="E165" s="44" t="n"/>
+      <c r="G165" s="43" t="n">
+        <v>30</v>
+      </c>
       <c r="H165" s="44" t="n"/>
       <c r="I165" s="44" t="n"/>
       <c r="J165" s="44" t="n"/>
@@ -35392,6 +38510,9 @@
       <c r="C166" s="42" t="n"/>
       <c r="D166" s="42" t="n"/>
       <c r="E166" s="42" t="n"/>
+      <c r="G166" s="41" t="n">
+        <v>31</v>
+      </c>
       <c r="H166" s="42" t="n"/>
       <c r="I166" s="42" t="n"/>
       <c r="J166" s="42" t="n"/>
@@ -35405,6 +38526,9 @@
       <c r="C167" s="44" t="n"/>
       <c r="D167" s="44" t="n"/>
       <c r="E167" s="44" t="n"/>
+      <c r="G167" s="43" t="n">
+        <v>32</v>
+      </c>
       <c r="H167" s="44" t="n"/>
       <c r="I167" s="44" t="n"/>
       <c r="J167" s="44" t="n"/>
@@ -35418,6 +38542,9 @@
       <c r="C168" s="42" t="n"/>
       <c r="D168" s="42" t="n"/>
       <c r="E168" s="42" t="n"/>
+      <c r="G168" s="41" t="n">
+        <v>33</v>
+      </c>
       <c r="H168" s="42" t="n"/>
       <c r="I168" s="42" t="n"/>
       <c r="J168" s="42" t="n"/>
@@ -35431,6 +38558,9 @@
       <c r="C169" s="44" t="n"/>
       <c r="D169" s="44" t="n"/>
       <c r="E169" s="44" t="n"/>
+      <c r="G169" s="43" t="n">
+        <v>34</v>
+      </c>
       <c r="H169" s="44" t="n"/>
       <c r="I169" s="44" t="n"/>
       <c r="J169" s="44" t="n"/>
@@ -35444,6 +38574,9 @@
       <c r="C170" s="42" t="n"/>
       <c r="D170" s="42" t="n"/>
       <c r="E170" s="42" t="n"/>
+      <c r="G170" s="41" t="n">
+        <v>35</v>
+      </c>
       <c r="H170" s="42" t="n"/>
       <c r="I170" s="42" t="n"/>
       <c r="J170" s="42" t="n"/>
@@ -35457,6 +38590,9 @@
       <c r="C171" s="44" t="n"/>
       <c r="D171" s="44" t="n"/>
       <c r="E171" s="44" t="n"/>
+      <c r="G171" s="43" t="n">
+        <v>36</v>
+      </c>
       <c r="H171" s="44" t="n"/>
       <c r="I171" s="44" t="n"/>
       <c r="J171" s="44" t="n"/>
@@ -35470,6 +38606,9 @@
       <c r="C172" s="42" t="n"/>
       <c r="D172" s="42" t="n"/>
       <c r="E172" s="42" t="n"/>
+      <c r="G172" s="41" t="n">
+        <v>37</v>
+      </c>
       <c r="H172" s="42" t="n"/>
       <c r="I172" s="42" t="n"/>
       <c r="J172" s="42" t="n"/>
@@ -35483,6 +38622,9 @@
       <c r="C173" s="44" t="n"/>
       <c r="D173" s="44" t="n"/>
       <c r="E173" s="44" t="n"/>
+      <c r="G173" s="43" t="n">
+        <v>38</v>
+      </c>
       <c r="H173" s="44" t="n"/>
       <c r="I173" s="44" t="n"/>
       <c r="J173" s="44" t="n"/>
@@ -35496,6 +38638,9 @@
       <c r="C174" s="42" t="n"/>
       <c r="D174" s="42" t="n"/>
       <c r="E174" s="42" t="n"/>
+      <c r="G174" s="41" t="n">
+        <v>39</v>
+      </c>
       <c r="H174" s="42" t="n"/>
       <c r="I174" s="42" t="n"/>
       <c r="J174" s="42" t="n"/>
@@ -35509,6 +38654,9 @@
       <c r="C175" s="44" t="n"/>
       <c r="D175" s="44" t="n"/>
       <c r="E175" s="44" t="n"/>
+      <c r="G175" s="43" t="n">
+        <v>40</v>
+      </c>
       <c r="H175" s="44" t="n"/>
       <c r="I175" s="44" t="n"/>
       <c r="J175" s="44" t="n"/>
@@ -35631,6 +38779,9 @@
       <c r="C180" s="42" t="n"/>
       <c r="D180" s="42" t="n"/>
       <c r="E180" s="42" t="n"/>
+      <c r="G180" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H180" s="42" t="n"/>
       <c r="I180" s="42" t="n"/>
       <c r="J180" s="42" t="n"/>
@@ -35644,6 +38795,9 @@
       <c r="C181" s="44" t="n"/>
       <c r="D181" s="44" t="n"/>
       <c r="E181" s="44" t="n"/>
+      <c r="G181" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H181" s="44" t="n"/>
       <c r="I181" s="44" t="n"/>
       <c r="J181" s="44" t="n"/>
@@ -35657,6 +38811,9 @@
       <c r="C182" s="42" t="n"/>
       <c r="D182" s="42" t="n"/>
       <c r="E182" s="42" t="n"/>
+      <c r="G182" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H182" s="42" t="n"/>
       <c r="I182" s="42" t="n"/>
       <c r="J182" s="42" t="n"/>
@@ -35670,6 +38827,9 @@
       <c r="C183" s="44" t="n"/>
       <c r="D183" s="44" t="n"/>
       <c r="E183" s="44" t="n"/>
+      <c r="G183" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H183" s="44" t="n"/>
       <c r="I183" s="44" t="n"/>
       <c r="J183" s="44" t="n"/>
@@ -35683,6 +38843,9 @@
       <c r="C184" s="42" t="n"/>
       <c r="D184" s="42" t="n"/>
       <c r="E184" s="42" t="n"/>
+      <c r="G184" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H184" s="42" t="n"/>
       <c r="I184" s="42" t="n"/>
       <c r="J184" s="42" t="n"/>
@@ -35696,6 +38859,9 @@
       <c r="C185" s="44" t="n"/>
       <c r="D185" s="44" t="n"/>
       <c r="E185" s="44" t="n"/>
+      <c r="G185" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H185" s="44" t="n"/>
       <c r="I185" s="44" t="n"/>
       <c r="J185" s="44" t="n"/>
@@ -35709,6 +38875,9 @@
       <c r="C186" s="42" t="n"/>
       <c r="D186" s="42" t="n"/>
       <c r="E186" s="42" t="n"/>
+      <c r="G186" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H186" s="42" t="n"/>
       <c r="I186" s="42" t="n"/>
       <c r="J186" s="42" t="n"/>
@@ -35722,6 +38891,9 @@
       <c r="C187" s="44" t="n"/>
       <c r="D187" s="44" t="n"/>
       <c r="E187" s="44" t="n"/>
+      <c r="G187" s="43" t="n">
+        <v>8</v>
+      </c>
       <c r="H187" s="44" t="n"/>
       <c r="I187" s="44" t="n"/>
       <c r="J187" s="44" t="n"/>
@@ -35735,6 +38907,9 @@
       <c r="C188" s="42" t="n"/>
       <c r="D188" s="42" t="n"/>
       <c r="E188" s="42" t="n"/>
+      <c r="G188" s="41" t="n">
+        <v>9</v>
+      </c>
       <c r="H188" s="42" t="n"/>
       <c r="I188" s="42" t="n"/>
       <c r="J188" s="42" t="n"/>
@@ -35748,6 +38923,9 @@
       <c r="C189" s="44" t="n"/>
       <c r="D189" s="44" t="n"/>
       <c r="E189" s="44" t="n"/>
+      <c r="G189" s="43" t="n">
+        <v>10</v>
+      </c>
       <c r="H189" s="44" t="n"/>
       <c r="I189" s="44" t="n"/>
       <c r="J189" s="44" t="n"/>
@@ -35761,6 +38939,9 @@
       <c r="C190" s="42" t="n"/>
       <c r="D190" s="42" t="n"/>
       <c r="E190" s="42" t="n"/>
+      <c r="G190" s="41" t="n">
+        <v>11</v>
+      </c>
       <c r="H190" s="42" t="n"/>
       <c r="I190" s="42" t="n"/>
       <c r="J190" s="42" t="n"/>
@@ -35774,6 +38955,9 @@
       <c r="C191" s="44" t="n"/>
       <c r="D191" s="44" t="n"/>
       <c r="E191" s="44" t="n"/>
+      <c r="G191" s="43" t="n">
+        <v>12</v>
+      </c>
       <c r="H191" s="44" t="n"/>
       <c r="I191" s="44" t="n"/>
       <c r="J191" s="44" t="n"/>
@@ -35787,6 +38971,9 @@
       <c r="C192" s="42" t="n"/>
       <c r="D192" s="42" t="n"/>
       <c r="E192" s="42" t="n"/>
+      <c r="G192" s="41" t="n">
+        <v>13</v>
+      </c>
       <c r="H192" s="42" t="n"/>
       <c r="I192" s="42" t="n"/>
       <c r="J192" s="42" t="n"/>
@@ -35800,6 +38987,9 @@
       <c r="C193" s="44" t="n"/>
       <c r="D193" s="44" t="n"/>
       <c r="E193" s="44" t="n"/>
+      <c r="G193" s="43" t="n">
+        <v>14</v>
+      </c>
       <c r="H193" s="44" t="n"/>
       <c r="I193" s="44" t="n"/>
       <c r="J193" s="44" t="n"/>
@@ -35813,6 +39003,9 @@
       <c r="C194" s="42" t="n"/>
       <c r="D194" s="42" t="n"/>
       <c r="E194" s="42" t="n"/>
+      <c r="G194" s="41" t="n">
+        <v>15</v>
+      </c>
       <c r="H194" s="42" t="n"/>
       <c r="I194" s="42" t="n"/>
       <c r="J194" s="42" t="n"/>
@@ -35826,6 +39019,9 @@
       <c r="C195" s="44" t="n"/>
       <c r="D195" s="44" t="n"/>
       <c r="E195" s="44" t="n"/>
+      <c r="G195" s="43" t="n">
+        <v>16</v>
+      </c>
       <c r="H195" s="44" t="n"/>
       <c r="I195" s="44" t="n"/>
       <c r="J195" s="44" t="n"/>
@@ -35839,6 +39035,9 @@
       <c r="C196" s="42" t="n"/>
       <c r="D196" s="42" t="n"/>
       <c r="E196" s="42" t="n"/>
+      <c r="G196" s="41" t="n">
+        <v>17</v>
+      </c>
       <c r="H196" s="42" t="n"/>
       <c r="I196" s="42" t="n"/>
       <c r="J196" s="42" t="n"/>
@@ -35852,6 +39051,9 @@
       <c r="C197" s="44" t="n"/>
       <c r="D197" s="44" t="n"/>
       <c r="E197" s="44" t="n"/>
+      <c r="G197" s="43" t="n">
+        <v>18</v>
+      </c>
       <c r="H197" s="44" t="n"/>
       <c r="I197" s="44" t="n"/>
       <c r="J197" s="44" t="n"/>
@@ -35865,6 +39067,9 @@
       <c r="C198" s="42" t="n"/>
       <c r="D198" s="42" t="n"/>
       <c r="E198" s="42" t="n"/>
+      <c r="G198" s="41" t="n">
+        <v>19</v>
+      </c>
       <c r="H198" s="42" t="n"/>
       <c r="I198" s="42" t="n"/>
       <c r="J198" s="42" t="n"/>
@@ -35878,6 +39083,9 @@
       <c r="C199" s="44" t="n"/>
       <c r="D199" s="44" t="n"/>
       <c r="E199" s="44" t="n"/>
+      <c r="G199" s="43" t="n">
+        <v>20</v>
+      </c>
       <c r="H199" s="44" t="n"/>
       <c r="I199" s="44" t="n"/>
       <c r="J199" s="44" t="n"/>
@@ -35891,6 +39099,9 @@
       <c r="C200" s="42" t="n"/>
       <c r="D200" s="42" t="n"/>
       <c r="E200" s="42" t="n"/>
+      <c r="G200" s="41" t="n">
+        <v>21</v>
+      </c>
       <c r="H200" s="42" t="n"/>
       <c r="I200" s="42" t="n"/>
       <c r="J200" s="42" t="n"/>
@@ -35904,6 +39115,9 @@
       <c r="C201" s="44" t="n"/>
       <c r="D201" s="44" t="n"/>
       <c r="E201" s="44" t="n"/>
+      <c r="G201" s="43" t="n">
+        <v>22</v>
+      </c>
       <c r="H201" s="44" t="n"/>
       <c r="I201" s="44" t="n"/>
       <c r="J201" s="44" t="n"/>
@@ -35917,6 +39131,9 @@
       <c r="C202" s="42" t="n"/>
       <c r="D202" s="42" t="n"/>
       <c r="E202" s="42" t="n"/>
+      <c r="G202" s="41" t="n">
+        <v>23</v>
+      </c>
       <c r="H202" s="42" t="n"/>
       <c r="I202" s="42" t="n"/>
       <c r="J202" s="42" t="n"/>
@@ -35930,6 +39147,9 @@
       <c r="C203" s="44" t="n"/>
       <c r="D203" s="44" t="n"/>
       <c r="E203" s="44" t="n"/>
+      <c r="G203" s="43" t="n">
+        <v>24</v>
+      </c>
       <c r="H203" s="44" t="n"/>
       <c r="I203" s="44" t="n"/>
       <c r="J203" s="44" t="n"/>
@@ -35943,6 +39163,9 @@
       <c r="C204" s="42" t="n"/>
       <c r="D204" s="42" t="n"/>
       <c r="E204" s="42" t="n"/>
+      <c r="G204" s="41" t="n">
+        <v>25</v>
+      </c>
       <c r="H204" s="42" t="n"/>
       <c r="I204" s="42" t="n"/>
       <c r="J204" s="42" t="n"/>
@@ -35956,6 +39179,9 @@
       <c r="C205" s="44" t="n"/>
       <c r="D205" s="44" t="n"/>
       <c r="E205" s="44" t="n"/>
+      <c r="G205" s="43" t="n">
+        <v>26</v>
+      </c>
       <c r="H205" s="44" t="n"/>
       <c r="I205" s="44" t="n"/>
       <c r="J205" s="44" t="n"/>
@@ -35969,6 +39195,9 @@
       <c r="C206" s="42" t="n"/>
       <c r="D206" s="42" t="n"/>
       <c r="E206" s="42" t="n"/>
+      <c r="G206" s="41" t="n">
+        <v>27</v>
+      </c>
       <c r="H206" s="42" t="n"/>
       <c r="I206" s="42" t="n"/>
       <c r="J206" s="42" t="n"/>
@@ -35982,6 +39211,9 @@
       <c r="C207" s="44" t="n"/>
       <c r="D207" s="44" t="n"/>
       <c r="E207" s="44" t="n"/>
+      <c r="G207" s="43" t="n">
+        <v>28</v>
+      </c>
       <c r="H207" s="44" t="n"/>
       <c r="I207" s="44" t="n"/>
       <c r="J207" s="44" t="n"/>
@@ -35995,6 +39227,9 @@
       <c r="C208" s="42" t="n"/>
       <c r="D208" s="42" t="n"/>
       <c r="E208" s="42" t="n"/>
+      <c r="G208" s="41" t="n">
+        <v>29</v>
+      </c>
       <c r="H208" s="42" t="n"/>
       <c r="I208" s="42" t="n"/>
       <c r="J208" s="42" t="n"/>
@@ -36008,6 +39243,9 @@
       <c r="C209" s="44" t="n"/>
       <c r="D209" s="44" t="n"/>
       <c r="E209" s="44" t="n"/>
+      <c r="G209" s="43" t="n">
+        <v>30</v>
+      </c>
       <c r="H209" s="44" t="n"/>
       <c r="I209" s="44" t="n"/>
       <c r="J209" s="44" t="n"/>
@@ -36021,6 +39259,9 @@
       <c r="C210" s="42" t="n"/>
       <c r="D210" s="42" t="n"/>
       <c r="E210" s="42" t="n"/>
+      <c r="G210" s="41" t="n">
+        <v>31</v>
+      </c>
       <c r="H210" s="42" t="n"/>
       <c r="I210" s="42" t="n"/>
       <c r="J210" s="42" t="n"/>
@@ -36034,6 +39275,9 @@
       <c r="C211" s="44" t="n"/>
       <c r="D211" s="44" t="n"/>
       <c r="E211" s="44" t="n"/>
+      <c r="G211" s="43" t="n">
+        <v>32</v>
+      </c>
       <c r="H211" s="44" t="n"/>
       <c r="I211" s="44" t="n"/>
       <c r="J211" s="44" t="n"/>
@@ -36047,6 +39291,9 @@
       <c r="C212" s="42" t="n"/>
       <c r="D212" s="42" t="n"/>
       <c r="E212" s="42" t="n"/>
+      <c r="G212" s="41" t="n">
+        <v>33</v>
+      </c>
       <c r="H212" s="42" t="n"/>
       <c r="I212" s="42" t="n"/>
       <c r="J212" s="42" t="n"/>
@@ -36060,6 +39307,9 @@
       <c r="C213" s="44" t="n"/>
       <c r="D213" s="44" t="n"/>
       <c r="E213" s="44" t="n"/>
+      <c r="G213" s="43" t="n">
+        <v>34</v>
+      </c>
       <c r="H213" s="44" t="n"/>
       <c r="I213" s="44" t="n"/>
       <c r="J213" s="44" t="n"/>
@@ -36073,6 +39323,9 @@
       <c r="C214" s="42" t="n"/>
       <c r="D214" s="42" t="n"/>
       <c r="E214" s="42" t="n"/>
+      <c r="G214" s="41" t="n">
+        <v>35</v>
+      </c>
       <c r="H214" s="42" t="n"/>
       <c r="I214" s="42" t="n"/>
       <c r="J214" s="42" t="n"/>
@@ -36086,6 +39339,9 @@
       <c r="C215" s="44" t="n"/>
       <c r="D215" s="44" t="n"/>
       <c r="E215" s="44" t="n"/>
+      <c r="G215" s="43" t="n">
+        <v>36</v>
+      </c>
       <c r="H215" s="44" t="n"/>
       <c r="I215" s="44" t="n"/>
       <c r="J215" s="44" t="n"/>
@@ -36099,6 +39355,9 @@
       <c r="C216" s="42" t="n"/>
       <c r="D216" s="42" t="n"/>
       <c r="E216" s="42" t="n"/>
+      <c r="G216" s="41" t="n">
+        <v>37</v>
+      </c>
       <c r="H216" s="42" t="n"/>
       <c r="I216" s="42" t="n"/>
       <c r="J216" s="42" t="n"/>
@@ -36112,6 +39371,9 @@
       <c r="C217" s="44" t="n"/>
       <c r="D217" s="44" t="n"/>
       <c r="E217" s="44" t="n"/>
+      <c r="G217" s="43" t="n">
+        <v>38</v>
+      </c>
       <c r="H217" s="44" t="n"/>
       <c r="I217" s="44" t="n"/>
       <c r="J217" s="44" t="n"/>
@@ -36125,6 +39387,9 @@
       <c r="C218" s="42" t="n"/>
       <c r="D218" s="42" t="n"/>
       <c r="E218" s="42" t="n"/>
+      <c r="G218" s="41" t="n">
+        <v>39</v>
+      </c>
       <c r="H218" s="42" t="n"/>
       <c r="I218" s="42" t="n"/>
       <c r="J218" s="42" t="n"/>
@@ -36138,6 +39403,9 @@
       <c r="C219" s="44" t="n"/>
       <c r="D219" s="44" t="n"/>
       <c r="E219" s="44" t="n"/>
+      <c r="G219" s="43" t="n">
+        <v>40</v>
+      </c>
       <c r="H219" s="44" t="n"/>
       <c r="I219" s="44" t="n"/>
       <c r="J219" s="44" t="n"/>
@@ -36316,6 +39584,9 @@
       <c r="C4" s="42" t="n"/>
       <c r="D4" s="42" t="n"/>
       <c r="E4" s="42" t="n"/>
+      <c r="G4" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H4" s="42" t="n"/>
       <c r="I4" s="42" t="n"/>
       <c r="J4" s="42" t="n"/>
@@ -36329,6 +39600,9 @@
       <c r="C5" s="44" t="n"/>
       <c r="D5" s="44" t="n"/>
       <c r="E5" s="44" t="n"/>
+      <c r="G5" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H5" s="44" t="n"/>
       <c r="I5" s="44" t="n"/>
       <c r="J5" s="44" t="n"/>
@@ -36342,6 +39616,9 @@
       <c r="C6" s="42" t="n"/>
       <c r="D6" s="42" t="n"/>
       <c r="E6" s="42" t="n"/>
+      <c r="G6" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H6" s="42" t="n"/>
       <c r="I6" s="42" t="n"/>
       <c r="J6" s="42" t="n"/>
@@ -36355,6 +39632,9 @@
       <c r="C7" s="44" t="n"/>
       <c r="D7" s="44" t="n"/>
       <c r="E7" s="44" t="n"/>
+      <c r="G7" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H7" s="44" t="n"/>
       <c r="I7" s="44" t="n"/>
       <c r="J7" s="44" t="n"/>
@@ -36368,6 +39648,9 @@
       <c r="C8" s="42" t="n"/>
       <c r="D8" s="42" t="n"/>
       <c r="E8" s="42" t="n"/>
+      <c r="G8" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H8" s="42" t="n"/>
       <c r="I8" s="42" t="n"/>
       <c r="J8" s="42" t="n"/>
@@ -36381,6 +39664,9 @@
       <c r="C9" s="44" t="n"/>
       <c r="D9" s="44" t="n"/>
       <c r="E9" s="44" t="n"/>
+      <c r="G9" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H9" s="44" t="n"/>
       <c r="I9" s="44" t="n"/>
       <c r="J9" s="44" t="n"/>
@@ -36394,6 +39680,9 @@
       <c r="C10" s="42" t="n"/>
       <c r="D10" s="42" t="n"/>
       <c r="E10" s="42" t="n"/>
+      <c r="G10" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H10" s="42" t="n"/>
       <c r="I10" s="42" t="n"/>
       <c r="J10" s="42" t="n"/>
@@ -36496,6 +39785,9 @@
       <c r="C14" s="42" t="n"/>
       <c r="D14" s="42" t="n"/>
       <c r="E14" s="42" t="n"/>
+      <c r="G14" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H14" s="42" t="n"/>
       <c r="I14" s="42" t="n"/>
       <c r="J14" s="42" t="n"/>
@@ -36509,6 +39801,9 @@
       <c r="C15" s="44" t="n"/>
       <c r="D15" s="44" t="n"/>
       <c r="E15" s="44" t="n"/>
+      <c r="G15" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H15" s="44" t="n"/>
       <c r="I15" s="44" t="n"/>
       <c r="J15" s="44" t="n"/>
@@ -36522,6 +39817,9 @@
       <c r="C16" s="42" t="n"/>
       <c r="D16" s="42" t="n"/>
       <c r="E16" s="42" t="n"/>
+      <c r="G16" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H16" s="42" t="n"/>
       <c r="I16" s="42" t="n"/>
       <c r="J16" s="42" t="n"/>
@@ -36535,6 +39833,9 @@
       <c r="C17" s="44" t="n"/>
       <c r="D17" s="44" t="n"/>
       <c r="E17" s="44" t="n"/>
+      <c r="G17" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H17" s="44" t="n"/>
       <c r="I17" s="44" t="n"/>
       <c r="J17" s="44" t="n"/>
@@ -36548,6 +39849,9 @@
       <c r="C18" s="42" t="n"/>
       <c r="D18" s="42" t="n"/>
       <c r="E18" s="42" t="n"/>
+      <c r="G18" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H18" s="42" t="n"/>
       <c r="I18" s="42" t="n"/>
       <c r="J18" s="42" t="n"/>
@@ -36561,6 +39865,9 @@
       <c r="C19" s="44" t="n"/>
       <c r="D19" s="44" t="n"/>
       <c r="E19" s="44" t="n"/>
+      <c r="G19" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H19" s="44" t="n"/>
       <c r="I19" s="44" t="n"/>
       <c r="J19" s="44" t="n"/>
@@ -36574,6 +39881,9 @@
       <c r="C20" s="42" t="n"/>
       <c r="D20" s="42" t="n"/>
       <c r="E20" s="42" t="n"/>
+      <c r="G20" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H20" s="42" t="n"/>
       <c r="I20" s="42" t="n"/>
       <c r="J20" s="42" t="n"/>
@@ -36676,6 +39986,9 @@
       <c r="C24" s="42" t="n"/>
       <c r="D24" s="42" t="n"/>
       <c r="E24" s="42" t="n"/>
+      <c r="G24" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H24" s="42" t="n"/>
       <c r="I24" s="42" t="n"/>
       <c r="J24" s="42" t="n"/>
@@ -36689,6 +40002,9 @@
       <c r="C25" s="44" t="n"/>
       <c r="D25" s="44" t="n"/>
       <c r="E25" s="44" t="n"/>
+      <c r="G25" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H25" s="44" t="n"/>
       <c r="I25" s="44" t="n"/>
       <c r="J25" s="44" t="n"/>
@@ -36702,6 +40018,9 @@
       <c r="C26" s="42" t="n"/>
       <c r="D26" s="42" t="n"/>
       <c r="E26" s="42" t="n"/>
+      <c r="G26" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H26" s="42" t="n"/>
       <c r="I26" s="42" t="n"/>
       <c r="J26" s="42" t="n"/>
@@ -36715,6 +40034,9 @@
       <c r="C27" s="44" t="n"/>
       <c r="D27" s="44" t="n"/>
       <c r="E27" s="44" t="n"/>
+      <c r="G27" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H27" s="44" t="n"/>
       <c r="I27" s="44" t="n"/>
       <c r="J27" s="44" t="n"/>
@@ -36728,6 +40050,9 @@
       <c r="C28" s="42" t="n"/>
       <c r="D28" s="42" t="n"/>
       <c r="E28" s="42" t="n"/>
+      <c r="G28" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H28" s="42" t="n"/>
       <c r="I28" s="42" t="n"/>
       <c r="J28" s="42" t="n"/>
@@ -36741,6 +40066,9 @@
       <c r="C29" s="44" t="n"/>
       <c r="D29" s="44" t="n"/>
       <c r="E29" s="44" t="n"/>
+      <c r="G29" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H29" s="44" t="n"/>
       <c r="I29" s="44" t="n"/>
       <c r="J29" s="44" t="n"/>
@@ -36754,6 +40082,9 @@
       <c r="C30" s="42" t="n"/>
       <c r="D30" s="42" t="n"/>
       <c r="E30" s="42" t="n"/>
+      <c r="G30" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H30" s="42" t="n"/>
       <c r="I30" s="42" t="n"/>
       <c r="J30" s="42" t="n"/>
@@ -36856,6 +40187,9 @@
       <c r="C34" s="42" t="n"/>
       <c r="D34" s="42" t="n"/>
       <c r="E34" s="42" t="n"/>
+      <c r="G34" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H34" s="42" t="n"/>
       <c r="I34" s="42" t="n"/>
       <c r="J34" s="42" t="n"/>
@@ -36869,6 +40203,9 @@
       <c r="C35" s="44" t="n"/>
       <c r="D35" s="44" t="n"/>
       <c r="E35" s="44" t="n"/>
+      <c r="G35" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H35" s="44" t="n"/>
       <c r="I35" s="44" t="n"/>
       <c r="J35" s="44" t="n"/>
@@ -36882,6 +40219,9 @@
       <c r="C36" s="42" t="n"/>
       <c r="D36" s="42" t="n"/>
       <c r="E36" s="42" t="n"/>
+      <c r="G36" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H36" s="42" t="n"/>
       <c r="I36" s="42" t="n"/>
       <c r="J36" s="42" t="n"/>
@@ -36895,6 +40235,9 @@
       <c r="C37" s="44" t="n"/>
       <c r="D37" s="44" t="n"/>
       <c r="E37" s="44" t="n"/>
+      <c r="G37" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H37" s="44" t="n"/>
       <c r="I37" s="44" t="n"/>
       <c r="J37" s="44" t="n"/>
@@ -36908,6 +40251,9 @@
       <c r="C38" s="42" t="n"/>
       <c r="D38" s="42" t="n"/>
       <c r="E38" s="42" t="n"/>
+      <c r="G38" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H38" s="42" t="n"/>
       <c r="I38" s="42" t="n"/>
       <c r="J38" s="42" t="n"/>
@@ -36921,6 +40267,9 @@
       <c r="C39" s="44" t="n"/>
       <c r="D39" s="44" t="n"/>
       <c r="E39" s="44" t="n"/>
+      <c r="G39" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H39" s="44" t="n"/>
       <c r="I39" s="44" t="n"/>
       <c r="J39" s="44" t="n"/>
@@ -36934,6 +40283,9 @@
       <c r="C40" s="42" t="n"/>
       <c r="D40" s="42" t="n"/>
       <c r="E40" s="42" t="n"/>
+      <c r="G40" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H40" s="42" t="n"/>
       <c r="I40" s="42" t="n"/>
       <c r="J40" s="42" t="n"/>
@@ -37036,6 +40388,9 @@
       <c r="C44" s="42" t="n"/>
       <c r="D44" s="42" t="n"/>
       <c r="E44" s="42" t="n"/>
+      <c r="G44" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H44" s="42" t="n"/>
       <c r="I44" s="42" t="n"/>
       <c r="J44" s="42" t="n"/>
@@ -37049,6 +40404,9 @@
       <c r="C45" s="44" t="n"/>
       <c r="D45" s="44" t="n"/>
       <c r="E45" s="44" t="n"/>
+      <c r="G45" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H45" s="44" t="n"/>
       <c r="I45" s="44" t="n"/>
       <c r="J45" s="44" t="n"/>
@@ -37062,6 +40420,9 @@
       <c r="C46" s="42" t="n"/>
       <c r="D46" s="42" t="n"/>
       <c r="E46" s="42" t="n"/>
+      <c r="G46" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H46" s="42" t="n"/>
       <c r="I46" s="42" t="n"/>
       <c r="J46" s="42" t="n"/>
@@ -37075,6 +40436,9 @@
       <c r="C47" s="44" t="n"/>
       <c r="D47" s="44" t="n"/>
       <c r="E47" s="44" t="n"/>
+      <c r="G47" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H47" s="44" t="n"/>
       <c r="I47" s="44" t="n"/>
       <c r="J47" s="44" t="n"/>
@@ -37088,6 +40452,9 @@
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
+      <c r="G48" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H48" s="42" t="n"/>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
@@ -37101,6 +40468,9 @@
       <c r="C49" s="44" t="n"/>
       <c r="D49" s="44" t="n"/>
       <c r="E49" s="44" t="n"/>
+      <c r="G49" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H49" s="44" t="n"/>
       <c r="I49" s="44" t="n"/>
       <c r="J49" s="44" t="n"/>
@@ -37114,6 +40484,9 @@
       <c r="C50" s="42" t="n"/>
       <c r="D50" s="42" t="n"/>
       <c r="E50" s="42" t="n"/>
+      <c r="G50" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H50" s="42" t="n"/>
       <c r="I50" s="42" t="n"/>
       <c r="J50" s="42" t="n"/>
@@ -37216,6 +40589,9 @@
       <c r="C54" s="42" t="n"/>
       <c r="D54" s="42" t="n"/>
       <c r="E54" s="42" t="n"/>
+      <c r="G54" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H54" s="42" t="n"/>
       <c r="I54" s="42" t="n"/>
       <c r="J54" s="42" t="n"/>
@@ -37229,6 +40605,9 @@
       <c r="C55" s="44" t="n"/>
       <c r="D55" s="44" t="n"/>
       <c r="E55" s="44" t="n"/>
+      <c r="G55" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H55" s="44" t="n"/>
       <c r="I55" s="44" t="n"/>
       <c r="J55" s="44" t="n"/>
@@ -37242,6 +40621,9 @@
       <c r="C56" s="42" t="n"/>
       <c r="D56" s="42" t="n"/>
       <c r="E56" s="42" t="n"/>
+      <c r="G56" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H56" s="42" t="n"/>
       <c r="I56" s="42" t="n"/>
       <c r="J56" s="42" t="n"/>
@@ -37255,6 +40637,9 @@
       <c r="C57" s="44" t="n"/>
       <c r="D57" s="44" t="n"/>
       <c r="E57" s="44" t="n"/>
+      <c r="G57" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H57" s="44" t="n"/>
       <c r="I57" s="44" t="n"/>
       <c r="J57" s="44" t="n"/>
@@ -37268,6 +40653,9 @@
       <c r="C58" s="42" t="n"/>
       <c r="D58" s="42" t="n"/>
       <c r="E58" s="42" t="n"/>
+      <c r="G58" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H58" s="42" t="n"/>
       <c r="I58" s="42" t="n"/>
       <c r="J58" s="42" t="n"/>
@@ -37281,6 +40669,9 @@
       <c r="C59" s="44" t="n"/>
       <c r="D59" s="44" t="n"/>
       <c r="E59" s="44" t="n"/>
+      <c r="G59" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H59" s="44" t="n"/>
       <c r="I59" s="44" t="n"/>
       <c r="J59" s="44" t="n"/>
@@ -37294,6 +40685,9 @@
       <c r="C60" s="42" t="n"/>
       <c r="D60" s="42" t="n"/>
       <c r="E60" s="42" t="n"/>
+      <c r="G60" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H60" s="42" t="n"/>
       <c r="I60" s="42" t="n"/>
       <c r="J60" s="42" t="n"/>
@@ -37396,6 +40790,9 @@
       <c r="C64" s="42" t="n"/>
       <c r="D64" s="42" t="n"/>
       <c r="E64" s="42" t="n"/>
+      <c r="G64" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H64" s="42" t="n"/>
       <c r="I64" s="42" t="n"/>
       <c r="J64" s="42" t="n"/>
@@ -37409,6 +40806,9 @@
       <c r="C65" s="44" t="n"/>
       <c r="D65" s="44" t="n"/>
       <c r="E65" s="44" t="n"/>
+      <c r="G65" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H65" s="44" t="n"/>
       <c r="I65" s="44" t="n"/>
       <c r="J65" s="44" t="n"/>
@@ -37422,6 +40822,9 @@
       <c r="C66" s="42" t="n"/>
       <c r="D66" s="42" t="n"/>
       <c r="E66" s="42" t="n"/>
+      <c r="G66" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H66" s="42" t="n"/>
       <c r="I66" s="42" t="n"/>
       <c r="J66" s="42" t="n"/>
@@ -37435,6 +40838,9 @@
       <c r="C67" s="44" t="n"/>
       <c r="D67" s="44" t="n"/>
       <c r="E67" s="44" t="n"/>
+      <c r="G67" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H67" s="44" t="n"/>
       <c r="I67" s="44" t="n"/>
       <c r="J67" s="44" t="n"/>
@@ -37448,6 +40854,9 @@
       <c r="C68" s="42" t="n"/>
       <c r="D68" s="42" t="n"/>
       <c r="E68" s="42" t="n"/>
+      <c r="G68" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H68" s="42" t="n"/>
       <c r="I68" s="42" t="n"/>
       <c r="J68" s="42" t="n"/>
@@ -37461,6 +40870,9 @@
       <c r="C69" s="44" t="n"/>
       <c r="D69" s="44" t="n"/>
       <c r="E69" s="44" t="n"/>
+      <c r="G69" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H69" s="44" t="n"/>
       <c r="I69" s="44" t="n"/>
       <c r="J69" s="44" t="n"/>
@@ -37474,6 +40886,9 @@
       <c r="C70" s="42" t="n"/>
       <c r="D70" s="42" t="n"/>
       <c r="E70" s="42" t="n"/>
+      <c r="G70" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H70" s="42" t="n"/>
       <c r="I70" s="42" t="n"/>
       <c r="J70" s="42" t="n"/>
@@ -37576,6 +40991,9 @@
       <c r="C74" s="42" t="n"/>
       <c r="D74" s="42" t="n"/>
       <c r="E74" s="42" t="n"/>
+      <c r="G74" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H74" s="42" t="n"/>
       <c r="I74" s="42" t="n"/>
       <c r="J74" s="42" t="n"/>
@@ -37589,6 +41007,9 @@
       <c r="C75" s="44" t="n"/>
       <c r="D75" s="44" t="n"/>
       <c r="E75" s="44" t="n"/>
+      <c r="G75" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H75" s="44" t="n"/>
       <c r="I75" s="44" t="n"/>
       <c r="J75" s="44" t="n"/>
@@ -37602,6 +41023,9 @@
       <c r="C76" s="42" t="n"/>
       <c r="D76" s="42" t="n"/>
       <c r="E76" s="42" t="n"/>
+      <c r="G76" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H76" s="42" t="n"/>
       <c r="I76" s="42" t="n"/>
       <c r="J76" s="42" t="n"/>
@@ -37615,6 +41039,9 @@
       <c r="C77" s="44" t="n"/>
       <c r="D77" s="44" t="n"/>
       <c r="E77" s="44" t="n"/>
+      <c r="G77" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H77" s="44" t="n"/>
       <c r="I77" s="44" t="n"/>
       <c r="J77" s="44" t="n"/>
@@ -37628,6 +41055,9 @@
       <c r="C78" s="42" t="n"/>
       <c r="D78" s="42" t="n"/>
       <c r="E78" s="42" t="n"/>
+      <c r="G78" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H78" s="42" t="n"/>
       <c r="I78" s="42" t="n"/>
       <c r="J78" s="42" t="n"/>
@@ -37641,6 +41071,9 @@
       <c r="C79" s="44" t="n"/>
       <c r="D79" s="44" t="n"/>
       <c r="E79" s="44" t="n"/>
+      <c r="G79" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H79" s="44" t="n"/>
       <c r="I79" s="44" t="n"/>
       <c r="J79" s="44" t="n"/>
@@ -37654,6 +41087,9 @@
       <c r="C80" s="42" t="n"/>
       <c r="D80" s="42" t="n"/>
       <c r="E80" s="42" t="n"/>
+      <c r="G80" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H80" s="42" t="n"/>
       <c r="I80" s="42" t="n"/>
       <c r="J80" s="42" t="n"/>
@@ -37756,6 +41192,9 @@
       <c r="C84" s="42" t="n"/>
       <c r="D84" s="42" t="n"/>
       <c r="E84" s="42" t="n"/>
+      <c r="G84" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H84" s="42" t="n"/>
       <c r="I84" s="42" t="n"/>
       <c r="J84" s="42" t="n"/>
@@ -37769,6 +41208,9 @@
       <c r="C85" s="44" t="n"/>
       <c r="D85" s="44" t="n"/>
       <c r="E85" s="44" t="n"/>
+      <c r="G85" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H85" s="44" t="n"/>
       <c r="I85" s="44" t="n"/>
       <c r="J85" s="44" t="n"/>
@@ -37782,6 +41224,9 @@
       <c r="C86" s="42" t="n"/>
       <c r="D86" s="42" t="n"/>
       <c r="E86" s="42" t="n"/>
+      <c r="G86" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H86" s="42" t="n"/>
       <c r="I86" s="42" t="n"/>
       <c r="J86" s="42" t="n"/>
@@ -37795,6 +41240,9 @@
       <c r="C87" s="44" t="n"/>
       <c r="D87" s="44" t="n"/>
       <c r="E87" s="44" t="n"/>
+      <c r="G87" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H87" s="44" t="n"/>
       <c r="I87" s="44" t="n"/>
       <c r="J87" s="44" t="n"/>
@@ -37808,6 +41256,9 @@
       <c r="C88" s="42" t="n"/>
       <c r="D88" s="42" t="n"/>
       <c r="E88" s="42" t="n"/>
+      <c r="G88" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H88" s="42" t="n"/>
       <c r="I88" s="42" t="n"/>
       <c r="J88" s="42" t="n"/>
@@ -37821,6 +41272,9 @@
       <c r="C89" s="44" t="n"/>
       <c r="D89" s="44" t="n"/>
       <c r="E89" s="44" t="n"/>
+      <c r="G89" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H89" s="44" t="n"/>
       <c r="I89" s="44" t="n"/>
       <c r="J89" s="44" t="n"/>
@@ -37834,6 +41288,9 @@
       <c r="C90" s="42" t="n"/>
       <c r="D90" s="42" t="n"/>
       <c r="E90" s="42" t="n"/>
+      <c r="G90" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H90" s="42" t="n"/>
       <c r="I90" s="42" t="n"/>
       <c r="J90" s="42" t="n"/>
@@ -37936,6 +41393,9 @@
       <c r="C94" s="42" t="n"/>
       <c r="D94" s="42" t="n"/>
       <c r="E94" s="42" t="n"/>
+      <c r="G94" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H94" s="42" t="n"/>
       <c r="I94" s="42" t="n"/>
       <c r="J94" s="42" t="n"/>
@@ -37949,6 +41409,9 @@
       <c r="C95" s="44" t="n"/>
       <c r="D95" s="44" t="n"/>
       <c r="E95" s="44" t="n"/>
+      <c r="G95" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H95" s="44" t="n"/>
       <c r="I95" s="44" t="n"/>
       <c r="J95" s="44" t="n"/>
@@ -37962,6 +41425,9 @@
       <c r="C96" s="42" t="n"/>
       <c r="D96" s="42" t="n"/>
       <c r="E96" s="42" t="n"/>
+      <c r="G96" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H96" s="42" t="n"/>
       <c r="I96" s="42" t="n"/>
       <c r="J96" s="42" t="n"/>
@@ -37975,6 +41441,9 @@
       <c r="C97" s="44" t="n"/>
       <c r="D97" s="44" t="n"/>
       <c r="E97" s="44" t="n"/>
+      <c r="G97" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H97" s="44" t="n"/>
       <c r="I97" s="44" t="n"/>
       <c r="J97" s="44" t="n"/>
@@ -37988,6 +41457,9 @@
       <c r="C98" s="42" t="n"/>
       <c r="D98" s="42" t="n"/>
       <c r="E98" s="42" t="n"/>
+      <c r="G98" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H98" s="42" t="n"/>
       <c r="I98" s="42" t="n"/>
       <c r="J98" s="42" t="n"/>
@@ -38001,6 +41473,9 @@
       <c r="C99" s="44" t="n"/>
       <c r="D99" s="44" t="n"/>
       <c r="E99" s="44" t="n"/>
+      <c r="G99" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H99" s="44" t="n"/>
       <c r="I99" s="44" t="n"/>
       <c r="J99" s="44" t="n"/>
@@ -38014,6 +41489,9 @@
       <c r="C100" s="42" t="n"/>
       <c r="D100" s="42" t="n"/>
       <c r="E100" s="42" t="n"/>
+      <c r="G100" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H100" s="42" t="n"/>
       <c r="I100" s="42" t="n"/>
       <c r="J100" s="42" t="n"/>
@@ -38116,6 +41594,9 @@
       <c r="C104" s="42" t="n"/>
       <c r="D104" s="42" t="n"/>
       <c r="E104" s="42" t="n"/>
+      <c r="G104" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H104" s="42" t="n"/>
       <c r="I104" s="42" t="n"/>
       <c r="J104" s="42" t="n"/>
@@ -38129,6 +41610,9 @@
       <c r="C105" s="44" t="n"/>
       <c r="D105" s="44" t="n"/>
       <c r="E105" s="44" t="n"/>
+      <c r="G105" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H105" s="44" t="n"/>
       <c r="I105" s="44" t="n"/>
       <c r="J105" s="44" t="n"/>
@@ -38142,6 +41626,9 @@
       <c r="C106" s="42" t="n"/>
       <c r="D106" s="42" t="n"/>
       <c r="E106" s="42" t="n"/>
+      <c r="G106" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H106" s="42" t="n"/>
       <c r="I106" s="42" t="n"/>
       <c r="J106" s="42" t="n"/>
@@ -38155,6 +41642,9 @@
       <c r="C107" s="44" t="n"/>
       <c r="D107" s="44" t="n"/>
       <c r="E107" s="44" t="n"/>
+      <c r="G107" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H107" s="44" t="n"/>
       <c r="I107" s="44" t="n"/>
       <c r="J107" s="44" t="n"/>
@@ -38168,6 +41658,9 @@
       <c r="C108" s="42" t="n"/>
       <c r="D108" s="42" t="n"/>
       <c r="E108" s="42" t="n"/>
+      <c r="G108" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H108" s="42" t="n"/>
       <c r="I108" s="42" t="n"/>
       <c r="J108" s="42" t="n"/>
@@ -38181,6 +41674,9 @@
       <c r="C109" s="44" t="n"/>
       <c r="D109" s="44" t="n"/>
       <c r="E109" s="44" t="n"/>
+      <c r="G109" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H109" s="44" t="n"/>
       <c r="I109" s="44" t="n"/>
       <c r="J109" s="44" t="n"/>
@@ -38194,6 +41690,9 @@
       <c r="C110" s="42" t="n"/>
       <c r="D110" s="42" t="n"/>
       <c r="E110" s="42" t="n"/>
+      <c r="G110" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H110" s="42" t="n"/>
       <c r="I110" s="42" t="n"/>
       <c r="J110" s="42" t="n"/>
@@ -38296,6 +41795,9 @@
       <c r="C114" s="42" t="n"/>
       <c r="D114" s="42" t="n"/>
       <c r="E114" s="42" t="n"/>
+      <c r="G114" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H114" s="42" t="n"/>
       <c r="I114" s="42" t="n"/>
       <c r="J114" s="42" t="n"/>
@@ -38309,6 +41811,9 @@
       <c r="C115" s="44" t="n"/>
       <c r="D115" s="44" t="n"/>
       <c r="E115" s="44" t="n"/>
+      <c r="G115" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H115" s="44" t="n"/>
       <c r="I115" s="44" t="n"/>
       <c r="J115" s="44" t="n"/>
@@ -38322,6 +41827,9 @@
       <c r="C116" s="42" t="n"/>
       <c r="D116" s="42" t="n"/>
       <c r="E116" s="42" t="n"/>
+      <c r="G116" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H116" s="42" t="n"/>
       <c r="I116" s="42" t="n"/>
       <c r="J116" s="42" t="n"/>
@@ -38335,6 +41843,9 @@
       <c r="C117" s="44" t="n"/>
       <c r="D117" s="44" t="n"/>
       <c r="E117" s="44" t="n"/>
+      <c r="G117" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H117" s="44" t="n"/>
       <c r="I117" s="44" t="n"/>
       <c r="J117" s="44" t="n"/>
@@ -38348,6 +41859,9 @@
       <c r="C118" s="42" t="n"/>
       <c r="D118" s="42" t="n"/>
       <c r="E118" s="42" t="n"/>
+      <c r="G118" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H118" s="42" t="n"/>
       <c r="I118" s="42" t="n"/>
       <c r="J118" s="42" t="n"/>
@@ -38361,6 +41875,9 @@
       <c r="C119" s="44" t="n"/>
       <c r="D119" s="44" t="n"/>
       <c r="E119" s="44" t="n"/>
+      <c r="G119" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H119" s="44" t="n"/>
       <c r="I119" s="44" t="n"/>
       <c r="J119" s="44" t="n"/>
@@ -38374,6 +41891,9 @@
       <c r="C120" s="42" t="n"/>
       <c r="D120" s="42" t="n"/>
       <c r="E120" s="42" t="n"/>
+      <c r="G120" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H120" s="42" t="n"/>
       <c r="I120" s="42" t="n"/>
       <c r="J120" s="42" t="n"/>
@@ -38476,6 +41996,9 @@
       <c r="C124" s="42" t="n"/>
       <c r="D124" s="42" t="n"/>
       <c r="E124" s="42" t="n"/>
+      <c r="G124" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H124" s="42" t="n"/>
       <c r="I124" s="42" t="n"/>
       <c r="J124" s="42" t="n"/>
@@ -38489,6 +42012,9 @@
       <c r="C125" s="44" t="n"/>
       <c r="D125" s="44" t="n"/>
       <c r="E125" s="44" t="n"/>
+      <c r="G125" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H125" s="44" t="n"/>
       <c r="I125" s="44" t="n"/>
       <c r="J125" s="44" t="n"/>
@@ -38502,6 +42028,9 @@
       <c r="C126" s="42" t="n"/>
       <c r="D126" s="42" t="n"/>
       <c r="E126" s="42" t="n"/>
+      <c r="G126" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H126" s="42" t="n"/>
       <c r="I126" s="42" t="n"/>
       <c r="J126" s="42" t="n"/>
@@ -38515,6 +42044,9 @@
       <c r="C127" s="44" t="n"/>
       <c r="D127" s="44" t="n"/>
       <c r="E127" s="44" t="n"/>
+      <c r="G127" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H127" s="44" t="n"/>
       <c r="I127" s="44" t="n"/>
       <c r="J127" s="44" t="n"/>
@@ -38528,6 +42060,9 @@
       <c r="C128" s="42" t="n"/>
       <c r="D128" s="42" t="n"/>
       <c r="E128" s="42" t="n"/>
+      <c r="G128" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H128" s="42" t="n"/>
       <c r="I128" s="42" t="n"/>
       <c r="J128" s="42" t="n"/>
@@ -38541,6 +42076,9 @@
       <c r="C129" s="44" t="n"/>
       <c r="D129" s="44" t="n"/>
       <c r="E129" s="44" t="n"/>
+      <c r="G129" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H129" s="44" t="n"/>
       <c r="I129" s="44" t="n"/>
       <c r="J129" s="44" t="n"/>
@@ -38554,6 +42092,9 @@
       <c r="C130" s="42" t="n"/>
       <c r="D130" s="42" t="n"/>
       <c r="E130" s="42" t="n"/>
+      <c r="G130" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H130" s="42" t="n"/>
       <c r="I130" s="42" t="n"/>
       <c r="J130" s="42" t="n"/>
@@ -38656,6 +42197,9 @@
       <c r="C134" s="42" t="n"/>
       <c r="D134" s="42" t="n"/>
       <c r="E134" s="42" t="n"/>
+      <c r="G134" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H134" s="42" t="n"/>
       <c r="I134" s="42" t="n"/>
       <c r="J134" s="42" t="n"/>
@@ -38669,6 +42213,9 @@
       <c r="C135" s="44" t="n"/>
       <c r="D135" s="44" t="n"/>
       <c r="E135" s="44" t="n"/>
+      <c r="G135" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H135" s="44" t="n"/>
       <c r="I135" s="44" t="n"/>
       <c r="J135" s="44" t="n"/>
@@ -38682,6 +42229,9 @@
       <c r="C136" s="42" t="n"/>
       <c r="D136" s="42" t="n"/>
       <c r="E136" s="42" t="n"/>
+      <c r="G136" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H136" s="42" t="n"/>
       <c r="I136" s="42" t="n"/>
       <c r="J136" s="42" t="n"/>
@@ -38695,6 +42245,9 @@
       <c r="C137" s="44" t="n"/>
       <c r="D137" s="44" t="n"/>
       <c r="E137" s="44" t="n"/>
+      <c r="G137" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H137" s="44" t="n"/>
       <c r="I137" s="44" t="n"/>
       <c r="J137" s="44" t="n"/>
@@ -38708,6 +42261,9 @@
       <c r="C138" s="42" t="n"/>
       <c r="D138" s="42" t="n"/>
       <c r="E138" s="42" t="n"/>
+      <c r="G138" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H138" s="42" t="n"/>
       <c r="I138" s="42" t="n"/>
       <c r="J138" s="42" t="n"/>
@@ -38721,6 +42277,9 @@
       <c r="C139" s="44" t="n"/>
       <c r="D139" s="44" t="n"/>
       <c r="E139" s="44" t="n"/>
+      <c r="G139" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H139" s="44" t="n"/>
       <c r="I139" s="44" t="n"/>
       <c r="J139" s="44" t="n"/>
@@ -38734,6 +42293,9 @@
       <c r="C140" s="42" t="n"/>
       <c r="D140" s="42" t="n"/>
       <c r="E140" s="42" t="n"/>
+      <c r="G140" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H140" s="42" t="n"/>
       <c r="I140" s="42" t="n"/>
       <c r="J140" s="42" t="n"/>
@@ -38836,6 +42398,9 @@
       <c r="C144" s="42" t="n"/>
       <c r="D144" s="42" t="n"/>
       <c r="E144" s="42" t="n"/>
+      <c r="G144" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H144" s="42" t="n"/>
       <c r="I144" s="42" t="n"/>
       <c r="J144" s="42" t="n"/>
@@ -38849,6 +42414,9 @@
       <c r="C145" s="44" t="n"/>
       <c r="D145" s="44" t="n"/>
       <c r="E145" s="44" t="n"/>
+      <c r="G145" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H145" s="44" t="n"/>
       <c r="I145" s="44" t="n"/>
       <c r="J145" s="44" t="n"/>
@@ -38862,6 +42430,9 @@
       <c r="C146" s="42" t="n"/>
       <c r="D146" s="42" t="n"/>
       <c r="E146" s="42" t="n"/>
+      <c r="G146" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H146" s="42" t="n"/>
       <c r="I146" s="42" t="n"/>
       <c r="J146" s="42" t="n"/>
@@ -38875,6 +42446,9 @@
       <c r="C147" s="44" t="n"/>
       <c r="D147" s="44" t="n"/>
       <c r="E147" s="44" t="n"/>
+      <c r="G147" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H147" s="44" t="n"/>
       <c r="I147" s="44" t="n"/>
       <c r="J147" s="44" t="n"/>
@@ -38888,6 +42462,9 @@
       <c r="C148" s="42" t="n"/>
       <c r="D148" s="42" t="n"/>
       <c r="E148" s="42" t="n"/>
+      <c r="G148" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H148" s="42" t="n"/>
       <c r="I148" s="42" t="n"/>
       <c r="J148" s="42" t="n"/>
@@ -38901,6 +42478,9 @@
       <c r="C149" s="44" t="n"/>
       <c r="D149" s="44" t="n"/>
       <c r="E149" s="44" t="n"/>
+      <c r="G149" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H149" s="44" t="n"/>
       <c r="I149" s="44" t="n"/>
       <c r="J149" s="44" t="n"/>
@@ -38914,6 +42494,9 @@
       <c r="C150" s="42" t="n"/>
       <c r="D150" s="42" t="n"/>
       <c r="E150" s="42" t="n"/>
+      <c r="G150" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H150" s="42" t="n"/>
       <c r="I150" s="42" t="n"/>
       <c r="J150" s="42" t="n"/>
@@ -39016,6 +42599,9 @@
       <c r="C154" s="42" t="n"/>
       <c r="D154" s="42" t="n"/>
       <c r="E154" s="42" t="n"/>
+      <c r="G154" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H154" s="42" t="n"/>
       <c r="I154" s="42" t="n"/>
       <c r="J154" s="42" t="n"/>
@@ -39029,6 +42615,9 @@
       <c r="C155" s="44" t="n"/>
       <c r="D155" s="44" t="n"/>
       <c r="E155" s="44" t="n"/>
+      <c r="G155" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H155" s="44" t="n"/>
       <c r="I155" s="44" t="n"/>
       <c r="J155" s="44" t="n"/>
@@ -39042,6 +42631,9 @@
       <c r="C156" s="42" t="n"/>
       <c r="D156" s="42" t="n"/>
       <c r="E156" s="42" t="n"/>
+      <c r="G156" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H156" s="42" t="n"/>
       <c r="I156" s="42" t="n"/>
       <c r="J156" s="42" t="n"/>
@@ -39055,6 +42647,9 @@
       <c r="C157" s="44" t="n"/>
       <c r="D157" s="44" t="n"/>
       <c r="E157" s="44" t="n"/>
+      <c r="G157" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H157" s="44" t="n"/>
       <c r="I157" s="44" t="n"/>
       <c r="J157" s="44" t="n"/>
@@ -39068,6 +42663,9 @@
       <c r="C158" s="42" t="n"/>
       <c r="D158" s="42" t="n"/>
       <c r="E158" s="42" t="n"/>
+      <c r="G158" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H158" s="42" t="n"/>
       <c r="I158" s="42" t="n"/>
       <c r="J158" s="42" t="n"/>
@@ -39081,6 +42679,9 @@
       <c r="C159" s="44" t="n"/>
       <c r="D159" s="44" t="n"/>
       <c r="E159" s="44" t="n"/>
+      <c r="G159" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H159" s="44" t="n"/>
       <c r="I159" s="44" t="n"/>
       <c r="J159" s="44" t="n"/>
@@ -39094,6 +42695,9 @@
       <c r="C160" s="42" t="n"/>
       <c r="D160" s="42" t="n"/>
       <c r="E160" s="42" t="n"/>
+      <c r="G160" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H160" s="42" t="n"/>
       <c r="I160" s="42" t="n"/>
       <c r="J160" s="42" t="n"/>
@@ -39196,6 +42800,9 @@
       <c r="C164" s="42" t="n"/>
       <c r="D164" s="42" t="n"/>
       <c r="E164" s="42" t="n"/>
+      <c r="G164" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H164" s="42" t="n"/>
       <c r="I164" s="42" t="n"/>
       <c r="J164" s="42" t="n"/>
@@ -39209,6 +42816,9 @@
       <c r="C165" s="44" t="n"/>
       <c r="D165" s="44" t="n"/>
       <c r="E165" s="44" t="n"/>
+      <c r="G165" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H165" s="44" t="n"/>
       <c r="I165" s="44" t="n"/>
       <c r="J165" s="44" t="n"/>
@@ -39222,6 +42832,9 @@
       <c r="C166" s="42" t="n"/>
       <c r="D166" s="42" t="n"/>
       <c r="E166" s="42" t="n"/>
+      <c r="G166" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H166" s="42" t="n"/>
       <c r="I166" s="42" t="n"/>
       <c r="J166" s="42" t="n"/>
@@ -39235,6 +42848,9 @@
       <c r="C167" s="44" t="n"/>
       <c r="D167" s="44" t="n"/>
       <c r="E167" s="44" t="n"/>
+      <c r="G167" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H167" s="44" t="n"/>
       <c r="I167" s="44" t="n"/>
       <c r="J167" s="44" t="n"/>
@@ -39248,6 +42864,9 @@
       <c r="C168" s="42" t="n"/>
       <c r="D168" s="42" t="n"/>
       <c r="E168" s="42" t="n"/>
+      <c r="G168" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H168" s="42" t="n"/>
       <c r="I168" s="42" t="n"/>
       <c r="J168" s="42" t="n"/>
@@ -39261,6 +42880,9 @@
       <c r="C169" s="44" t="n"/>
       <c r="D169" s="44" t="n"/>
       <c r="E169" s="44" t="n"/>
+      <c r="G169" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H169" s="44" t="n"/>
       <c r="I169" s="44" t="n"/>
       <c r="J169" s="44" t="n"/>
@@ -39274,6 +42896,9 @@
       <c r="C170" s="42" t="n"/>
       <c r="D170" s="42" t="n"/>
       <c r="E170" s="42" t="n"/>
+      <c r="G170" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H170" s="42" t="n"/>
       <c r="I170" s="42" t="n"/>
       <c r="J170" s="42" t="n"/>
@@ -39376,6 +43001,9 @@
       <c r="C174" s="42" t="n"/>
       <c r="D174" s="42" t="n"/>
       <c r="E174" s="42" t="n"/>
+      <c r="G174" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H174" s="42" t="n"/>
       <c r="I174" s="42" t="n"/>
       <c r="J174" s="42" t="n"/>
@@ -39389,6 +43017,9 @@
       <c r="C175" s="44" t="n"/>
       <c r="D175" s="44" t="n"/>
       <c r="E175" s="44" t="n"/>
+      <c r="G175" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H175" s="44" t="n"/>
       <c r="I175" s="44" t="n"/>
       <c r="J175" s="44" t="n"/>
@@ -39402,6 +43033,9 @@
       <c r="C176" s="42" t="n"/>
       <c r="D176" s="42" t="n"/>
       <c r="E176" s="42" t="n"/>
+      <c r="G176" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H176" s="42" t="n"/>
       <c r="I176" s="42" t="n"/>
       <c r="J176" s="42" t="n"/>
@@ -39415,6 +43049,9 @@
       <c r="C177" s="44" t="n"/>
       <c r="D177" s="44" t="n"/>
       <c r="E177" s="44" t="n"/>
+      <c r="G177" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H177" s="44" t="n"/>
       <c r="I177" s="44" t="n"/>
       <c r="J177" s="44" t="n"/>
@@ -39428,6 +43065,9 @@
       <c r="C178" s="42" t="n"/>
       <c r="D178" s="42" t="n"/>
       <c r="E178" s="42" t="n"/>
+      <c r="G178" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H178" s="42" t="n"/>
       <c r="I178" s="42" t="n"/>
       <c r="J178" s="42" t="n"/>
@@ -39441,6 +43081,9 @@
       <c r="C179" s="44" t="n"/>
       <c r="D179" s="44" t="n"/>
       <c r="E179" s="44" t="n"/>
+      <c r="G179" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H179" s="44" t="n"/>
       <c r="I179" s="44" t="n"/>
       <c r="J179" s="44" t="n"/>
@@ -39454,6 +43097,9 @@
       <c r="C180" s="42" t="n"/>
       <c r="D180" s="42" t="n"/>
       <c r="E180" s="42" t="n"/>
+      <c r="G180" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H180" s="42" t="n"/>
       <c r="I180" s="42" t="n"/>
       <c r="J180" s="42" t="n"/>
@@ -39556,6 +43202,9 @@
       <c r="C184" s="42" t="n"/>
       <c r="D184" s="42" t="n"/>
       <c r="E184" s="42" t="n"/>
+      <c r="G184" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H184" s="42" t="n"/>
       <c r="I184" s="42" t="n"/>
       <c r="J184" s="42" t="n"/>
@@ -39569,6 +43218,9 @@
       <c r="C185" s="44" t="n"/>
       <c r="D185" s="44" t="n"/>
       <c r="E185" s="44" t="n"/>
+      <c r="G185" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H185" s="44" t="n"/>
       <c r="I185" s="44" t="n"/>
       <c r="J185" s="44" t="n"/>
@@ -39582,6 +43234,9 @@
       <c r="C186" s="42" t="n"/>
       <c r="D186" s="42" t="n"/>
       <c r="E186" s="42" t="n"/>
+      <c r="G186" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H186" s="42" t="n"/>
       <c r="I186" s="42" t="n"/>
       <c r="J186" s="42" t="n"/>
@@ -39595,6 +43250,9 @@
       <c r="C187" s="44" t="n"/>
       <c r="D187" s="44" t="n"/>
       <c r="E187" s="44" t="n"/>
+      <c r="G187" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H187" s="44" t="n"/>
       <c r="I187" s="44" t="n"/>
       <c r="J187" s="44" t="n"/>
@@ -39608,6 +43266,9 @@
       <c r="C188" s="42" t="n"/>
       <c r="D188" s="42" t="n"/>
       <c r="E188" s="42" t="n"/>
+      <c r="G188" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H188" s="42" t="n"/>
       <c r="I188" s="42" t="n"/>
       <c r="J188" s="42" t="n"/>
@@ -39621,6 +43282,9 @@
       <c r="C189" s="44" t="n"/>
       <c r="D189" s="44" t="n"/>
       <c r="E189" s="44" t="n"/>
+      <c r="G189" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H189" s="44" t="n"/>
       <c r="I189" s="44" t="n"/>
       <c r="J189" s="44" t="n"/>
@@ -39634,6 +43298,9 @@
       <c r="C190" s="42" t="n"/>
       <c r="D190" s="42" t="n"/>
       <c r="E190" s="42" t="n"/>
+      <c r="G190" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H190" s="42" t="n"/>
       <c r="I190" s="42" t="n"/>
       <c r="J190" s="42" t="n"/>
@@ -39736,6 +43403,9 @@
       <c r="C194" s="42" t="n"/>
       <c r="D194" s="42" t="n"/>
       <c r="E194" s="42" t="n"/>
+      <c r="G194" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H194" s="42" t="n"/>
       <c r="I194" s="42" t="n"/>
       <c r="J194" s="42" t="n"/>
@@ -39749,6 +43419,9 @@
       <c r="C195" s="44" t="n"/>
       <c r="D195" s="44" t="n"/>
       <c r="E195" s="44" t="n"/>
+      <c r="G195" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H195" s="44" t="n"/>
       <c r="I195" s="44" t="n"/>
       <c r="J195" s="44" t="n"/>
@@ -39762,6 +43435,9 @@
       <c r="C196" s="42" t="n"/>
       <c r="D196" s="42" t="n"/>
       <c r="E196" s="42" t="n"/>
+      <c r="G196" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H196" s="42" t="n"/>
       <c r="I196" s="42" t="n"/>
       <c r="J196" s="42" t="n"/>
@@ -39775,6 +43451,9 @@
       <c r="C197" s="44" t="n"/>
       <c r="D197" s="44" t="n"/>
       <c r="E197" s="44" t="n"/>
+      <c r="G197" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H197" s="44" t="n"/>
       <c r="I197" s="44" t="n"/>
       <c r="J197" s="44" t="n"/>
@@ -39788,6 +43467,9 @@
       <c r="C198" s="42" t="n"/>
       <c r="D198" s="42" t="n"/>
       <c r="E198" s="42" t="n"/>
+      <c r="G198" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H198" s="42" t="n"/>
       <c r="I198" s="42" t="n"/>
       <c r="J198" s="42" t="n"/>
@@ -39801,6 +43483,9 @@
       <c r="C199" s="44" t="n"/>
       <c r="D199" s="44" t="n"/>
       <c r="E199" s="44" t="n"/>
+      <c r="G199" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H199" s="44" t="n"/>
       <c r="I199" s="44" t="n"/>
       <c r="J199" s="44" t="n"/>
@@ -39814,6 +43499,9 @@
       <c r="C200" s="42" t="n"/>
       <c r="D200" s="42" t="n"/>
       <c r="E200" s="42" t="n"/>
+      <c r="G200" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H200" s="42" t="n"/>
       <c r="I200" s="42" t="n"/>
       <c r="J200" s="42" t="n"/>
@@ -39916,6 +43604,9 @@
       <c r="C204" s="42" t="n"/>
       <c r="D204" s="42" t="n"/>
       <c r="E204" s="42" t="n"/>
+      <c r="G204" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H204" s="42" t="n"/>
       <c r="I204" s="42" t="n"/>
       <c r="J204" s="42" t="n"/>
@@ -39929,6 +43620,9 @@
       <c r="C205" s="44" t="n"/>
       <c r="D205" s="44" t="n"/>
       <c r="E205" s="44" t="n"/>
+      <c r="G205" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H205" s="44" t="n"/>
       <c r="I205" s="44" t="n"/>
       <c r="J205" s="44" t="n"/>
@@ -39942,6 +43636,9 @@
       <c r="C206" s="42" t="n"/>
       <c r="D206" s="42" t="n"/>
       <c r="E206" s="42" t="n"/>
+      <c r="G206" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H206" s="42" t="n"/>
       <c r="I206" s="42" t="n"/>
       <c r="J206" s="42" t="n"/>
@@ -39955,6 +43652,9 @@
       <c r="C207" s="44" t="n"/>
       <c r="D207" s="44" t="n"/>
       <c r="E207" s="44" t="n"/>
+      <c r="G207" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H207" s="44" t="n"/>
       <c r="I207" s="44" t="n"/>
       <c r="J207" s="44" t="n"/>
@@ -39968,6 +43668,9 @@
       <c r="C208" s="42" t="n"/>
       <c r="D208" s="42" t="n"/>
       <c r="E208" s="42" t="n"/>
+      <c r="G208" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H208" s="42" t="n"/>
       <c r="I208" s="42" t="n"/>
       <c r="J208" s="42" t="n"/>
@@ -39981,6 +43684,9 @@
       <c r="C209" s="44" t="n"/>
       <c r="D209" s="44" t="n"/>
       <c r="E209" s="44" t="n"/>
+      <c r="G209" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H209" s="44" t="n"/>
       <c r="I209" s="44" t="n"/>
       <c r="J209" s="44" t="n"/>
@@ -39994,6 +43700,9 @@
       <c r="C210" s="42" t="n"/>
       <c r="D210" s="42" t="n"/>
       <c r="E210" s="42" t="n"/>
+      <c r="G210" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H210" s="42" t="n"/>
       <c r="I210" s="42" t="n"/>
       <c r="J210" s="42" t="n"/>
@@ -40096,6 +43805,9 @@
       <c r="C214" s="42" t="n"/>
       <c r="D214" s="42" t="n"/>
       <c r="E214" s="42" t="n"/>
+      <c r="G214" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H214" s="42" t="n"/>
       <c r="I214" s="42" t="n"/>
       <c r="J214" s="42" t="n"/>
@@ -40109,6 +43821,9 @@
       <c r="C215" s="44" t="n"/>
       <c r="D215" s="44" t="n"/>
       <c r="E215" s="44" t="n"/>
+      <c r="G215" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H215" s="44" t="n"/>
       <c r="I215" s="44" t="n"/>
       <c r="J215" s="44" t="n"/>
@@ -40122,6 +43837,9 @@
       <c r="C216" s="42" t="n"/>
       <c r="D216" s="42" t="n"/>
       <c r="E216" s="42" t="n"/>
+      <c r="G216" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H216" s="42" t="n"/>
       <c r="I216" s="42" t="n"/>
       <c r="J216" s="42" t="n"/>
@@ -40135,6 +43853,9 @@
       <c r="C217" s="44" t="n"/>
       <c r="D217" s="44" t="n"/>
       <c r="E217" s="44" t="n"/>
+      <c r="G217" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H217" s="44" t="n"/>
       <c r="I217" s="44" t="n"/>
       <c r="J217" s="44" t="n"/>
@@ -40148,6 +43869,9 @@
       <c r="C218" s="42" t="n"/>
       <c r="D218" s="42" t="n"/>
       <c r="E218" s="42" t="n"/>
+      <c r="G218" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H218" s="42" t="n"/>
       <c r="I218" s="42" t="n"/>
       <c r="J218" s="42" t="n"/>
@@ -40161,6 +43885,9 @@
       <c r="C219" s="44" t="n"/>
       <c r="D219" s="44" t="n"/>
       <c r="E219" s="44" t="n"/>
+      <c r="G219" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H219" s="44" t="n"/>
       <c r="I219" s="44" t="n"/>
       <c r="J219" s="44" t="n"/>
@@ -40174,6 +43901,9 @@
       <c r="C220" s="42" t="n"/>
       <c r="D220" s="42" t="n"/>
       <c r="E220" s="42" t="n"/>
+      <c r="G220" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H220" s="42" t="n"/>
       <c r="I220" s="42" t="n"/>
       <c r="J220" s="42" t="n"/>
@@ -40276,6 +44006,9 @@
       <c r="C224" s="42" t="n"/>
       <c r="D224" s="42" t="n"/>
       <c r="E224" s="42" t="n"/>
+      <c r="G224" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H224" s="42" t="n"/>
       <c r="I224" s="42" t="n"/>
       <c r="J224" s="42" t="n"/>
@@ -40289,6 +44022,9 @@
       <c r="C225" s="44" t="n"/>
       <c r="D225" s="44" t="n"/>
       <c r="E225" s="44" t="n"/>
+      <c r="G225" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H225" s="44" t="n"/>
       <c r="I225" s="44" t="n"/>
       <c r="J225" s="44" t="n"/>
@@ -40302,6 +44038,9 @@
       <c r="C226" s="42" t="n"/>
       <c r="D226" s="42" t="n"/>
       <c r="E226" s="42" t="n"/>
+      <c r="G226" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H226" s="42" t="n"/>
       <c r="I226" s="42" t="n"/>
       <c r="J226" s="42" t="n"/>
@@ -40315,6 +44054,9 @@
       <c r="C227" s="44" t="n"/>
       <c r="D227" s="44" t="n"/>
       <c r="E227" s="44" t="n"/>
+      <c r="G227" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H227" s="44" t="n"/>
       <c r="I227" s="44" t="n"/>
       <c r="J227" s="44" t="n"/>
@@ -40328,6 +44070,9 @@
       <c r="C228" s="42" t="n"/>
       <c r="D228" s="42" t="n"/>
       <c r="E228" s="42" t="n"/>
+      <c r="G228" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H228" s="42" t="n"/>
       <c r="I228" s="42" t="n"/>
       <c r="J228" s="42" t="n"/>
@@ -40341,6 +44086,9 @@
       <c r="C229" s="44" t="n"/>
       <c r="D229" s="44" t="n"/>
       <c r="E229" s="44" t="n"/>
+      <c r="G229" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H229" s="44" t="n"/>
       <c r="I229" s="44" t="n"/>
       <c r="J229" s="44" t="n"/>
@@ -40354,6 +44102,9 @@
       <c r="C230" s="42" t="n"/>
       <c r="D230" s="42" t="n"/>
       <c r="E230" s="42" t="n"/>
+      <c r="G230" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H230" s="42" t="n"/>
       <c r="I230" s="42" t="n"/>
       <c r="J230" s="42" t="n"/>
@@ -40456,6 +44207,9 @@
       <c r="C234" s="42" t="n"/>
       <c r="D234" s="42" t="n"/>
       <c r="E234" s="42" t="n"/>
+      <c r="G234" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H234" s="42" t="n"/>
       <c r="I234" s="42" t="n"/>
       <c r="J234" s="42" t="n"/>
@@ -40469,6 +44223,9 @@
       <c r="C235" s="44" t="n"/>
       <c r="D235" s="44" t="n"/>
       <c r="E235" s="44" t="n"/>
+      <c r="G235" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H235" s="44" t="n"/>
       <c r="I235" s="44" t="n"/>
       <c r="J235" s="44" t="n"/>
@@ -40482,6 +44239,9 @@
       <c r="C236" s="42" t="n"/>
       <c r="D236" s="42" t="n"/>
       <c r="E236" s="42" t="n"/>
+      <c r="G236" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H236" s="42" t="n"/>
       <c r="I236" s="42" t="n"/>
       <c r="J236" s="42" t="n"/>
@@ -40495,6 +44255,9 @@
       <c r="C237" s="44" t="n"/>
       <c r="D237" s="44" t="n"/>
       <c r="E237" s="44" t="n"/>
+      <c r="G237" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H237" s="44" t="n"/>
       <c r="I237" s="44" t="n"/>
       <c r="J237" s="44" t="n"/>
@@ -40508,6 +44271,9 @@
       <c r="C238" s="42" t="n"/>
       <c r="D238" s="42" t="n"/>
       <c r="E238" s="42" t="n"/>
+      <c r="G238" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H238" s="42" t="n"/>
       <c r="I238" s="42" t="n"/>
       <c r="J238" s="42" t="n"/>
@@ -40521,6 +44287,9 @@
       <c r="C239" s="44" t="n"/>
       <c r="D239" s="44" t="n"/>
       <c r="E239" s="44" t="n"/>
+      <c r="G239" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H239" s="44" t="n"/>
       <c r="I239" s="44" t="n"/>
       <c r="J239" s="44" t="n"/>
@@ -40534,6 +44303,9 @@
       <c r="C240" s="42" t="n"/>
       <c r="D240" s="42" t="n"/>
       <c r="E240" s="42" t="n"/>
+      <c r="G240" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H240" s="42" t="n"/>
       <c r="I240" s="42" t="n"/>
       <c r="J240" s="42" t="n"/>
@@ -40636,6 +44408,9 @@
       <c r="C244" s="42" t="n"/>
       <c r="D244" s="42" t="n"/>
       <c r="E244" s="42" t="n"/>
+      <c r="G244" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H244" s="42" t="n"/>
       <c r="I244" s="42" t="n"/>
       <c r="J244" s="42" t="n"/>
@@ -40649,6 +44424,9 @@
       <c r="C245" s="44" t="n"/>
       <c r="D245" s="44" t="n"/>
       <c r="E245" s="44" t="n"/>
+      <c r="G245" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H245" s="44" t="n"/>
       <c r="I245" s="44" t="n"/>
       <c r="J245" s="44" t="n"/>
@@ -40662,6 +44440,9 @@
       <c r="C246" s="42" t="n"/>
       <c r="D246" s="42" t="n"/>
       <c r="E246" s="42" t="n"/>
+      <c r="G246" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H246" s="42" t="n"/>
       <c r="I246" s="42" t="n"/>
       <c r="J246" s="42" t="n"/>
@@ -40675,6 +44456,9 @@
       <c r="C247" s="44" t="n"/>
       <c r="D247" s="44" t="n"/>
       <c r="E247" s="44" t="n"/>
+      <c r="G247" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H247" s="44" t="n"/>
       <c r="I247" s="44" t="n"/>
       <c r="J247" s="44" t="n"/>
@@ -40688,6 +44472,9 @@
       <c r="C248" s="42" t="n"/>
       <c r="D248" s="42" t="n"/>
       <c r="E248" s="42" t="n"/>
+      <c r="G248" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H248" s="42" t="n"/>
       <c r="I248" s="42" t="n"/>
       <c r="J248" s="42" t="n"/>
@@ -40701,6 +44488,9 @@
       <c r="C249" s="44" t="n"/>
       <c r="D249" s="44" t="n"/>
       <c r="E249" s="44" t="n"/>
+      <c r="G249" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H249" s="44" t="n"/>
       <c r="I249" s="44" t="n"/>
       <c r="J249" s="44" t="n"/>
@@ -40714,6 +44504,9 @@
       <c r="C250" s="42" t="n"/>
       <c r="D250" s="42" t="n"/>
       <c r="E250" s="42" t="n"/>
+      <c r="G250" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H250" s="42" t="n"/>
       <c r="I250" s="42" t="n"/>
       <c r="J250" s="42" t="n"/>
@@ -40816,6 +44609,9 @@
       <c r="C254" s="42" t="n"/>
       <c r="D254" s="42" t="n"/>
       <c r="E254" s="42" t="n"/>
+      <c r="G254" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H254" s="42" t="n"/>
       <c r="I254" s="42" t="n"/>
       <c r="J254" s="42" t="n"/>
@@ -40829,6 +44625,9 @@
       <c r="C255" s="44" t="n"/>
       <c r="D255" s="44" t="n"/>
       <c r="E255" s="44" t="n"/>
+      <c r="G255" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H255" s="44" t="n"/>
       <c r="I255" s="44" t="n"/>
       <c r="J255" s="44" t="n"/>
@@ -40842,6 +44641,9 @@
       <c r="C256" s="42" t="n"/>
       <c r="D256" s="42" t="n"/>
       <c r="E256" s="42" t="n"/>
+      <c r="G256" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H256" s="42" t="n"/>
       <c r="I256" s="42" t="n"/>
       <c r="J256" s="42" t="n"/>
@@ -40855,6 +44657,9 @@
       <c r="C257" s="44" t="n"/>
       <c r="D257" s="44" t="n"/>
       <c r="E257" s="44" t="n"/>
+      <c r="G257" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H257" s="44" t="n"/>
       <c r="I257" s="44" t="n"/>
       <c r="J257" s="44" t="n"/>
@@ -40868,6 +44673,9 @@
       <c r="C258" s="42" t="n"/>
       <c r="D258" s="42" t="n"/>
       <c r="E258" s="42" t="n"/>
+      <c r="G258" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H258" s="42" t="n"/>
       <c r="I258" s="42" t="n"/>
       <c r="J258" s="42" t="n"/>
@@ -40881,6 +44689,9 @@
       <c r="C259" s="44" t="n"/>
       <c r="D259" s="44" t="n"/>
       <c r="E259" s="44" t="n"/>
+      <c r="G259" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H259" s="44" t="n"/>
       <c r="I259" s="44" t="n"/>
       <c r="J259" s="44" t="n"/>
@@ -40894,6 +44705,9 @@
       <c r="C260" s="42" t="n"/>
       <c r="D260" s="42" t="n"/>
       <c r="E260" s="42" t="n"/>
+      <c r="G260" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H260" s="42" t="n"/>
       <c r="I260" s="42" t="n"/>
       <c r="J260" s="42" t="n"/>
@@ -40996,6 +44810,9 @@
       <c r="C264" s="42" t="n"/>
       <c r="D264" s="42" t="n"/>
       <c r="E264" s="42" t="n"/>
+      <c r="G264" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H264" s="42" t="n"/>
       <c r="I264" s="42" t="n"/>
       <c r="J264" s="42" t="n"/>
@@ -41009,6 +44826,9 @@
       <c r="C265" s="44" t="n"/>
       <c r="D265" s="44" t="n"/>
       <c r="E265" s="44" t="n"/>
+      <c r="G265" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H265" s="44" t="n"/>
       <c r="I265" s="44" t="n"/>
       <c r="J265" s="44" t="n"/>
@@ -41022,6 +44842,9 @@
       <c r="C266" s="42" t="n"/>
       <c r="D266" s="42" t="n"/>
       <c r="E266" s="42" t="n"/>
+      <c r="G266" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H266" s="42" t="n"/>
       <c r="I266" s="42" t="n"/>
       <c r="J266" s="42" t="n"/>
@@ -41035,6 +44858,9 @@
       <c r="C267" s="44" t="n"/>
       <c r="D267" s="44" t="n"/>
       <c r="E267" s="44" t="n"/>
+      <c r="G267" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H267" s="44" t="n"/>
       <c r="I267" s="44" t="n"/>
       <c r="J267" s="44" t="n"/>
@@ -41048,6 +44874,9 @@
       <c r="C268" s="42" t="n"/>
       <c r="D268" s="42" t="n"/>
       <c r="E268" s="42" t="n"/>
+      <c r="G268" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H268" s="42" t="n"/>
       <c r="I268" s="42" t="n"/>
       <c r="J268" s="42" t="n"/>
@@ -41061,6 +44890,9 @@
       <c r="C269" s="44" t="n"/>
       <c r="D269" s="44" t="n"/>
       <c r="E269" s="44" t="n"/>
+      <c r="G269" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H269" s="44" t="n"/>
       <c r="I269" s="44" t="n"/>
       <c r="J269" s="44" t="n"/>
@@ -41074,6 +44906,9 @@
       <c r="C270" s="42" t="n"/>
       <c r="D270" s="42" t="n"/>
       <c r="E270" s="42" t="n"/>
+      <c r="G270" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H270" s="42" t="n"/>
       <c r="I270" s="42" t="n"/>
       <c r="J270" s="42" t="n"/>
@@ -41176,6 +45011,9 @@
       <c r="C274" s="42" t="n"/>
       <c r="D274" s="42" t="n"/>
       <c r="E274" s="42" t="n"/>
+      <c r="G274" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H274" s="42" t="n"/>
       <c r="I274" s="42" t="n"/>
       <c r="J274" s="42" t="n"/>
@@ -41189,6 +45027,9 @@
       <c r="C275" s="44" t="n"/>
       <c r="D275" s="44" t="n"/>
       <c r="E275" s="44" t="n"/>
+      <c r="G275" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H275" s="44" t="n"/>
       <c r="I275" s="44" t="n"/>
       <c r="J275" s="44" t="n"/>
@@ -41202,6 +45043,9 @@
       <c r="C276" s="42" t="n"/>
       <c r="D276" s="42" t="n"/>
       <c r="E276" s="42" t="n"/>
+      <c r="G276" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H276" s="42" t="n"/>
       <c r="I276" s="42" t="n"/>
       <c r="J276" s="42" t="n"/>
@@ -41215,6 +45059,9 @@
       <c r="C277" s="44" t="n"/>
       <c r="D277" s="44" t="n"/>
       <c r="E277" s="44" t="n"/>
+      <c r="G277" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H277" s="44" t="n"/>
       <c r="I277" s="44" t="n"/>
       <c r="J277" s="44" t="n"/>
@@ -41228,6 +45075,9 @@
       <c r="C278" s="42" t="n"/>
       <c r="D278" s="42" t="n"/>
       <c r="E278" s="42" t="n"/>
+      <c r="G278" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H278" s="42" t="n"/>
       <c r="I278" s="42" t="n"/>
       <c r="J278" s="42" t="n"/>
@@ -41241,6 +45091,9 @@
       <c r="C279" s="44" t="n"/>
       <c r="D279" s="44" t="n"/>
       <c r="E279" s="44" t="n"/>
+      <c r="G279" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H279" s="44" t="n"/>
       <c r="I279" s="44" t="n"/>
       <c r="J279" s="44" t="n"/>
@@ -41254,6 +45107,9 @@
       <c r="C280" s="42" t="n"/>
       <c r="D280" s="42" t="n"/>
       <c r="E280" s="42" t="n"/>
+      <c r="G280" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H280" s="42" t="n"/>
       <c r="I280" s="42" t="n"/>
       <c r="J280" s="42" t="n"/>
@@ -41356,6 +45212,9 @@
       <c r="C284" s="42" t="n"/>
       <c r="D284" s="42" t="n"/>
       <c r="E284" s="42" t="n"/>
+      <c r="G284" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H284" s="42" t="n"/>
       <c r="I284" s="42" t="n"/>
       <c r="J284" s="42" t="n"/>
@@ -41369,6 +45228,9 @@
       <c r="C285" s="44" t="n"/>
       <c r="D285" s="44" t="n"/>
       <c r="E285" s="44" t="n"/>
+      <c r="G285" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H285" s="44" t="n"/>
       <c r="I285" s="44" t="n"/>
       <c r="J285" s="44" t="n"/>
@@ -41382,6 +45244,9 @@
       <c r="C286" s="42" t="n"/>
       <c r="D286" s="42" t="n"/>
       <c r="E286" s="42" t="n"/>
+      <c r="G286" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H286" s="42" t="n"/>
       <c r="I286" s="42" t="n"/>
       <c r="J286" s="42" t="n"/>
@@ -41395,6 +45260,9 @@
       <c r="C287" s="44" t="n"/>
       <c r="D287" s="44" t="n"/>
       <c r="E287" s="44" t="n"/>
+      <c r="G287" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H287" s="44" t="n"/>
       <c r="I287" s="44" t="n"/>
       <c r="J287" s="44" t="n"/>
@@ -41408,6 +45276,9 @@
       <c r="C288" s="42" t="n"/>
       <c r="D288" s="42" t="n"/>
       <c r="E288" s="42" t="n"/>
+      <c r="G288" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H288" s="42" t="n"/>
       <c r="I288" s="42" t="n"/>
       <c r="J288" s="42" t="n"/>
@@ -41421,6 +45292,9 @@
       <c r="C289" s="44" t="n"/>
       <c r="D289" s="44" t="n"/>
       <c r="E289" s="44" t="n"/>
+      <c r="G289" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H289" s="44" t="n"/>
       <c r="I289" s="44" t="n"/>
       <c r="J289" s="44" t="n"/>
@@ -41434,6 +45308,9 @@
       <c r="C290" s="42" t="n"/>
       <c r="D290" s="42" t="n"/>
       <c r="E290" s="42" t="n"/>
+      <c r="G290" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H290" s="42" t="n"/>
       <c r="I290" s="42" t="n"/>
       <c r="J290" s="42" t="n"/>
@@ -41536,6 +45413,9 @@
       <c r="C294" s="42" t="n"/>
       <c r="D294" s="42" t="n"/>
       <c r="E294" s="42" t="n"/>
+      <c r="G294" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H294" s="42" t="n"/>
       <c r="I294" s="42" t="n"/>
       <c r="J294" s="42" t="n"/>
@@ -41549,6 +45429,9 @@
       <c r="C295" s="44" t="n"/>
       <c r="D295" s="44" t="n"/>
       <c r="E295" s="44" t="n"/>
+      <c r="G295" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H295" s="44" t="n"/>
       <c r="I295" s="44" t="n"/>
       <c r="J295" s="44" t="n"/>
@@ -41562,6 +45445,9 @@
       <c r="C296" s="42" t="n"/>
       <c r="D296" s="42" t="n"/>
       <c r="E296" s="42" t="n"/>
+      <c r="G296" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H296" s="42" t="n"/>
       <c r="I296" s="42" t="n"/>
       <c r="J296" s="42" t="n"/>
@@ -41575,6 +45461,9 @@
       <c r="C297" s="44" t="n"/>
       <c r="D297" s="44" t="n"/>
       <c r="E297" s="44" t="n"/>
+      <c r="G297" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H297" s="44" t="n"/>
       <c r="I297" s="44" t="n"/>
       <c r="J297" s="44" t="n"/>
@@ -41588,6 +45477,9 @@
       <c r="C298" s="42" t="n"/>
       <c r="D298" s="42" t="n"/>
       <c r="E298" s="42" t="n"/>
+      <c r="G298" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H298" s="42" t="n"/>
       <c r="I298" s="42" t="n"/>
       <c r="J298" s="42" t="n"/>
@@ -41601,6 +45493,9 @@
       <c r="C299" s="44" t="n"/>
       <c r="D299" s="44" t="n"/>
       <c r="E299" s="44" t="n"/>
+      <c r="G299" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H299" s="44" t="n"/>
       <c r="I299" s="44" t="n"/>
       <c r="J299" s="44" t="n"/>
@@ -41614,6 +45509,9 @@
       <c r="C300" s="42" t="n"/>
       <c r="D300" s="42" t="n"/>
       <c r="E300" s="42" t="n"/>
+      <c r="G300" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H300" s="42" t="n"/>
       <c r="I300" s="42" t="n"/>
       <c r="J300" s="42" t="n"/>
@@ -41837,6 +45735,9 @@
       <c r="C4" s="42" t="n"/>
       <c r="D4" s="42" t="n"/>
       <c r="E4" s="42" t="n"/>
+      <c r="G4" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H4" s="42" t="n"/>
       <c r="I4" s="42" t="n"/>
       <c r="J4" s="42" t="n"/>
@@ -41850,6 +45751,9 @@
       <c r="C5" s="44" t="n"/>
       <c r="D5" s="44" t="n"/>
       <c r="E5" s="44" t="n"/>
+      <c r="G5" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H5" s="44" t="n"/>
       <c r="I5" s="44" t="n"/>
       <c r="J5" s="44" t="n"/>
@@ -41863,6 +45767,9 @@
       <c r="C6" s="42" t="n"/>
       <c r="D6" s="42" t="n"/>
       <c r="E6" s="42" t="n"/>
+      <c r="G6" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H6" s="42" t="n"/>
       <c r="I6" s="42" t="n"/>
       <c r="J6" s="42" t="n"/>
@@ -41876,6 +45783,9 @@
       <c r="C7" s="44" t="n"/>
       <c r="D7" s="44" t="n"/>
       <c r="E7" s="44" t="n"/>
+      <c r="G7" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H7" s="44" t="n"/>
       <c r="I7" s="44" t="n"/>
       <c r="J7" s="44" t="n"/>
@@ -41889,6 +45799,9 @@
       <c r="C8" s="42" t="n"/>
       <c r="D8" s="42" t="n"/>
       <c r="E8" s="42" t="n"/>
+      <c r="G8" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H8" s="42" t="n"/>
       <c r="I8" s="42" t="n"/>
       <c r="J8" s="42" t="n"/>
@@ -41902,6 +45815,9 @@
       <c r="C9" s="44" t="n"/>
       <c r="D9" s="44" t="n"/>
       <c r="E9" s="44" t="n"/>
+      <c r="G9" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H9" s="44" t="n"/>
       <c r="I9" s="44" t="n"/>
       <c r="J9" s="44" t="n"/>
@@ -41915,6 +45831,9 @@
       <c r="C10" s="42" t="n"/>
       <c r="D10" s="42" t="n"/>
       <c r="E10" s="42" t="n"/>
+      <c r="G10" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H10" s="42" t="n"/>
       <c r="I10" s="42" t="n"/>
       <c r="J10" s="42" t="n"/>
@@ -41928,6 +45847,9 @@
       <c r="C11" s="44" t="n"/>
       <c r="D11" s="44" t="n"/>
       <c r="E11" s="44" t="n"/>
+      <c r="G11" s="43" t="n">
+        <v>8</v>
+      </c>
       <c r="H11" s="44" t="n"/>
       <c r="I11" s="44" t="n"/>
       <c r="J11" s="44" t="n"/>
@@ -41941,6 +45863,9 @@
       <c r="C12" s="42" t="n"/>
       <c r="D12" s="42" t="n"/>
       <c r="E12" s="42" t="n"/>
+      <c r="G12" s="41" t="n">
+        <v>9</v>
+      </c>
       <c r="H12" s="42" t="n"/>
       <c r="I12" s="42" t="n"/>
       <c r="J12" s="42" t="n"/>
@@ -41954,6 +45879,9 @@
       <c r="C13" s="44" t="n"/>
       <c r="D13" s="44" t="n"/>
       <c r="E13" s="44" t="n"/>
+      <c r="G13" s="43" t="n">
+        <v>10</v>
+      </c>
       <c r="H13" s="44" t="n"/>
       <c r="I13" s="44" t="n"/>
       <c r="J13" s="44" t="n"/>
@@ -41967,6 +45895,9 @@
       <c r="C14" s="42" t="n"/>
       <c r="D14" s="42" t="n"/>
       <c r="E14" s="42" t="n"/>
+      <c r="G14" s="41" t="n">
+        <v>11</v>
+      </c>
       <c r="H14" s="42" t="n"/>
       <c r="I14" s="42" t="n"/>
       <c r="J14" s="42" t="n"/>
@@ -41980,6 +45911,9 @@
       <c r="C15" s="44" t="n"/>
       <c r="D15" s="44" t="n"/>
       <c r="E15" s="44" t="n"/>
+      <c r="G15" s="43" t="n">
+        <v>12</v>
+      </c>
       <c r="H15" s="44" t="n"/>
       <c r="I15" s="44" t="n"/>
       <c r="J15" s="44" t="n"/>
@@ -41993,6 +45927,9 @@
       <c r="C16" s="42" t="n"/>
       <c r="D16" s="42" t="n"/>
       <c r="E16" s="42" t="n"/>
+      <c r="G16" s="41" t="n">
+        <v>13</v>
+      </c>
       <c r="H16" s="42" t="n"/>
       <c r="I16" s="42" t="n"/>
       <c r="J16" s="42" t="n"/>
@@ -42006,6 +45943,9 @@
       <c r="C17" s="44" t="n"/>
       <c r="D17" s="44" t="n"/>
       <c r="E17" s="44" t="n"/>
+      <c r="G17" s="43" t="n">
+        <v>14</v>
+      </c>
       <c r="H17" s="44" t="n"/>
       <c r="I17" s="44" t="n"/>
       <c r="J17" s="44" t="n"/>
@@ -42019,6 +45959,9 @@
       <c r="C18" s="42" t="n"/>
       <c r="D18" s="42" t="n"/>
       <c r="E18" s="42" t="n"/>
+      <c r="G18" s="41" t="n">
+        <v>15</v>
+      </c>
       <c r="H18" s="42" t="n"/>
       <c r="I18" s="42" t="n"/>
       <c r="J18" s="42" t="n"/>
@@ -42032,6 +45975,9 @@
       <c r="C19" s="44" t="n"/>
       <c r="D19" s="44" t="n"/>
       <c r="E19" s="44" t="n"/>
+      <c r="G19" s="43" t="n">
+        <v>16</v>
+      </c>
       <c r="H19" s="44" t="n"/>
       <c r="I19" s="44" t="n"/>
       <c r="J19" s="44" t="n"/>
@@ -42045,6 +45991,9 @@
       <c r="C20" s="42" t="n"/>
       <c r="D20" s="42" t="n"/>
       <c r="E20" s="42" t="n"/>
+      <c r="G20" s="41" t="n">
+        <v>17</v>
+      </c>
       <c r="H20" s="42" t="n"/>
       <c r="I20" s="42" t="n"/>
       <c r="J20" s="42" t="n"/>
@@ -42058,6 +46007,9 @@
       <c r="C21" s="44" t="n"/>
       <c r="D21" s="44" t="n"/>
       <c r="E21" s="44" t="n"/>
+      <c r="G21" s="43" t="n">
+        <v>18</v>
+      </c>
       <c r="H21" s="44" t="n"/>
       <c r="I21" s="44" t="n"/>
       <c r="J21" s="44" t="n"/>
@@ -42071,6 +46023,9 @@
       <c r="C22" s="42" t="n"/>
       <c r="D22" s="42" t="n"/>
       <c r="E22" s="42" t="n"/>
+      <c r="G22" s="41" t="n">
+        <v>19</v>
+      </c>
       <c r="H22" s="42" t="n"/>
       <c r="I22" s="42" t="n"/>
       <c r="J22" s="42" t="n"/>
@@ -42084,6 +46039,9 @@
       <c r="C23" s="44" t="n"/>
       <c r="D23" s="44" t="n"/>
       <c r="E23" s="44" t="n"/>
+      <c r="G23" s="43" t="n">
+        <v>20</v>
+      </c>
       <c r="H23" s="44" t="n"/>
       <c r="I23" s="44" t="n"/>
       <c r="J23" s="44" t="n"/>
@@ -42097,6 +46055,9 @@
       <c r="C24" s="42" t="n"/>
       <c r="D24" s="42" t="n"/>
       <c r="E24" s="42" t="n"/>
+      <c r="G24" s="41" t="n">
+        <v>21</v>
+      </c>
       <c r="H24" s="42" t="n"/>
       <c r="I24" s="42" t="n"/>
       <c r="J24" s="42" t="n"/>
@@ -42110,6 +46071,9 @@
       <c r="C25" s="44" t="n"/>
       <c r="D25" s="44" t="n"/>
       <c r="E25" s="44" t="n"/>
+      <c r="G25" s="43" t="n">
+        <v>22</v>
+      </c>
       <c r="H25" s="44" t="n"/>
       <c r="I25" s="44" t="n"/>
       <c r="J25" s="44" t="n"/>
@@ -42123,6 +46087,9 @@
       <c r="C26" s="42" t="n"/>
       <c r="D26" s="42" t="n"/>
       <c r="E26" s="42" t="n"/>
+      <c r="G26" s="41" t="n">
+        <v>23</v>
+      </c>
       <c r="H26" s="42" t="n"/>
       <c r="I26" s="42" t="n"/>
       <c r="J26" s="42" t="n"/>
@@ -42136,6 +46103,9 @@
       <c r="C27" s="44" t="n"/>
       <c r="D27" s="44" t="n"/>
       <c r="E27" s="44" t="n"/>
+      <c r="G27" s="43" t="n">
+        <v>24</v>
+      </c>
       <c r="H27" s="44" t="n"/>
       <c r="I27" s="44" t="n"/>
       <c r="J27" s="44" t="n"/>
@@ -42149,6 +46119,9 @@
       <c r="C28" s="42" t="n"/>
       <c r="D28" s="42" t="n"/>
       <c r="E28" s="42" t="n"/>
+      <c r="G28" s="41" t="n">
+        <v>25</v>
+      </c>
       <c r="H28" s="42" t="n"/>
       <c r="I28" s="42" t="n"/>
       <c r="J28" s="42" t="n"/>
@@ -42162,6 +46135,9 @@
       <c r="C29" s="44" t="n"/>
       <c r="D29" s="44" t="n"/>
       <c r="E29" s="44" t="n"/>
+      <c r="G29" s="43" t="n">
+        <v>26</v>
+      </c>
       <c r="H29" s="44" t="n"/>
       <c r="I29" s="44" t="n"/>
       <c r="J29" s="44" t="n"/>
@@ -42175,6 +46151,9 @@
       <c r="C30" s="42" t="n"/>
       <c r="D30" s="42" t="n"/>
       <c r="E30" s="42" t="n"/>
+      <c r="G30" s="41" t="n">
+        <v>27</v>
+      </c>
       <c r="H30" s="42" t="n"/>
       <c r="I30" s="42" t="n"/>
       <c r="J30" s="42" t="n"/>
@@ -42188,6 +46167,9 @@
       <c r="C31" s="44" t="n"/>
       <c r="D31" s="44" t="n"/>
       <c r="E31" s="44" t="n"/>
+      <c r="G31" s="43" t="n">
+        <v>28</v>
+      </c>
       <c r="H31" s="44" t="n"/>
       <c r="I31" s="44" t="n"/>
       <c r="J31" s="44" t="n"/>
@@ -42201,6 +46183,9 @@
       <c r="C32" s="42" t="n"/>
       <c r="D32" s="42" t="n"/>
       <c r="E32" s="42" t="n"/>
+      <c r="G32" s="41" t="n">
+        <v>29</v>
+      </c>
       <c r="H32" s="42" t="n"/>
       <c r="I32" s="42" t="n"/>
       <c r="J32" s="42" t="n"/>
@@ -42214,6 +46199,9 @@
       <c r="C33" s="44" t="n"/>
       <c r="D33" s="44" t="n"/>
       <c r="E33" s="44" t="n"/>
+      <c r="G33" s="43" t="n">
+        <v>30</v>
+      </c>
       <c r="H33" s="44" t="n"/>
       <c r="I33" s="44" t="n"/>
       <c r="J33" s="44" t="n"/>
@@ -42227,6 +46215,9 @@
       <c r="C34" s="42" t="n"/>
       <c r="D34" s="42" t="n"/>
       <c r="E34" s="42" t="n"/>
+      <c r="G34" s="41" t="n">
+        <v>31</v>
+      </c>
       <c r="H34" s="42" t="n"/>
       <c r="I34" s="42" t="n"/>
       <c r="J34" s="42" t="n"/>
@@ -42240,6 +46231,9 @@
       <c r="C35" s="44" t="n"/>
       <c r="D35" s="44" t="n"/>
       <c r="E35" s="44" t="n"/>
+      <c r="G35" s="43" t="n">
+        <v>32</v>
+      </c>
       <c r="H35" s="44" t="n"/>
       <c r="I35" s="44" t="n"/>
       <c r="J35" s="44" t="n"/>
@@ -42253,6 +46247,9 @@
       <c r="C36" s="42" t="n"/>
       <c r="D36" s="42" t="n"/>
       <c r="E36" s="42" t="n"/>
+      <c r="G36" s="41" t="n">
+        <v>33</v>
+      </c>
       <c r="H36" s="42" t="n"/>
       <c r="I36" s="42" t="n"/>
       <c r="J36" s="42" t="n"/>
@@ -42266,6 +46263,9 @@
       <c r="C37" s="44" t="n"/>
       <c r="D37" s="44" t="n"/>
       <c r="E37" s="44" t="n"/>
+      <c r="G37" s="43" t="n">
+        <v>34</v>
+      </c>
       <c r="H37" s="44" t="n"/>
       <c r="I37" s="44" t="n"/>
       <c r="J37" s="44" t="n"/>
@@ -42279,6 +46279,9 @@
       <c r="C38" s="42" t="n"/>
       <c r="D38" s="42" t="n"/>
       <c r="E38" s="42" t="n"/>
+      <c r="G38" s="41" t="n">
+        <v>35</v>
+      </c>
       <c r="H38" s="42" t="n"/>
       <c r="I38" s="42" t="n"/>
       <c r="J38" s="42" t="n"/>
@@ -42292,6 +46295,9 @@
       <c r="C39" s="44" t="n"/>
       <c r="D39" s="44" t="n"/>
       <c r="E39" s="44" t="n"/>
+      <c r="G39" s="43" t="n">
+        <v>36</v>
+      </c>
       <c r="H39" s="44" t="n"/>
       <c r="I39" s="44" t="n"/>
       <c r="J39" s="44" t="n"/>
@@ -42305,6 +46311,9 @@
       <c r="C40" s="42" t="n"/>
       <c r="D40" s="42" t="n"/>
       <c r="E40" s="42" t="n"/>
+      <c r="G40" s="41" t="n">
+        <v>37</v>
+      </c>
       <c r="H40" s="42" t="n"/>
       <c r="I40" s="42" t="n"/>
       <c r="J40" s="42" t="n"/>
@@ -42318,6 +46327,9 @@
       <c r="C41" s="44" t="n"/>
       <c r="D41" s="44" t="n"/>
       <c r="E41" s="44" t="n"/>
+      <c r="G41" s="43" t="n">
+        <v>38</v>
+      </c>
       <c r="H41" s="44" t="n"/>
       <c r="I41" s="44" t="n"/>
       <c r="J41" s="44" t="n"/>
@@ -42331,6 +46343,9 @@
       <c r="C42" s="42" t="n"/>
       <c r="D42" s="42" t="n"/>
       <c r="E42" s="42" t="n"/>
+      <c r="G42" s="41" t="n">
+        <v>39</v>
+      </c>
       <c r="H42" s="42" t="n"/>
       <c r="I42" s="42" t="n"/>
       <c r="J42" s="42" t="n"/>
@@ -42344,6 +46359,9 @@
       <c r="C43" s="44" t="n"/>
       <c r="D43" s="44" t="n"/>
       <c r="E43" s="44" t="n"/>
+      <c r="G43" s="43" t="n">
+        <v>40</v>
+      </c>
       <c r="H43" s="44" t="n"/>
       <c r="I43" s="44" t="n"/>
       <c r="J43" s="44" t="n"/>
@@ -42466,6 +46484,9 @@
       <c r="C48" s="42" t="n"/>
       <c r="D48" s="42" t="n"/>
       <c r="E48" s="42" t="n"/>
+      <c r="G48" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H48" s="42" t="n"/>
       <c r="I48" s="42" t="n"/>
       <c r="J48" s="42" t="n"/>
@@ -42479,6 +46500,9 @@
       <c r="C49" s="44" t="n"/>
       <c r="D49" s="44" t="n"/>
       <c r="E49" s="44" t="n"/>
+      <c r="G49" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="H49" s="44" t="n"/>
       <c r="I49" s="44" t="n"/>
       <c r="J49" s="44" t="n"/>
@@ -42492,6 +46516,9 @@
       <c r="C50" s="42" t="n"/>
       <c r="D50" s="42" t="n"/>
       <c r="E50" s="42" t="n"/>
+      <c r="G50" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="H50" s="42" t="n"/>
       <c r="I50" s="42" t="n"/>
       <c r="J50" s="42" t="n"/>
@@ -42505,6 +46532,9 @@
       <c r="C51" s="44" t="n"/>
       <c r="D51" s="44" t="n"/>
       <c r="E51" s="44" t="n"/>
+      <c r="G51" s="43" t="n">
+        <v>4</v>
+      </c>
       <c r="H51" s="44" t="n"/>
       <c r="I51" s="44" t="n"/>
       <c r="J51" s="44" t="n"/>
@@ -42518,6 +46548,9 @@
       <c r="C52" s="42" t="n"/>
       <c r="D52" s="42" t="n"/>
       <c r="E52" s="42" t="n"/>
+      <c r="G52" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="H52" s="42" t="n"/>
       <c r="I52" s="42" t="n"/>
       <c r="J52" s="42" t="n"/>
@@ -42531,6 +46564,9 @@
       <c r="C53" s="44" t="n"/>
       <c r="D53" s="44" t="n"/>
       <c r="E53" s="44" t="n"/>
+      <c r="G53" s="43" t="n">
+        <v>6</v>
+      </c>
       <c r="H53" s="44" t="n"/>
       <c r="I53" s="44" t="n"/>
       <c r="J53" s="44" t="n"/>
@@ -42544,6 +46580,9 @@
       <c r="C54" s="42" t="n"/>
       <c r="D54" s="42" t="n"/>
       <c r="E54" s="42" t="n"/>
+      <c r="G54" s="41" t="n">
+        <v>7</v>
+      </c>
       <c r="H54" s="42" t="n"/>
       <c r="I54" s="42" t="n"/>
       <c r="J54" s="42" t="n"/>
@@ -42557,6 +46596,9 @@
       <c r="C55" s="44" t="n"/>
       <c r="D55" s="44" t="n"/>
       <c r="E55" s="44" t="n"/>
+      <c r="G55" s="43" t="n">
+        <v>8</v>
+      </c>
       <c r="H55" s="44" t="n"/>
       <c r="I55" s="44" t="n"/>
       <c r="J55" s="44" t="n"/>
@@ -42570,6 +46612,9 @@
       <c r="C56" s="42" t="n"/>
       <c r="D56" s="42" t="n"/>
       <c r="E56" s="42" t="n"/>
+      <c r="G56" s="41" t="n">
+        <v>9</v>
+      </c>
       <c r="H56" s="42" t="n"/>
       <c r="I56" s="42" t="n"/>
       <c r="J56" s="42" t="n"/>
@@ -42583,6 +46628,9 @@
       <c r="C57" s="44" t="n"/>
       <c r="D57" s="44" t="n"/>
       <c r="E57" s="44" t="n"/>
+      <c r="G57" s="43" t="n">
+        <v>10</v>
+      </c>
       <c r="H57" s="44" t="n"/>
       <c r="I57" s="44" t="n"/>
       <c r="J57" s="44" t="n"/>
@@ -42596,6 +46644,9 @@
       <c r="C58" s="42" t="n"/>
       <c r="D58" s="42" t="n"/>
       <c r="E58" s="42" t="n"/>
+      <c r="G58" s="41" t="n">
+        <v>11</v>
+      </c>
       <c r="H58" s="42" t="n"/>
       <c r="I58" s="42" t="n"/>
       <c r="J58" s="42" t="n"/>
@@ -42609,6 +46660,9 @@
       <c r="C59" s="44" t="n"/>
       <c r="D59" s="44" t="n"/>
       <c r="E59" s="44" t="n"/>
+      <c r="G59" s="43" t="n">
+        <v>12</v>
+      </c>
       <c r="H59" s="44" t="n"/>
       <c r="I59" s="44" t="n"/>
       <c r="J59" s="44" t="n"/>
@@ -42622,6 +46676,9 @@
       <c r="C60" s="42" t="n"/>
       <c r="D60" s="42" t="n"/>
       <c r="E60" s="42" t="n"/>
+      <c r="G60" s="41" t="n">
+        <v>13</v>
+      </c>
       <c r="H60" s="42" t="n"/>
       <c r="I60" s="42" t="n"/>
       <c r="J60" s="42" t="n"/>
@@ -42635,6 +46692,9 @@
       <c r="C61" s="44" t="n"/>
       <c r="D61" s="44" t="n"/>
       <c r="E61" s="44" t="n"/>
+      <c r="G61" s="43" t="n">
+        <v>14</v>
+      </c>
       <c r="H61" s="44" t="n"/>
       <c r="I61" s="44" t="n"/>
       <c r="J61" s="44" t="n"/>
@@ -42648,6 +46708,9 @@
       <c r="C62" s="42" t="n"/>
       <c r="D62" s="42" t="n"/>
       <c r="E62" s="42" t="n"/>
+      <c r="G62" s="41" t="n">
+        <v>15</v>
+      </c>
       <c r="H62" s="42" t="n"/>
       <c r="I62" s="42" t="n"/>
       <c r="J62" s="42" t="n"/>
@@ -42661,6 +46724,9 @@
       <c r="C63" s="44" t="n"/>
       <c r="D63" s="44" t="n"/>
       <c r="E63" s="44" t="n"/>
+      <c r="G63" s="43" t="n">
+        <v>16</v>
+      </c>
       <c r="H63" s="44" t="n"/>
       <c r="I63" s="44" t="n"/>
       <c r="J63" s="44" t="n"/>
@@ -42674,6 +46740,9 @@
       <c r="C64" s="42" t="n"/>
       <c r="D64" s="42" t="n"/>
       <c r="E64" s="42" t="n"/>
+      <c r="G64" s="41" t="n">
+        <v>17</v>
+      </c>
       <c r="H64" s="42" t="n"/>
       <c r="I64" s="42" t="n"/>
       <c r="J64" s="42" t="n"/>
@@ -42687,6 +46756,9 @@
       <c r="C65" s="44" t="n"/>
       <c r="D65" s="44" t="n"/>
       <c r="E65" s="44" t="n"/>
+      <c r="G65" s="43" t="n">
+        <v>18</v>
+      </c>
       <c r="H65" s="44" t="n"/>
       <c r="I65" s="44" t="n"/>
       <c r="J65" s="44" t="n"/>
@@ -42700,6 +46772,9 @@
       <c r="C66" s="42" t="n"/>
       <c r="D66" s="42" t="n"/>
       <c r="E66" s="42" t="n"/>
+      <c r="G66" s="41" t="n">
+        <v>19</v>
+      </c>
       <c r="H66" s="42" t="n"/>
       <c r="I66" s="42" t="n"/>
       <c r="J66" s="42" t="n"/>
@@ -42713,6 +46788,9 @@
       <c r="C67" s="44" t="n"/>
       <c r="D67" s="44" t="n"/>
       <c r="E67" s="44" t="n"/>
+      <c r="G67" s="43" t="n">
+        <v>20</v>
+      </c>
       <c r="H67" s="44" t="n"/>
       <c r="I67" s="44" t="n"/>
       <c r="J67" s="44" t="n"/>
@@ -42726,6 +46804,9 @@
       <c r="C68" s="42" t="n"/>
       <c r="D68" s="42" t="n"/>
       <c r="E68" s="42" t="n"/>
+      <c r="G68" s="41" t="n">
+        <v>21</v>
+      </c>
       <c r="H68" s="42" t="n"/>
       <c r="I68" s="42" t="n"/>
       <c r="J68" s="42" t="n"/>
@@ -42739,6 +46820,9 @@
       <c r="C69" s="44" t="n"/>
       <c r="D69" s="44" t="n"/>
       <c r="E69" s="44" t="n"/>
+      <c r="G69" s="43" t="n">
+        <v>22</v>
+      </c>
       <c r="H69" s="44" t="n"/>
       <c r="I69" s="44" t="n"/>
       <c r="J69" s="44" t="n"/>
@@ -42752,6 +46836,9 @@
       <c r="C70" s="42" t="n"/>
       <c r="D70" s="42" t="n"/>
       <c r="E70" s="42" t="n"/>
+      <c r="G70" s="41" t="n">
+        <v>23</v>
+      </c>
       <c r="H70" s="42" t="n"/>
       <c r="I70" s="42" t="n"/>
       <c r="J70" s="42" t="n"/>
@@ -42765,6 +46852,9 @@
       <c r="C71" s="44" t="n"/>
       <c r="D71" s="44" t="n"/>
       <c r="E71" s="44" t="n"/>
+      <c r="G71" s="43" t="n">
+        <v>24</v>
+      </c>
       <c r="H71" s="44" t="n"/>
       <c r="I71" s="44" t="n"/>
       <c r="J71" s="44" t="n"/>
@@ -42778,6 +46868,9 @@
       <c r="C72" s="42" t="n"/>
       <c r="D72" s="42" t="n"/>
       <c r="E72" s="42" t="n"/>
+      <c r="G72" s="41" t="n">
+        <v>25</v>
+      </c>
       <c r="H72" s="42" t="n"/>
       <c r="I72" s="42" t="n"/>
       <c r="J72" s="42" t="n"/>
@@ -42791,6 +46884,9 @@
       <c r="C73" s="44" t="n"/>
       <c r="D73" s="44" t="n"/>
       <c r="E73" s="44" t="n"/>
+      <c r="G73" s="43" t="n">
+        <v>26</v>
+      </c>
       <c r="H73" s="44" t="n"/>
       <c r="I73" s="44" t="n"/>
       <c r="J73" s="44" t="n"/>
@@ -42804,6 +46900,9 @@
       <c r="C74" s="42" t="n"/>
       <c r="D74" s="42" t="n"/>
       <c r="E74" s="42" t="n"/>
+      <c r="G74" s="41" t="n">
+        <v>27</v>
+      </c>
       <c r="H74" s="42" t="n"/>
       <c r="I74" s="42" t="n"/>
       <c r="J74" s="42" t="n"/>
@@ -42817,6 +46916,9 @@
       <c r="C75" s="44" t="n"/>
       <c r="D75" s="44" t="n"/>
       <c r="E75" s="44" t="n"/>
+      <c r="G75" s="43" t="n">
+        <v>28</v>
+      </c>
       <c r="H75" s="44" t="n"/>
       <c r="I75" s="44" t="n"/>
       <c r="J75" s="44" t="n"/>
@@ -42830,6 +46932,9 @@
       <c r="C76" s="42" t="n"/>
       <c r="D76" s="42" t="n"/>
       <c r="E76" s="42" t="n"/>
+      <c r="G76" s="41" t="n">
+        <v>29</v>
+      </c>
       <c r="H76" s="42" t="n"/>
       <c r="I76" s="42" t="n"/>
       <c r="J76" s="42" t="n"/>
@@ -42843,6 +46948,9 @@
       <c r="C77" s="44" t="n"/>
       <c r="D77" s="44" t="n"/>
       <c r="E77" s="44" t="n"/>
+      <c r="G77" s="43" t="n">
+        <v>30</v>
+      </c>
       <c r="H77" s="44" t="n"/>
       <c r="I77" s="44" t="n"/>
       <c r="J77" s="44" t="n"/>
@@ -42856,6 +46964,9 @@
       <c r="C78" s="42" t="n"/>
       <c r="D78" s="42" t="n"/>
       <c r="E78" s="42" t="n"/>
+      <c r="G78" s="41" t="n">
+        <v>31</v>
+      </c>
       <c r="H78" s="42" t="n"/>
       <c r="I78" s="42" t="n"/>
       <c r="J78" s="42" t="n"/>
@@ -42869,6 +46980,9 @@
       <c r="C79" s="44" t="n"/>
       <c r="D79" s="44" t="n"/>
       <c r="E79" s="44" t="n"/>
+      <c r="G79" s="43" t="n">
+        <v>32</v>
+      </c>
       <c r="H79" s="44" t="n"/>
       <c r="I79" s="44" t="n"/>
       <c r="J79" s="44" t="n"/>
@@ -42882,6 +46996,9 @@
       <c r="C80" s="42" t="n"/>
       <c r="D80" s="42" t="n"/>
       <c r="E80" s="42" t="n"/>
+      <c r="G80" s="41" t="n">
+        <v>33</v>
+      </c>
       <c r="H80" s="42" t="n"/>
       <c r="I80" s="42" t="n"/>
       <c r="J80" s="42" t="n"/>
@@ -42895,6 +47012,9 @@
       <c r="C81" s="44" t="n"/>
       <c r="D81" s="44" t="n"/>
       <c r="E81" s="44" t="n"/>
+      <c r="G81" s="43" t="n">
+        <v>34</v>
+      </c>
       <c r="H81" s="44" t="n"/>
       <c r="I81" s="44" t="n"/>
       <c r="J81" s="44" t="n"/>
@@ -42908,6 +47028,9 @@
       <c r="C82" s="42" t="n"/>
       <c r="D82" s="42" t="n"/>
       <c r="E82" s="42" t="n"/>
+      <c r="G82" s="41" t="n">
+        <v>35</v>
+      </c>
       <c r="H82" s="42" t="n"/>
       <c r="I82" s="42" t="n"/>
       <c r="J82" s="42" t="n"/>
@@ -42921,6 +47044,9 @@
       <c r="C83" s="44" t="n"/>
       <c r="D83" s="44" t="n"/>
       <c r="E83" s="44" t="n"/>
+      <c r="G83" s="43" t="n">
+        <v>36</v>
+      </c>
       <c r="H83" s="44" t="n"/>
       <c r="I83" s="44" t="n"/>
       <c r="J83" s="44" t="n"/>
@@ -42934,6 +47060,9 @@
       <c r="C84" s="42" t="n"/>
       <c r="D84" s="42" t="n"/>
       <c r="E84" s="42" t="n"/>
+      <c r="G84" s="41" t="n">
+        <v>37</v>
+      </c>
       <c r="H84" s="42" t="n"/>
       <c r="I84" s="42" t="n"/>
       <c r="J84" s="42" t="n"/>
@@ -42947,6 +47076,9 @@
       <c r="C85" s="44" t="n"/>
       <c r="D85" s="44" t="n"/>
       <c r="E85" s="44" t="n"/>
+      <c r="G85" s="43" t="n">
+        <v>38</v>
+      </c>
       <c r="H85" s="44" t="n"/>
       <c r="I85" s="44" t="n"/>
       <c r="J85" s="44" t="n"/>
@@ -42960,6 +47092,9 @@
       <c r="C86" s="42" t="n"/>
       <c r="D86" s="42" t="n"/>
       <c r="E86" s="42" t="n"/>
+      <c r="G86" s="41" t="n">
+        <v>39</v>
+      </c>
       <c r="H86" s="42" t="n"/>
       <c r="I86" s="42" t="n"/>
       <c r="J86" s="42" t="n"/>
@@ -42973,6 +47108,9 @@
       <c r="C87" s="44" t="n"/>
       <c r="D87" s="44" t="n"/>
       <c r="E87" s="44" t="n"/>
+      <c r="G87" s="43" t="n">
+        <v>40</v>
+      </c>
       <c r="H87" s="44" t="n"/>
       <c r="I87" s="44" t="n"/>
       <c r="J87" s="44" t="n"/>
